--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>509751000</v>
+        <v>489516000</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>380059001</v>
+        <v>371964001</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>349916000</v>
+        <v>328181000</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>215092000</v>
+        <v>209522000</v>
       </c>
     </row>
   </sheetData>
@@ -516,61 +516,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>69350000</v>
+        <v>52000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>66300000</v>
+        <v>43350000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>53400000</v>
+        <v>42300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>24300000</v>
+        <v>25500000</v>
       </c>
     </row>
   </sheetData>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>395600000</v>
+        <v>424700000</v>
       </c>
       <c r="D2" t="n">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="E2" t="n">
-        <v>3186632000</v>
+        <v>3179032000</v>
       </c>
     </row>
     <row r="3">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>329400000</v>
+        <v>338400000</v>
       </c>
       <c r="D3" t="n">
-        <v>1792</v>
+        <v>1779</v>
       </c>
       <c r="E3" t="n">
-        <v>2188715000</v>
+        <v>2187905000</v>
       </c>
     </row>
     <row r="4">
@@ -676,17 +676,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>221700000</v>
+        <v>269150000</v>
       </c>
       <c r="D4" t="n">
-        <v>1980</v>
+        <v>2445</v>
       </c>
       <c r="E4" t="n">
-        <v>2456717000</v>
+        <v>2937975000</v>
       </c>
     </row>
     <row r="5">
@@ -697,17 +697,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>218550000</v>
+        <v>248100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2412</v>
+        <v>1977</v>
       </c>
       <c r="E5" t="n">
-        <v>2901080000</v>
+        <v>2467304000</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>24000000</v>
+        <v>28500000</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="H2" t="n">
-        <v>524577000</v>
+        <v>528702000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>25000000</v>
+        <v>44700000</v>
       </c>
       <c r="G3" t="n">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="H3" t="n">
-        <v>314299000</v>
+        <v>332358000</v>
       </c>
       <c r="I3" t="n">
         <v>17</v>
@@ -882,7 +882,7 @@
         <v>181826000</v>
       </c>
       <c r="M3" t="n">
-        <v>57.85</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="4">
@@ -911,25 +911,25 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H4" t="n">
-        <v>401559000</v>
+        <v>399109000</v>
       </c>
       <c r="I4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>28173000</v>
+        <v>24005000</v>
       </c>
       <c r="K4" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L4" t="n">
-        <v>154754000</v>
+        <v>151114000</v>
       </c>
       <c r="M4" t="n">
-        <v>38.54</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="5">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>102400000</v>
+        <v>106000000</v>
       </c>
       <c r="G5" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H5" t="n">
-        <v>772058000</v>
+        <v>771578000</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>24974000</v>
+        <v>15550000</v>
       </c>
       <c r="K5" t="n">
         <v>9</v>
@@ -996,25 +996,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>29350000</v>
+        <v>35950000</v>
       </c>
       <c r="G6" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H6" t="n">
-        <v>338905000</v>
+        <v>343696000</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J6" t="n">
-        <v>31977000</v>
+        <v>26337000</v>
       </c>
       <c r="K6" t="n">
         <v>117</v>
@@ -1023,7 +1023,7 @@
         <v>95054000</v>
       </c>
       <c r="M6" t="n">
-        <v>28.05</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="7">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>37800000</v>
+        <v>54000000</v>
       </c>
       <c r="G7" t="n">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="H7" t="n">
-        <v>547882000</v>
+        <v>560732000</v>
       </c>
       <c r="I7" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J7" t="n">
-        <v>119600000</v>
+        <v>114200000</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -1070,7 +1070,7 @@
         <v>60325000</v>
       </c>
       <c r="M7" t="n">
-        <v>11.01</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="8">
@@ -1146,25 +1146,25 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="H9" t="n">
-        <v>377969000</v>
+        <v>374869000</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>21872000</v>
+        <v>11932000</v>
       </c>
       <c r="K9" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L9" t="n">
-        <v>140860000</v>
+        <v>140560000</v>
       </c>
       <c r="M9" t="n">
-        <v>37.27</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10">
@@ -1243,7 +1243,7 @@
         <v>468</v>
       </c>
       <c r="H11" t="n">
-        <v>603545000</v>
+        <v>602845000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1278,19 +1278,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>72900000</v>
+        <v>95700000</v>
       </c>
       <c r="G12" t="n">
         <v>483</v>
       </c>
       <c r="H12" t="n">
-        <v>776331000</v>
+        <v>790988000</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -1305,7 +1305,7 @@
         <v>26070000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -1337,7 +1337,7 @@
         <v>229</v>
       </c>
       <c r="H13" t="n">
-        <v>303264000</v>
+        <v>302139000</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
@@ -1349,10 +1349,10 @@
         <v>68</v>
       </c>
       <c r="L13" t="n">
-        <v>67179000</v>
+        <v>66879000</v>
       </c>
       <c r="M13" t="n">
-        <v>22.15</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="14">
@@ -1372,34 +1372,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>51300000</v>
+        <v>54900000</v>
       </c>
       <c r="G14" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H14" t="n">
-        <v>347628000</v>
+        <v>348483000</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>19050000</v>
+        <v>11610000</v>
       </c>
       <c r="K14" t="n">
         <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>109270000</v>
+        <v>108370000</v>
       </c>
       <c r="M14" t="n">
-        <v>31.43</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="15">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>95000000</v>
+        <v>99500000</v>
       </c>
       <c r="G15" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H15" t="n">
-        <v>759880000</v>
+        <v>753955000</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>38876000</v>
+        <v>32285000</v>
       </c>
       <c r="K15" t="n">
         <v>55</v>
@@ -1446,7 +1446,7 @@
         <v>39486000</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="16">
@@ -1466,34 +1466,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>94800000</v>
+        <v>100800000</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
-        <v>522042000</v>
+        <v>518692000</v>
       </c>
       <c r="I16" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>48640000</v>
+        <v>33930000</v>
       </c>
       <c r="K16" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L16" t="n">
-        <v>97820000</v>
+        <v>91920000</v>
       </c>
       <c r="M16" t="n">
-        <v>18.74</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="17">
@@ -1525,13 +1525,13 @@
         <v>306</v>
       </c>
       <c r="H17" t="n">
-        <v>376813000</v>
+        <v>375378000</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>16610000</v>
+        <v>8655000</v>
       </c>
       <c r="K17" t="n">
         <v>115</v>
@@ -1540,7 +1540,7 @@
         <v>130620000</v>
       </c>
       <c r="M17" t="n">
-        <v>34.66</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="18">
@@ -1607,34 +1607,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>98700000</v>
+        <v>117300000</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="H19" t="n">
-        <v>842974000</v>
+        <v>852084000</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>15142000</v>
+        <v>450000</v>
       </c>
       <c r="K19" t="n">
         <v>42</v>
       </c>
       <c r="L19" t="n">
-        <v>38750000</v>
+        <v>38375000</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20">
@@ -1663,16 +1663,16 @@
         <v>103500000</v>
       </c>
       <c r="G20" t="n">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="H20" t="n">
-        <v>679523000</v>
+        <v>673523000</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>9575000</v>
+        <v>5900000</v>
       </c>
       <c r="K20" t="n">
         <v>70</v>
@@ -1681,7 +1681,7 @@
         <v>69410000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.21</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="21">
@@ -1697,38 +1697,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ahmed . Hassan Yusif -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>58250000</v>
       </c>
       <c r="G21" t="n">
-        <v>255</v>
+        <v>444</v>
       </c>
       <c r="H21" t="n">
-        <v>294212000</v>
+        <v>484249000</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>16168000</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>55520000</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>18.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1744,23 +1744,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>58250000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>447</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>486499000</v>
+        <v>12500000</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>12500000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -1791,23 +1791,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>23250000</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>12500000</v>
+        <v>21318000</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1838,38 +1838,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>23250000</v>
+        <v>74700000</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>418</v>
       </c>
       <c r="H24" t="n">
-        <v>21318000</v>
+        <v>502336000</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>76440000</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>77892000</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="25">
@@ -1885,38 +1885,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>65700000</v>
+        <v>111300000</v>
       </c>
       <c r="G25" t="n">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="H25" t="n">
-        <v>495226000</v>
+        <v>725504000</v>
       </c>
       <c r="I25" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>81990000</v>
+        <v>13700000</v>
       </c>
       <c r="K25" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>77892000</v>
+        <v>40945000</v>
       </c>
       <c r="M25" t="n">
-        <v>15.73</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="26">
@@ -1932,38 +1932,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>111300000</v>
+        <v>70900000</v>
       </c>
       <c r="G26" t="n">
-        <v>471</v>
+        <v>284</v>
       </c>
       <c r="H26" t="n">
-        <v>728204000</v>
+        <v>357243000</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>16400000</v>
+        <v>13918000</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L26" t="n">
-        <v>40945000</v>
+        <v>55520000</v>
       </c>
       <c r="M26" t="n">
-        <v>5.62</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="27">
@@ -1979,85 +1979,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>70900000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="H27" t="n">
-        <v>64831000</v>
+        <v>84755000</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>38000000</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>149</v>
-      </c>
-      <c r="H28" t="n">
-        <v>85925000</v>
-      </c>
-      <c r="I28" t="n">
-        <v>28</v>
-      </c>
-      <c r="J28" t="n">
-        <v>20800000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>67</v>
-      </c>
-      <c r="L28" t="n">
-        <v>38370000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>44.66</v>
+        <v>44.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>489516000</v>
+        <v>461311000</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>371964001</v>
+        <v>367484001</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>328181000</v>
+        <v>327356000</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>209522000</v>
+        <v>195067000</v>
       </c>
     </row>
   </sheetData>
@@ -539,14 +539,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>43350000</v>
+        <v>42300000</v>
       </c>
     </row>
     <row r="4">
@@ -557,14 +557,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>42300000</v>
+        <v>25500000</v>
       </c>
     </row>
     <row r="5">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>25500000</v>
+        <v>21000000</v>
       </c>
     </row>
   </sheetData>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>424700000</v>
+        <v>429200000</v>
       </c>
       <c r="D2" t="n">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="E2" t="n">
-        <v>3179032000</v>
+        <v>3180532000</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>1779</v>
       </c>
       <c r="E3" t="n">
-        <v>2187905000</v>
+        <v>2172200000</v>
       </c>
     </row>
     <row r="4">
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>269150000</v>
+        <v>319200000</v>
       </c>
       <c r="D4" t="n">
-        <v>2445</v>
+        <v>2450</v>
       </c>
       <c r="E4" t="n">
-        <v>2937975000</v>
+        <v>2951444000</v>
       </c>
     </row>
     <row r="5">
@@ -704,10 +704,10 @@
         <v>248100000</v>
       </c>
       <c r="D5" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="E5" t="n">
-        <v>2467304000</v>
+        <v>2462064000</v>
       </c>
     </row>
   </sheetData>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>28500000</v>
+        <v>46200000</v>
       </c>
       <c r="G2" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H2" t="n">
-        <v>528702000</v>
+        <v>543707000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>44700000</v>
+        <v>50700000</v>
       </c>
       <c r="G3" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H3" t="n">
-        <v>332358000</v>
+        <v>337685000</v>
       </c>
       <c r="I3" t="n">
         <v>17</v>
@@ -882,7 +882,7 @@
         <v>181826000</v>
       </c>
       <c r="M3" t="n">
-        <v>54.71</v>
+        <v>53.84</v>
       </c>
     </row>
     <row r="4">
@@ -902,25 +902,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8250000</v>
       </c>
       <c r="G4" t="n">
         <v>378</v>
       </c>
       <c r="H4" t="n">
-        <v>399109000</v>
+        <v>403684000</v>
       </c>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>24005000</v>
+        <v>17605000</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -929,7 +929,7 @@
         <v>151114000</v>
       </c>
       <c r="M4" t="n">
-        <v>37.86</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="5">
@@ -961,7 +961,7 @@
         <v>440</v>
       </c>
       <c r="H5" t="n">
-        <v>771578000</v>
+        <v>769553000</v>
       </c>
       <c r="I5" t="n">
         <v>11</v>
@@ -996,19 +996,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>35950000</v>
+        <v>46850000</v>
       </c>
       <c r="G6" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H6" t="n">
-        <v>343696000</v>
+        <v>353688000</v>
       </c>
       <c r="I6" t="n">
         <v>29</v>
@@ -1023,7 +1023,7 @@
         <v>95054000</v>
       </c>
       <c r="M6" t="n">
-        <v>27.66</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="7">
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61200000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>493</v>
+      </c>
+      <c r="H7" t="n">
+        <v>541327000</v>
+      </c>
+      <c r="I7" t="n">
         <v>9</v>
       </c>
-      <c r="E7" t="n">
-        <v>27</v>
-      </c>
-      <c r="F7" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>505</v>
-      </c>
-      <c r="H7" t="n">
-        <v>560732000</v>
-      </c>
-      <c r="I7" t="n">
-        <v>147</v>
-      </c>
       <c r="J7" t="n">
-        <v>114200000</v>
+        <v>5925000</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L7" t="n">
-        <v>60325000</v>
+        <v>56125000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.76</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="8">
@@ -1146,25 +1146,25 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H9" t="n">
-        <v>374869000</v>
+        <v>371829000</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>11932000</v>
+        <v>11212000</v>
       </c>
       <c r="K9" t="n">
         <v>166</v>
       </c>
       <c r="L9" t="n">
-        <v>140560000</v>
+        <v>138600000</v>
       </c>
       <c r="M9" t="n">
-        <v>37.5</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="10">
@@ -1287,16 +1287,16 @@
         <v>95700000</v>
       </c>
       <c r="G12" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H12" t="n">
-        <v>790988000</v>
+        <v>788788000</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>8100000</v>
+        <v>900000</v>
       </c>
       <c r="K12" t="n">
         <v>17</v>
@@ -1305,7 +1305,7 @@
         <v>26070000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="13">
@@ -1431,7 +1431,7 @@
         <v>522</v>
       </c>
       <c r="H15" t="n">
-        <v>753955000</v>
+        <v>752455000</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
@@ -1446,7 +1446,7 @@
         <v>39486000</v>
       </c>
       <c r="M15" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="16">
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
-        <v>117300000</v>
+        <v>121800000</v>
       </c>
       <c r="G19" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>852084000</v>
+        <v>856209000</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -1634,7 +1634,7 @@
         <v>38375000</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="20">
@@ -1666,13 +1666,13 @@
         <v>560</v>
       </c>
       <c r="H20" t="n">
-        <v>673523000</v>
+        <v>672398000</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>5900000</v>
+        <v>950000</v>
       </c>
       <c r="K20" t="n">
         <v>70</v>
@@ -1681,7 +1681,7 @@
         <v>69410000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.31</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="21">
@@ -1854,22 +1854,22 @@
         <v>418</v>
       </c>
       <c r="H24" t="n">
-        <v>502336000</v>
+        <v>488171000</v>
       </c>
       <c r="I24" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>76440000</v>
+        <v>8980000</v>
       </c>
       <c r="K24" t="n">
         <v>60</v>
       </c>
       <c r="L24" t="n">
-        <v>77892000</v>
+        <v>76742000</v>
       </c>
       <c r="M24" t="n">
-        <v>15.51</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="25">
@@ -1901,13 +1901,13 @@
         <v>471</v>
       </c>
       <c r="H25" t="n">
-        <v>725504000</v>
+        <v>724254000</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>13700000</v>
+        <v>7300000</v>
       </c>
       <c r="K25" t="n">
         <v>24</v>
@@ -1916,7 +1916,7 @@
         <v>40945000</v>
       </c>
       <c r="M25" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="26">
@@ -1995,7 +1995,7 @@
         <v>143</v>
       </c>
       <c r="H27" t="n">
-        <v>84755000</v>
+        <v>84465000</v>
       </c>
       <c r="I27" t="n">
         <v>25</v>
@@ -2007,10 +2007,10 @@
         <v>64</v>
       </c>
       <c r="L27" t="n">
-        <v>38000000</v>
+        <v>37710000</v>
       </c>
       <c r="M27" t="n">
-        <v>44.84</v>
+        <v>44.65</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>203494000</v>
+        <v>103494000</v>
       </c>
     </row>
     <row r="3">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>209789000</v>
+        <v>109789000</v>
       </c>
     </row>
     <row r="5">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>480989500</v>
+        <v>350989500</v>
       </c>
     </row>
     <row r="8">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>117350500</v>
+        <v>110350500</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -444,27 +444,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>461311000</v>
+        <v>551836000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>367484001</v>
+        <v>450549000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>327356000</v>
+        <v>448879001</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>195067000</v>
+        <v>290332000</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>52000000</v>
+        <v>42500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>42300000</v>
+        <v>37800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,28 +561,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>25500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>النجف</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>21000000</v>
+        <v>18300000</v>
       </c>
     </row>
   </sheetData>
@@ -629,7 +611,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,61 +620,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>429200000</v>
+        <v>25500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2274</v>
+        <v>2355</v>
       </c>
       <c r="E2" t="n">
-        <v>3180532000</v>
+        <v>3206273980</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>338400000</v>
+        <v>18200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1779</v>
+        <v>2522</v>
       </c>
       <c r="E3" t="n">
-        <v>2172200000</v>
+        <v>2972579040.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>319200000</v>
+        <v>9500000</v>
       </c>
       <c r="D4" t="n">
-        <v>2450</v>
+        <v>1863</v>
       </c>
       <c r="E4" t="n">
-        <v>2951444000</v>
+        <v>2189929160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -701,13 +683,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>248100000</v>
+        <v>4500000</v>
       </c>
       <c r="D5" t="n">
-        <v>1973</v>
+        <v>2092</v>
       </c>
       <c r="E5" t="n">
-        <v>2462064000</v>
+        <v>2482958600.32</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,7 +776,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -808,40 +790,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>46200000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>396</v>
       </c>
       <c r="H2" t="n">
-        <v>543707000</v>
+        <v>536245640</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>376851000</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>700000</v>
+        <v>5388640</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -851,44 +833,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Hussein . Kadhum Dhahi -</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>50700000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>337685000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8395000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>181826000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>53.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -898,7 +880,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -908,34 +890,34 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>8250000</v>
+        <v>3600000</v>
       </c>
       <c r="G4" t="n">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="H4" t="n">
-        <v>403684000</v>
+        <v>342403520</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="J4" t="n">
-        <v>17605000</v>
+        <v>95490000</v>
       </c>
       <c r="K4" t="n">
-        <v>115</v>
+        <v>217</v>
       </c>
       <c r="L4" t="n">
-        <v>151114000</v>
+        <v>195074520</v>
       </c>
       <c r="M4" t="n">
-        <v>37.43</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -945,44 +927,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>106000000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="H5" t="n">
-        <v>769553000</v>
+        <v>431989480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>215</v>
       </c>
       <c r="J5" t="n">
-        <v>15550000</v>
+        <v>184679000</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="L5" t="n">
-        <v>12875000</v>
+        <v>195205480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.67</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -992,44 +974,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>46850000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="H6" t="n">
-        <v>353688000</v>
+        <v>752134600</v>
       </c>
       <c r="I6" t="n">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="J6" t="n">
-        <v>26337000</v>
+        <v>487322000</v>
       </c>
       <c r="K6" t="n">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>95054000</v>
+        <v>30316600</v>
       </c>
       <c r="M6" t="n">
-        <v>26.88</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1039,44 +1021,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>61200000</v>
+        <v>3600000</v>
       </c>
       <c r="G7" t="n">
-        <v>493</v>
+        <v>424</v>
       </c>
       <c r="H7" t="n">
-        <v>541327000</v>
+        <v>349918000</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="J7" t="n">
-        <v>5925000</v>
+        <v>171339000</v>
       </c>
       <c r="K7" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="L7" t="n">
-        <v>56125000</v>
+        <v>111020000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.37</v>
+        <v>31.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1086,54 +1068,54 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>laith Lewaa Mohammad .</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>11000000</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
-        <v>1800000</v>
+        <v>558087800</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>424977000</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>62690800</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>laith Lewaa Mohammad .</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1146,31 +1128,31 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>379</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>371829000</v>
+        <v>1800000</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>11212000</v>
+        <v>1800000</v>
       </c>
       <c r="K9" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>138600000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>37.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1180,7 +1162,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1193,31 +1175,31 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="H10" t="n">
-        <v>47980000</v>
+        <v>367339000</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>186617000</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="L10" t="n">
-        <v>47980000</v>
+        <v>142560000</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1231,40 +1213,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>77400000</v>
+        <v>4500000</v>
       </c>
       <c r="G11" t="n">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="H11" t="n">
-        <v>602845000</v>
+        <v>597810200</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>481745000</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>2000000</v>
+        <v>7260200</v>
       </c>
       <c r="M11" t="n">
-        <v>0.33</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1278,40 +1260,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>95700000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H12" t="n">
-        <v>788788000</v>
+        <v>770953000</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>335</v>
       </c>
       <c r="J12" t="n">
-        <v>900000</v>
+        <v>548045000</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>26070000</v>
+        <v>26970000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1325,40 +1307,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>20100000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="H13" t="n">
-        <v>302139000</v>
+        <v>316454280.32</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="J13" t="n">
-        <v>3800000</v>
+        <v>180995000</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="L13" t="n">
-        <v>66879000</v>
+        <v>89864280.31999999</v>
       </c>
       <c r="M13" t="n">
-        <v>22.14</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1372,40 +1354,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>54900000</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="H14" t="n">
-        <v>348483000</v>
+        <v>363940800</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="J14" t="n">
-        <v>11610000</v>
+        <v>187928000</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="L14" t="n">
-        <v>108370000</v>
+        <v>136337800</v>
       </c>
       <c r="M14" t="n">
-        <v>31.1</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1419,40 +1401,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>99500000</v>
+        <v>6600000</v>
       </c>
       <c r="G15" t="n">
-        <v>522</v>
+        <v>557</v>
       </c>
       <c r="H15" t="n">
-        <v>752455000</v>
+        <v>762752160</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="J15" t="n">
-        <v>32285000</v>
+        <v>408293000</v>
       </c>
       <c r="K15" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="L15" t="n">
-        <v>39486000</v>
+        <v>78172160</v>
       </c>
       <c r="M15" t="n">
-        <v>5.25</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1462,44 +1444,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>100800000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>92</v>
       </c>
       <c r="H16" t="n">
-        <v>518692000</v>
+        <v>66461320</v>
       </c>
       <c r="I16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>33930000</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="L16" t="n">
-        <v>91920000</v>
+        <v>66461320</v>
       </c>
       <c r="M16" t="n">
-        <v>17.72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,44 +1491,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>3600000</v>
+        <v>14400000</v>
       </c>
       <c r="G17" t="n">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="H17" t="n">
-        <v>375378000</v>
+        <v>536451440</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="J17" t="n">
-        <v>8655000</v>
+        <v>228237000</v>
       </c>
       <c r="K17" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="L17" t="n">
-        <v>130620000</v>
+        <v>134599440</v>
       </c>
       <c r="M17" t="n">
-        <v>34.8</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1556,7 +1538,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1569,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5400000</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1581,19 +1563,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5400000</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,44 +1585,44 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>121800000</v>
+        <v>4500000</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>342</v>
       </c>
       <c r="H19" t="n">
-        <v>856209000</v>
+        <v>398259880</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="J19" t="n">
-        <v>450000</v>
+        <v>173434000</v>
       </c>
       <c r="K19" t="n">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="L19" t="n">
-        <v>38375000</v>
+        <v>165251880</v>
       </c>
       <c r="M19" t="n">
-        <v>4.48</v>
+        <v>41.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1650,101 +1632,101 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Nadhir . Mohammad Kadhom -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>103500000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>560</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>672398000</v>
+        <v>5400000</v>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>69410000</v>
+        <v>5400000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>58250000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>444</v>
+        <v>564</v>
       </c>
       <c r="H21" t="n">
-        <v>484249000</v>
+        <v>837967500</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>564124000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>38825000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1757,31 +1739,31 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>566</v>
       </c>
       <c r="H22" t="n">
-        <v>12500000</v>
+        <v>665443000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>426568000</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="L22" t="n">
-        <v>12500000</v>
+        <v>73330000</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1791,23 +1773,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Ahmed . Hassan Yusif -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>23250000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>21318000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1828,7 +1810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1838,44 +1820,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>74700000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="H24" t="n">
-        <v>488171000</v>
+        <v>467440000</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>305</v>
       </c>
       <c r="J24" t="n">
-        <v>8980000</v>
+        <v>342997000</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>76742000</v>
+        <v>396000</v>
       </c>
       <c r="M24" t="n">
-        <v>15.72</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1885,44 +1867,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>111300000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>471</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>724254000</v>
+        <v>15470000</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>7300000</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L25" t="n">
-        <v>40945000</v>
+        <v>15470000</v>
       </c>
       <c r="M25" t="n">
-        <v>5.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1932,44 +1914,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>70900000</v>
+        <v>9500000</v>
       </c>
       <c r="G26" t="n">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="H26" t="n">
-        <v>357243000</v>
+        <v>255724360</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="J26" t="n">
-        <v>13918000</v>
+        <v>135850000</v>
       </c>
       <c r="K26" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L26" t="n">
-        <v>55520000</v>
+        <v>60777360</v>
       </c>
       <c r="M26" t="n">
-        <v>15.54</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1979,38 +1961,226 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Baydaa . Hameed Mizher -</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ibtihal Hamza  Hussain -</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>445</v>
+      </c>
+      <c r="H28" t="n">
+        <v>517878200</v>
+      </c>
+      <c r="I28" t="n">
+        <v>312</v>
+      </c>
+      <c r="J28" t="n">
+        <v>343040000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>94</v>
+      </c>
+      <c r="L28" t="n">
+        <v>116439200</v>
+      </c>
+      <c r="M28" t="n">
+        <v>122.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>472</v>
+      </c>
+      <c r="H29" t="n">
+        <v>707942000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>314</v>
+      </c>
+      <c r="J29" t="n">
+        <v>456212000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>32</v>
+      </c>
+      <c r="L29" t="n">
+        <v>50883000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>102</v>
+      </c>
+      <c r="H30" t="n">
+        <v>129750000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>37</v>
+      </c>
+      <c r="J30" t="n">
+        <v>56285000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>26</v>
+      </c>
+      <c r="L30" t="n">
+        <v>15744000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>143</v>
-      </c>
-      <c r="H27" t="n">
-        <v>84465000</v>
-      </c>
-      <c r="I27" t="n">
-        <v>25</v>
-      </c>
-      <c r="J27" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>64</v>
-      </c>
-      <c r="L27" t="n">
-        <v>37710000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>44.65</v>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>164</v>
+      </c>
+      <c r="H31" t="n">
+        <v>94668600</v>
+      </c>
+      <c r="I31" t="n">
+        <v>54</v>
+      </c>
+      <c r="J31" t="n">
+        <v>26755000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>110</v>
+      </c>
+      <c r="L31" t="n">
+        <v>67913600</v>
+      </c>
+      <c r="M31" t="n">
+        <v>71.73999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2024,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2066,7 +2236,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103494000</v>
+        <v>98494000</v>
       </c>
     </row>
     <row r="3">
@@ -2086,7 +2256,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>166238</v>
+        <v>160238</v>
       </c>
     </row>
     <row r="4">
@@ -2106,7 +2276,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>109789000</v>
+        <v>146489000</v>
       </c>
     </row>
     <row r="5">
@@ -2126,7 +2296,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14094000</v>
+        <v>34359000</v>
       </c>
     </row>
     <row r="6">
@@ -2142,11 +2312,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hindya safe</t>
+          <t>Bank Hindya</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>375895000</v>
       </c>
     </row>
     <row r="7">
@@ -2157,36 +2327,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>karbala</t>
+          <t>Najaf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bank Hindya</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>350989500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Najaf</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>110350500</v>
+        <v>61350500</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -12,6 +12,7 @@
     <sheet name="الأداء - فروع" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="الأداء - موظفين" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="الأرصدة" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="التاريخ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>551836000</v>
+        <v>551386000</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>450549000</v>
+        <v>447620000</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>448879001</v>
+        <v>447064001</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>290332000</v>
+        <v>289282000</v>
       </c>
     </row>
   </sheetData>
@@ -2342,4 +2343,198 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الفرع</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>صرف_2026-01</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-01</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>صرف_2026-02</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-02</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>صرف_2026-03</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-03</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>صرف_None</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>متأخر_None</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>النجف</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>550290000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>285486000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>480050000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>303946000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>432800000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>324966000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>447620000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>306450000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>184335000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>241900000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>186212000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>338400000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>194867000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>289282000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الحلة</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>404010000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>436001000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>424900000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>437156000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>323950000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>459416000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18200000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>551386000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الديوانية</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>396500000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>377739001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>327500000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>365486001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>248100000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>365124001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>447064001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>551386000</v>
+        <v>568576000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>447620000</v>
+        <v>447964001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>447064001</v>
+        <v>444515000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>289282000</v>
+        <v>282497000</v>
       </c>
     </row>
   </sheetData>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>42500000</v>
+        <v>38000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -547,25 +547,43 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>37800000</v>
+        <v>32400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>النجف</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>الحلة</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>18300000</v>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8100000</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +630,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -621,19 +639,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25500000</v>
+        <v>43500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2355</v>
+        <v>2261</v>
       </c>
       <c r="E2" t="n">
-        <v>3206273980</v>
+        <v>3097223500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -642,19 +660,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18200000</v>
+        <v>39800000</v>
       </c>
       <c r="D3" t="n">
-        <v>2522</v>
+        <v>2431</v>
       </c>
       <c r="E3" t="n">
-        <v>2972579040.6</v>
+        <v>2897049000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -663,19 +681,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9500000</v>
+        <v>32000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1863</v>
+        <v>1752</v>
       </c>
       <c r="E4" t="n">
-        <v>2189929160</v>
+        <v>2092272000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -684,13 +702,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4500000</v>
+        <v>26100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2092</v>
+        <v>1960</v>
       </c>
       <c r="E5" t="n">
-        <v>2482958600.32</v>
+        <v>2373079000</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,7 +795,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -800,31 +818,31 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H2" t="n">
-        <v>536245640</v>
+        <v>524597000</v>
       </c>
       <c r="I2" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="J2" t="n">
-        <v>376851000</v>
+        <v>331207000</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>5388640</v>
+        <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -834,44 +852,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hussein . Kadhum Dhahi -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>334490000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>82437000</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>189021000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -881,44 +899,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="H4" t="n">
-        <v>342403520</v>
+        <v>385479000</v>
       </c>
       <c r="I4" t="n">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="J4" t="n">
-        <v>95490000</v>
+        <v>158871000</v>
       </c>
       <c r="K4" t="n">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="L4" t="n">
-        <v>195074520</v>
+        <v>154070000</v>
       </c>
       <c r="M4" t="n">
-        <v>56.97</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -928,44 +946,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>21600000</v>
       </c>
       <c r="G5" t="n">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="H5" t="n">
-        <v>431989480.6</v>
+        <v>751123000</v>
       </c>
       <c r="I5" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J5" t="n">
-        <v>184679000</v>
+        <v>401915000</v>
       </c>
       <c r="K5" t="n">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>195205480.6</v>
+        <v>27175000</v>
       </c>
       <c r="M5" t="n">
-        <v>45.19</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -975,44 +993,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G6" t="n">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>752134600</v>
+        <v>346858000</v>
       </c>
       <c r="I6" t="n">
-        <v>283</v>
+        <v>196</v>
       </c>
       <c r="J6" t="n">
-        <v>487322000</v>
+        <v>154807000</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="L6" t="n">
-        <v>30316600</v>
+        <v>110420000</v>
       </c>
       <c r="M6" t="n">
-        <v>4.03</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1022,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1032,34 +1050,34 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3600000</v>
+        <v>11000000</v>
       </c>
       <c r="G7" t="n">
-        <v>424</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>349918000</v>
+        <v>552702000</v>
       </c>
       <c r="I7" t="n">
-        <v>217</v>
+        <v>390</v>
       </c>
       <c r="J7" t="n">
-        <v>171339000</v>
+        <v>407648000</v>
       </c>
       <c r="K7" t="n">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="L7" t="n">
-        <v>111020000</v>
+        <v>59800000</v>
       </c>
       <c r="M7" t="n">
-        <v>31.73</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,54 +1087,54 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>laith Lewaa Mohammad .</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="G8" t="n">
-        <v>508</v>
-      </c>
       <c r="H8" t="n">
-        <v>558087800</v>
+        <v>1800000</v>
       </c>
       <c r="I8" t="n">
-        <v>405</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>424977000</v>
+        <v>1800000</v>
       </c>
       <c r="K8" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>62690800</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>11.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>laith Lewaa Mohammad .</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1129,31 +1147,31 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>1800000</v>
+        <v>362874000</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="J9" t="n">
-        <v>1800000</v>
+        <v>172311000</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>140400000</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1163,7 +1181,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1176,31 +1194,31 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>379</v>
+        <v>56</v>
       </c>
       <c r="H10" t="n">
-        <v>367339000</v>
+        <v>47980000</v>
       </c>
       <c r="I10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>186617000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>142560000</v>
+        <v>47980000</v>
       </c>
       <c r="M10" t="n">
-        <v>38.81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1214,40 +1232,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>4500000</v>
+        <v>26100000</v>
       </c>
       <c r="G11" t="n">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="H11" t="n">
-        <v>597810200</v>
+        <v>589165000</v>
       </c>
       <c r="I11" t="n">
-        <v>368</v>
+        <v>278</v>
       </c>
       <c r="J11" t="n">
-        <v>481745000</v>
+        <v>352250000</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>7260200</v>
+        <v>2000000</v>
       </c>
       <c r="M11" t="n">
-        <v>1.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1270,16 +1288,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H12" t="n">
-        <v>770953000</v>
+        <v>744928000</v>
       </c>
       <c r="I12" t="n">
-        <v>335</v>
+        <v>251</v>
       </c>
       <c r="J12" t="n">
-        <v>548045000</v>
+        <v>396335000</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
@@ -1288,13 +1306,13 @@
         <v>26970000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1317,31 +1335,31 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="H13" t="n">
-        <v>316454280.32</v>
+        <v>289234000</v>
       </c>
       <c r="I13" t="n">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="J13" t="n">
-        <v>180995000</v>
+        <v>141650000</v>
       </c>
       <c r="K13" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="L13" t="n">
-        <v>89864280.31999999</v>
+        <v>68729000</v>
       </c>
       <c r="M13" t="n">
-        <v>28.4</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1364,31 +1382,31 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="H14" t="n">
-        <v>363940800</v>
+        <v>338898000</v>
       </c>
       <c r="I14" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="J14" t="n">
-        <v>187928000</v>
+        <v>149108000</v>
       </c>
       <c r="K14" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="L14" t="n">
-        <v>136337800</v>
+        <v>114970000</v>
       </c>
       <c r="M14" t="n">
-        <v>37.46</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1411,31 +1429,31 @@
         <v>6600000</v>
       </c>
       <c r="G15" t="n">
-        <v>557</v>
+        <v>519</v>
       </c>
       <c r="H15" t="n">
-        <v>762752160</v>
+        <v>722566000</v>
       </c>
       <c r="I15" t="n">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="J15" t="n">
-        <v>408293000</v>
+        <v>308986000</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>78172160</v>
+        <v>51236000</v>
       </c>
       <c r="M15" t="n">
-        <v>10.25</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1445,44 +1463,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="G16" t="n">
-        <v>92</v>
+        <v>316</v>
       </c>
       <c r="H16" t="n">
-        <v>66461320</v>
+        <v>514777000</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>164562000</v>
       </c>
       <c r="K16" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="L16" t="n">
-        <v>66461320</v>
+        <v>118950000</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1492,44 +1510,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>14400000</v>
+        <v>4500000</v>
       </c>
       <c r="G17" t="n">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="H17" t="n">
-        <v>536451440</v>
+        <v>360678000</v>
       </c>
       <c r="I17" t="n">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="J17" t="n">
-        <v>228237000</v>
+        <v>114216000</v>
       </c>
       <c r="K17" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>134599440</v>
+        <v>134265000</v>
       </c>
       <c r="M17" t="n">
-        <v>25.09</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1539,7 +1557,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Nadhir . Mohammad Kadhom -</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1552,10 +1570,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5400000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1564,19 +1582,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5400000</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1586,44 +1604,44 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4500000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>342</v>
+        <v>558</v>
       </c>
       <c r="H19" t="n">
-        <v>398259880</v>
+        <v>828252500</v>
       </c>
       <c r="I19" t="n">
-        <v>136</v>
+        <v>329</v>
       </c>
       <c r="J19" t="n">
-        <v>173434000</v>
+        <v>510909000</v>
       </c>
       <c r="K19" t="n">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="L19" t="n">
-        <v>165251880</v>
+        <v>38825000</v>
       </c>
       <c r="M19" t="n">
-        <v>41.49</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1633,101 +1651,101 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>562</v>
       </c>
       <c r="H20" t="n">
-        <v>5400000</v>
+        <v>665550000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>352875000</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="L20" t="n">
-        <v>5400000</v>
+        <v>70210000</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="G21" t="n">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="H21" t="n">
-        <v>837967500</v>
+        <v>459044000</v>
       </c>
       <c r="I21" t="n">
-        <v>367</v>
+        <v>233</v>
       </c>
       <c r="J21" t="n">
-        <v>564124000</v>
+        <v>258078000</v>
       </c>
       <c r="K21" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>38825000</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1740,31 +1758,31 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>566</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>665443000</v>
+        <v>12500000</v>
       </c>
       <c r="I22" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>426568000</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>73330000</v>
+        <v>12500000</v>
       </c>
       <c r="M22" t="n">
-        <v>11.02</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1774,44 +1792,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ahmed . Hassan Yusif -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>21500000</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>254567000</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>117966000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>50920000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1821,7 +1839,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1834,31 +1852,31 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="H24" t="n">
-        <v>467440000</v>
+        <v>477931000</v>
       </c>
       <c r="I24" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="J24" t="n">
-        <v>342997000</v>
+        <v>292079000</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="L24" t="n">
-        <v>396000</v>
+        <v>85122000</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1868,7 +1886,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1881,31 +1899,31 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>463</v>
       </c>
       <c r="H25" t="n">
-        <v>15470000</v>
+        <v>685084000</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>319617000</v>
       </c>
       <c r="K25" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L25" t="n">
-        <v>15470000</v>
+        <v>48045000</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1915,44 +1933,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>9500000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="H26" t="n">
-        <v>255724360</v>
+        <v>118831000</v>
       </c>
       <c r="I26" t="n">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>135850000</v>
+        <v>38760000</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="L26" t="n">
-        <v>60777360</v>
+        <v>10200000</v>
       </c>
       <c r="M26" t="n">
-        <v>23.77</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1962,7 +1980,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baydaa . Hameed Mizher -</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1975,213 +1993,25 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="H27" t="n">
-        <v>1056000</v>
+        <v>84315000</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>26305000</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="L27" t="n">
-        <v>1056000</v>
+        <v>57710000</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ibtihal Hamza  Hussain -</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>445</v>
-      </c>
-      <c r="H28" t="n">
-        <v>517878200</v>
-      </c>
-      <c r="I28" t="n">
-        <v>312</v>
-      </c>
-      <c r="J28" t="n">
-        <v>343040000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>94</v>
-      </c>
-      <c r="L28" t="n">
-        <v>116439200</v>
-      </c>
-      <c r="M28" t="n">
-        <v>122.04</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jawnaa . Radhi Shimran -</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>472</v>
-      </c>
-      <c r="H29" t="n">
-        <v>707942000</v>
-      </c>
-      <c r="I29" t="n">
-        <v>314</v>
-      </c>
-      <c r="J29" t="n">
-        <v>456212000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>32</v>
-      </c>
-      <c r="L29" t="n">
-        <v>50883000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>102</v>
-      </c>
-      <c r="H30" t="n">
-        <v>129750000</v>
-      </c>
-      <c r="I30" t="n">
-        <v>37</v>
-      </c>
-      <c r="J30" t="n">
-        <v>56285000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>26</v>
-      </c>
-      <c r="L30" t="n">
-        <v>15744000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>12.13</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>164</v>
-      </c>
-      <c r="H31" t="n">
-        <v>94668600</v>
-      </c>
-      <c r="I31" t="n">
-        <v>54</v>
-      </c>
-      <c r="J31" t="n">
-        <v>26755000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>110</v>
-      </c>
-      <c r="L31" t="n">
-        <v>67913600</v>
-      </c>
-      <c r="M31" t="n">
-        <v>71.73999999999999</v>
+        <v>68.45</v>
       </c>
     </row>
   </sheetData>
@@ -2432,10 +2262,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>25500000</v>
+        <v>43500000</v>
       </c>
       <c r="J2" t="n">
-        <v>447620000</v>
+        <v>444515000</v>
       </c>
     </row>
     <row r="3">
@@ -2464,10 +2294,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>9500000</v>
+        <v>32000000</v>
       </c>
       <c r="J3" t="n">
-        <v>289282000</v>
+        <v>282497000</v>
       </c>
     </row>
     <row r="4">
@@ -2496,10 +2326,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>18200000</v>
+        <v>39800000</v>
       </c>
       <c r="J4" t="n">
-        <v>551386000</v>
+        <v>568576000</v>
       </c>
     </row>
     <row r="5">
@@ -2528,10 +2358,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>4500000</v>
+        <v>26100000</v>
       </c>
       <c r="J5" t="n">
-        <v>447064001</v>
+        <v>447964001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,11 @@
           <t>محفظة القروض</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>رصيد المتأخر &gt;30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -647,6 +652,9 @@
       <c r="E2" t="n">
         <v>3097223500</v>
       </c>
+      <c r="F2" t="n">
+        <v>418886000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -668,6 +676,9 @@
       <c r="E3" t="n">
         <v>2897049000</v>
       </c>
+      <c r="F3" t="n">
+        <v>541186000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,6 +700,9 @@
       <c r="E4" t="n">
         <v>2092272000</v>
       </c>
+      <c r="F4" t="n">
+        <v>264497000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -709,6 +723,9 @@
       </c>
       <c r="E5" t="n">
         <v>2373079000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>401049000</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>568576000</v>
+        <v>580321000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>447964001</v>
+        <v>447759001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>444515000</v>
+        <v>440940000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>282497000</v>
+        <v>295042000</v>
       </c>
     </row>
   </sheetData>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,64 +526,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>38000000</v>
+        <v>25500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>32400000</v>
+        <v>11100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>13500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الحلة</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8100000</v>
+        <v>6600000</v>
       </c>
     </row>
   </sheetData>
@@ -635,97 +617,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43500000</v>
+        <v>74500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2261</v>
+        <v>1758</v>
       </c>
       <c r="E2" t="n">
-        <v>3097223500</v>
+        <v>2112151000</v>
       </c>
       <c r="F2" t="n">
-        <v>418886000</v>
+        <v>263297000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39800000</v>
+        <v>66000000</v>
       </c>
       <c r="D3" t="n">
-        <v>2431</v>
+        <v>2270</v>
       </c>
       <c r="E3" t="n">
-        <v>2897049000</v>
+        <v>3086533500</v>
       </c>
       <c r="F3" t="n">
-        <v>541186000</v>
+        <v>416286000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32000000</v>
+        <v>60900000</v>
       </c>
       <c r="D4" t="n">
-        <v>1752</v>
+        <v>1960</v>
       </c>
       <c r="E4" t="n">
-        <v>2092272000</v>
+        <v>2370309000</v>
       </c>
       <c r="F4" t="n">
-        <v>264497000</v>
+        <v>400699000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26100000</v>
+        <v>50000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1960</v>
+        <v>2428</v>
       </c>
       <c r="E5" t="n">
-        <v>2373079000</v>
+        <v>2882869000</v>
       </c>
       <c r="F5" t="n">
-        <v>401049000</v>
+        <v>538061000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -838,13 +820,13 @@
         <v>391</v>
       </c>
       <c r="H2" t="n">
-        <v>524597000</v>
+        <v>518572000</v>
       </c>
       <c r="I2" t="n">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="J2" t="n">
-        <v>331207000</v>
+        <v>290088000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +841,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +855,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3600000</v>
+        <v>13800000</v>
       </c>
       <c r="G3" t="n">
         <v>313</v>
       </c>
       <c r="H3" t="n">
-        <v>334490000</v>
+        <v>340195000</v>
       </c>
       <c r="I3" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J3" t="n">
-        <v>82437000</v>
+        <v>60302000</v>
       </c>
       <c r="K3" t="n">
         <v>202</v>
@@ -900,13 +882,13 @@
         <v>189021000</v>
       </c>
       <c r="M3" t="n">
-        <v>56.51</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +911,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H4" t="n">
-        <v>385479000</v>
+        <v>380479000</v>
       </c>
       <c r="I4" t="n">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="J4" t="n">
-        <v>158871000</v>
+        <v>134335000</v>
       </c>
       <c r="K4" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>154070000</v>
+        <v>151295000</v>
       </c>
       <c r="M4" t="n">
-        <v>39.97</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,28 +961,28 @@
         <v>431</v>
       </c>
       <c r="H5" t="n">
-        <v>751123000</v>
+        <v>746713000</v>
       </c>
       <c r="I5" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="J5" t="n">
-        <v>401915000</v>
+        <v>376564000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>27175000</v>
+        <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1008,13 @@
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>346858000</v>
+        <v>345058000</v>
       </c>
       <c r="I6" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J6" t="n">
-        <v>154807000</v>
+        <v>144127000</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -1041,13 +1023,13 @@
         <v>110420000</v>
       </c>
       <c r="M6" t="n">
-        <v>31.83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1055,13 @@
         <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>552702000</v>
+        <v>550052000</v>
       </c>
       <c r="I7" t="n">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="J7" t="n">
-        <v>407648000</v>
+        <v>393528000</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -1088,13 +1070,13 @@
         <v>59800000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.82</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,7 +1123,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1167,13 +1149,13 @@
         <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>362874000</v>
+        <v>362514000</v>
       </c>
       <c r="I9" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J9" t="n">
-        <v>172311000</v>
+        <v>169011000</v>
       </c>
       <c r="K9" t="n">
         <v>169</v>
@@ -1182,13 +1164,13 @@
         <v>140400000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.69</v>
+        <v>38.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1217,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,16 +1240,16 @@
         <v>26100000</v>
       </c>
       <c r="G11" t="n">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H11" t="n">
-        <v>589165000</v>
+        <v>579115000</v>
       </c>
       <c r="I11" t="n">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="J11" t="n">
-        <v>352250000</v>
+        <v>291955000</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -1276,13 +1258,13 @@
         <v>2000000</v>
       </c>
       <c r="M11" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1278,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>34800000</v>
       </c>
       <c r="G12" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="H12" t="n">
-        <v>744928000</v>
+        <v>760148000</v>
       </c>
       <c r="I12" t="n">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="J12" t="n">
-        <v>396335000</v>
+        <v>324385000</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>26970000</v>
+        <v>26620000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1337,13 @@
         <v>227</v>
       </c>
       <c r="H13" t="n">
-        <v>289234000</v>
+        <v>285299000</v>
       </c>
       <c r="I13" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="J13" t="n">
-        <v>141650000</v>
+        <v>113520000</v>
       </c>
       <c r="K13" t="n">
         <v>69</v>
@@ -1370,13 +1352,13 @@
         <v>68729000</v>
       </c>
       <c r="M13" t="n">
-        <v>23.76</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,13 +1384,13 @@
         <v>359</v>
       </c>
       <c r="H14" t="n">
-        <v>338898000</v>
+        <v>335253000</v>
       </c>
       <c r="I14" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="J14" t="n">
-        <v>149108000</v>
+        <v>126698000</v>
       </c>
       <c r="K14" t="n">
         <v>123</v>
@@ -1417,13 +1399,13 @@
         <v>114970000</v>
       </c>
       <c r="M14" t="n">
-        <v>33.92</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,16 +1428,16 @@
         <v>6600000</v>
       </c>
       <c r="G15" t="n">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H15" t="n">
-        <v>722566000</v>
+        <v>714791000</v>
       </c>
       <c r="I15" t="n">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="J15" t="n">
-        <v>308986000</v>
+        <v>264455000</v>
       </c>
       <c r="K15" t="n">
         <v>59</v>
@@ -1464,13 +1446,13 @@
         <v>51236000</v>
       </c>
       <c r="M15" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,28 +1478,28 @@
         <v>316</v>
       </c>
       <c r="H16" t="n">
-        <v>514777000</v>
+        <v>509227000</v>
       </c>
       <c r="I16" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>164562000</v>
+        <v>129872000</v>
       </c>
       <c r="K16" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L16" t="n">
-        <v>118950000</v>
+        <v>117350000</v>
       </c>
       <c r="M16" t="n">
-        <v>23.11</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1513,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>4500000</v>
+        <v>13500000</v>
       </c>
       <c r="G17" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H17" t="n">
-        <v>360678000</v>
+        <v>363963000</v>
       </c>
       <c r="I17" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="J17" t="n">
-        <v>114216000</v>
+        <v>87251000</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>134265000</v>
+        <v>133265000</v>
       </c>
       <c r="M17" t="n">
-        <v>37.23</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,7 +1593,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1607,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G19" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>828252500</v>
+        <v>828952500</v>
       </c>
       <c r="I19" t="n">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="J19" t="n">
-        <v>510909000</v>
+        <v>461444000</v>
       </c>
       <c r="K19" t="n">
         <v>45</v>
@@ -1652,13 +1634,13 @@
         <v>38825000</v>
       </c>
       <c r="M19" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1654,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>18000000</v>
+        <v>22500000</v>
       </c>
       <c r="G20" t="n">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H20" t="n">
-        <v>665550000</v>
+        <v>664200000</v>
       </c>
       <c r="I20" t="n">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="J20" t="n">
-        <v>352875000</v>
+        <v>321144000</v>
       </c>
       <c r="K20" t="n">
         <v>76</v>
@@ -1699,13 +1681,13 @@
         <v>70210000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.55</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,25 +1701,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>10500000</v>
+        <v>37500000</v>
       </c>
       <c r="G21" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H21" t="n">
-        <v>459044000</v>
+        <v>476264000</v>
       </c>
       <c r="I21" t="n">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="J21" t="n">
-        <v>258078000</v>
+        <v>210683000</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1752,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1799,7 +1781,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1795,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>21500000</v>
+        <v>25000000</v>
       </c>
       <c r="G23" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H23" t="n">
-        <v>254567000</v>
+        <v>254926000</v>
       </c>
       <c r="I23" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="J23" t="n">
-        <v>117966000</v>
+        <v>106391000</v>
       </c>
       <c r="K23" t="n">
         <v>60</v>
       </c>
       <c r="L23" t="n">
-        <v>50920000</v>
+        <v>50620000</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,7 +1854,7 @@
         <v>413</v>
       </c>
       <c r="H24" t="n">
-        <v>477931000</v>
+        <v>477131000</v>
       </c>
       <c r="I24" t="n">
         <v>263</v>
@@ -1884,16 +1866,16 @@
         <v>67</v>
       </c>
       <c r="L24" t="n">
-        <v>85122000</v>
+        <v>84322000</v>
       </c>
       <c r="M24" t="n">
-        <v>17.81</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1907,25 +1889,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="G25" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H25" t="n">
-        <v>685084000</v>
+        <v>688284000</v>
       </c>
       <c r="I25" t="n">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="J25" t="n">
-        <v>319617000</v>
+        <v>282997000</v>
       </c>
       <c r="K25" t="n">
         <v>29</v>
@@ -1934,13 +1916,13 @@
         <v>48045000</v>
       </c>
       <c r="M25" t="n">
-        <v>7.01</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1966,7 +1948,7 @@
         <v>88</v>
       </c>
       <c r="H26" t="n">
-        <v>118831000</v>
+        <v>118731000</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
@@ -1978,16 +1960,16 @@
         <v>17</v>
       </c>
       <c r="L26" t="n">
-        <v>10200000</v>
+        <v>10100000</v>
       </c>
       <c r="M26" t="n">
-        <v>8.58</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2279,10 +2261,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>43500000</v>
+        <v>66000000</v>
       </c>
       <c r="J2" t="n">
-        <v>444515000</v>
+        <v>440940000</v>
       </c>
     </row>
     <row r="3">
@@ -2311,10 +2293,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>32000000</v>
+        <v>74500000</v>
       </c>
       <c r="J3" t="n">
-        <v>282497000</v>
+        <v>295042000</v>
       </c>
     </row>
     <row r="4">
@@ -2343,10 +2325,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>39800000</v>
+        <v>50000000</v>
       </c>
       <c r="J4" t="n">
-        <v>568576000</v>
+        <v>580321000</v>
       </c>
     </row>
     <row r="5">
@@ -2375,10 +2357,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>26100000</v>
+        <v>60900000</v>
       </c>
       <c r="J5" t="n">
-        <v>447964001</v>
+        <v>447759001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>580321000</v>
+        <v>607641000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>447759001</v>
+        <v>460285000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>440940000</v>
+        <v>448619001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>295042000</v>
+        <v>303957000</v>
       </c>
     </row>
   </sheetData>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,46 +526,64 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>25500000</v>
+        <v>71100000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>11100000</v>
+        <v>38100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6600000</v>
+        <v>22200000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الحلة</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16200000</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -626,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74500000</v>
+        <v>97000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1758</v>
+        <v>1771</v>
       </c>
       <c r="E2" t="n">
-        <v>2112151000</v>
+        <v>2115753000</v>
       </c>
       <c r="F2" t="n">
         <v>263297000</v>
@@ -641,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66000000</v>
+        <v>70500000</v>
       </c>
       <c r="D3" t="n">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="E3" t="n">
-        <v>3086533500</v>
+        <v>3077323500</v>
       </c>
       <c r="F3" t="n">
         <v>416286000</v>
@@ -665,49 +683,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60900000</v>
+        <v>62000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1960</v>
+        <v>2425</v>
       </c>
       <c r="E4" t="n">
-        <v>2370309000</v>
+        <v>2871404000</v>
       </c>
       <c r="F4" t="n">
-        <v>400699000</v>
+        <v>537221000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50000000</v>
+        <v>60900000</v>
       </c>
       <c r="D5" t="n">
-        <v>2428</v>
+        <v>1948</v>
       </c>
       <c r="E5" t="n">
-        <v>2882869000</v>
+        <v>2343579000</v>
       </c>
       <c r="F5" t="n">
-        <v>538061000</v>
+        <v>400199000</v>
       </c>
     </row>
   </sheetData>
@@ -794,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -817,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H2" t="n">
-        <v>518572000</v>
+        <v>511022000</v>
       </c>
       <c r="I2" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="J2" t="n">
-        <v>290088000</v>
+        <v>249136000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -835,13 +853,13 @@
         <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -867,28 +885,28 @@
         <v>313</v>
       </c>
       <c r="H3" t="n">
-        <v>340195000</v>
+        <v>338425000</v>
       </c>
       <c r="I3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>60302000</v>
+        <v>49337000</v>
       </c>
       <c r="K3" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L3" t="n">
-        <v>189021000</v>
+        <v>188181000</v>
       </c>
       <c r="M3" t="n">
-        <v>55.56</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -914,13 +932,13 @@
         <v>367</v>
       </c>
       <c r="H4" t="n">
-        <v>380479000</v>
+        <v>379204000</v>
       </c>
       <c r="I4" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="J4" t="n">
-        <v>134335000</v>
+        <v>125464000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -929,13 +947,13 @@
         <v>151295000</v>
       </c>
       <c r="M4" t="n">
-        <v>39.76</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -961,13 +979,13 @@
         <v>431</v>
       </c>
       <c r="H5" t="n">
-        <v>746713000</v>
+        <v>740913000</v>
       </c>
       <c r="I5" t="n">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="J5" t="n">
-        <v>376564000</v>
+        <v>334488000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -976,13 +994,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1008,13 +1026,13 @@
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>345058000</v>
+        <v>343348000</v>
       </c>
       <c r="I6" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="J6" t="n">
-        <v>144127000</v>
+        <v>134287000</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -1023,13 +1041,13 @@
         <v>110420000</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1043,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>11000000</v>
+        <v>23000000</v>
       </c>
       <c r="G7" t="n">
         <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>550052000</v>
+        <v>557052000</v>
       </c>
       <c r="I7" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J7" t="n">
-        <v>393528000</v>
+        <v>389728000</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -1070,13 +1088,13 @@
         <v>59800000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.87</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1102,13 +1120,13 @@
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1800000</v>
+        <v>1440000</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1123,7 +1141,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1149,13 +1167,13 @@
         <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>362514000</v>
+        <v>360704000</v>
       </c>
       <c r="I9" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="J9" t="n">
-        <v>169011000</v>
+        <v>157171000</v>
       </c>
       <c r="K9" t="n">
         <v>169</v>
@@ -1164,13 +1182,13 @@
         <v>140400000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.73</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1217,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1243,13 +1261,13 @@
         <v>465</v>
       </c>
       <c r="H11" t="n">
-        <v>579115000</v>
+        <v>568085000</v>
       </c>
       <c r="I11" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="J11" t="n">
-        <v>291955000</v>
+        <v>226430000</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -1264,7 +1282,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1287,31 +1305,31 @@
         <v>34800000</v>
       </c>
       <c r="G12" t="n">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="H12" t="n">
-        <v>760148000</v>
+        <v>748448000</v>
       </c>
       <c r="I12" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="J12" t="n">
-        <v>324385000</v>
+        <v>253235000</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>26620000</v>
+        <v>26120000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1337,13 +1355,13 @@
         <v>227</v>
       </c>
       <c r="H13" t="n">
-        <v>285299000</v>
+        <v>284189000</v>
       </c>
       <c r="I13" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="J13" t="n">
-        <v>113520000</v>
+        <v>105504000</v>
       </c>
       <c r="K13" t="n">
         <v>69</v>
@@ -1352,13 +1370,13 @@
         <v>68729000</v>
       </c>
       <c r="M13" t="n">
-        <v>24.09</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1384,13 +1402,13 @@
         <v>359</v>
       </c>
       <c r="H14" t="n">
-        <v>335253000</v>
+        <v>334173000</v>
       </c>
       <c r="I14" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J14" t="n">
-        <v>126698000</v>
+        <v>119018000</v>
       </c>
       <c r="K14" t="n">
         <v>123</v>
@@ -1399,13 +1417,13 @@
         <v>114970000</v>
       </c>
       <c r="M14" t="n">
-        <v>34.29</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1431,13 +1449,13 @@
         <v>516</v>
       </c>
       <c r="H15" t="n">
-        <v>714791000</v>
+        <v>711096000</v>
       </c>
       <c r="I15" t="n">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="J15" t="n">
-        <v>264455000</v>
+        <v>236036000</v>
       </c>
       <c r="K15" t="n">
         <v>59</v>
@@ -1446,13 +1464,13 @@
         <v>51236000</v>
       </c>
       <c r="M15" t="n">
-        <v>7.17</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1478,13 +1496,13 @@
         <v>316</v>
       </c>
       <c r="H16" t="n">
-        <v>509227000</v>
+        <v>508127000</v>
       </c>
       <c r="I16" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J16" t="n">
-        <v>129872000</v>
+        <v>122832000</v>
       </c>
       <c r="K16" t="n">
         <v>75</v>
@@ -1493,13 +1511,13 @@
         <v>117350000</v>
       </c>
       <c r="M16" t="n">
-        <v>23.04</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1513,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>13500000</v>
+        <v>18000000</v>
       </c>
       <c r="G17" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H17" t="n">
-        <v>363963000</v>
+        <v>365848000</v>
       </c>
       <c r="I17" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J17" t="n">
-        <v>87251000</v>
+        <v>68906000</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
@@ -1540,13 +1558,13 @@
         <v>133265000</v>
       </c>
       <c r="M17" t="n">
-        <v>36.61</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1593,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1619,13 +1637,13 @@
         <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>828952500</v>
+        <v>825702500</v>
       </c>
       <c r="I19" t="n">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="J19" t="n">
-        <v>461444000</v>
+        <v>442944000</v>
       </c>
       <c r="K19" t="n">
         <v>45</v>
@@ -1634,13 +1652,13 @@
         <v>38825000</v>
       </c>
       <c r="M19" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1666,13 +1684,13 @@
         <v>565</v>
       </c>
       <c r="H20" t="n">
-        <v>664200000</v>
+        <v>661150000</v>
       </c>
       <c r="I20" t="n">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="J20" t="n">
-        <v>321144000</v>
+        <v>306242000</v>
       </c>
       <c r="K20" t="n">
         <v>76</v>
@@ -1681,13 +1699,13 @@
         <v>70210000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1701,25 +1719,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>37500000</v>
+        <v>60000000</v>
       </c>
       <c r="G21" t="n">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="H21" t="n">
-        <v>476264000</v>
+        <v>491191000</v>
       </c>
       <c r="I21" t="n">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="J21" t="n">
-        <v>210683000</v>
+        <v>175172000</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1734,7 +1752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1781,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1807,13 +1825,13 @@
         <v>212</v>
       </c>
       <c r="H23" t="n">
-        <v>254926000</v>
+        <v>253526000</v>
       </c>
       <c r="I23" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J23" t="n">
-        <v>106391000</v>
+        <v>98623000</v>
       </c>
       <c r="K23" t="n">
         <v>60</v>
@@ -1822,13 +1840,13 @@
         <v>50620000</v>
       </c>
       <c r="M23" t="n">
-        <v>19.86</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1901,13 +1919,13 @@
         <v>460</v>
       </c>
       <c r="H25" t="n">
-        <v>688284000</v>
+        <v>682359000</v>
       </c>
       <c r="I25" t="n">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="J25" t="n">
-        <v>282997000</v>
+        <v>241631000</v>
       </c>
       <c r="K25" t="n">
         <v>29</v>
@@ -1916,13 +1934,13 @@
         <v>48045000</v>
       </c>
       <c r="M25" t="n">
-        <v>6.98</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1948,7 +1966,7 @@
         <v>88</v>
       </c>
       <c r="H26" t="n">
-        <v>118731000</v>
+        <v>114731000</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
@@ -1963,13 +1981,13 @@
         <v>10100000</v>
       </c>
       <c r="M26" t="n">
-        <v>8.51</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2084,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98494000</v>
+        <v>138919000</v>
       </c>
     </row>
     <row r="3">
@@ -2086,7 +2104,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>160238</v>
+        <v>237336000</v>
       </c>
     </row>
     <row r="4">
@@ -2106,7 +2124,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>146489000</v>
+        <v>268100400</v>
       </c>
     </row>
     <row r="5">
@@ -2126,7 +2144,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34359000</v>
+        <v>100397500</v>
       </c>
     </row>
     <row r="6">
@@ -2146,7 +2164,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>375895000</v>
+        <v>479479500</v>
       </c>
     </row>
     <row r="7">
@@ -2166,7 +2184,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61350500</v>
+        <v>123286320</v>
       </c>
     </row>
   </sheetData>
@@ -2261,10 +2279,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>66000000</v>
+        <v>70500000</v>
       </c>
       <c r="J2" t="n">
-        <v>440940000</v>
+        <v>460285000</v>
       </c>
     </row>
     <row r="3">
@@ -2293,10 +2311,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>74500000</v>
+        <v>97000000</v>
       </c>
       <c r="J3" t="n">
-        <v>295042000</v>
+        <v>303957000</v>
       </c>
     </row>
     <row r="4">
@@ -2325,10 +2343,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>50000000</v>
+        <v>62000000</v>
       </c>
       <c r="J4" t="n">
-        <v>580321000</v>
+        <v>607641000</v>
       </c>
     </row>
     <row r="5">
@@ -2360,7 +2378,7 @@
         <v>60900000</v>
       </c>
       <c r="J5" t="n">
-        <v>447759001</v>
+        <v>448619001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>607641000</v>
+        <v>575721000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>460285000</v>
+        <v>444388000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>448619001</v>
+        <v>422219001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>303957000</v>
+        <v>275627000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>71100000</v>
+        <v>97200000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>38100000</v>
+        <v>66000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>22200000</v>
+        <v>43440000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16200000</v>
+        <v>14700000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97000000</v>
+        <v>176800000</v>
       </c>
       <c r="D2" t="n">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="E2" t="n">
-        <v>2115753000</v>
+        <v>2109577000</v>
       </c>
       <c r="F2" t="n">
-        <v>263297000</v>
+        <v>241867000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,64 +668,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70500000</v>
+        <v>126600000</v>
       </c>
       <c r="D3" t="n">
-        <v>2273</v>
+        <v>2281</v>
       </c>
       <c r="E3" t="n">
-        <v>3077323500</v>
+        <v>3034062500</v>
       </c>
       <c r="F3" t="n">
-        <v>416286000</v>
+        <v>397556000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62000000</v>
+        <v>75300000</v>
       </c>
       <c r="D4" t="n">
-        <v>2425</v>
+        <v>1933</v>
       </c>
       <c r="E4" t="n">
-        <v>2871404000</v>
+        <v>2271029000</v>
       </c>
       <c r="F4" t="n">
-        <v>537221000</v>
+        <v>391319000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60900000</v>
+        <v>68000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1948</v>
+        <v>2410</v>
       </c>
       <c r="E5" t="n">
-        <v>2343579000</v>
+        <v>2755441000</v>
       </c>
       <c r="F5" t="n">
-        <v>400199000</v>
+        <v>530051000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
-        <v>511022000</v>
+        <v>474437000</v>
       </c>
       <c r="I2" t="n">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="J2" t="n">
-        <v>249136000</v>
+        <v>29577000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -853,13 +853,13 @@
         <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>13800000</v>
+        <v>19800000</v>
       </c>
       <c r="G3" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H3" t="n">
-        <v>338425000</v>
+        <v>339847000</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>49337000</v>
+        <v>25917000</v>
       </c>
       <c r="K3" t="n">
         <v>199</v>
       </c>
       <c r="L3" t="n">
-        <v>188181000</v>
+        <v>186606000</v>
       </c>
       <c r="M3" t="n">
-        <v>55.6</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H4" t="n">
-        <v>379204000</v>
+        <v>368794000</v>
       </c>
       <c r="I4" t="n">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="J4" t="n">
-        <v>125464000</v>
+        <v>66986000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -947,13 +947,13 @@
         <v>151295000</v>
       </c>
       <c r="M4" t="n">
-        <v>39.9</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>21600000</v>
       </c>
       <c r="G5" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H5" t="n">
-        <v>740913000</v>
+        <v>708103000</v>
       </c>
       <c r="I5" t="n">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
-        <v>334488000</v>
+        <v>114036000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,28 +1026,28 @@
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>343348000</v>
+        <v>331663000</v>
       </c>
       <c r="I6" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="J6" t="n">
-        <v>134287000</v>
+        <v>67282000</v>
       </c>
       <c r="K6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>110420000</v>
+        <v>108050000</v>
       </c>
       <c r="M6" t="n">
-        <v>32.16</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,41 +1070,41 @@
         <v>23000000</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="H7" t="n">
-        <v>557052000</v>
+        <v>532597000</v>
       </c>
       <c r="I7" t="n">
-        <v>375</v>
+        <v>251</v>
       </c>
       <c r="J7" t="n">
-        <v>389728000</v>
+        <v>236315000</v>
       </c>
       <c r="K7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L7" t="n">
-        <v>59800000</v>
+        <v>56575000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.74</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>laith Lewaa Mohammad .</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1117,31 +1117,31 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>373</v>
       </c>
       <c r="H8" t="n">
-        <v>1440000</v>
+        <v>348394000</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>77136000</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>136720000</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1164,31 +1164,31 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>373</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>360704000</v>
+        <v>47980000</v>
       </c>
       <c r="I9" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>157171000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>140400000</v>
+        <v>47980000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1198,44 +1198,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Hussein . Flaih Abdul Hassan -</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>40500000</v>
       </c>
       <c r="G10" t="n">
+        <v>459</v>
+      </c>
+      <c r="H10" t="n">
+        <v>557165000</v>
+      </c>
+      <c r="I10" t="n">
         <v>56</v>
       </c>
-      <c r="H10" t="n">
-        <v>47980000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>85710000</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>47980000</v>
+        <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1245,44 +1245,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hussein . Flaih Abdul Hassan -</t>
+          <t>Sadikh . Najee Jawad -</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>26100000</v>
+        <v>34800000</v>
       </c>
       <c r="G11" t="n">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H11" t="n">
-        <v>568085000</v>
+        <v>719203000</v>
       </c>
       <c r="I11" t="n">
-        <v>165</v>
+        <v>33</v>
       </c>
       <c r="J11" t="n">
-        <v>226430000</v>
+        <v>66140000</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>2000000</v>
+        <v>25720000</v>
       </c>
       <c r="M11" t="n">
-        <v>0.35</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1292,44 +1292,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sadikh . Najee Jawad -</t>
+          <t>Shamil Kamil Hadhod .</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>34800000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>468</v>
+        <v>227</v>
       </c>
       <c r="H12" t="n">
-        <v>748448000</v>
+        <v>271379000</v>
       </c>
       <c r="I12" t="n">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>253235000</v>
+        <v>21425000</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>26120000</v>
+        <v>66329000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.49</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shamil Kamil Hadhod .</t>
+          <t>Shiab Ghanim Abd zaid</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1352,78 +1352,78 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>227</v>
+        <v>359</v>
       </c>
       <c r="H13" t="n">
-        <v>284189000</v>
+        <v>326908000</v>
       </c>
       <c r="I13" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>105504000</v>
+        <v>86443000</v>
       </c>
       <c r="K13" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>68729000</v>
+        <v>112570000</v>
       </c>
       <c r="M13" t="n">
-        <v>24.18</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shiab Ghanim Abd zaid</t>
+          <t>Hasanen Nadher Muhammed .</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>26700000</v>
       </c>
       <c r="G14" t="n">
-        <v>359</v>
+        <v>522</v>
       </c>
       <c r="H14" t="n">
-        <v>334173000</v>
+        <v>711067000</v>
       </c>
       <c r="I14" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="J14" t="n">
-        <v>119018000</v>
+        <v>128537000</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>114970000</v>
+        <v>42586000</v>
       </c>
       <c r="M14" t="n">
-        <v>34.4</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hasanen Nadher Muhammed .</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1443,34 +1443,34 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>6600000</v>
+        <v>14400000</v>
       </c>
       <c r="G15" t="n">
-        <v>516</v>
+        <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>711096000</v>
+        <v>497977000</v>
       </c>
       <c r="I15" t="n">
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="J15" t="n">
-        <v>236036000</v>
+        <v>74902000</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="L15" t="n">
-        <v>51236000</v>
+        <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>7.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>14400000</v>
+        <v>31200000</v>
       </c>
       <c r="G16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
-        <v>508127000</v>
+        <v>369620000</v>
       </c>
       <c r="I16" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>122832000</v>
+        <v>30415000</v>
       </c>
       <c r="K16" t="n">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="L16" t="n">
-        <v>117350000</v>
+        <v>128935000</v>
       </c>
       <c r="M16" t="n">
-        <v>23.09</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1537,34 +1537,34 @@
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>18000000</v>
+        <v>18900000</v>
       </c>
       <c r="G17" t="n">
-        <v>309</v>
+        <v>561</v>
       </c>
       <c r="H17" t="n">
-        <v>365848000</v>
+        <v>813787500</v>
       </c>
       <c r="I17" t="n">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="J17" t="n">
-        <v>68906000</v>
+        <v>326688000</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
-        <v>133265000</v>
+        <v>38675000</v>
       </c>
       <c r="M17" t="n">
-        <v>36.43</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,138 +1574,138 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>35400000</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>565</v>
       </c>
       <c r="H18" t="n">
-        <v>5400000</v>
+        <v>641611000</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>101266000</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="L18" t="n">
-        <v>5400000</v>
+        <v>70210000</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>9000000</v>
+        <v>78700000</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>450</v>
       </c>
       <c r="H19" t="n">
-        <v>825702500</v>
+        <v>490680000</v>
       </c>
       <c r="I19" t="n">
-        <v>285</v>
+        <v>71</v>
       </c>
       <c r="J19" t="n">
-        <v>442944000</v>
+        <v>65780000</v>
       </c>
       <c r="K19" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>38825000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>22500000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>565</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>661150000</v>
+        <v>12500000</v>
       </c>
       <c r="I20" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>306242000</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>70210000</v>
+        <v>12500000</v>
       </c>
       <c r="M20" t="n">
-        <v>10.62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,44 +1715,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>60000000</v>
+        <v>54600000</v>
       </c>
       <c r="G21" t="n">
-        <v>450</v>
+        <v>213</v>
       </c>
       <c r="H21" t="n">
-        <v>491191000</v>
+        <v>268501000</v>
       </c>
       <c r="I21" t="n">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="J21" t="n">
-        <v>175172000</v>
+        <v>57451000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>48920000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1775,31 +1775,31 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>411</v>
       </c>
       <c r="H22" t="n">
-        <v>12500000</v>
+        <v>459761000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>188176000</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="L22" t="n">
-        <v>12500000</v>
+        <v>79742000</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>25000000</v>
+        <v>43500000</v>
       </c>
       <c r="G23" t="n">
-        <v>212</v>
+        <v>467</v>
       </c>
       <c r="H23" t="n">
-        <v>253526000</v>
+        <v>690884000</v>
       </c>
       <c r="I23" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="J23" t="n">
-        <v>98623000</v>
+        <v>121086000</v>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>50620000</v>
+        <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>19.97</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1869,31 +1869,31 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>413</v>
+        <v>85</v>
       </c>
       <c r="H24" t="n">
-        <v>477131000</v>
+        <v>109006000</v>
       </c>
       <c r="I24" t="n">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>292079000</v>
+        <v>2000000</v>
       </c>
       <c r="K24" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>84322000</v>
+        <v>8750000</v>
       </c>
       <c r="M24" t="n">
-        <v>17.67</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,132 +1903,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>460</v>
+        <v>138</v>
       </c>
       <c r="H25" t="n">
-        <v>682359000</v>
+        <v>78245000</v>
       </c>
       <c r="I25" t="n">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="J25" t="n">
-        <v>241631000</v>
+        <v>28075000</v>
       </c>
       <c r="K25" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="L25" t="n">
-        <v>48045000</v>
+        <v>43910000</v>
       </c>
       <c r="M25" t="n">
-        <v>7.04</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>88</v>
-      </c>
-      <c r="H26" t="n">
-        <v>114731000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>38760000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>17</v>
-      </c>
-      <c r="L26" t="n">
-        <v>10100000</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>143</v>
-      </c>
-      <c r="H27" t="n">
-        <v>84315000</v>
-      </c>
-      <c r="I27" t="n">
-        <v>52</v>
-      </c>
-      <c r="J27" t="n">
-        <v>26305000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>89</v>
-      </c>
-      <c r="L27" t="n">
-        <v>57710000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>68.45</v>
+        <v>56.12</v>
       </c>
     </row>
   </sheetData>
@@ -2279,10 +2185,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>70500000</v>
+        <v>126600000</v>
       </c>
       <c r="J2" t="n">
-        <v>460285000</v>
+        <v>444388000</v>
       </c>
     </row>
     <row r="3">
@@ -2311,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>97000000</v>
+        <v>176800000</v>
       </c>
       <c r="J3" t="n">
-        <v>303957000</v>
+        <v>275627000</v>
       </c>
     </row>
     <row r="4">
@@ -2343,10 +2249,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>62000000</v>
+        <v>68000000</v>
       </c>
       <c r="J4" t="n">
-        <v>607641000</v>
+        <v>575721000</v>
       </c>
     </row>
     <row r="5">
@@ -2375,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>60900000</v>
+        <v>75300000</v>
       </c>
       <c r="J5" t="n">
-        <v>448619001</v>
+        <v>422219001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>575721000</v>
+        <v>555491000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>444388000</v>
+        <v>430603000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>422219001</v>
+        <v>401799001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>275627000</v>
+        <v>252907000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>97200000</v>
+        <v>137100000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>66000000</v>
+        <v>118800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>43440000</v>
+        <v>112540000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>14700000</v>
+        <v>82200000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>176800000</v>
+        <v>185800000</v>
       </c>
       <c r="D2" t="n">
-        <v>1769</v>
+        <v>1757</v>
       </c>
       <c r="E2" t="n">
-        <v>2109577000</v>
+        <v>2088032000</v>
       </c>
       <c r="F2" t="n">
-        <v>241867000</v>
+        <v>233867000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,19 +671,19 @@
         <v>126600000</v>
       </c>
       <c r="D3" t="n">
-        <v>2281</v>
+        <v>2275</v>
       </c>
       <c r="E3" t="n">
-        <v>3034062500</v>
+        <v>3018577500</v>
       </c>
       <c r="F3" t="n">
-        <v>397556000</v>
+        <v>394806000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75300000</v>
+        <v>83100000</v>
       </c>
       <c r="D4" t="n">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="E4" t="n">
-        <v>2271029000</v>
+        <v>2254134000</v>
       </c>
       <c r="F4" t="n">
-        <v>391319000</v>
+        <v>389069000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>68000000</v>
       </c>
       <c r="D5" t="n">
-        <v>2410</v>
+        <v>2391</v>
       </c>
       <c r="E5" t="n">
-        <v>2755441000</v>
+        <v>2731711000</v>
       </c>
       <c r="F5" t="n">
-        <v>530051000</v>
+        <v>527151000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H2" t="n">
-        <v>474437000</v>
+        <v>470937000</v>
       </c>
       <c r="I2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J2" t="n">
-        <v>29577000</v>
+        <v>18677000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -882,31 +882,31 @@
         <v>19800000</v>
       </c>
       <c r="G3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H3" t="n">
-        <v>339847000</v>
+        <v>336367000</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>25917000</v>
+        <v>16017000</v>
       </c>
       <c r="K3" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>186606000</v>
+        <v>184206000</v>
       </c>
       <c r="M3" t="n">
-        <v>54.91</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>364</v>
       </c>
       <c r="H4" t="n">
-        <v>368794000</v>
+        <v>365484000</v>
       </c>
       <c r="I4" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>66986000</v>
+        <v>55797000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>151295000</v>
+        <v>150795000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.02</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>21600000</v>
       </c>
       <c r="G5" t="n">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="H5" t="n">
-        <v>708103000</v>
+        <v>698353000</v>
       </c>
       <c r="I5" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J5" t="n">
-        <v>114036000</v>
+        <v>59624000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>331663000</v>
+        <v>327973000</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="J6" t="n">
-        <v>67282000</v>
+        <v>43300000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>108050000</v>
       </c>
       <c r="M6" t="n">
-        <v>32.58</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1117,31 +1117,31 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>348394000</v>
+        <v>342149000</v>
       </c>
       <c r="I8" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J8" t="n">
-        <v>77136000</v>
+        <v>52216000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
       </c>
       <c r="L8" t="n">
-        <v>136720000</v>
+        <v>134770000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.24</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>40500000</v>
+        <v>43500000</v>
       </c>
       <c r="G10" t="n">
         <v>459</v>
       </c>
       <c r="H10" t="n">
-        <v>557165000</v>
+        <v>551965000</v>
       </c>
       <c r="I10" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="J10" t="n">
-        <v>85710000</v>
+        <v>43520000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>34800000</v>
+        <v>39600000</v>
       </c>
       <c r="G11" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>719203000</v>
+        <v>720603000</v>
       </c>
       <c r="I11" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>66140000</v>
+        <v>49890000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>25720000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1305,31 +1305,31 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H12" t="n">
-        <v>271379000</v>
+        <v>269329000</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>21425000</v>
+        <v>8060000</v>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>66329000</v>
+        <v>66029000</v>
       </c>
       <c r="M12" t="n">
-        <v>24.44</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>359</v>
       </c>
       <c r="H13" t="n">
-        <v>326908000</v>
+        <v>322108000</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
-        <v>86443000</v>
+        <v>56848000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>112570000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.43</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,28 +1402,28 @@
         <v>522</v>
       </c>
       <c r="H14" t="n">
-        <v>711067000</v>
+        <v>706807000</v>
       </c>
       <c r="I14" t="n">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="J14" t="n">
-        <v>128537000</v>
+        <v>104142000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>42586000</v>
+        <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.99</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>497977000</v>
+        <v>496477000</v>
       </c>
       <c r="I15" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J15" t="n">
-        <v>74902000</v>
+        <v>62392000</v>
       </c>
       <c r="K15" t="n">
         <v>75</v>
@@ -1464,13 +1464,13 @@
         <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.53</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,31 +1493,31 @@
         <v>31200000</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H16" t="n">
-        <v>369620000</v>
+        <v>367570000</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>30415000</v>
+        <v>27955000</v>
       </c>
       <c r="K16" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L16" t="n">
-        <v>128935000</v>
+        <v>127185000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.88</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1540,31 +1540,31 @@
         <v>18900000</v>
       </c>
       <c r="G17" t="n">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H17" t="n">
-        <v>813787500</v>
+        <v>810637500</v>
       </c>
       <c r="I17" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="J17" t="n">
-        <v>326688000</v>
+        <v>312258000</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>38675000</v>
+        <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,28 +1590,28 @@
         <v>565</v>
       </c>
       <c r="H18" t="n">
-        <v>641611000</v>
+        <v>637086000</v>
       </c>
       <c r="I18" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J18" t="n">
-        <v>101266000</v>
+        <v>80720000</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
       </c>
       <c r="L18" t="n">
-        <v>70210000</v>
+        <v>70110000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>78700000</v>
       </c>
       <c r="G19" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H19" t="n">
-        <v>490680000</v>
+        <v>485930000</v>
       </c>
       <c r="I19" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J19" t="n">
-        <v>65780000</v>
+        <v>45981000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,16 +1728,16 @@
         <v>54600000</v>
       </c>
       <c r="G21" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H21" t="n">
-        <v>268501000</v>
+        <v>265726000</v>
       </c>
       <c r="I21" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>57451000</v>
+        <v>37483000</v>
       </c>
       <c r="K21" t="n">
         <v>58</v>
@@ -1746,13 +1746,13 @@
         <v>48920000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.22</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G22" t="n">
         <v>411</v>
       </c>
       <c r="H22" t="n">
-        <v>459761000</v>
+        <v>455101000</v>
       </c>
       <c r="I22" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="J22" t="n">
-        <v>188176000</v>
+        <v>114080000</v>
       </c>
       <c r="K22" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>79742000</v>
+        <v>73392000</v>
       </c>
       <c r="M22" t="n">
-        <v>17.34</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,16 +1822,16 @@
         <v>43500000</v>
       </c>
       <c r="G23" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H23" t="n">
-        <v>690884000</v>
+        <v>686274000</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="J23" t="n">
-        <v>121086000</v>
+        <v>85195000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,13 +1840,13 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H25" t="n">
-        <v>78245000</v>
+        <v>73495000</v>
       </c>
       <c r="I25" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>28075000</v>
+        <v>16825000</v>
       </c>
       <c r="K25" t="n">
         <v>74</v>
       </c>
       <c r="L25" t="n">
-        <v>43910000</v>
+        <v>42260000</v>
       </c>
       <c r="M25" t="n">
-        <v>56.12</v>
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>
@@ -2188,7 +2188,7 @@
         <v>126600000</v>
       </c>
       <c r="J2" t="n">
-        <v>444388000</v>
+        <v>430603000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>176800000</v>
+        <v>185800000</v>
       </c>
       <c r="J3" t="n">
-        <v>275627000</v>
+        <v>252907000</v>
       </c>
     </row>
     <row r="4">
@@ -2252,7 +2252,7 @@
         <v>68000000</v>
       </c>
       <c r="J4" t="n">
-        <v>575721000</v>
+        <v>555491000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>75300000</v>
+        <v>83100000</v>
       </c>
       <c r="J5" t="n">
-        <v>422219001</v>
+        <v>401799001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -647,13 +647,13 @@
         <v>185800000</v>
       </c>
       <c r="D2" t="n">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="E2" t="n">
-        <v>2088032000</v>
+        <v>2084307000</v>
       </c>
       <c r="F2" t="n">
-        <v>233867000</v>
+        <v>233667000</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         <v>2275</v>
       </c>
       <c r="E3" t="n">
-        <v>3018577500</v>
+        <v>3013352500</v>
       </c>
       <c r="F3" t="n">
         <v>394806000</v>
@@ -698,7 +698,7 @@
         <v>1928</v>
       </c>
       <c r="E4" t="n">
-        <v>2254134000</v>
+        <v>2251259000</v>
       </c>
       <c r="F4" t="n">
         <v>389069000</v>
@@ -722,7 +722,7 @@
         <v>2391</v>
       </c>
       <c r="E5" t="n">
-        <v>2731711000</v>
+        <v>2730351000</v>
       </c>
       <c r="F5" t="n">
         <v>527151000</v>
@@ -838,13 +838,13 @@
         <v>379</v>
       </c>
       <c r="H2" t="n">
-        <v>470937000</v>
+        <v>470437000</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>18677000</v>
+        <v>16677000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -1026,13 +1026,13 @@
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>327973000</v>
+        <v>327113000</v>
       </c>
       <c r="I6" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J6" t="n">
-        <v>43300000</v>
+        <v>38860000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,7 +1041,7 @@
         <v>108050000</v>
       </c>
       <c r="M6" t="n">
-        <v>32.94</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="7">
@@ -1120,13 +1120,13 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>342149000</v>
+        <v>339874000</v>
       </c>
       <c r="I8" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="J8" t="n">
-        <v>52216000</v>
+        <v>41246000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,7 +1135,7 @@
         <v>134770000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.39</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="9">
@@ -1214,7 +1214,7 @@
         <v>459</v>
       </c>
       <c r="H10" t="n">
-        <v>551965000</v>
+        <v>551365000</v>
       </c>
       <c r="I10" t="n">
         <v>29</v>
@@ -1402,13 +1402,13 @@
         <v>522</v>
       </c>
       <c r="H14" t="n">
-        <v>706807000</v>
+        <v>705932000</v>
       </c>
       <c r="I14" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J14" t="n">
-        <v>104142000</v>
+        <v>99992000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,7 +1417,7 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="15">
@@ -1449,13 +1449,13 @@
         <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>496477000</v>
+        <v>496077000</v>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J15" t="n">
-        <v>62392000</v>
+        <v>58472000</v>
       </c>
       <c r="K15" t="n">
         <v>75</v>
@@ -1464,7 +1464,7 @@
         <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.6</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="16">
@@ -1496,13 +1496,13 @@
         <v>314</v>
       </c>
       <c r="H16" t="n">
-        <v>367570000</v>
+        <v>365520000</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>27955000</v>
+        <v>13765000</v>
       </c>
       <c r="K16" t="n">
         <v>116</v>
@@ -1511,7 +1511,7 @@
         <v>127185000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="17">
@@ -1543,13 +1543,13 @@
         <v>558</v>
       </c>
       <c r="H17" t="n">
-        <v>810637500</v>
+        <v>810237500</v>
       </c>
       <c r="I17" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J17" t="n">
-        <v>312258000</v>
+        <v>308338000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1590,13 +1590,13 @@
         <v>565</v>
       </c>
       <c r="H18" t="n">
-        <v>637086000</v>
+        <v>635586000</v>
       </c>
       <c r="I18" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J18" t="n">
-        <v>80720000</v>
+        <v>73220000</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1605,7 +1605,7 @@
         <v>70110000</v>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="19">
@@ -1637,13 +1637,13 @@
         <v>447</v>
       </c>
       <c r="H19" t="n">
-        <v>485930000</v>
+        <v>484655000</v>
       </c>
       <c r="I19" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J19" t="n">
-        <v>45981000</v>
+        <v>38767000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1731,13 +1731,13 @@
         <v>210</v>
       </c>
       <c r="H21" t="n">
-        <v>265726000</v>
+        <v>265276000</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>37483000</v>
+        <v>34708000</v>
       </c>
       <c r="K21" t="n">
         <v>58</v>
@@ -1746,7 +1746,7 @@
         <v>48920000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.41</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="22">
@@ -1778,7 +1778,7 @@
         <v>411</v>
       </c>
       <c r="H22" t="n">
-        <v>455101000</v>
+        <v>454901000</v>
       </c>
       <c r="I22" t="n">
         <v>128</v>
@@ -1790,10 +1790,10 @@
         <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>73392000</v>
+        <v>73192000</v>
       </c>
       <c r="M22" t="n">
-        <v>16.13</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="23">
@@ -1825,13 +1825,13 @@
         <v>464</v>
       </c>
       <c r="H23" t="n">
-        <v>686274000</v>
+        <v>684774000</v>
       </c>
       <c r="I23" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J23" t="n">
-        <v>85195000</v>
+        <v>80695000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,7 +1840,7 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="24">
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H25" t="n">
-        <v>73495000</v>
+        <v>73195000</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>16825000</v>
+        <v>16525000</v>
       </c>
       <c r="K25" t="n">
         <v>74</v>
@@ -1934,7 +1934,7 @@
         <v>42260000</v>
       </c>
       <c r="M25" t="n">
-        <v>57.5</v>
+        <v>57.74</v>
       </c>
     </row>
   </sheetData>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>237336000</v>
+        <v>363235000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>268100400</v>
+        <v>374562400</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>100397500</v>
+        <v>79897500</v>
       </c>
     </row>
     <row r="6">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>123286320</v>
+        <v>169014330</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,41 +441,241 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>555491000</v>
+        <v>179216000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>430603000</v>
+        <v>146015000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>401799001</v>
+        <v>140330000</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>252907000</v>
+        <v>124455000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Shiab Ghanim Abd zaid</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>107585000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tariq .Abdul Reda Mohammed</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>96240000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Thamir  . Musa Shimran -</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>91485000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maki  . Malik Tahir -</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>85300000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sanaa . Mahdi Ahmed -</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>73213000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ibtihal Hamza  Hussain -</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>72792000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Shamil Kamil Hadhod .</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>69229001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Zainab . Salim Essa -</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>68160000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hasanen Nadher Muhammed .</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51850000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hussain . Ali Atchan -</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>47980000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Azher Alaa Yass .</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>46670000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>45575000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nisreen . Nadum Waheed -</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38760000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sanaa . Jawad Hasan -</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24180000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sadikh . Najee Jawad -</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19120000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anwar . Jalil Abbas -</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12500000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7850000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hussein . Flaih Abdul Hassan -</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ali  . Abbas khalaf -</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2750000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Eman . Abdul Kareem -</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2500000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +717,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +726,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>137100000</v>
+        <v>105300000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +744,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>118800000</v>
+        <v>87900000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>112540000</v>
+        <v>72250000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>82200000</v>
+        <v>62440000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +835,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +844,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>185800000</v>
+        <v>233400000</v>
       </c>
       <c r="D2" t="n">
-        <v>1754</v>
+        <v>1766</v>
       </c>
       <c r="E2" t="n">
-        <v>2084307000</v>
+        <v>2098922000</v>
       </c>
       <c r="F2" t="n">
-        <v>233667000</v>
+        <v>228517000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,64 +868,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>126600000</v>
+        <v>193500000</v>
       </c>
       <c r="D3" t="n">
-        <v>2275</v>
+        <v>2281</v>
       </c>
       <c r="E3" t="n">
-        <v>3013352500</v>
+        <v>3046277500</v>
       </c>
       <c r="F3" t="n">
-        <v>394806000</v>
+        <v>393056000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83100000</v>
+        <v>157400000</v>
       </c>
       <c r="D4" t="n">
-        <v>1928</v>
+        <v>2414</v>
       </c>
       <c r="E4" t="n">
-        <v>2251259000</v>
+        <v>2791595000</v>
       </c>
       <c r="F4" t="n">
-        <v>389069000</v>
+        <v>526701000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68000000</v>
+        <v>131100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2391</v>
+        <v>1932</v>
       </c>
       <c r="E5" t="n">
-        <v>2730351000</v>
+        <v>2283004000</v>
       </c>
       <c r="F5" t="n">
-        <v>527151000</v>
+        <v>388869000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +1012,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -838,13 +1038,13 @@
         <v>379</v>
       </c>
       <c r="H2" t="n">
-        <v>470437000</v>
+        <v>468412000</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>16677000</v>
+        <v>6375000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +1059,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +1073,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26600000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>320</v>
+      </c>
+      <c r="H3" t="n">
+        <v>341401000</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
-        <v>19800000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>314</v>
-      </c>
-      <c r="H3" t="n">
-        <v>336367000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18</v>
-      </c>
       <c r="J3" t="n">
-        <v>16017000</v>
+        <v>5235000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,13 +1100,13 @@
         <v>184206000</v>
       </c>
       <c r="M3" t="n">
-        <v>54.76</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,13 +1132,13 @@
         <v>364</v>
       </c>
       <c r="H4" t="n">
-        <v>365484000</v>
+        <v>363584000</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J4" t="n">
-        <v>55797000</v>
+        <v>45122000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -947,13 +1147,13 @@
         <v>150795000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.26</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +1167,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>21600000</v>
+        <v>73800000</v>
       </c>
       <c r="G5" t="n">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="H5" t="n">
-        <v>698353000</v>
+        <v>738310000</v>
       </c>
       <c r="I5" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
-        <v>59624000</v>
+        <v>37599000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +1194,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1214,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>3600000</v>
+        <v>10600000</v>
       </c>
       <c r="G6" t="n">
         <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>327113000</v>
+        <v>331691000</v>
       </c>
       <c r="I6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>38860000</v>
+        <v>34060000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1241,13 @@
         <v>108050000</v>
       </c>
       <c r="M6" t="n">
-        <v>33.03</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1261,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>23000000</v>
+        <v>46400000</v>
       </c>
       <c r="G7" t="n">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>532597000</v>
+        <v>548197000</v>
       </c>
       <c r="I7" t="n">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="J7" t="n">
-        <v>236315000</v>
+        <v>217493000</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
       </c>
       <c r="L7" t="n">
-        <v>56575000</v>
+        <v>56125000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.62</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1320,13 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>339874000</v>
+        <v>339514000</v>
       </c>
       <c r="I8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
-        <v>41246000</v>
+        <v>39446000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,13 +1335,13 @@
         <v>134770000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.65</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1388,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1402,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>43500000</v>
+        <v>62100000</v>
       </c>
       <c r="G10" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H10" t="n">
-        <v>551365000</v>
+        <v>563705000</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>43520000</v>
+        <v>40820000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1229,13 +1429,13 @@
         <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1449,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>39600000</v>
+        <v>64500000</v>
       </c>
       <c r="G11" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="H11" t="n">
-        <v>720603000</v>
+        <v>738663000</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>49890000</v>
+        <v>21450000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>25720000</v>
+        <v>25520000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1496,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4500000</v>
       </c>
       <c r="G12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H12" t="n">
-        <v>269329000</v>
+        <v>273004000</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>8060000</v>
+        <v>5000000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
@@ -1323,13 +1523,13 @@
         <v>66029000</v>
       </c>
       <c r="M12" t="n">
-        <v>24.52</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1555,13 @@
         <v>359</v>
       </c>
       <c r="H13" t="n">
-        <v>322108000</v>
+        <v>320138000</v>
       </c>
       <c r="I13" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="J13" t="n">
-        <v>56848000</v>
+        <v>44562000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1570,13 @@
         <v>112570000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.95</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,25 +1590,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>26700000</v>
+        <v>55500000</v>
       </c>
       <c r="G14" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H14" t="n">
-        <v>705932000</v>
+        <v>725702000</v>
       </c>
       <c r="I14" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J14" t="n">
-        <v>99992000</v>
+        <v>71322000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,13 +1617,13 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.97</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1649,13 @@
         <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>496077000</v>
+        <v>494587000</v>
       </c>
       <c r="I15" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J15" t="n">
-        <v>58472000</v>
+        <v>49250000</v>
       </c>
       <c r="K15" t="n">
         <v>75</v>
@@ -1464,13 +1664,13 @@
         <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.62</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,19 +1684,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>31200000</v>
+        <v>36600000</v>
       </c>
       <c r="G16" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
-        <v>365520000</v>
+        <v>369820000</v>
       </c>
       <c r="I16" t="n">
         <v>18</v>
@@ -1508,16 +1708,16 @@
         <v>116</v>
       </c>
       <c r="L16" t="n">
-        <v>127185000</v>
+        <v>126535000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.8</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1731,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>18900000</v>
+        <v>47100000</v>
       </c>
       <c r="G17" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H17" t="n">
-        <v>810237500</v>
+        <v>823542500</v>
       </c>
       <c r="I17" t="n">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="J17" t="n">
-        <v>308338000</v>
+        <v>232961000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,13 +1758,13 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.72</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1778,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>35400000</v>
+        <v>39900000</v>
       </c>
       <c r="G18" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H18" t="n">
-        <v>635586000</v>
+        <v>632626000</v>
       </c>
       <c r="I18" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
-        <v>73220000</v>
+        <v>42295000</v>
       </c>
       <c r="K18" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L18" t="n">
-        <v>70110000</v>
+        <v>69010000</v>
       </c>
       <c r="M18" t="n">
-        <v>11.03</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,13 +1837,13 @@
         <v>447</v>
       </c>
       <c r="H19" t="n">
-        <v>484655000</v>
+        <v>478530000</v>
       </c>
       <c r="I19" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>38767000</v>
+        <v>8825000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1858,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1905,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1919,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>54600000</v>
+        <v>61100000</v>
       </c>
       <c r="G21" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
-        <v>265276000</v>
+        <v>262335000</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>34708000</v>
+        <v>12518000</v>
       </c>
       <c r="K21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L21" t="n">
-        <v>48920000</v>
+        <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.44</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,13 +1978,13 @@
         <v>411</v>
       </c>
       <c r="H22" t="n">
-        <v>454901000</v>
+        <v>450601000</v>
       </c>
       <c r="I22" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="J22" t="n">
-        <v>114080000</v>
+        <v>82465000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1793,13 +1993,13 @@
         <v>73192000</v>
       </c>
       <c r="M22" t="n">
-        <v>16.09</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +2013,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
-        <v>43500000</v>
+        <v>72600000</v>
       </c>
       <c r="G23" t="n">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="H23" t="n">
-        <v>684774000</v>
+        <v>704854000</v>
       </c>
       <c r="I23" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J23" t="n">
-        <v>80695000</v>
+        <v>49540000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,13 +2040,13 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>7.02</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +2060,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="G24" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H24" t="n">
-        <v>109006000</v>
+        <v>119507000</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,13 +2087,13 @@
         <v>8750000</v>
       </c>
       <c r="M24" t="n">
-        <v>8.029999999999999</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1916,25 +2116,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H25" t="n">
-        <v>73195000</v>
+        <v>70595000</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>16525000</v>
+        <v>15625000</v>
       </c>
       <c r="K25" t="n">
         <v>74</v>
       </c>
       <c r="L25" t="n">
-        <v>42260000</v>
+        <v>41760000</v>
       </c>
       <c r="M25" t="n">
-        <v>57.74</v>
+        <v>59.15</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2385,7 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>126600000</v>
+        <v>193500000</v>
       </c>
       <c r="J2" t="n">
         <v>430603000</v>
@@ -2217,7 +2417,7 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>185800000</v>
+        <v>233400000</v>
       </c>
       <c r="J3" t="n">
         <v>252907000</v>
@@ -2249,7 +2449,7 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>68000000</v>
+        <v>157400000</v>
       </c>
       <c r="J4" t="n">
         <v>555491000</v>
@@ -2281,7 +2481,7 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>83100000</v>
+        <v>131100000</v>
       </c>
       <c r="J5" t="n">
         <v>401799001</v>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,241 +441,41 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>179216000</v>
+        <v>537926000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>146015000</v>
+        <v>401978000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>140330000</v>
+        <v>391744001</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>124455000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Shiab Ghanim Abd zaid</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>107585000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>96240000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Thamir  . Musa Shimran -</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>91485000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Maki  . Malik Tahir -</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>85300000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>73213000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ibtihal Hamza  Hussain -</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>72792000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Shamil Kamil Hadhod .</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>69229001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Zainab . Salim Essa -</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>68160000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Hasanen Nadher Muhammed .</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>51850000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hussain . Ali Atchan -</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>47980000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Azher Alaa Yass .</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>46670000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Jawnaa . Radhi Shimran -</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>45575000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>38760000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sanaa . Jawad Hasan -</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>24180000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sadikh . Najee Jawad -</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>19120000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Anwar . Jalil Abbas -</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12500000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>7850000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hussein . Flaih Abdul Hassan -</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7500000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ali  . Abbas khalaf -</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2750000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Eman . Abdul Kareem -</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2500000</v>
+        <v>226897000</v>
       </c>
     </row>
   </sheetData>
@@ -2388,7 +2188,7 @@
         <v>193500000</v>
       </c>
       <c r="J2" t="n">
-        <v>430603000</v>
+        <v>401978000</v>
       </c>
     </row>
     <row r="3">
@@ -2420,7 +2220,7 @@
         <v>233400000</v>
       </c>
       <c r="J3" t="n">
-        <v>252907000</v>
+        <v>226897000</v>
       </c>
     </row>
     <row r="4">
@@ -2452,7 +2252,7 @@
         <v>157400000</v>
       </c>
       <c r="J4" t="n">
-        <v>555491000</v>
+        <v>537926000</v>
       </c>
     </row>
     <row r="5">
@@ -2484,7 +2284,7 @@
         <v>131100000</v>
       </c>
       <c r="J5" t="n">
-        <v>401799001</v>
+        <v>391744001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>537926000</v>
+        <v>528151000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>401978000</v>
+        <v>397803000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>391744001</v>
+        <v>390144001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>226897000</v>
+        <v>222997000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>105300000</v>
+        <v>93900000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>87900000</v>
+        <v>65000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>72250000</v>
+        <v>45200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>62440000</v>
+        <v>42550000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>233400000</v>
+        <v>293500000</v>
       </c>
       <c r="D2" t="n">
-        <v>1766</v>
+        <v>1788</v>
       </c>
       <c r="E2" t="n">
-        <v>2098922000</v>
+        <v>2145305000</v>
       </c>
       <c r="F2" t="n">
         <v>228517000</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>193500000</v>
+        <v>230940000</v>
       </c>
       <c r="D3" t="n">
-        <v>2281</v>
+        <v>2308</v>
       </c>
       <c r="E3" t="n">
-        <v>3046277500</v>
+        <v>3071498500</v>
       </c>
       <c r="F3" t="n">
         <v>393056000</v>
@@ -683,7 +683,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>157400000</v>
+        <v>219500000</v>
       </c>
       <c r="D4" t="n">
-        <v>2414</v>
+        <v>2426</v>
       </c>
       <c r="E4" t="n">
-        <v>2791595000</v>
+        <v>2830943000</v>
       </c>
       <c r="F4" t="n">
-        <v>526701000</v>
+        <v>520650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>131100000</v>
+        <v>159900000</v>
       </c>
       <c r="D5" t="n">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="E5" t="n">
-        <v>2283004000</v>
+        <v>2306859000</v>
       </c>
       <c r="F5" t="n">
-        <v>388869000</v>
+        <v>388394000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>23500000</v>
       </c>
       <c r="G2" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
-        <v>468412000</v>
+        <v>486107000</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>6375000</v>
+        <v>4575000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -853,13 +853,13 @@
         <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -882,16 +882,16 @@
         <v>26600000</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H3" t="n">
-        <v>341401000</v>
+        <v>340801000</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>5235000</v>
+        <v>4635000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,13 +900,13 @@
         <v>184206000</v>
       </c>
       <c r="M3" t="n">
-        <v>53.96</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H4" t="n">
-        <v>363584000</v>
+        <v>362684000</v>
       </c>
       <c r="I4" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
-        <v>45122000</v>
+        <v>43322000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -947,13 +947,13 @@
         <v>150795000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.47</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" t="n">
+        <v>90600000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>434</v>
+      </c>
+      <c r="H5" t="n">
+        <v>751032000</v>
+      </c>
+      <c r="I5" t="n">
         <v>22</v>
       </c>
-      <c r="F5" t="n">
-        <v>73800000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>428</v>
-      </c>
-      <c r="H5" t="n">
-        <v>738310000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30</v>
-      </c>
       <c r="J5" t="n">
-        <v>37599000</v>
+        <v>27239000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>10600000</v>
+        <v>21600000</v>
       </c>
       <c r="G6" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="H6" t="n">
-        <v>331691000</v>
+        <v>340517000</v>
       </c>
       <c r="I6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J6" t="n">
-        <v>34060000</v>
+        <v>28711000</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L6" t="n">
-        <v>108050000</v>
+        <v>105599000</v>
       </c>
       <c r="M6" t="n">
-        <v>32.58</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>46400000</v>
+        <v>57200000</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H7" t="n">
-        <v>548197000</v>
+        <v>549802000</v>
       </c>
       <c r="I7" t="n">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="J7" t="n">
-        <v>217493000</v>
+        <v>180038000</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L7" t="n">
-        <v>56125000</v>
+        <v>52525000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.24</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>339514000</v>
+        <v>339114000</v>
       </c>
       <c r="I8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J8" t="n">
-        <v>39446000</v>
+        <v>35926000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,13 +1135,13 @@
         <v>134770000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.69</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>62100000</v>
+        <v>72900000</v>
       </c>
       <c r="G10" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="H10" t="n">
-        <v>563705000</v>
+        <v>573060000</v>
       </c>
       <c r="I10" t="n">
         <v>21</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
-        <v>64500000</v>
+        <v>78000000</v>
       </c>
       <c r="G11" t="n">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>738663000</v>
+        <v>749913000</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>21450000</v>
+        <v>17700000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>25520000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>4500000</v>
+        <v>9000000</v>
       </c>
       <c r="G12" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H12" t="n">
-        <v>273004000</v>
+        <v>276654000</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -1320,16 +1320,16 @@
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>66029000</v>
+        <v>65554000</v>
       </c>
       <c r="M12" t="n">
-        <v>24.19</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,13 +1402,13 @@
         <v>525</v>
       </c>
       <c r="H14" t="n">
-        <v>725702000</v>
+        <v>723777000</v>
       </c>
       <c r="I14" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="J14" t="n">
-        <v>71322000</v>
+        <v>65621000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,13 +1417,13 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>494587000</v>
+        <v>493487000</v>
       </c>
       <c r="I15" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J15" t="n">
-        <v>49250000</v>
+        <v>43850000</v>
       </c>
       <c r="K15" t="n">
         <v>75</v>
@@ -1464,13 +1464,13 @@
         <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.69</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>36600000</v>
+        <v>48900000</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>369820000</v>
+        <v>381010000</v>
       </c>
       <c r="I16" t="n">
         <v>18</v>
@@ -1511,13 +1511,13 @@
         <v>126535000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.22</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>47100000</v>
+        <v>63240000</v>
       </c>
       <c r="G17" t="n">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="H17" t="n">
-        <v>823542500</v>
+        <v>833345500</v>
       </c>
       <c r="I17" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="J17" t="n">
-        <v>232961000</v>
+        <v>196437000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,13 +1558,13 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.64</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
-        <v>39900000</v>
+        <v>48900000</v>
       </c>
       <c r="G18" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="H18" t="n">
-        <v>632626000</v>
+        <v>639879000</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J18" t="n">
-        <v>42295000</v>
+        <v>41295000</v>
       </c>
       <c r="K18" t="n">
         <v>73</v>
@@ -1605,13 +1605,13 @@
         <v>69010000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>78700000</v>
+        <v>74700000</v>
       </c>
       <c r="G19" t="n">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H19" t="n">
-        <v>478530000</v>
+        <v>473012000</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>8825000</v>
+        <v>1800000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>61100000</v>
+        <v>84100000</v>
       </c>
       <c r="G21" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H21" t="n">
-        <v>262335000</v>
+        <v>283220000</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
@@ -1746,13 +1746,13 @@
         <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>16.88</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>9000000</v>
+        <v>14100000</v>
       </c>
       <c r="G22" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H22" t="n">
-        <v>450601000</v>
+        <v>455191000</v>
       </c>
       <c r="I22" t="n">
         <v>110</v>
@@ -1793,13 +1793,13 @@
         <v>73192000</v>
       </c>
       <c r="M22" t="n">
-        <v>16.24</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>72600000</v>
+        <v>83100000</v>
       </c>
       <c r="G23" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H23" t="n">
-        <v>704854000</v>
+        <v>709629000</v>
       </c>
       <c r="I23" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>49540000</v>
+        <v>16480000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,13 +1840,13 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.82</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>12000000</v>
+        <v>37500000</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H24" t="n">
-        <v>119507000</v>
+        <v>141158000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,13 +1887,13 @@
         <v>8750000</v>
       </c>
       <c r="M24" t="n">
-        <v>7.32</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>363235000</v>
+        <v>280337000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>374562400</v>
+        <v>377562400</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79897500</v>
+        <v>42897500</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>479479500</v>
+        <v>525479500</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>169014330</v>
+        <v>109831330</v>
       </c>
     </row>
   </sheetData>
@@ -2185,10 +2185,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>193500000</v>
+        <v>230940000</v>
       </c>
       <c r="J2" t="n">
-        <v>401978000</v>
+        <v>397803000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>233400000</v>
+        <v>293500000</v>
       </c>
       <c r="J3" t="n">
-        <v>226897000</v>
+        <v>222997000</v>
       </c>
     </row>
     <row r="4">
@@ -2249,10 +2249,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>157400000</v>
+        <v>219500000</v>
       </c>
       <c r="J4" t="n">
-        <v>537926000</v>
+        <v>528151000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>131100000</v>
+        <v>159900000</v>
       </c>
       <c r="J5" t="n">
-        <v>391744001</v>
+        <v>390144001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293500000</v>
+        <v>310600000</v>
       </c>
       <c r="D2" t="n">
-        <v>1788</v>
+        <v>1797</v>
       </c>
       <c r="E2" t="n">
-        <v>2145305000</v>
+        <v>2159722000</v>
       </c>
       <c r="F2" t="n">
         <v>228517000</v>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>230940000</v>
+        <v>256240000</v>
       </c>
       <c r="D3" t="n">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="E3" t="n">
-        <v>3071498500</v>
+        <v>3087685500</v>
       </c>
       <c r="F3" t="n">
         <v>393056000</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>219500000</v>
+        <v>227750000</v>
       </c>
       <c r="D4" t="n">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="E4" t="n">
-        <v>2830943000</v>
+        <v>2836675000</v>
       </c>
       <c r="F4" t="n">
         <v>520650000</v>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>159900000</v>
+        <v>164700000</v>
       </c>
       <c r="D5" t="n">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="E5" t="n">
-        <v>2306859000</v>
+        <v>2311179000</v>
       </c>
       <c r="F5" t="n">
         <v>388394000</v>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>23500000</v>
+        <v>26500000</v>
       </c>
       <c r="G2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H2" t="n">
-        <v>486107000</v>
+        <v>488909000</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>26600000</v>
+        <v>31850000</v>
       </c>
       <c r="G3" t="n">
         <v>317</v>
       </c>
       <c r="H3" t="n">
-        <v>340801000</v>
+        <v>345196000</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4635000</v>
+        <v>4215000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,7 +900,7 @@
         <v>184206000</v>
       </c>
       <c r="M3" t="n">
-        <v>54.05</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="4">
@@ -932,13 +932,13 @@
         <v>361</v>
       </c>
       <c r="H4" t="n">
-        <v>362684000</v>
+        <v>361694000</v>
       </c>
       <c r="I4" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
-        <v>43322000</v>
+        <v>38567000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -947,7 +947,7 @@
         <v>150795000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.58</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="5">
@@ -979,13 +979,13 @@
         <v>434</v>
       </c>
       <c r="H5" t="n">
-        <v>751032000</v>
+        <v>750557000</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>27239000</v>
+        <v>23914000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>72900000</v>
+        <v>77700000</v>
       </c>
       <c r="G10" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>573060000</v>
+        <v>577380000</v>
       </c>
       <c r="I10" t="n">
         <v>21</v>
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>55500000</v>
+        <v>60300000</v>
       </c>
       <c r="G14" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H14" t="n">
-        <v>723777000</v>
+        <v>728097000</v>
       </c>
       <c r="I14" t="n">
         <v>59</v>
@@ -1417,7 +1417,7 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.82</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="15">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
-        <v>48900000</v>
+        <v>57400000</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="H16" t="n">
-        <v>381010000</v>
+        <v>387527000</v>
       </c>
       <c r="I16" t="n">
         <v>18</v>
@@ -1511,7 +1511,7 @@
         <v>126535000</v>
       </c>
       <c r="M16" t="n">
-        <v>33.21</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="17">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>63240000</v>
+        <v>75240000</v>
       </c>
       <c r="G17" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H17" t="n">
-        <v>833345500</v>
+        <v>838695500</v>
       </c>
       <c r="I17" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="J17" t="n">
-        <v>196437000</v>
+        <v>174327000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,7 +1558,7 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="18">
@@ -1637,7 +1637,7 @@
         <v>442</v>
       </c>
       <c r="H19" t="n">
-        <v>473012000</v>
+        <v>472412000</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>84100000</v>
+        <v>90100000</v>
       </c>
       <c r="G21" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H21" t="n">
-        <v>283220000</v>
+        <v>288722000</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
@@ -1746,7 +1746,7 @@
         <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.63</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="22">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F23" t="n">
-        <v>83100000</v>
+        <v>89700000</v>
       </c>
       <c r="G23" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H23" t="n">
-        <v>709629000</v>
+        <v>715019000</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>16480000</v>
+        <v>14280000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,7 +1840,7 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.77</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="24">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>37500000</v>
+        <v>42000000</v>
       </c>
       <c r="G24" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H24" t="n">
-        <v>141158000</v>
+        <v>145283000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>8750000</v>
       </c>
       <c r="M24" t="n">
-        <v>6.2</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="25">
@@ -2185,7 +2185,7 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>230940000</v>
+        <v>256240000</v>
       </c>
       <c r="J2" t="n">
         <v>397803000</v>
@@ -2217,7 +2217,7 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>293500000</v>
+        <v>310600000</v>
       </c>
       <c r="J3" t="n">
         <v>222997000</v>
@@ -2249,7 +2249,7 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>219500000</v>
+        <v>227750000</v>
       </c>
       <c r="J4" t="n">
         <v>528151000</v>
@@ -2281,7 +2281,7 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>159900000</v>
+        <v>164700000</v>
       </c>
       <c r="J5" t="n">
         <v>390144001</v>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>528151000</v>
+        <v>521066000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>397803000</v>
+        <v>387399001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>390144001</v>
+        <v>384880000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>222997000</v>
+        <v>216497000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,61 +529,61 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>93900000</v>
+        <v>123600000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>65000000</v>
+        <v>84900000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>45200000</v>
+        <v>49900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>42550000</v>
+        <v>39850000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>310600000</v>
+        <v>316900000</v>
       </c>
       <c r="D2" t="n">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="E2" t="n">
-        <v>2159722000</v>
+        <v>2163667000</v>
       </c>
       <c r="F2" t="n">
         <v>228517000</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>256240000</v>
+        <v>282840000</v>
       </c>
       <c r="D3" t="n">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="E3" t="n">
-        <v>3087685500</v>
+        <v>3105500500</v>
       </c>
       <c r="F3" t="n">
-        <v>393056000</v>
+        <v>392456000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>227750000</v>
+        <v>245850000</v>
       </c>
       <c r="D4" t="n">
-        <v>2429</v>
+        <v>2438</v>
       </c>
       <c r="E4" t="n">
-        <v>2836675000</v>
+        <v>2848271000</v>
       </c>
       <c r="F4" t="n">
-        <v>520650000</v>
+        <v>519800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>164700000</v>
+        <v>186300000</v>
       </c>
       <c r="D5" t="n">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="E5" t="n">
-        <v>2311179000</v>
+        <v>2326909000</v>
       </c>
       <c r="F5" t="n">
         <v>388394000</v>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>26500000</v>
+        <v>32000000</v>
       </c>
       <c r="G2" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H2" t="n">
-        <v>488909000</v>
+        <v>493502000</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4575000</v>
+        <v>1800000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>31850000</v>
+        <v>34850000</v>
       </c>
       <c r="G3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H3" t="n">
-        <v>345196000</v>
+        <v>347947000</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -900,13 +900,13 @@
         <v>184206000</v>
       </c>
       <c r="M3" t="n">
-        <v>53.36</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>361</v>
       </c>
       <c r="H4" t="n">
-        <v>361694000</v>
+        <v>360094000</v>
       </c>
       <c r="I4" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J4" t="n">
-        <v>38567000</v>
+        <v>33767000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>150795000</v>
+        <v>150395000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.69</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,13 +979,13 @@
         <v>434</v>
       </c>
       <c r="H5" t="n">
-        <v>750557000</v>
+        <v>748757000</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>23914000</v>
+        <v>15514000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>26825000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>21600000</v>
+        <v>24800000</v>
       </c>
       <c r="G6" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="H6" t="n">
-        <v>340517000</v>
+        <v>343451000</v>
       </c>
       <c r="I6" t="n">
         <v>34</v>
@@ -1041,13 +1041,13 @@
         <v>105599000</v>
       </c>
       <c r="M6" t="n">
-        <v>31.01</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>57200000</v>
+        <v>63600000</v>
       </c>
       <c r="G7" t="n">
         <v>502</v>
       </c>
       <c r="H7" t="n">
-        <v>549802000</v>
+        <v>554520000</v>
       </c>
       <c r="I7" t="n">
         <v>194</v>
@@ -1085,16 +1085,16 @@
         <v>48</v>
       </c>
       <c r="L7" t="n">
-        <v>52525000</v>
+        <v>52075000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.550000000000001</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>339114000</v>
+        <v>338754000</v>
       </c>
       <c r="I8" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>35926000</v>
+        <v>33706000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,13 +1135,13 @@
         <v>134770000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.74</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>77700000</v>
+        <v>83700000</v>
       </c>
       <c r="G10" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H10" t="n">
-        <v>577380000</v>
+        <v>580340000</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>40820000</v>
+        <v>30020000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1229,13 +1229,13 @@
         <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>78000000</v>
+        <v>81000000</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H11" t="n">
-        <v>749913000</v>
+        <v>751913000</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>17700000</v>
+        <v>12800000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>25520000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>9000000</v>
+        <v>18000000</v>
       </c>
       <c r="G12" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H12" t="n">
-        <v>276654000</v>
+        <v>284904000</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -1323,13 +1323,13 @@
         <v>65554000</v>
       </c>
       <c r="M12" t="n">
-        <v>23.7</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G13" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H13" t="n">
-        <v>320138000</v>
+        <v>323018000</v>
       </c>
       <c r="I13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>44562000</v>
+        <v>41982000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>112570000</v>
       </c>
       <c r="M13" t="n">
-        <v>35.16</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>60300000</v>
+        <v>72900000</v>
       </c>
       <c r="G14" t="n">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="H14" t="n">
-        <v>728097000</v>
+        <v>738237000</v>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J14" t="n">
-        <v>65621000</v>
+        <v>59021000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,13 +1417,13 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.79</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>316</v>
       </c>
       <c r="H15" t="n">
-        <v>493487000</v>
+        <v>491687000</v>
       </c>
       <c r="I15" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>43850000</v>
+        <v>33650000</v>
       </c>
       <c r="K15" t="n">
         <v>75</v>
@@ -1464,13 +1464,13 @@
         <v>117150000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.74</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,10 +1493,10 @@
         <v>57400000</v>
       </c>
       <c r="G16" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H16" t="n">
-        <v>387527000</v>
+        <v>386127000</v>
       </c>
       <c r="I16" t="n">
         <v>18</v>
@@ -1508,16 +1508,16 @@
         <v>116</v>
       </c>
       <c r="L16" t="n">
-        <v>126535000</v>
+        <v>125935000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.65</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1543,13 +1543,13 @@
         <v>577</v>
       </c>
       <c r="H17" t="n">
-        <v>838695500</v>
+        <v>838245500</v>
       </c>
       <c r="I17" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J17" t="n">
-        <v>174327000</v>
+        <v>172527000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1564,7 +1564,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>48900000</v>
+        <v>62900000</v>
       </c>
       <c r="G18" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="H18" t="n">
-        <v>639879000</v>
+        <v>651204000</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J18" t="n">
-        <v>41295000</v>
+        <v>31065000</v>
       </c>
       <c r="K18" t="n">
         <v>73</v>
@@ -1605,13 +1605,13 @@
         <v>69010000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>74700000</v>
+        <v>76500000</v>
       </c>
       <c r="G19" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H19" t="n">
-        <v>472412000</v>
+        <v>473132000</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>90100000</v>
+        <v>78100000</v>
       </c>
       <c r="G21" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H21" t="n">
-        <v>288722000</v>
+        <v>277922000</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
@@ -1746,13 +1746,13 @@
         <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.33</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>14100000</v>
+        <v>18600000</v>
       </c>
       <c r="G22" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H22" t="n">
-        <v>455191000</v>
+        <v>459316000</v>
       </c>
       <c r="I22" t="n">
         <v>110</v>
@@ -1793,13 +1793,13 @@
         <v>73192000</v>
       </c>
       <c r="M22" t="n">
-        <v>16.08</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,7 +1825,7 @@
         <v>481</v>
       </c>
       <c r="H23" t="n">
-        <v>715019000</v>
+        <v>714119000</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
@@ -1840,13 +1840,13 @@
         <v>48045000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.72</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>42000000</v>
+        <v>54000000</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H24" t="n">
-        <v>145283000</v>
+        <v>156083000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,13 +1887,13 @@
         <v>8750000</v>
       </c>
       <c r="M24" t="n">
-        <v>6.02</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2185,10 +2185,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>256240000</v>
+        <v>282840000</v>
       </c>
       <c r="J2" t="n">
-        <v>397803000</v>
+        <v>384880000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>310600000</v>
+        <v>316900000</v>
       </c>
       <c r="J3" t="n">
-        <v>222997000</v>
+        <v>216497000</v>
       </c>
     </row>
     <row r="4">
@@ -2249,10 +2249,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>227750000</v>
+        <v>245850000</v>
       </c>
       <c r="J4" t="n">
-        <v>528151000</v>
+        <v>521066000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>164700000</v>
+        <v>186300000</v>
       </c>
       <c r="J5" t="n">
-        <v>390144001</v>
+        <v>387399001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>521066000</v>
+        <v>511656000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>387399001</v>
+        <v>377079001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>384880000</v>
+        <v>367295000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>216497000</v>
+        <v>213522000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>123600000</v>
+        <v>78300000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>84900000</v>
+        <v>40500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>49900000</v>
+        <v>37300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>39850000</v>
+        <v>33200000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,70 +644,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>316900000</v>
+        <v>358650000</v>
       </c>
       <c r="D2" t="n">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="E2" t="n">
-        <v>2163667000</v>
+        <v>2191945000</v>
       </c>
       <c r="F2" t="n">
-        <v>228517000</v>
+        <v>221417000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>282840000</v>
+        <v>331250000</v>
       </c>
       <c r="D3" t="n">
-        <v>2329</v>
+        <v>2464</v>
       </c>
       <c r="E3" t="n">
-        <v>3105500500</v>
+        <v>2910075000</v>
       </c>
       <c r="F3" t="n">
-        <v>392456000</v>
+        <v>512480000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>245850000</v>
+        <v>310740000</v>
       </c>
       <c r="D4" t="n">
-        <v>2438</v>
+        <v>2336</v>
       </c>
       <c r="E4" t="n">
-        <v>2848271000</v>
+        <v>3103277500</v>
       </c>
       <c r="F4" t="n">
-        <v>519800000</v>
+        <v>386176000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>186300000</v>
+        <v>239700000</v>
       </c>
       <c r="D5" t="n">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="E5" t="n">
-        <v>2326909000</v>
+        <v>2356895000</v>
       </c>
       <c r="F5" t="n">
-        <v>388394000</v>
+        <v>383844000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>32000000</v>
+        <v>49500000</v>
       </c>
       <c r="G2" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H2" t="n">
-        <v>493502000</v>
+        <v>506246000</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>34850000</v>
+        <v>50050000</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H3" t="n">
-        <v>347947000</v>
+        <v>358722000</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4215000</v>
+        <v>3675000</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>184206000</v>
+        <v>181586000</v>
       </c>
       <c r="M3" t="n">
-        <v>52.94</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>361</v>
       </c>
       <c r="H4" t="n">
-        <v>360094000</v>
+        <v>359044000</v>
       </c>
       <c r="I4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J4" t="n">
-        <v>33767000</v>
+        <v>30065000</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>150395000</v>
+        <v>149945000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.77</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>90600000</v>
+        <v>111900000</v>
       </c>
       <c r="G5" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H5" t="n">
-        <v>748757000</v>
+        <v>762454000</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>15514000</v>
+        <v>16814000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>26825000</v>
+        <v>23325000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>24800000</v>
+        <v>48400000</v>
       </c>
       <c r="G6" t="n">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="H6" t="n">
-        <v>343451000</v>
+        <v>363287000</v>
       </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J6" t="n">
-        <v>28711000</v>
+        <v>24061000</v>
       </c>
       <c r="K6" t="n">
         <v>129</v>
       </c>
       <c r="L6" t="n">
-        <v>105599000</v>
+        <v>104849000</v>
       </c>
       <c r="M6" t="n">
-        <v>30.75</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>63600000</v>
+        <v>71400000</v>
       </c>
       <c r="G7" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="H7" t="n">
-        <v>554520000</v>
+        <v>560322000</v>
       </c>
       <c r="I7" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J7" t="n">
-        <v>180038000</v>
+        <v>175988000</v>
       </c>
       <c r="K7" t="n">
         <v>48</v>
@@ -1088,13 +1088,13 @@
         <v>52075000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,19 +1120,19 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>338754000</v>
+        <v>336554000</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>33706000</v>
+        <v>29272000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
       </c>
       <c r="L8" t="n">
-        <v>134770000</v>
+        <v>133870000</v>
       </c>
       <c r="M8" t="n">
         <v>39.78</v>
@@ -1141,7 +1141,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>83700000</v>
+        <v>105300000</v>
       </c>
       <c r="G10" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H10" t="n">
-        <v>580340000</v>
+        <v>591740000</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>30020000</v>
+        <v>1600000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>81000000</v>
+        <v>98100000</v>
       </c>
       <c r="G11" t="n">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H11" t="n">
-        <v>751913000</v>
+        <v>764953000</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>12800000</v>
+        <v>16300000</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>25520000</v>
+        <v>21870000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.39</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>18000000</v>
+        <v>29100000</v>
       </c>
       <c r="G12" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H12" t="n">
-        <v>284904000</v>
+        <v>291480000</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>5000000</v>
+        <v>1400000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
@@ -1323,13 +1323,13 @@
         <v>65554000</v>
       </c>
       <c r="M12" t="n">
-        <v>23.01</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>3600000</v>
+        <v>7200000</v>
       </c>
       <c r="G13" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>323018000</v>
+        <v>324188000</v>
       </c>
       <c r="I13" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J13" t="n">
-        <v>41982000</v>
+        <v>29382000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>112570000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.85</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
-        <v>72900000</v>
+        <v>78900000</v>
       </c>
       <c r="G14" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H14" t="n">
-        <v>738237000</v>
+        <v>739689000</v>
       </c>
       <c r="I14" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J14" t="n">
-        <v>59021000</v>
+        <v>52271000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,13 +1417,13 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,31 +1446,31 @@
         <v>14400000</v>
       </c>
       <c r="G15" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H15" t="n">
-        <v>491687000</v>
+        <v>486937000</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>33650000</v>
+        <v>27390000</v>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L15" t="n">
-        <v>117150000</v>
+        <v>110870000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.83</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,13 +1496,13 @@
         <v>330</v>
       </c>
       <c r="H16" t="n">
-        <v>386127000</v>
+        <v>384642000</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>13765000</v>
+        <v>9045000</v>
       </c>
       <c r="K16" t="n">
         <v>116</v>
@@ -1511,13 +1511,13 @@
         <v>125935000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.61</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>75240000</v>
+        <v>83340000</v>
       </c>
       <c r="G17" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>838245500</v>
+        <v>832735500</v>
       </c>
       <c r="I17" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="J17" t="n">
-        <v>172527000</v>
+        <v>114137000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,13 +1558,13 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>62900000</v>
+        <v>76700000</v>
       </c>
       <c r="G18" t="n">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H18" t="n">
-        <v>651204000</v>
+        <v>659274000</v>
       </c>
       <c r="I18" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>31065000</v>
+        <v>23565000</v>
       </c>
       <c r="K18" t="n">
         <v>73</v>
@@ -1605,13 +1605,13 @@
         <v>69010000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.6</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>444</v>
       </c>
       <c r="H19" t="n">
-        <v>473132000</v>
+        <v>472682000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
-        <v>78100000</v>
+        <v>87850000</v>
       </c>
       <c r="G21" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H21" t="n">
-        <v>277922000</v>
+        <v>286860000</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
@@ -1746,13 +1746,13 @@
         <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.93</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>18600000</v>
+        <v>50600000</v>
       </c>
       <c r="G22" t="n">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H22" t="n">
-        <v>459316000</v>
+        <v>483906000</v>
       </c>
       <c r="I22" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J22" t="n">
-        <v>82465000</v>
+        <v>79090000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>73192000</v>
+        <v>72692000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.93</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,28 +1825,28 @@
         <v>481</v>
       </c>
       <c r="H23" t="n">
-        <v>714119000</v>
+        <v>711819000</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>14280000</v>
+        <v>11400000</v>
       </c>
       <c r="K23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L23" t="n">
-        <v>48045000</v>
+        <v>43545000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.73</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1919,22 +1919,22 @@
         <v>129</v>
       </c>
       <c r="H25" t="n">
-        <v>70595000</v>
+        <v>68095000</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>15625000</v>
+        <v>12650000</v>
       </c>
       <c r="K25" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>41760000</v>
+        <v>39660000</v>
       </c>
       <c r="M25" t="n">
-        <v>59.15</v>
+        <v>58.24</v>
       </c>
     </row>
   </sheetData>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>280337000</v>
+        <v>202337000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>377562400</v>
+        <v>284562400</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42897500</v>
+        <v>50897500</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>525479500</v>
+        <v>468449500</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>109831330</v>
+        <v>81965330</v>
       </c>
     </row>
   </sheetData>
@@ -2185,10 +2185,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>282840000</v>
+        <v>310740000</v>
       </c>
       <c r="J2" t="n">
-        <v>384880000</v>
+        <v>367295000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>316900000</v>
+        <v>358650000</v>
       </c>
       <c r="J3" t="n">
-        <v>216497000</v>
+        <v>213522000</v>
       </c>
     </row>
     <row r="4">
@@ -2249,10 +2249,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>245850000</v>
+        <v>331250000</v>
       </c>
       <c r="J4" t="n">
-        <v>521066000</v>
+        <v>511656000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>186300000</v>
+        <v>239700000</v>
       </c>
       <c r="J5" t="n">
-        <v>387399001</v>
+        <v>377079001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>78300000</v>
+        <v>106500000</v>
       </c>
     </row>
     <row r="3">
@@ -540,14 +540,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>40500000</v>
+        <v>55800000</v>
       </c>
     </row>
     <row r="4">
@@ -558,14 +558,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>37300000</v>
+        <v>47300000</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>33200000</v>
+        <v>32600000</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -647,13 +647,13 @@
         <v>358650000</v>
       </c>
       <c r="D2" t="n">
-        <v>1812</v>
+        <v>1807</v>
       </c>
       <c r="E2" t="n">
-        <v>2191945000</v>
+        <v>2183095000</v>
       </c>
       <c r="F2" t="n">
-        <v>221417000</v>
+        <v>221167000</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>331250000</v>
+        <v>354650000</v>
       </c>
       <c r="D3" t="n">
         <v>2464</v>
       </c>
       <c r="E3" t="n">
-        <v>2910075000</v>
+        <v>2914800000</v>
       </c>
       <c r="F3" t="n">
-        <v>512480000</v>
+        <v>511280000</v>
       </c>
     </row>
     <row r="4">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>310740000</v>
+        <v>321340000</v>
       </c>
       <c r="D4" t="n">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="E4" t="n">
-        <v>3103277500</v>
+        <v>3095544500</v>
       </c>
       <c r="F4" t="n">
-        <v>386176000</v>
+        <v>385976000</v>
       </c>
     </row>
     <row r="5">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>239700000</v>
+        <v>261300000</v>
       </c>
       <c r="D5" t="n">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="E5" t="n">
-        <v>2356895000</v>
+        <v>2373185000</v>
       </c>
       <c r="F5" t="n">
-        <v>383844000</v>
+        <v>383444000</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>49500000</v>
+        <v>55800000</v>
       </c>
       <c r="G2" t="n">
         <v>391</v>
       </c>
       <c r="H2" t="n">
-        <v>506246000</v>
+        <v>510866000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>50050000</v>
+        <v>59950000</v>
       </c>
       <c r="G3" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H3" t="n">
-        <v>358722000</v>
+        <v>367392000</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -897,10 +897,10 @@
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>181586000</v>
+        <v>181286000</v>
       </c>
       <c r="M3" t="n">
-        <v>50.62</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="4">
@@ -929,25 +929,25 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H4" t="n">
-        <v>359044000</v>
+        <v>357694000</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J4" t="n">
-        <v>30065000</v>
+        <v>27815000</v>
       </c>
       <c r="K4" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
-        <v>149945000</v>
+        <v>149045000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.76</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="5">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>111900000</v>
+        <v>119100000</v>
       </c>
       <c r="G5" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H5" t="n">
-        <v>762454000</v>
+        <v>767209000</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>16814000</v>
+        <v>15239000</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
@@ -994,7 +994,7 @@
         <v>23325000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="6">
@@ -1070,16 +1070,16 @@
         <v>71400000</v>
       </c>
       <c r="G7" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="H7" t="n">
-        <v>560322000</v>
+        <v>548352000</v>
       </c>
       <c r="I7" t="n">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="J7" t="n">
-        <v>175988000</v>
+        <v>116589000</v>
       </c>
       <c r="K7" t="n">
         <v>48</v>
@@ -1088,7 +1088,7 @@
         <v>52075000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
@@ -1120,13 +1120,13 @@
         <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>336554000</v>
+        <v>335804000</v>
       </c>
       <c r="I8" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>29272000</v>
+        <v>27172000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,7 +1135,7 @@
         <v>133870000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.78</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>98100000</v>
+        <v>119700000</v>
       </c>
       <c r="G11" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="H11" t="n">
-        <v>764953000</v>
+        <v>782393000</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>16300000</v>
+        <v>6500000</v>
       </c>
       <c r="K11" t="n">
         <v>14</v>
@@ -1276,7 +1276,7 @@
         <v>21870000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -1355,7 +1355,7 @@
         <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>324188000</v>
+        <v>323788000</v>
       </c>
       <c r="I13" t="n">
         <v>33</v>
@@ -1367,10 +1367,10 @@
         <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>112570000</v>
+        <v>112170000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.72</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="14">
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>78900000</v>
+        <v>86500000</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H14" t="n">
-        <v>739689000</v>
+        <v>744480000</v>
       </c>
       <c r="I14" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>52271000</v>
+        <v>37181000</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1417,7 +1417,7 @@
         <v>42136000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="15">
@@ -1446,16 +1446,16 @@
         <v>14400000</v>
       </c>
       <c r="G15" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H15" t="n">
-        <v>486937000</v>
+        <v>485437000</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>27390000</v>
+        <v>22590000</v>
       </c>
       <c r="K15" t="n">
         <v>69</v>
@@ -1464,7 +1464,7 @@
         <v>110870000</v>
       </c>
       <c r="M15" t="n">
-        <v>22.77</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="16">
@@ -1493,10 +1493,10 @@
         <v>57400000</v>
       </c>
       <c r="G16" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
-        <v>384642000</v>
+        <v>382242000</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
@@ -1511,7 +1511,7 @@
         <v>125935000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.74</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="17">
@@ -1543,13 +1543,13 @@
         <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>832735500</v>
+        <v>821760500</v>
       </c>
       <c r="I17" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J17" t="n">
-        <v>114137000</v>
+        <v>39627000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,7 +1558,7 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="18">
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>76700000</v>
+        <v>79700000</v>
       </c>
       <c r="G18" t="n">
         <v>575</v>
       </c>
       <c r="H18" t="n">
-        <v>659274000</v>
+        <v>661625000</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>23565000</v>
+        <v>21405000</v>
       </c>
       <c r="K18" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>69010000</v>
+        <v>68810000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.47</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="19">
@@ -1634,10 +1634,10 @@
         <v>76500000</v>
       </c>
       <c r="G19" t="n">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H19" t="n">
-        <v>472682000</v>
+        <v>470732000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1731,7 +1731,7 @@
         <v>217</v>
       </c>
       <c r="H21" t="n">
-        <v>286860000</v>
+        <v>284460000</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
@@ -1746,7 +1746,7 @@
         <v>44270000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.43</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="22">
@@ -1778,13 +1778,13 @@
         <v>424</v>
       </c>
       <c r="H22" t="n">
-        <v>483906000</v>
+        <v>481256000</v>
       </c>
       <c r="I22" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J22" t="n">
-        <v>79090000</v>
+        <v>71465000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1793,7 +1793,7 @@
         <v>72692000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.02</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="23">
@@ -1825,7 +1825,7 @@
         <v>481</v>
       </c>
       <c r="H23" t="n">
-        <v>711819000</v>
+        <v>710669000</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
@@ -1840,7 +1840,7 @@
         <v>43545000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.12</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="24">
@@ -1872,7 +1872,7 @@
         <v>112</v>
       </c>
       <c r="H24" t="n">
-        <v>156083000</v>
+        <v>155833000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1884,10 +1884,10 @@
         <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>8750000</v>
+        <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.61</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="25">
@@ -1919,13 +1919,13 @@
         <v>129</v>
       </c>
       <c r="H25" t="n">
-        <v>68095000</v>
+        <v>67645000</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>12650000</v>
+        <v>11300000</v>
       </c>
       <c r="K25" t="n">
         <v>68</v>
@@ -1934,7 +1934,7 @@
         <v>39660000</v>
       </c>
       <c r="M25" t="n">
-        <v>58.24</v>
+        <v>58.63</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2185,7 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>310740000</v>
+        <v>321340000</v>
       </c>
       <c r="J2" t="n">
         <v>367295000</v>
@@ -2249,7 +2249,7 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>331250000</v>
+        <v>354650000</v>
       </c>
       <c r="J4" t="n">
         <v>511656000</v>
@@ -2281,7 +2281,7 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>239700000</v>
+        <v>261300000</v>
       </c>
       <c r="J5" t="n">
         <v>377079001</v>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>511656000</v>
+        <v>492141000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>377079001</v>
+        <v>373259001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>367295000</v>
+        <v>348646000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>213522000</v>
+        <v>208907000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,49 +529,49 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>106500000</v>
+        <v>88200000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>55800000</v>
+        <v>43100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>47300000</v>
+        <v>42300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>32600000</v>
+        <v>31600000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>358650000</v>
+        <v>381150000</v>
       </c>
       <c r="D2" t="n">
-        <v>1807</v>
+        <v>1819</v>
       </c>
       <c r="E2" t="n">
-        <v>2183095000</v>
+        <v>2198330000</v>
       </c>
       <c r="F2" t="n">
-        <v>221167000</v>
+        <v>216767000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>354650000</v>
+        <v>374450000</v>
       </c>
       <c r="D3" t="n">
-        <v>2464</v>
+        <v>2472</v>
       </c>
       <c r="E3" t="n">
-        <v>2914800000</v>
+        <v>2926731000</v>
       </c>
       <c r="F3" t="n">
-        <v>511280000</v>
+        <v>508305000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>321340000</v>
+        <v>346840000</v>
       </c>
       <c r="D4" t="n">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="E4" t="n">
-        <v>3095544500</v>
+        <v>3110744500</v>
       </c>
       <c r="F4" t="n">
-        <v>385976000</v>
+        <v>383576000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>261300000</v>
+        <v>271500000</v>
       </c>
       <c r="D5" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="E5" t="n">
-        <v>2373185000</v>
+        <v>2381095000</v>
       </c>
       <c r="F5" t="n">
         <v>383444000</v>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>55800000</v>
+        <v>61800000</v>
       </c>
       <c r="G2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H2" t="n">
-        <v>510866000</v>
+        <v>516266000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>59950000</v>
+        <v>66550000</v>
       </c>
       <c r="G3" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="H3" t="n">
-        <v>367392000</v>
+        <v>372368000</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3675000</v>
+        <v>750000</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L3" t="n">
-        <v>181286000</v>
+        <v>179911000</v>
       </c>
       <c r="M3" t="n">
-        <v>49.34</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H4" t="n">
-        <v>357694000</v>
+        <v>355434000</v>
       </c>
       <c r="I4" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J4" t="n">
-        <v>27815000</v>
+        <v>24035000</v>
       </c>
       <c r="K4" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L4" t="n">
-        <v>149045000</v>
+        <v>148045000</v>
       </c>
       <c r="M4" t="n">
-        <v>41.67</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,13 +979,13 @@
         <v>438</v>
       </c>
       <c r="H5" t="n">
-        <v>767209000</v>
+        <v>766684000</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>15239000</v>
+        <v>11144000</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
@@ -1000,7 +1000,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>48400000</v>
+        <v>55600000</v>
       </c>
       <c r="G6" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="H6" t="n">
-        <v>363287000</v>
+        <v>368887000</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J6" t="n">
-        <v>24061000</v>
+        <v>22061000</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>104849000</v>
+        <v>104249000</v>
       </c>
       <c r="M6" t="n">
-        <v>28.86</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1073,13 @@
         <v>502</v>
       </c>
       <c r="H7" t="n">
-        <v>548352000</v>
+        <v>547092000</v>
       </c>
       <c r="I7" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J7" t="n">
-        <v>116589000</v>
+        <v>108609000</v>
       </c>
       <c r="K7" t="n">
         <v>48</v>
@@ -1088,13 +1088,13 @@
         <v>52075000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>10200000</v>
       </c>
       <c r="G8" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H8" t="n">
-        <v>335804000</v>
+        <v>344164000</v>
       </c>
       <c r="I8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>27172000</v>
+        <v>22992000</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -1135,13 +1135,13 @@
         <v>133870000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.87</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>323788000</v>
+        <v>323338000</v>
       </c>
       <c r="I13" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J13" t="n">
-        <v>29382000</v>
+        <v>27057000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>112170000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.64</v>
+        <v>34.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,7 +1402,7 @@
         <v>544</v>
       </c>
       <c r="H14" t="n">
-        <v>744480000</v>
+        <v>744180000</v>
       </c>
       <c r="I14" t="n">
         <v>40</v>
@@ -1423,7 +1423,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,28 +1449,28 @@
         <v>310</v>
       </c>
       <c r="H15" t="n">
-        <v>485437000</v>
+        <v>483087000</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>22590000</v>
+        <v>21540000</v>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L15" t="n">
-        <v>110870000</v>
+        <v>108470000</v>
       </c>
       <c r="M15" t="n">
-        <v>22.84</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>57400000</v>
+        <v>63700000</v>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H16" t="n">
-        <v>382242000</v>
+        <v>386487000</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>9045000</v>
+        <v>3540000</v>
       </c>
       <c r="K16" t="n">
         <v>116</v>
@@ -1511,13 +1511,13 @@
         <v>125935000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.95</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
-        <v>83340000</v>
+        <v>97740000</v>
       </c>
       <c r="G17" t="n">
         <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>821760500</v>
+        <v>831545500</v>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>39627000</v>
+        <v>27497000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,13 +1558,13 @@
         <v>38225000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" t="n">
-        <v>79700000</v>
+        <v>84500000</v>
       </c>
       <c r="G18" t="n">
         <v>575</v>
       </c>
       <c r="H18" t="n">
-        <v>661625000</v>
+        <v>665445000</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>21405000</v>
+        <v>20705000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
@@ -1605,13 +1605,13 @@
         <v>68810000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.4</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>439</v>
       </c>
       <c r="H19" t="n">
-        <v>470732000</v>
+        <v>470432000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,28 +1778,28 @@
         <v>424</v>
       </c>
       <c r="H22" t="n">
-        <v>481256000</v>
+        <v>477466000</v>
       </c>
       <c r="I22" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J22" t="n">
-        <v>71465000</v>
+        <v>64590000</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L22" t="n">
-        <v>72692000</v>
+        <v>68292000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,13 +1825,13 @@
         <v>481</v>
       </c>
       <c r="H23" t="n">
-        <v>710669000</v>
+        <v>709519000</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>11400000</v>
+        <v>10600000</v>
       </c>
       <c r="K23" t="n">
         <v>26</v>
@@ -1840,13 +1840,13 @@
         <v>43545000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.13</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>54000000</v>
+        <v>76500000</v>
       </c>
       <c r="G24" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H24" t="n">
-        <v>155833000</v>
+        <v>176308000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,13 +1887,13 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.45</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2185,10 +2185,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>321340000</v>
+        <v>346840000</v>
       </c>
       <c r="J2" t="n">
-        <v>367295000</v>
+        <v>348646000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2217,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>358650000</v>
+        <v>381150000</v>
       </c>
       <c r="J3" t="n">
-        <v>213522000</v>
+        <v>208907000</v>
       </c>
     </row>
     <row r="4">
@@ -2249,10 +2249,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>354650000</v>
+        <v>374450000</v>
       </c>
       <c r="J4" t="n">
-        <v>511656000</v>
+        <v>492141000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2281,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>261300000</v>
+        <v>271500000</v>
       </c>
       <c r="J5" t="n">
-        <v>377079001</v>
+        <v>373259001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>492141000</v>
+        <v>483916000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>373259001</v>
+        <v>366239001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>348646000</v>
+        <v>332406000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>208907000</v>
+        <v>204957000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>88200000</v>
+        <v>63000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>43100000</v>
+        <v>39400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>42300000</v>
+        <v>33600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>31600000</v>
+        <v>20800000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>381150000</v>
+        <v>408650000</v>
       </c>
       <c r="D2" t="n">
-        <v>1819</v>
+        <v>1918</v>
       </c>
       <c r="E2" t="n">
-        <v>2198330000</v>
+        <v>2277725160</v>
       </c>
       <c r="F2" t="n">
-        <v>216767000</v>
+        <v>276649160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>374450000</v>
+        <v>395150000</v>
       </c>
       <c r="D3" t="n">
-        <v>2472</v>
+        <v>2541</v>
       </c>
       <c r="E3" t="n">
-        <v>2926731000</v>
+        <v>2982248560.6</v>
       </c>
       <c r="F3" t="n">
-        <v>508305000</v>
+        <v>554350560.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,19 +695,19 @@
         <v>346840000</v>
       </c>
       <c r="D4" t="n">
-        <v>2337</v>
+        <v>2406</v>
       </c>
       <c r="E4" t="n">
-        <v>3110744500</v>
+        <v>3154871020</v>
       </c>
       <c r="F4" t="n">
-        <v>383576000</v>
+        <v>508053840</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>271500000</v>
+        <v>313200000</v>
       </c>
       <c r="D5" t="n">
-        <v>1972</v>
+        <v>2111</v>
       </c>
       <c r="E5" t="n">
-        <v>2381095000</v>
+        <v>2473075440.32</v>
       </c>
       <c r="F5" t="n">
-        <v>383444000</v>
+        <v>377668120.32</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>61800000</v>
+        <v>76500000</v>
       </c>
       <c r="G2" t="n">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H2" t="n">
-        <v>516266000</v>
+        <v>530412160</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -847,19 +847,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>700000</v>
+        <v>5139160</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,44 +869,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Hussein . Kadhum Dhahi -</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>66550000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>372368000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>179911000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>48.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>66550000</v>
       </c>
       <c r="G4" t="n">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="H4" t="n">
-        <v>355434000</v>
+        <v>378221520</v>
       </c>
       <c r="I4" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>24035000</v>
+        <v>750000</v>
       </c>
       <c r="K4" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>148045000</v>
+        <v>185764520</v>
       </c>
       <c r="M4" t="n">
-        <v>41.65</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,44 +963,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>119100000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="H5" t="n">
-        <v>766684000</v>
+        <v>384369480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>11144000</v>
+        <v>15009000</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>23325000</v>
+        <v>181205480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.04</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>55600000</v>
+        <v>119100000</v>
       </c>
       <c r="G6" t="n">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="H6" t="n">
-        <v>368887000</v>
+        <v>767720600</v>
       </c>
       <c r="I6" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>22061000</v>
+        <v>3500000</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>104249000</v>
+        <v>25966600</v>
       </c>
       <c r="M6" t="n">
-        <v>28.26</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1057,91 +1057,91 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>71400000</v>
+        <v>55600000</v>
       </c>
       <c r="G7" t="n">
-        <v>502</v>
+        <v>457</v>
       </c>
       <c r="H7" t="n">
-        <v>547092000</v>
+        <v>367867000</v>
       </c>
       <c r="I7" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
-        <v>108609000</v>
+        <v>20210000</v>
       </c>
       <c r="K7" t="n">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="L7" t="n">
-        <v>52075000</v>
+        <v>101309000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.52</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>10200000</v>
+        <v>77400000</v>
       </c>
       <c r="G8" t="n">
-        <v>373</v>
+        <v>509</v>
       </c>
       <c r="H8" t="n">
-        <v>344164000</v>
+        <v>553657800</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="J8" t="n">
-        <v>22992000</v>
+        <v>102084000</v>
       </c>
       <c r="K8" t="n">
-        <v>166</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>133870000</v>
+        <v>54965800</v>
       </c>
       <c r="M8" t="n">
-        <v>38.9</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>14700000</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>47980000</v>
+        <v>342864000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>7940000</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="L9" t="n">
-        <v>47980000</v>
+        <v>131995000</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,31 +1211,31 @@
         <v>105300000</v>
       </c>
       <c r="G10" t="n">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H10" t="n">
-        <v>591740000</v>
+        <v>596600200</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>2000000</v>
+        <v>7260200</v>
       </c>
       <c r="M10" t="n">
-        <v>0.34</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,7 +1261,7 @@
         <v>482</v>
       </c>
       <c r="H11" t="n">
-        <v>782393000</v>
+        <v>782248000</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
@@ -1273,16 +1273,16 @@
         <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>21870000</v>
+        <v>21725000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>29100000</v>
+        <v>66300000</v>
       </c>
       <c r="G12" t="n">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="H12" t="n">
-        <v>291480000</v>
+        <v>342536120.32</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -1317,19 +1317,19 @@
         <v>1400000</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="L12" t="n">
-        <v>65554000</v>
+        <v>85490120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>22.49</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1352,10 +1352,10 @@
         <v>7200000</v>
       </c>
       <c r="G13" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>323338000</v>
+        <v>342365800</v>
       </c>
       <c r="I13" t="n">
         <v>30</v>
@@ -1364,19 +1364,19 @@
         <v>27057000</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>112170000</v>
+        <v>131197800</v>
       </c>
       <c r="M13" t="n">
-        <v>34.69</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>86500000</v>
       </c>
       <c r="G14" t="n">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="H14" t="n">
-        <v>744180000</v>
+        <v>765600200</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>37181000</v>
+        <v>24390000</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="L14" t="n">
-        <v>42136000</v>
+        <v>68021200</v>
       </c>
       <c r="M14" t="n">
-        <v>5.66</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>14400000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>310</v>
+        <v>92</v>
       </c>
       <c r="H15" t="n">
-        <v>483087000</v>
+        <v>66461320</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>21540000</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="L15" t="n">
-        <v>108470000</v>
+        <v>66461320</v>
       </c>
       <c r="M15" t="n">
-        <v>22.45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>63700000</v>
+        <v>14400000</v>
       </c>
       <c r="G16" t="n">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
-        <v>386487000</v>
+        <v>488386440</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>3540000</v>
+        <v>13380000</v>
       </c>
       <c r="K16" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="L16" t="n">
-        <v>125935000</v>
+        <v>111219440</v>
       </c>
       <c r="M16" t="n">
-        <v>32.58</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>97740000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>831545500</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>27497000</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>38225000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,70 +1574,70 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>84500000</v>
+        <v>63700000</v>
       </c>
       <c r="G18" t="n">
-        <v>575</v>
+        <v>366</v>
       </c>
       <c r="H18" t="n">
-        <v>665445000</v>
+        <v>412538880</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>20705000</v>
+        <v>2100000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="L18" t="n">
-        <v>68810000</v>
+        <v>152346880</v>
       </c>
       <c r="M18" t="n">
-        <v>10.34</v>
+        <v>36.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Nadhir . Mohammad Kadhom -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>76500000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>470432000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1658,101 +1658,101 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>97740000</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>578</v>
       </c>
       <c r="H20" t="n">
-        <v>12500000</v>
+        <v>824580500</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>7100000</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>12500000</v>
+        <v>38225000</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F21" t="n">
-        <v>87850000</v>
+        <v>84500000</v>
       </c>
       <c r="G21" t="n">
-        <v>217</v>
+        <v>572</v>
       </c>
       <c r="H21" t="n">
-        <v>284460000</v>
+        <v>663765000</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>12518000</v>
+        <v>4125000</v>
       </c>
       <c r="K21" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>44270000</v>
+        <v>71780000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.56</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1762,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Ahmed . Hassan Yusif -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>50600000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>477466000</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>64590000</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>68292000</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>89700000</v>
+        <v>76500000</v>
       </c>
       <c r="G23" t="n">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="H23" t="n">
-        <v>709519000</v>
+        <v>470828000</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10600000</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>43545000</v>
+        <v>396000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.14</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,23 +1856,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>76500000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>176308000</v>
+        <v>15470000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1881,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>8500000</v>
+        <v>15470000</v>
       </c>
       <c r="M24" t="n">
-        <v>4.82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,38 +1903,273 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Azher Alaa Yass .</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>36</v>
+      </c>
+      <c r="F25" t="n">
+        <v>87850000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>228</v>
+      </c>
+      <c r="H25" t="n">
+        <v>290617360</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10118000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>63</v>
+      </c>
+      <c r="L25" t="n">
+        <v>51527360</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Baydaa . Hameed Mizher -</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ibtihal Hamza  Hussain -</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F27" t="n">
+        <v>78100000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>466</v>
+      </c>
+      <c r="H27" t="n">
+        <v>533496200</v>
+      </c>
+      <c r="I27" t="n">
+        <v>88</v>
+      </c>
+      <c r="J27" t="n">
+        <v>64590000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>84</v>
+      </c>
+      <c r="L27" t="n">
+        <v>99259200</v>
+      </c>
+      <c r="M27" t="n">
+        <v>118.15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>89700000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>481</v>
+      </c>
+      <c r="H28" t="n">
+        <v>706557000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45033000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41</v>
+      </c>
+      <c r="F29" t="n">
+        <v>76500000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>133</v>
+      </c>
+      <c r="H29" t="n">
+        <v>181852000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>23</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14044000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>129</v>
-      </c>
-      <c r="H25" t="n">
-        <v>67645000</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>150</v>
+      </c>
+      <c r="H30" t="n">
+        <v>77848600</v>
+      </c>
+      <c r="I30" t="n">
         <v>21</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J30" t="n">
         <v>11300000</v>
       </c>
-      <c r="K25" t="n">
-        <v>68</v>
-      </c>
-      <c r="L25" t="n">
-        <v>39660000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>58.63</v>
+      <c r="K30" t="n">
+        <v>89</v>
+      </c>
+      <c r="L30" t="n">
+        <v>49863600</v>
+      </c>
+      <c r="M30" t="n">
+        <v>64.05</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +2225,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>138919000</v>
+        <v>88919000</v>
       </c>
     </row>
     <row r="3">
@@ -2010,7 +2245,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>202337000</v>
+        <v>71365000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2265,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>284562400</v>
+        <v>245362400</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2285,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50897500</v>
+        <v>69897500</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2305,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>468449500</v>
+        <v>418449500</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2325,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81965330</v>
+        <v>167704330</v>
       </c>
     </row>
   </sheetData>
@@ -2188,7 +2423,7 @@
         <v>346840000</v>
       </c>
       <c r="J2" t="n">
-        <v>348646000</v>
+        <v>332406000</v>
       </c>
     </row>
     <row r="3">
@@ -2217,10 +2452,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>381150000</v>
+        <v>408650000</v>
       </c>
       <c r="J3" t="n">
-        <v>208907000</v>
+        <v>204957000</v>
       </c>
     </row>
     <row r="4">
@@ -2249,10 +2484,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>374450000</v>
+        <v>395150000</v>
       </c>
       <c r="J4" t="n">
-        <v>492141000</v>
+        <v>483916000</v>
       </c>
     </row>
     <row r="5">
@@ -2281,10 +2516,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>271500000</v>
+        <v>313200000</v>
       </c>
       <c r="J5" t="n">
-        <v>373259001</v>
+        <v>366239001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>483916000</v>
+        <v>513081000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>366239001</v>
+        <v>413354001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>332406000</v>
+        <v>411979000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>204957000</v>
+        <v>243312000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>63000000</v>
+        <v>59400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>33600000</v>
+        <v>21600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -647,10 +647,10 @@
         <v>408650000</v>
       </c>
       <c r="D2" t="n">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="E2" t="n">
-        <v>2277725160</v>
+        <v>2259745160</v>
       </c>
       <c r="F2" t="n">
         <v>276649160</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,19 +671,19 @@
         <v>395150000</v>
       </c>
       <c r="D3" t="n">
-        <v>2541</v>
+        <v>2518</v>
       </c>
       <c r="E3" t="n">
-        <v>2982248560.6</v>
+        <v>2955263560.6</v>
       </c>
       <c r="F3" t="n">
-        <v>554350560.6</v>
+        <v>550750560.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>346840000</v>
+        <v>358840000</v>
       </c>
       <c r="D4" t="n">
-        <v>2406</v>
+        <v>2399</v>
       </c>
       <c r="E4" t="n">
-        <v>3154871020</v>
+        <v>3142451020</v>
       </c>
       <c r="F4" t="n">
-        <v>508053840</v>
+        <v>503928840</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>313200000</v>
+        <v>316800000</v>
       </c>
       <c r="D5" t="n">
-        <v>2111</v>
+        <v>2103</v>
       </c>
       <c r="E5" t="n">
-        <v>2473075440.32</v>
+        <v>2460025440.32</v>
       </c>
       <c r="F5" t="n">
-        <v>377668120.32</v>
+        <v>368208120.32</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>342</v>
       </c>
       <c r="H4" t="n">
-        <v>378221520</v>
+        <v>377021520</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>750000</v>
+        <v>1200000</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L4" t="n">
-        <v>185764520</v>
+        <v>184114520</v>
       </c>
       <c r="M4" t="n">
-        <v>49.12</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,31 +976,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H5" t="n">
-        <v>384369480.6</v>
+        <v>380714480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>15009000</v>
+        <v>6265000</v>
       </c>
       <c r="K5" t="n">
         <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>181205480.6</v>
+        <v>180305480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>47.14</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>446</v>
       </c>
       <c r="H6" t="n">
-        <v>767720600</v>
+        <v>766470600</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3500000</v>
+        <v>2500000</v>
       </c>
       <c r="K6" t="n">
         <v>23</v>
@@ -1041,13 +1041,13 @@
         <v>25966600</v>
       </c>
       <c r="M6" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1117,31 +1117,31 @@
         <v>77400000</v>
       </c>
       <c r="G8" t="n">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="H8" t="n">
-        <v>553657800</v>
+        <v>532777800</v>
       </c>
       <c r="I8" t="n">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>102084000</v>
+        <v>8490000</v>
       </c>
       <c r="K8" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L8" t="n">
-        <v>54965800</v>
+        <v>53915800</v>
       </c>
       <c r="M8" t="n">
-        <v>9.93</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1164,31 +1164,31 @@
         <v>14700000</v>
       </c>
       <c r="G9" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H9" t="n">
-        <v>342864000</v>
+        <v>340564000</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>7940000</v>
+        <v>5660000</v>
       </c>
       <c r="K9" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L9" t="n">
-        <v>131995000</v>
+        <v>130535000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.5</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,10 +1211,10 @@
         <v>105300000</v>
       </c>
       <c r="G10" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H10" t="n">
-        <v>596600200</v>
+        <v>594525200</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,10 +1258,10 @@
         <v>119700000</v>
       </c>
       <c r="G11" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H11" t="n">
-        <v>782248000</v>
+        <v>778483000</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
@@ -1276,13 +1276,13 @@
         <v>21725000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>66300000</v>
+        <v>69900000</v>
       </c>
       <c r="G12" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H12" t="n">
-        <v>342536120.32</v>
+        <v>345011120.32</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -1323,13 +1323,13 @@
         <v>85490120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>24.96</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,28 +1355,28 @@
         <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>342365800</v>
+        <v>334980800</v>
       </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
-        <v>27057000</v>
+        <v>4167000</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L13" t="n">
-        <v>131197800</v>
+        <v>123197800</v>
       </c>
       <c r="M13" t="n">
-        <v>38.32</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,7 +1402,7 @@
         <v>573</v>
       </c>
       <c r="H14" t="n">
-        <v>765600200</v>
+        <v>758400200</v>
       </c>
       <c r="I14" t="n">
         <v>18</v>
@@ -1417,13 +1417,13 @@
         <v>68021200</v>
       </c>
       <c r="M14" t="n">
-        <v>8.880000000000001</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,31 +1493,31 @@
         <v>14400000</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H16" t="n">
-        <v>488386440</v>
+        <v>485286440</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>13380000</v>
+        <v>14680000</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L16" t="n">
-        <v>111219440</v>
+        <v>107969440</v>
       </c>
       <c r="M16" t="n">
-        <v>22.77</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,7 +1590,7 @@
         <v>366</v>
       </c>
       <c r="H18" t="n">
-        <v>412538880</v>
+        <v>411038880</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -1602,16 +1602,16 @@
         <v>152</v>
       </c>
       <c r="L18" t="n">
-        <v>152346880</v>
+        <v>151846880</v>
       </c>
       <c r="M18" t="n">
-        <v>36.93</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>97740000</v>
+        <v>109740000</v>
       </c>
       <c r="G20" t="n">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H20" t="n">
-        <v>824580500</v>
+        <v>826885500</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>7100000</v>
+        <v>4025000</v>
       </c>
       <c r="K20" t="n">
         <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>38225000</v>
+        <v>37850000</v>
       </c>
       <c r="M20" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1731,13 +1731,13 @@
         <v>572</v>
       </c>
       <c r="H21" t="n">
-        <v>663765000</v>
+        <v>660840000</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4125000</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1746,13 +1746,13 @@
         <v>71780000</v>
       </c>
       <c r="M21" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,7 +1825,7 @@
         <v>442</v>
       </c>
       <c r="H23" t="n">
-        <v>470828000</v>
+        <v>470078000</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2010,16 +2010,16 @@
         <v>78100000</v>
       </c>
       <c r="G27" t="n">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H27" t="n">
-        <v>533496200</v>
+        <v>518816200</v>
       </c>
       <c r="I27" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>64590000</v>
+        <v>8720000</v>
       </c>
       <c r="K27" t="n">
         <v>84</v>
@@ -2028,13 +2028,13 @@
         <v>99259200</v>
       </c>
       <c r="M27" t="n">
-        <v>118.15</v>
+        <v>118.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2060,7 +2060,7 @@
         <v>481</v>
       </c>
       <c r="H28" t="n">
-        <v>706557000</v>
+        <v>704257000</v>
       </c>
       <c r="I28" t="n">
         <v>3</v>
@@ -2075,13 +2075,13 @@
         <v>45033000</v>
       </c>
       <c r="M28" t="n">
-        <v>6.37</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2154,13 +2154,13 @@
         <v>150</v>
       </c>
       <c r="H30" t="n">
-        <v>77848600</v>
+        <v>77598600</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>11300000</v>
+        <v>9800000</v>
       </c>
       <c r="K30" t="n">
         <v>89</v>
@@ -2169,7 +2169,7 @@
         <v>49863600</v>
       </c>
       <c r="M30" t="n">
-        <v>64.05</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2420,10 +2420,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>346840000</v>
+        <v>358840000</v>
       </c>
       <c r="J2" t="n">
-        <v>332406000</v>
+        <v>411979000</v>
       </c>
     </row>
     <row r="3">
@@ -2455,7 +2455,7 @@
         <v>408650000</v>
       </c>
       <c r="J3" t="n">
-        <v>204957000</v>
+        <v>243312000</v>
       </c>
     </row>
     <row r="4">
@@ -2487,7 +2487,7 @@
         <v>395150000</v>
       </c>
       <c r="J4" t="n">
-        <v>483916000</v>
+        <v>513081000</v>
       </c>
     </row>
     <row r="5">
@@ -2516,10 +2516,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>313200000</v>
+        <v>316800000</v>
       </c>
       <c r="J5" t="n">
-        <v>366239001</v>
+        <v>413354001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>513081000</v>
+        <v>457931000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>413354001</v>
+        <v>356554001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>411979000</v>
+        <v>327656000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>243312000</v>
+        <v>192417000</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2423,7 @@
         <v>358840000</v>
       </c>
       <c r="J2" t="n">
-        <v>411979000</v>
+        <v>327656000</v>
       </c>
     </row>
     <row r="3">
@@ -2455,7 +2455,7 @@
         <v>408650000</v>
       </c>
       <c r="J3" t="n">
-        <v>243312000</v>
+        <v>192417000</v>
       </c>
     </row>
     <row r="4">
@@ -2487,7 +2487,7 @@
         <v>395150000</v>
       </c>
       <c r="J4" t="n">
-        <v>513081000</v>
+        <v>457931000</v>
       </c>
     </row>
     <row r="5">
@@ -2519,7 +2519,7 @@
         <v>316800000</v>
       </c>
       <c r="J5" t="n">
-        <v>413354001</v>
+        <v>356554001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>457931000</v>
+        <v>536341000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>356554001</v>
+        <v>456265000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>327656000</v>
+        <v>428704001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>192417000</v>
+        <v>278262000</v>
       </c>
     </row>
   </sheetData>
@@ -517,25 +517,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>59400000</v>
+        <v>33400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>39400000</v>
+        <v>16500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,28 +562,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>21600000</v>
+        <v>11400000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>20800000</v>
+        <v>5400000</v>
       </c>
     </row>
   </sheetData>
@@ -635,31 +635,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>408650000</v>
+        <v>68400000</v>
       </c>
       <c r="D2" t="n">
-        <v>1916</v>
+        <v>2111</v>
       </c>
       <c r="E2" t="n">
-        <v>2259745160</v>
+        <v>2468420440.32</v>
       </c>
       <c r="F2" t="n">
-        <v>276649160</v>
+        <v>383065120.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>395150000</v>
+        <v>22900000</v>
       </c>
       <c r="D3" t="n">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="E3" t="n">
-        <v>2955263560.6</v>
+        <v>2917801560.6</v>
       </c>
       <c r="F3" t="n">
-        <v>550750560.6</v>
+        <v>565482560.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,40 +692,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>358840000</v>
+        <v>21000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2399</v>
+        <v>2387</v>
       </c>
       <c r="E4" t="n">
-        <v>3142451020</v>
+        <v>3105974720</v>
       </c>
       <c r="F4" t="n">
-        <v>503928840</v>
+        <v>536778040</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>316800000</v>
+        <v>18500000</v>
       </c>
       <c r="D5" t="n">
-        <v>2103</v>
+        <v>1905</v>
       </c>
       <c r="E5" t="n">
-        <v>2460025440.32</v>
+        <v>2236654160</v>
       </c>
       <c r="F5" t="n">
-        <v>368208120.32</v>
+        <v>300699160</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>76500000</v>
+        <v>8000000</v>
       </c>
       <c r="G2" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="H2" t="n">
-        <v>530412160</v>
+        <v>521213160</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>336564000</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
@@ -853,13 +853,13 @@
         <v>5139160</v>
       </c>
       <c r="M2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,40 +920,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>66550000</v>
+        <v>3200000</v>
       </c>
       <c r="G4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H4" t="n">
-        <v>377021520</v>
+        <v>376998520</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="J4" t="n">
-        <v>1200000</v>
+        <v>130729000</v>
       </c>
       <c r="K4" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L4" t="n">
-        <v>184114520</v>
+        <v>185314520</v>
       </c>
       <c r="M4" t="n">
-        <v>48.83</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,31 +976,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H5" t="n">
-        <v>380714480.6</v>
+        <v>372539480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>212</v>
       </c>
       <c r="J5" t="n">
-        <v>6265000</v>
+        <v>157929000</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
-        <v>180305480.6</v>
+        <v>182030480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>47.36</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>119100000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H6" t="n">
-        <v>766470600</v>
+        <v>747350600</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>287</v>
       </c>
       <c r="J6" t="n">
-        <v>2500000</v>
+        <v>508195000</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>25966600</v>
+        <v>28466600</v>
       </c>
       <c r="M6" t="n">
-        <v>3.39</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>55600000</v>
+        <v>7200000</v>
       </c>
       <c r="G7" t="n">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H7" t="n">
-        <v>367867000</v>
+        <v>367592000</v>
       </c>
       <c r="I7" t="n">
-        <v>23</v>
+        <v>248</v>
       </c>
       <c r="J7" t="n">
-        <v>20210000</v>
+        <v>181018000</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="L7" t="n">
-        <v>101309000</v>
+        <v>108941000</v>
       </c>
       <c r="M7" t="n">
-        <v>27.54</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>77400000</v>
+        <v>4500000</v>
       </c>
       <c r="G8" t="n">
         <v>488</v>
       </c>
       <c r="H8" t="n">
-        <v>532777800</v>
+        <v>532107800</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>382</v>
       </c>
       <c r="J8" t="n">
-        <v>8490000</v>
+        <v>409872000</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>53915800</v>
+        <v>55590800</v>
       </c>
       <c r="M8" t="n">
-        <v>10.12</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,40 +1155,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>14700000</v>
+        <v>3600000</v>
       </c>
       <c r="G9" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H9" t="n">
-        <v>340564000</v>
+        <v>341404000</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>183</v>
       </c>
       <c r="J9" t="n">
-        <v>5660000</v>
+        <v>184064000</v>
       </c>
       <c r="K9" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L9" t="n">
-        <v>130535000</v>
+        <v>134135000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.33</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>105300000</v>
+        <v>43200000</v>
       </c>
       <c r="G10" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="H10" t="n">
-        <v>594525200</v>
+        <v>611930200</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>403360000</v>
       </c>
       <c r="K10" t="n">
         <v>12</v>
@@ -1229,13 +1229,13 @@
         <v>7260200</v>
       </c>
       <c r="M10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>119700000</v>
+        <v>21600000</v>
       </c>
       <c r="G11" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H11" t="n">
-        <v>778483000</v>
+        <v>778173000</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>326</v>
       </c>
       <c r="J11" t="n">
-        <v>6500000</v>
+        <v>539613000</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>21725000</v>
+        <v>28225000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.79</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>69900000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>305</v>
       </c>
       <c r="H12" t="n">
-        <v>345011120.32</v>
+        <v>337901120.32</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>1400000</v>
+        <v>141129000</v>
       </c>
       <c r="K12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
-        <v>85490120.31999999</v>
+        <v>86890120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>24.78</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7200000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>334980800</v>
+        <v>332550800</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="J13" t="n">
-        <v>4167000</v>
+        <v>191911000</v>
       </c>
       <c r="K13" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>123197800</v>
+        <v>126554800</v>
       </c>
       <c r="M13" t="n">
-        <v>36.78</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>86500000</v>
+        <v>3000000</v>
       </c>
       <c r="G14" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H14" t="n">
-        <v>758400200</v>
+        <v>745750400</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="J14" t="n">
-        <v>24390000</v>
+        <v>446138000</v>
       </c>
       <c r="K14" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>68021200</v>
+        <v>85060400</v>
       </c>
       <c r="M14" t="n">
-        <v>8.970000000000001</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>14400000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>311</v>
       </c>
       <c r="H16" t="n">
-        <v>485286440</v>
+        <v>478986440</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="J16" t="n">
-        <v>14680000</v>
+        <v>285862000</v>
       </c>
       <c r="K16" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="L16" t="n">
-        <v>107969440</v>
+        <v>122449440</v>
       </c>
       <c r="M16" t="n">
-        <v>22.25</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>63700000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H18" t="n">
-        <v>411038880</v>
+        <v>402568880</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="J18" t="n">
-        <v>2100000</v>
+        <v>156104000</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L18" t="n">
-        <v>151846880</v>
+        <v>153271880</v>
       </c>
       <c r="M18" t="n">
-        <v>36.94</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>109740000</v>
+        <v>14400000</v>
       </c>
       <c r="G20" t="n">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="H20" t="n">
-        <v>826885500</v>
+        <v>828584000</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>396</v>
       </c>
       <c r="J20" t="n">
-        <v>4025000</v>
+        <v>584930000</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L20" t="n">
-        <v>37850000</v>
+        <v>41875000</v>
       </c>
       <c r="M20" t="n">
-        <v>4.58</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>84500000</v>
+        <v>3600000</v>
       </c>
       <c r="G21" t="n">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H21" t="n">
-        <v>660840000</v>
+        <v>650085000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>454200000</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>71780000</v>
+        <v>67660000</v>
       </c>
       <c r="M21" t="n">
-        <v>10.86</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>76500000</v>
+        <v>10200000</v>
       </c>
       <c r="G23" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H23" t="n">
-        <v>470078000</v>
+        <v>470508000</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>418061000</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1907,40 +1907,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>87850000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>228</v>
       </c>
       <c r="H25" t="n">
-        <v>290617360</v>
+        <v>286417360</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="J25" t="n">
-        <v>10118000</v>
+        <v>168731000</v>
       </c>
       <c r="K25" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>51527360</v>
+        <v>56627360</v>
       </c>
       <c r="M25" t="n">
-        <v>17.73</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2001,40 +2001,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>78100000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H27" t="n">
-        <v>518816200</v>
+        <v>515176200</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>293</v>
       </c>
       <c r="J27" t="n">
-        <v>8720000</v>
+        <v>308480000</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L27" t="n">
-        <v>99259200</v>
+        <v>105409200</v>
       </c>
       <c r="M27" t="n">
-        <v>118.67</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2048,40 +2048,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>89700000</v>
+        <v>8300000</v>
       </c>
       <c r="G28" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H28" t="n">
-        <v>704257000</v>
+        <v>691776000</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>314</v>
       </c>
       <c r="J28" t="n">
-        <v>3600000</v>
+        <v>458237000</v>
       </c>
       <c r="K28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L28" t="n">
-        <v>45033000</v>
+        <v>48633000</v>
       </c>
       <c r="M28" t="n">
-        <v>6.39</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2095,25 +2095,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>76500000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H29" t="n">
-        <v>181852000</v>
+        <v>179252000</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>97922000</v>
       </c>
       <c r="K29" t="n">
         <v>23</v>
@@ -2122,13 +2122,13 @@
         <v>14044000</v>
       </c>
       <c r="M29" t="n">
-        <v>7.72</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2151,25 +2151,25 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H30" t="n">
-        <v>77598600</v>
+        <v>76998600</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J30" t="n">
-        <v>9800000</v>
+        <v>17935000</v>
       </c>
       <c r="K30" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>49863600</v>
+        <v>59063600</v>
       </c>
       <c r="M30" t="n">
-        <v>64.26000000000001</v>
+        <v>76.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2339,7 +2339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,10 +2385,20 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>صرف_2026-04</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-04</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>صرف_None</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>متأخر_None</t>
         </is>
@@ -2425,6 +2435,12 @@
       <c r="J2" t="n">
         <v>327656000</v>
       </c>
+      <c r="K2" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>456265000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -2457,6 +2473,12 @@
       <c r="J3" t="n">
         <v>192417000</v>
       </c>
+      <c r="K3" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>278262000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -2489,6 +2511,12 @@
       <c r="J4" t="n">
         <v>457931000</v>
       </c>
+      <c r="K4" t="n">
+        <v>22900000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>536341000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -2520,6 +2548,12 @@
       </c>
       <c r="J5" t="n">
         <v>356554001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>68400000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>428704001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -647,13 +647,13 @@
         <v>68400000</v>
       </c>
       <c r="D2" t="n">
-        <v>2111</v>
+        <v>1990</v>
       </c>
       <c r="E2" t="n">
-        <v>2468420440.32</v>
+        <v>2403030000</v>
       </c>
       <c r="F2" t="n">
-        <v>383065120.32</v>
+        <v>385771000</v>
       </c>
     </row>
     <row r="3">
@@ -671,13 +671,13 @@
         <v>22900000</v>
       </c>
       <c r="D3" t="n">
-        <v>2519</v>
+        <v>2444</v>
       </c>
       <c r="E3" t="n">
-        <v>2917801560.6</v>
+        <v>2860061000</v>
       </c>
       <c r="F3" t="n">
-        <v>565482560.6</v>
+        <v>514097000</v>
       </c>
     </row>
     <row r="4">
@@ -695,13 +695,13 @@
         <v>21000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2387</v>
+        <v>2303</v>
       </c>
       <c r="E4" t="n">
-        <v>3105974720</v>
+        <v>3036569000</v>
       </c>
       <c r="F4" t="n">
-        <v>536778040</v>
+        <v>401451000</v>
       </c>
     </row>
     <row r="5">
@@ -719,13 +719,13 @@
         <v>18500000</v>
       </c>
       <c r="D5" t="n">
-        <v>1905</v>
+        <v>1815</v>
       </c>
       <c r="E5" t="n">
-        <v>2236654160</v>
+        <v>2174672000</v>
       </c>
       <c r="F5" t="n">
-        <v>300699160</v>
+        <v>239467000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,25 +835,25 @@
         <v>8000000</v>
       </c>
       <c r="G2" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H2" t="n">
-        <v>521213160</v>
+        <v>516324000</v>
       </c>
       <c r="I2" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J2" t="n">
-        <v>336564000</v>
+        <v>332154000</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>5139160</v>
+        <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.99</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
@@ -869,38 +869,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hussein . Kadhum Dhahi -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>370585000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>127789000</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>179261000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="4">
@@ -916,38 +916,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3200000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H4" t="n">
-        <v>376998520</v>
+        <v>334944000</v>
       </c>
       <c r="I4" t="n">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="J4" t="n">
-        <v>130729000</v>
+        <v>149754000</v>
       </c>
       <c r="K4" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>185314520</v>
+        <v>147170000</v>
       </c>
       <c r="M4" t="n">
-        <v>49.16</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +963,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -976,25 +976,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="H5" t="n">
-        <v>372539480.6</v>
+        <v>743209000</v>
       </c>
       <c r="I5" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="J5" t="n">
-        <v>157929000</v>
+        <v>502395000</v>
       </c>
       <c r="K5" t="n">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>182030480.6</v>
+        <v>25325000</v>
       </c>
       <c r="M5" t="n">
-        <v>48.86</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="6">
@@ -1010,38 +1010,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="G6" t="n">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="H6" t="n">
-        <v>747350600</v>
+        <v>365902000</v>
       </c>
       <c r="I6" t="n">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="J6" t="n">
-        <v>508195000</v>
+        <v>175847000</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="L6" t="n">
-        <v>28466600</v>
+        <v>108941000</v>
       </c>
       <c r="M6" t="n">
-        <v>3.81</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="7">
@@ -1057,38 +1057,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>7200000</v>
+        <v>4500000</v>
       </c>
       <c r="G7" t="n">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="H7" t="n">
-        <v>367592000</v>
+        <v>529097000</v>
       </c>
       <c r="I7" t="n">
-        <v>248</v>
+        <v>381</v>
       </c>
       <c r="J7" t="n">
-        <v>181018000</v>
+        <v>409512000</v>
       </c>
       <c r="K7" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>108941000</v>
+        <v>52700000</v>
       </c>
       <c r="M7" t="n">
-        <v>29.64</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1114,28 +1114,28 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>4500000</v>
+        <v>3600000</v>
       </c>
       <c r="G8" t="n">
-        <v>488</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>532107800</v>
+        <v>341404000</v>
       </c>
       <c r="I8" t="n">
-        <v>382</v>
+        <v>183</v>
       </c>
       <c r="J8" t="n">
-        <v>409872000</v>
+        <v>184064000</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="L8" t="n">
-        <v>55590800</v>
+        <v>134135000</v>
       </c>
       <c r="M8" t="n">
-        <v>10.45</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="9">
@@ -1151,38 +1151,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>341404000</v>
+        <v>47980000</v>
       </c>
       <c r="I9" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>184064000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>134135000</v>
+        <v>47980000</v>
       </c>
       <c r="M9" t="n">
-        <v>39.29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1211,25 +1211,25 @@
         <v>43200000</v>
       </c>
       <c r="G10" t="n">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>611930200</v>
+        <v>606220000</v>
       </c>
       <c r="I10" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J10" t="n">
-        <v>403360000</v>
+        <v>401560000</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>7260200</v>
+        <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.19</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="11">
@@ -1261,13 +1261,13 @@
         <v>478</v>
       </c>
       <c r="H11" t="n">
-        <v>778173000</v>
+        <v>777798000</v>
       </c>
       <c r="I11" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J11" t="n">
-        <v>539613000</v>
+        <v>535938000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1305,25 +1305,25 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="H12" t="n">
-        <v>337901120.32</v>
+        <v>316465000</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J12" t="n">
-        <v>141129000</v>
+        <v>139329000</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>86890120.31999999</v>
+        <v>65904000</v>
       </c>
       <c r="M12" t="n">
-        <v>25.71</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="13">
@@ -1352,25 +1352,25 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>332550800</v>
+        <v>313163000</v>
       </c>
       <c r="I13" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J13" t="n">
-        <v>191911000</v>
+        <v>190831000</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>126554800</v>
+        <v>107527000</v>
       </c>
       <c r="M13" t="n">
-        <v>38.06</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="14">
@@ -1399,10 +1399,10 @@
         <v>3000000</v>
       </c>
       <c r="G14" t="n">
-        <v>576</v>
+        <v>541</v>
       </c>
       <c r="H14" t="n">
-        <v>745750400</v>
+        <v>720116000</v>
       </c>
       <c r="I14" t="n">
         <v>353</v>
@@ -1411,13 +1411,13 @@
         <v>446138000</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>85060400</v>
+        <v>59426000</v>
       </c>
       <c r="M14" t="n">
-        <v>11.41</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="15">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1446,25 +1446,25 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>66461320</v>
+        <v>465137000</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>285862000</v>
       </c>
       <c r="K15" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="L15" t="n">
-        <v>66461320</v>
+        <v>108600000</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="16">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1493,25 +1493,25 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>478986440</v>
+        <v>375617000</v>
       </c>
       <c r="I16" t="n">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="J16" t="n">
-        <v>285862000</v>
+        <v>152774000</v>
       </c>
       <c r="K16" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="L16" t="n">
-        <v>122449440</v>
+        <v>126860000</v>
       </c>
       <c r="M16" t="n">
-        <v>25.56</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="17">
@@ -1527,38 +1527,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>828584000</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>584930000</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>41875000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="18">
@@ -1574,38 +1574,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G18" t="n">
-        <v>362</v>
+        <v>562</v>
       </c>
       <c r="H18" t="n">
-        <v>402568880</v>
+        <v>647115000</v>
       </c>
       <c r="I18" t="n">
-        <v>133</v>
+        <v>391</v>
       </c>
       <c r="J18" t="n">
-        <v>156104000</v>
+        <v>454200000</v>
       </c>
       <c r="K18" t="n">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>153271880</v>
+        <v>64690000</v>
       </c>
       <c r="M18" t="n">
-        <v>38.07</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -1616,34 +1616,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>10200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>469612000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>413476000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1663,43 +1663,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>14400000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>570</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>828584000</v>
+        <v>12500000</v>
       </c>
       <c r="I20" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>584930000</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>41875000</v>
+        <v>12500000</v>
       </c>
       <c r="M20" t="n">
-        <v>5.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1710,43 +1710,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>568</v>
+        <v>214</v>
       </c>
       <c r="H21" t="n">
-        <v>650085000</v>
+        <v>278910000</v>
       </c>
       <c r="I21" t="n">
-        <v>391</v>
+        <v>120</v>
       </c>
       <c r="J21" t="n">
-        <v>454200000</v>
+        <v>166438000</v>
       </c>
       <c r="K21" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>67660000</v>
+        <v>49370000</v>
       </c>
       <c r="M21" t="n">
-        <v>10.41</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="22">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ahmed . Hassan Yusif -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1775,25 +1775,25 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>484209000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>308480000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>74442000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="23">
@@ -1809,38 +1809,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>10200000</v>
+        <v>8300000</v>
       </c>
       <c r="G23" t="n">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="H23" t="n">
-        <v>470508000</v>
+        <v>688938000</v>
       </c>
       <c r="I23" t="n">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="J23" t="n">
-        <v>418061000</v>
+        <v>458237000</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>396000</v>
+        <v>45795000</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="24">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1869,25 +1869,25 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H24" t="n">
-        <v>15470000</v>
+        <v>173708000</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>97922000</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>15470000</v>
+        <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="25">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1916,260 +1916,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="H25" t="n">
-        <v>286417360</v>
+        <v>66795000</v>
       </c>
       <c r="I25" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="J25" t="n">
-        <v>168731000</v>
+        <v>17935000</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="L25" t="n">
-        <v>56627360</v>
+        <v>48860000</v>
       </c>
       <c r="M25" t="n">
-        <v>19.77</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Baydaa . Hameed Mizher -</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="M26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ibtihal Hamza  Hussain -</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>461</v>
-      </c>
-      <c r="H27" t="n">
-        <v>515176200</v>
-      </c>
-      <c r="I27" t="n">
-        <v>293</v>
-      </c>
-      <c r="J27" t="n">
-        <v>308480000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>86</v>
-      </c>
-      <c r="L27" t="n">
-        <v>105409200</v>
-      </c>
-      <c r="M27" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jawnaa . Radhi Shimran -</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>482</v>
-      </c>
-      <c r="H28" t="n">
-        <v>691776000</v>
-      </c>
-      <c r="I28" t="n">
-        <v>314</v>
-      </c>
-      <c r="J28" t="n">
-        <v>458237000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>32</v>
-      </c>
-      <c r="L28" t="n">
-        <v>48633000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7.03</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>131</v>
-      </c>
-      <c r="H29" t="n">
-        <v>179252000</v>
-      </c>
-      <c r="I29" t="n">
-        <v>58</v>
-      </c>
-      <c r="J29" t="n">
-        <v>97922000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>23</v>
-      </c>
-      <c r="L29" t="n">
-        <v>14044000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7.83</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>147</v>
-      </c>
-      <c r="H30" t="n">
-        <v>76998600</v>
-      </c>
-      <c r="I30" t="n">
-        <v>42</v>
-      </c>
-      <c r="J30" t="n">
-        <v>17935000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>105</v>
-      </c>
-      <c r="L30" t="n">
-        <v>59063600</v>
-      </c>
-      <c r="M30" t="n">
-        <v>76.70999999999999</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>536341000</v>
+        <v>535056000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>456265000</v>
+        <v>431100000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428704001</v>
+        <v>413199001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>278262000</v>
+        <v>269537000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>33400000</v>
+        <v>77050000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16500000</v>
+        <v>23700000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>11400000</v>
+        <v>13800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5400000</v>
+        <v>13500000</v>
       </c>
     </row>
   </sheetData>
@@ -635,97 +635,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68400000</v>
+        <v>86400000</v>
       </c>
       <c r="D2" t="n">
-        <v>1990</v>
+        <v>2320</v>
       </c>
       <c r="E2" t="n">
-        <v>2403030000</v>
+        <v>3043149000</v>
       </c>
       <c r="F2" t="n">
-        <v>385771000</v>
+        <v>399301000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22900000</v>
+        <v>73800000</v>
       </c>
       <c r="D3" t="n">
-        <v>2444</v>
+        <v>1990</v>
       </c>
       <c r="E3" t="n">
-        <v>2860061000</v>
+        <v>2369855000</v>
       </c>
       <c r="F3" t="n">
-        <v>514097000</v>
+        <v>385471000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21000000</v>
+        <v>61000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2303</v>
+        <v>1829</v>
       </c>
       <c r="E4" t="n">
-        <v>3036569000</v>
+        <v>2177749000</v>
       </c>
       <c r="F4" t="n">
-        <v>401451000</v>
+        <v>239467000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18500000</v>
+        <v>35500000</v>
       </c>
       <c r="D5" t="n">
-        <v>1815</v>
+        <v>2439</v>
       </c>
       <c r="E5" t="n">
-        <v>2174672000</v>
+        <v>2838251000</v>
       </c>
       <c r="F5" t="n">
-        <v>239467000</v>
+        <v>512272000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -838,13 +838,13 @@
         <v>405</v>
       </c>
       <c r="H2" t="n">
-        <v>516324000</v>
+        <v>511849000</v>
       </c>
       <c r="I2" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="J2" t="n">
-        <v>332154000</v>
+        <v>306147000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -882,16 +882,16 @@
         <v>3200000</v>
       </c>
       <c r="G3" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H3" t="n">
-        <v>370585000</v>
+        <v>367910000</v>
       </c>
       <c r="I3" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J3" t="n">
-        <v>127789000</v>
+        <v>107334000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -900,13 +900,13 @@
         <v>179261000</v>
       </c>
       <c r="M3" t="n">
-        <v>48.37</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>341</v>
       </c>
       <c r="H4" t="n">
-        <v>334944000</v>
+        <v>331444000</v>
       </c>
       <c r="I4" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="J4" t="n">
-        <v>149754000</v>
+        <v>138924000</v>
       </c>
       <c r="K4" t="n">
         <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>147170000</v>
+        <v>145695000</v>
       </c>
       <c r="M4" t="n">
-        <v>43.94</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G5" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H5" t="n">
-        <v>743209000</v>
+        <v>734859000</v>
       </c>
       <c r="I5" t="n">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="J5" t="n">
-        <v>502395000</v>
+        <v>386582000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>25325000</v>
+        <v>24975000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>463</v>
       </c>
       <c r="H6" t="n">
-        <v>365902000</v>
+        <v>362662000</v>
       </c>
       <c r="I6" t="n">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="J6" t="n">
-        <v>175847000</v>
+        <v>154197000</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -1041,13 +1041,13 @@
         <v>108941000</v>
       </c>
       <c r="M6" t="n">
-        <v>29.77</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>4500000</v>
+        <v>8100000</v>
       </c>
       <c r="G7" t="n">
         <v>479</v>
       </c>
       <c r="H7" t="n">
-        <v>529097000</v>
+        <v>529527000</v>
       </c>
       <c r="I7" t="n">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="J7" t="n">
-        <v>409512000</v>
+        <v>391312000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>52700000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>341404000</v>
+        <v>338244000</v>
       </c>
       <c r="I8" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="J8" t="n">
-        <v>184064000</v>
+        <v>158833000</v>
       </c>
       <c r="K8" t="n">
         <v>162</v>
@@ -1135,13 +1135,13 @@
         <v>134135000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.29</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>43200000</v>
+        <v>48600000</v>
       </c>
       <c r="G10" t="n">
         <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>606220000</v>
+        <v>598430000</v>
       </c>
       <c r="I10" t="n">
-        <v>321</v>
+        <v>263</v>
       </c>
       <c r="J10" t="n">
-        <v>401560000</v>
+        <v>325855000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,13 +1261,13 @@
         <v>478</v>
       </c>
       <c r="H11" t="n">
-        <v>777798000</v>
+        <v>761148000</v>
       </c>
       <c r="I11" t="n">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="J11" t="n">
-        <v>535938000</v>
+        <v>435008000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1276,13 +1276,13 @@
         <v>28225000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.63</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,28 +1308,28 @@
         <v>260</v>
       </c>
       <c r="H12" t="n">
-        <v>316465000</v>
+        <v>314040000</v>
       </c>
       <c r="I12" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J12" t="n">
-        <v>139329000</v>
+        <v>124929000</v>
       </c>
       <c r="K12" t="n">
         <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>65904000</v>
+        <v>65604000</v>
       </c>
       <c r="M12" t="n">
-        <v>20.83</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>313163000</v>
+        <v>310013000</v>
       </c>
       <c r="I13" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="J13" t="n">
-        <v>190831000</v>
+        <v>174226000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>107527000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.34</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,13 +1402,13 @@
         <v>541</v>
       </c>
       <c r="H14" t="n">
-        <v>720116000</v>
+        <v>707106000</v>
       </c>
       <c r="I14" t="n">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="J14" t="n">
-        <v>446138000</v>
+        <v>358291000</v>
       </c>
       <c r="K14" t="n">
         <v>65</v>
@@ -1417,13 +1417,13 @@
         <v>59426000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.25</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>465137000</v>
+        <v>458187000</v>
       </c>
       <c r="I15" t="n">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="J15" t="n">
-        <v>285862000</v>
+        <v>232362000</v>
       </c>
       <c r="K15" t="n">
         <v>69</v>
@@ -1464,13 +1464,13 @@
         <v>108600000</v>
       </c>
       <c r="M15" t="n">
-        <v>23.35</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,28 +1496,28 @@
         <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>375617000</v>
+        <v>369922000</v>
       </c>
       <c r="I16" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="J16" t="n">
-        <v>152774000</v>
+        <v>114230000</v>
       </c>
       <c r="K16" t="n">
         <v>115</v>
       </c>
       <c r="L16" t="n">
-        <v>126860000</v>
+        <v>126260000</v>
       </c>
       <c r="M16" t="n">
-        <v>33.77</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
-        <v>14400000</v>
+        <v>59400000</v>
       </c>
       <c r="G17" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>828584000</v>
+        <v>852509000</v>
       </c>
       <c r="I17" t="n">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="J17" t="n">
-        <v>584930000</v>
+        <v>505160000</v>
       </c>
       <c r="K17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
-        <v>41875000</v>
+        <v>41075000</v>
       </c>
       <c r="M17" t="n">
-        <v>5.05</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>3600000</v>
+        <v>24000000</v>
       </c>
       <c r="G18" t="n">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="H18" t="n">
-        <v>647115000</v>
+        <v>655425000</v>
       </c>
       <c r="I18" t="n">
-        <v>391</v>
+        <v>329</v>
       </c>
       <c r="J18" t="n">
-        <v>454200000</v>
+        <v>392562000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>64690000</v>
+        <v>63940000</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>10200000</v>
+        <v>41700000</v>
       </c>
       <c r="G19" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="H19" t="n">
-        <v>469612000</v>
+        <v>485065000</v>
       </c>
       <c r="I19" t="n">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="J19" t="n">
-        <v>413476000</v>
+        <v>338889000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1731,13 +1731,13 @@
         <v>214</v>
       </c>
       <c r="H21" t="n">
-        <v>278910000</v>
+        <v>273560000</v>
       </c>
       <c r="I21" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J21" t="n">
-        <v>166438000</v>
+        <v>132701000</v>
       </c>
       <c r="K21" t="n">
         <v>54</v>
@@ -1746,13 +1746,13 @@
         <v>49370000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.7</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,13 +1778,13 @@
         <v>434</v>
       </c>
       <c r="H22" t="n">
-        <v>484209000</v>
+        <v>482609000</v>
       </c>
       <c r="I22" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J22" t="n">
-        <v>308480000</v>
+        <v>298529000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1793,13 +1793,13 @@
         <v>74442000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.37</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>8300000</v>
+        <v>12800000</v>
       </c>
       <c r="G23" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H23" t="n">
-        <v>688938000</v>
+        <v>680403000</v>
       </c>
       <c r="I23" t="n">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="J23" t="n">
-        <v>458237000</v>
+        <v>371197000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,13 +1840,13 @@
         <v>45795000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.65</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6500000</v>
       </c>
       <c r="G24" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H24" t="n">
-        <v>173708000</v>
+        <v>176817000</v>
       </c>
       <c r="I24" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J24" t="n">
-        <v>97922000</v>
+        <v>81796000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,13 +1887,13 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2201,10 +2201,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>21000000</v>
+        <v>86400000</v>
       </c>
       <c r="L2" t="n">
-        <v>456265000</v>
+        <v>431100000</v>
       </c>
     </row>
     <row r="3">
@@ -2239,10 +2239,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>18500000</v>
+        <v>61000000</v>
       </c>
       <c r="L3" t="n">
-        <v>278262000</v>
+        <v>269537000</v>
       </c>
     </row>
     <row r="4">
@@ -2277,10 +2277,10 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>22900000</v>
+        <v>35500000</v>
       </c>
       <c r="L4" t="n">
-        <v>536341000</v>
+        <v>535056000</v>
       </c>
     </row>
     <row r="5">
@@ -2315,10 +2315,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>68400000</v>
+        <v>73800000</v>
       </c>
       <c r="L5" t="n">
-        <v>428704001</v>
+        <v>413199001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -12,7 +12,6 @@
     <sheet name="الأداء - فروع" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="الأداء - موظفين" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="الأرصدة" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="التاريخ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2096,232 +2095,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الفرع</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>صرف_2026-01</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-01</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>صرف_2026-02</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-02</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>صرف_2026-03</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-03</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>صرف_2026-04</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-04</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>صرف_None</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>متأخر_None</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>النجف</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>550290000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>285486000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>480050000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>303946000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>432800000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>324966000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>358840000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>327656000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>86400000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>431100000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>306450000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>184335000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>241900000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>186212000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>338400000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>194867000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>408650000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>192417000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>61000000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>269537000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>الحلة</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>404010000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>436001000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>424900000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>437156000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>323950000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>459416000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>395150000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>457931000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>35500000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>535056000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الديوانية</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>396500000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>377739001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>327500000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>365486001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>248100000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>365124001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>316800000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>356554001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>73800000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>413199001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -12,6 +12,7 @@
     <sheet name="الأداء - فروع" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="الأداء - موظفين" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="الأرصدة" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="التاريخ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2095,4 +2096,232 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الفرع</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>صرف_2026-01</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-01</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>صرف_2026-02</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-02</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>صرف_2026-03</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-03</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>صرف_2026-04</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-04</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>صرف_None</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>متأخر_None</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>النجف</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>550290000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>285486000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>480050000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>303946000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>432800000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>324966000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>358840000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>327656000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86400000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>431100000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>306450000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>184335000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>241900000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>186212000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>338400000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>194867000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>408650000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>192417000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>269537000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>الحلة</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>404010000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>436001000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>424900000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>437156000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>323950000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>459416000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>395150000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>457931000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>35500000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>535056000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>الديوانية</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>396500000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>377739001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>327500000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>365486001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>248100000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>365124001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>316800000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>356554001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>73800000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>413199001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>535056000</v>
+        <v>620751000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>431100000</v>
+        <v>488190000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>413199001</v>
+        <v>459209001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>269537000</v>
+        <v>322297000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>77050000</v>
+        <v>66600000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>23700000</v>
+        <v>49400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>13800000</v>
+        <v>48300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>13500000</v>
+        <v>32700000</v>
       </c>
     </row>
   </sheetData>
@@ -635,79 +635,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86400000</v>
+        <v>151750000</v>
       </c>
       <c r="D2" t="n">
-        <v>2320</v>
+        <v>1952</v>
       </c>
       <c r="E2" t="n">
-        <v>3043149000</v>
+        <v>2249404160</v>
       </c>
       <c r="F2" t="n">
-        <v>399301000</v>
+        <v>299774160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73800000</v>
+        <v>128700000</v>
       </c>
       <c r="D3" t="n">
-        <v>1990</v>
+        <v>2383</v>
       </c>
       <c r="E3" t="n">
-        <v>2369855000</v>
+        <v>3049889720</v>
       </c>
       <c r="F3" t="n">
-        <v>385471000</v>
+        <v>509223040</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61000000</v>
+        <v>84600000</v>
       </c>
       <c r="D4" t="n">
-        <v>1829</v>
+        <v>2081</v>
       </c>
       <c r="E4" t="n">
-        <v>2177749000</v>
+        <v>2348335440.32</v>
       </c>
       <c r="F4" t="n">
-        <v>239467000</v>
+        <v>381365120.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>35500000</v>
       </c>
       <c r="D5" t="n">
-        <v>2439</v>
+        <v>2489</v>
       </c>
       <c r="E5" t="n">
-        <v>2838251000</v>
+        <v>2796446560.6</v>
       </c>
       <c r="F5" t="n">
-        <v>512272000</v>
+        <v>560432560.6</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,31 +835,31 @@
         <v>8000000</v>
       </c>
       <c r="G2" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H2" t="n">
-        <v>511849000</v>
+        <v>491703160</v>
       </c>
       <c r="I2" t="n">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="J2" t="n">
-        <v>306147000</v>
+        <v>156217000</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>700000</v>
+        <v>5139160</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,44 +869,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Hussein . Kadhum Dhahi -</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3200000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>367910000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>107334000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>179261000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>48.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3200000</v>
       </c>
       <c r="G4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H4" t="n">
-        <v>331444000</v>
+        <v>369848520</v>
       </c>
       <c r="I4" t="n">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="J4" t="n">
-        <v>138924000</v>
+        <v>75166000</v>
       </c>
       <c r="K4" t="n">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="L4" t="n">
-        <v>145695000</v>
+        <v>184864520</v>
       </c>
       <c r="M4" t="n">
-        <v>43.96</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,44 +963,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>424</v>
+        <v>374</v>
       </c>
       <c r="H5" t="n">
-        <v>734859000</v>
+        <v>356554480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="J5" t="n">
-        <v>386582000</v>
+        <v>103033000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
-        <v>24975000</v>
+        <v>180555480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>7200000</v>
+        <v>9000000</v>
       </c>
       <c r="G6" t="n">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="H6" t="n">
-        <v>362662000</v>
+        <v>705780600</v>
       </c>
       <c r="I6" t="n">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="J6" t="n">
-        <v>154197000</v>
+        <v>215625000</v>
       </c>
       <c r="K6" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>108941000</v>
+        <v>28116600</v>
       </c>
       <c r="M6" t="n">
-        <v>30.04</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1067,81 +1067,81 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>8100000</v>
+        <v>7200000</v>
       </c>
       <c r="G7" t="n">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="H7" t="n">
-        <v>529527000</v>
+        <v>351722000</v>
       </c>
       <c r="I7" t="n">
-        <v>366</v>
+        <v>155</v>
       </c>
       <c r="J7" t="n">
-        <v>391312000</v>
+        <v>114714000</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>52700000</v>
+        <v>106166000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.949999999999999</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>3600000</v>
+        <v>8100000</v>
       </c>
       <c r="G8" t="n">
-        <v>368</v>
+        <v>485</v>
       </c>
       <c r="H8" t="n">
-        <v>338244000</v>
+        <v>520837800</v>
       </c>
       <c r="I8" t="n">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="J8" t="n">
-        <v>158833000</v>
+        <v>320491000</v>
       </c>
       <c r="K8" t="n">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>134135000</v>
+        <v>55590800</v>
       </c>
       <c r="M8" t="n">
-        <v>39.66</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>362</v>
       </c>
       <c r="H9" t="n">
-        <v>47980000</v>
+        <v>329274000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>102236000</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="L9" t="n">
-        <v>47980000</v>
+        <v>133835000</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>48600000</v>
+        <v>55800000</v>
       </c>
       <c r="G10" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H10" t="n">
-        <v>598430000</v>
+        <v>577650200</v>
       </c>
       <c r="I10" t="n">
-        <v>263</v>
+        <v>103</v>
       </c>
       <c r="J10" t="n">
-        <v>325855000</v>
+        <v>149155000</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>2000000</v>
+        <v>7260200</v>
       </c>
       <c r="M10" t="n">
-        <v>0.33</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,16 +1258,16 @@
         <v>21600000</v>
       </c>
       <c r="G11" t="n">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="H11" t="n">
-        <v>761148000</v>
+        <v>726783000</v>
       </c>
       <c r="I11" t="n">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="J11" t="n">
-        <v>435008000</v>
+        <v>210127000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1276,13 +1276,13 @@
         <v>28225000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G12" t="n">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="H12" t="n">
-        <v>314040000</v>
+        <v>325946120.32</v>
       </c>
       <c r="I12" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J12" t="n">
-        <v>124929000</v>
+        <v>45964000</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>65604000</v>
+        <v>85490120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>20.89</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1352,31 +1352,31 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>310013000</v>
+        <v>322220800</v>
       </c>
       <c r="I13" t="n">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="J13" t="n">
-        <v>174226000</v>
+        <v>137801000</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>107527000</v>
+        <v>126554800</v>
       </c>
       <c r="M13" t="n">
-        <v>34.68</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>3000000</v>
+        <v>16200000</v>
       </c>
       <c r="G14" t="n">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="H14" t="n">
-        <v>707106000</v>
+        <v>722125400</v>
       </c>
       <c r="I14" t="n">
-        <v>289</v>
+        <v>176</v>
       </c>
       <c r="J14" t="n">
-        <v>358291000</v>
+        <v>221838000</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>59426000</v>
+        <v>85060400</v>
       </c>
       <c r="M14" t="n">
-        <v>8.4</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1446,31 +1446,31 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>304</v>
+        <v>92</v>
       </c>
       <c r="H15" t="n">
-        <v>458187000</v>
+        <v>66461320</v>
       </c>
       <c r="I15" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>232362000</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="L15" t="n">
-        <v>108600000</v>
+        <v>66461320</v>
       </c>
       <c r="M15" t="n">
-        <v>23.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1493,31 +1493,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="H16" t="n">
-        <v>369922000</v>
+        <v>444061440</v>
       </c>
       <c r="I16" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="J16" t="n">
-        <v>114230000</v>
+        <v>107092000</v>
       </c>
       <c r="K16" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="L16" t="n">
-        <v>126260000</v>
+        <v>101029440</v>
       </c>
       <c r="M16" t="n">
-        <v>34.13</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>59400000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>582</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>852509000</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>505160000</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>41075000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,76 +1574,76 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>24000000</v>
+        <v>9600000</v>
       </c>
       <c r="G18" t="n">
-        <v>567</v>
+        <v>361</v>
       </c>
       <c r="H18" t="n">
-        <v>655425000</v>
+        <v>396023880</v>
       </c>
       <c r="I18" t="n">
-        <v>329</v>
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>392562000</v>
+        <v>58460000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="L18" t="n">
-        <v>63940000</v>
+        <v>151911880</v>
       </c>
       <c r="M18" t="n">
-        <v>9.76</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Nadhir . Mohammad Kadhom -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>41700000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>485065000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>338889000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,101 +1658,101 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>78900000</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>587</v>
       </c>
       <c r="H20" t="n">
-        <v>12500000</v>
+        <v>854484000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>407310000</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>12500000</v>
+        <v>37850000</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>24000000</v>
       </c>
       <c r="G21" t="n">
-        <v>214</v>
+        <v>560</v>
       </c>
       <c r="H21" t="n">
-        <v>273560000</v>
+        <v>633195000</v>
       </c>
       <c r="I21" t="n">
-        <v>101</v>
+        <v>198</v>
       </c>
       <c r="J21" t="n">
-        <v>132701000</v>
+        <v>236588000</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>49370000</v>
+        <v>66910000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.05</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Ahmed . Hassan Yusif -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1775,31 +1775,31 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>482609000</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>298529000</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>74442000</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>15.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>39</v>
+      </c>
+      <c r="F23" t="n">
+        <v>80050000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>464</v>
+      </c>
+      <c r="H23" t="n">
+        <v>494486000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>183</v>
+      </c>
+      <c r="J23" t="n">
+        <v>185674000</v>
+      </c>
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12800000</v>
-      </c>
-      <c r="G23" t="n">
-        <v>477</v>
-      </c>
-      <c r="H23" t="n">
-        <v>680403000</v>
-      </c>
-      <c r="I23" t="n">
-        <v>255</v>
-      </c>
-      <c r="J23" t="n">
-        <v>371197000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>29</v>
-      </c>
       <c r="L23" t="n">
-        <v>45795000</v>
+        <v>396000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.73</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,44 +1856,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>6500000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>176817000</v>
+        <v>15470000</v>
       </c>
       <c r="I24" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>81796000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>8500000</v>
+        <v>15470000</v>
       </c>
       <c r="M24" t="n">
-        <v>4.81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,38 +1903,273 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Azher Alaa Yass .</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>240</v>
+      </c>
+      <c r="H25" t="n">
+        <v>288305360</v>
+      </c>
+      <c r="I25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J25" t="n">
+        <v>80935000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>68</v>
+      </c>
+      <c r="L25" t="n">
+        <v>56427360</v>
+      </c>
+      <c r="M25" t="n">
+        <v>19.57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Baydaa . Hameed Mizher -</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ibtihal Hamza  Hussain -</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>459</v>
+      </c>
+      <c r="H27" t="n">
+        <v>510601200</v>
+      </c>
+      <c r="I27" t="n">
+        <v>273</v>
+      </c>
+      <c r="J27" t="n">
+        <v>287272000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>86</v>
+      </c>
+      <c r="L27" t="n">
+        <v>104684200</v>
+      </c>
+      <c r="M27" t="n">
+        <v>120.04</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>45200000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>490</v>
+      </c>
+      <c r="H28" t="n">
+        <v>687201000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>153</v>
+      </c>
+      <c r="J28" t="n">
+        <v>218886000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>48633000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>134</v>
+      </c>
+      <c r="H29" t="n">
+        <v>175786000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>23</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29519000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>23</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14044000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>126</v>
-      </c>
-      <c r="H25" t="n">
-        <v>66795000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>42</v>
-      </c>
-      <c r="J25" t="n">
-        <v>17935000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>84</v>
-      </c>
-      <c r="L25" t="n">
-        <v>48860000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>73.15000000000001</v>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>147</v>
+      </c>
+      <c r="H30" t="n">
+        <v>76498600</v>
+      </c>
+      <c r="I30" t="n">
+        <v>39</v>
+      </c>
+      <c r="J30" t="n">
+        <v>15935000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>105</v>
+      </c>
+      <c r="L30" t="n">
+        <v>59063600</v>
+      </c>
+      <c r="M30" t="n">
+        <v>77.20999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +2225,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88919000</v>
+        <v>131219000</v>
       </c>
     </row>
     <row r="3">
@@ -2010,7 +2245,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71365000</v>
+        <v>210414000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2265,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>245362400</v>
+        <v>335245310</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2285,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69897500</v>
+        <v>87253500</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2305,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>418449500</v>
+        <v>442924500</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2325,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>167704330</v>
+        <v>228974270</v>
       </c>
     </row>
   </sheetData>
@@ -2201,10 +2436,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>86400000</v>
+        <v>128700000</v>
       </c>
       <c r="L2" t="n">
-        <v>431100000</v>
+        <v>488190000</v>
       </c>
     </row>
     <row r="3">
@@ -2239,10 +2474,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>61000000</v>
+        <v>151750000</v>
       </c>
       <c r="L3" t="n">
-        <v>269537000</v>
+        <v>322297000</v>
       </c>
     </row>
     <row r="4">
@@ -2280,7 +2515,7 @@
         <v>35500000</v>
       </c>
       <c r="L4" t="n">
-        <v>535056000</v>
+        <v>620751000</v>
       </c>
     </row>
     <row r="5">
@@ -2315,10 +2550,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>73800000</v>
+        <v>84600000</v>
       </c>
       <c r="L5" t="n">
-        <v>413199001</v>
+        <v>459209001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>620751000</v>
+        <v>607211000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>488190000</v>
+        <v>470348000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>459209001</v>
+        <v>448129001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>322297000</v>
+        <v>312302000</v>
       </c>
     </row>
   </sheetData>
@@ -635,55 +635,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>151750000</v>
+        <v>170700000</v>
       </c>
       <c r="D2" t="n">
-        <v>1952</v>
+        <v>2293</v>
       </c>
       <c r="E2" t="n">
-        <v>2249404160</v>
+        <v>2984716000</v>
       </c>
       <c r="F2" t="n">
-        <v>299774160</v>
+        <v>373896000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>128700000</v>
+        <v>160150000</v>
       </c>
       <c r="D3" t="n">
-        <v>2383</v>
+        <v>1862</v>
       </c>
       <c r="E3" t="n">
-        <v>3049889720</v>
+        <v>2180308000</v>
       </c>
       <c r="F3" t="n">
-        <v>509223040</v>
+        <v>238542000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,19 +695,19 @@
         <v>84600000</v>
       </c>
       <c r="D4" t="n">
-        <v>2081</v>
+        <v>1960</v>
       </c>
       <c r="E4" t="n">
-        <v>2348335440.32</v>
+        <v>2265670000</v>
       </c>
       <c r="F4" t="n">
-        <v>381365120.32</v>
+        <v>383871000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>35500000</v>
       </c>
       <c r="D5" t="n">
-        <v>2489</v>
+        <v>2408</v>
       </c>
       <c r="E5" t="n">
-        <v>2796446560.6</v>
+        <v>2712636000</v>
       </c>
       <c r="F5" t="n">
-        <v>560432560.6</v>
+        <v>506987000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,31 +835,31 @@
         <v>8000000</v>
       </c>
       <c r="G2" t="n">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H2" t="n">
-        <v>491703160</v>
+        <v>478489000</v>
       </c>
       <c r="I2" t="n">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="J2" t="n">
-        <v>156217000</v>
+        <v>104879000</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>5139160</v>
+        <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,44 +869,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hussein . Kadhum Dhahi -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>361605000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>57611000</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>178811000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3200000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H4" t="n">
-        <v>369848520</v>
+        <v>320044000</v>
       </c>
       <c r="I4" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="J4" t="n">
-        <v>75166000</v>
+        <v>95621000</v>
       </c>
       <c r="K4" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>184864520</v>
+        <v>145695000</v>
       </c>
       <c r="M4" t="n">
-        <v>49.98</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,44 +963,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G5" t="n">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="H5" t="n">
-        <v>356554480.6</v>
+        <v>694589000</v>
       </c>
       <c r="I5" t="n">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="J5" t="n">
-        <v>103033000</v>
+        <v>164743000</v>
       </c>
       <c r="K5" t="n">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>180555480.6</v>
+        <v>24975000</v>
       </c>
       <c r="M5" t="n">
-        <v>50.64</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>9000000</v>
+        <v>7200000</v>
       </c>
       <c r="G6" t="n">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="H6" t="n">
-        <v>705780600</v>
+        <v>347892000</v>
       </c>
       <c r="I6" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="J6" t="n">
-        <v>215625000</v>
+        <v>101079000</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="L6" t="n">
-        <v>28116600</v>
+        <v>104106000</v>
       </c>
       <c r="M6" t="n">
-        <v>3.98</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1067,81 +1067,81 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>7200000</v>
+        <v>8100000</v>
       </c>
       <c r="G7" t="n">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="H7" t="n">
-        <v>351722000</v>
+        <v>510017000</v>
       </c>
       <c r="I7" t="n">
-        <v>155</v>
+        <v>269</v>
       </c>
       <c r="J7" t="n">
-        <v>114714000</v>
+        <v>270546000</v>
       </c>
       <c r="K7" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>106166000</v>
+        <v>52700000</v>
       </c>
       <c r="M7" t="n">
-        <v>30.18</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>8100000</v>
+        <v>3600000</v>
       </c>
       <c r="G8" t="n">
-        <v>485</v>
+        <v>362</v>
       </c>
       <c r="H8" t="n">
-        <v>520837800</v>
+        <v>327894000</v>
       </c>
       <c r="I8" t="n">
-        <v>310</v>
+        <v>114</v>
       </c>
       <c r="J8" t="n">
-        <v>320491000</v>
+        <v>94016000</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="L8" t="n">
-        <v>55590800</v>
+        <v>133835000</v>
       </c>
       <c r="M8" t="n">
-        <v>10.67</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>362</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>329274000</v>
+        <v>47980000</v>
       </c>
       <c r="I9" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>102236000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>133835000</v>
+        <v>47980000</v>
       </c>
       <c r="M9" t="n">
-        <v>40.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,31 +1211,31 @@
         <v>55800000</v>
       </c>
       <c r="G10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="H10" t="n">
-        <v>577650200</v>
+        <v>568250000</v>
       </c>
       <c r="I10" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="J10" t="n">
-        <v>149155000</v>
+        <v>123035000</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>7260200</v>
+        <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,28 +1261,28 @@
         <v>467</v>
       </c>
       <c r="H11" t="n">
-        <v>726783000</v>
+        <v>717773000</v>
       </c>
       <c r="I11" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="J11" t="n">
-        <v>210127000</v>
+        <v>162722000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>28225000</v>
+        <v>28025000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1305,31 +1305,31 @@
         <v>3600000</v>
       </c>
       <c r="G12" t="n">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="H12" t="n">
-        <v>325946120.32</v>
+        <v>302860000</v>
       </c>
       <c r="I12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J12" t="n">
-        <v>45964000</v>
+        <v>31440000</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>85490120.31999999</v>
+        <v>64504000</v>
       </c>
       <c r="M12" t="n">
-        <v>26.23</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1352,31 +1352,31 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>322220800</v>
+        <v>300913000</v>
       </c>
       <c r="I13" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="J13" t="n">
-        <v>137801000</v>
+        <v>120710000</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>126554800</v>
+        <v>107527000</v>
       </c>
       <c r="M13" t="n">
-        <v>39.28</v>
+        <v>35.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>16200000</v>
       </c>
       <c r="G14" t="n">
-        <v>571</v>
+        <v>536</v>
       </c>
       <c r="H14" t="n">
-        <v>722125400</v>
+        <v>693216000</v>
       </c>
       <c r="I14" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J14" t="n">
-        <v>221838000</v>
+        <v>200872000</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>85060400</v>
+        <v>59426000</v>
       </c>
       <c r="M14" t="n">
-        <v>11.78</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1446,31 +1446,31 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="H15" t="n">
-        <v>66461320</v>
+        <v>427062000</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>90562000</v>
       </c>
       <c r="K15" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>66461320</v>
+        <v>87180000</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9600000</v>
       </c>
       <c r="G16" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="H16" t="n">
-        <v>444061440</v>
+        <v>366022000</v>
       </c>
       <c r="I16" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="J16" t="n">
-        <v>107092000</v>
+        <v>38015000</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="L16" t="n">
-        <v>101029440</v>
+        <v>125500000</v>
       </c>
       <c r="M16" t="n">
-        <v>22.75</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>110700000</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>872460000</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>372955000</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>37850000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,76 +1574,76 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>9600000</v>
+        <v>34200000</v>
       </c>
       <c r="G18" t="n">
-        <v>361</v>
+        <v>554</v>
       </c>
       <c r="H18" t="n">
-        <v>396023880</v>
+        <v>625956000</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="J18" t="n">
-        <v>58460000</v>
+        <v>164368000</v>
       </c>
       <c r="K18" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>151911880</v>
+        <v>63940000</v>
       </c>
       <c r="M18" t="n">
-        <v>38.36</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>80050000</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>485165000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>117668000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,101 +1658,101 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>78900000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>587</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>854484000</v>
+        <v>12500000</v>
       </c>
       <c r="I20" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>407310000</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>37850000</v>
+        <v>12500000</v>
       </c>
       <c r="M20" t="n">
-        <v>4.43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>24000000</v>
+        <v>20000000</v>
       </c>
       <c r="G21" t="n">
-        <v>560</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
-        <v>633195000</v>
+        <v>279648000</v>
       </c>
       <c r="I21" t="n">
-        <v>198</v>
+        <v>46</v>
       </c>
       <c r="J21" t="n">
-        <v>236588000</v>
+        <v>75126000</v>
       </c>
       <c r="K21" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>66910000</v>
+        <v>49170000</v>
       </c>
       <c r="M21" t="n">
-        <v>10.57</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ahmed . Hassan Yusif -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1775,31 +1775,31 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>479634000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>287272000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>73717000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>80050000</v>
+        <v>53600000</v>
       </c>
       <c r="G23" t="n">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="H23" t="n">
-        <v>494486000</v>
+        <v>687724000</v>
       </c>
       <c r="I23" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="J23" t="n">
-        <v>185674000</v>
+        <v>187495000</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>396000</v>
+        <v>45795000</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,44 +1856,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6500000</v>
       </c>
       <c r="G24" t="n">
+        <v>122</v>
+      </c>
+      <c r="H24" t="n">
+        <v>169342000</v>
+      </c>
+      <c r="I24" t="n">
         <v>17</v>
       </c>
-      <c r="H24" t="n">
-        <v>15470000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>24944000</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>15470000</v>
+        <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,273 +1903,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="H25" t="n">
-        <v>288305360</v>
+        <v>66295000</v>
       </c>
       <c r="I25" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J25" t="n">
-        <v>80935000</v>
+        <v>15935000</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="L25" t="n">
-        <v>56427360</v>
+        <v>48860000</v>
       </c>
       <c r="M25" t="n">
-        <v>19.57</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Baydaa . Hameed Mizher -</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="M26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ibtihal Hamza  Hussain -</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>459</v>
-      </c>
-      <c r="H27" t="n">
-        <v>510601200</v>
-      </c>
-      <c r="I27" t="n">
-        <v>273</v>
-      </c>
-      <c r="J27" t="n">
-        <v>287272000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>86</v>
-      </c>
-      <c r="L27" t="n">
-        <v>104684200</v>
-      </c>
-      <c r="M27" t="n">
-        <v>120.04</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jawnaa . Radhi Shimran -</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>26</v>
-      </c>
-      <c r="F28" t="n">
-        <v>45200000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>490</v>
-      </c>
-      <c r="H28" t="n">
-        <v>687201000</v>
-      </c>
-      <c r="I28" t="n">
-        <v>153</v>
-      </c>
-      <c r="J28" t="n">
-        <v>218886000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>32</v>
-      </c>
-      <c r="L28" t="n">
-        <v>48633000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7.08</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>134</v>
-      </c>
-      <c r="H29" t="n">
-        <v>175786000</v>
-      </c>
-      <c r="I29" t="n">
-        <v>23</v>
-      </c>
-      <c r="J29" t="n">
-        <v>29519000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>23</v>
-      </c>
-      <c r="L29" t="n">
-        <v>14044000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>147</v>
-      </c>
-      <c r="H30" t="n">
-        <v>76498600</v>
-      </c>
-      <c r="I30" t="n">
-        <v>39</v>
-      </c>
-      <c r="J30" t="n">
-        <v>15935000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>105</v>
-      </c>
-      <c r="L30" t="n">
-        <v>59063600</v>
-      </c>
-      <c r="M30" t="n">
-        <v>77.20999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
   </sheetData>
@@ -2436,10 +2201,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>128700000</v>
+        <v>170700000</v>
       </c>
       <c r="L2" t="n">
-        <v>488190000</v>
+        <v>470348000</v>
       </c>
     </row>
     <row r="3">
@@ -2474,10 +2239,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>151750000</v>
+        <v>160150000</v>
       </c>
       <c r="L3" t="n">
-        <v>322297000</v>
+        <v>312302000</v>
       </c>
     </row>
     <row r="4">
@@ -2515,7 +2280,7 @@
         <v>35500000</v>
       </c>
       <c r="L4" t="n">
-        <v>620751000</v>
+        <v>607211000</v>
       </c>
     </row>
     <row r="5">
@@ -2553,7 +2318,7 @@
         <v>84600000</v>
       </c>
       <c r="L5" t="n">
-        <v>459209001</v>
+        <v>448129001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>607211000</v>
+        <v>520086000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>470348000</v>
+        <v>406728000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>448129001</v>
+        <v>395689001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>312302000</v>
+        <v>241542000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>170700000</v>
+        <v>214200000</v>
       </c>
       <c r="D2" t="n">
-        <v>2293</v>
+        <v>2280</v>
       </c>
       <c r="E2" t="n">
-        <v>2984716000</v>
+        <v>2942223000</v>
       </c>
       <c r="F2" t="n">
-        <v>373896000</v>
+        <v>371256000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>160150000</v>
+        <v>209350000</v>
       </c>
       <c r="D3" t="n">
-        <v>1862</v>
+        <v>1843</v>
       </c>
       <c r="E3" t="n">
-        <v>2180308000</v>
+        <v>2133530000</v>
       </c>
       <c r="F3" t="n">
-        <v>238542000</v>
+        <v>232342000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84600000</v>
+        <v>114300000</v>
       </c>
       <c r="D4" t="n">
-        <v>1960</v>
+        <v>1952</v>
       </c>
       <c r="E4" t="n">
-        <v>2265670000</v>
+        <v>2230570000</v>
       </c>
       <c r="F4" t="n">
-        <v>383871000</v>
+        <v>379121000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>35500000</v>
       </c>
       <c r="D5" t="n">
-        <v>2408</v>
+        <v>2382</v>
       </c>
       <c r="E5" t="n">
-        <v>2712636000</v>
+        <v>2615186000</v>
       </c>
       <c r="F5" t="n">
-        <v>506987000</v>
+        <v>503437000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,16 +835,16 @@
         <v>8000000</v>
       </c>
       <c r="G2" t="n">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H2" t="n">
-        <v>478489000</v>
+        <v>458564000</v>
       </c>
       <c r="I2" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>104879000</v>
+        <v>6402000</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -882,31 +882,31 @@
         <v>3200000</v>
       </c>
       <c r="G3" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H3" t="n">
-        <v>361605000</v>
+        <v>362760000</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>57611000</v>
+        <v>10842000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>178811000</v>
+        <v>178361000</v>
       </c>
       <c r="M3" t="n">
-        <v>49.45</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="H4" t="n">
-        <v>320044000</v>
+        <v>301484000</v>
       </c>
       <c r="I4" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="J4" t="n">
-        <v>95621000</v>
+        <v>43018000</v>
       </c>
       <c r="K4" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L4" t="n">
-        <v>145695000</v>
+        <v>143095000</v>
       </c>
       <c r="M4" t="n">
-        <v>45.52</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,31 +976,31 @@
         <v>9000000</v>
       </c>
       <c r="G5" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H5" t="n">
-        <v>694589000</v>
+        <v>667829000</v>
       </c>
       <c r="I5" t="n">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="J5" t="n">
-        <v>164743000</v>
+        <v>19374000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>24975000</v>
+        <v>24475000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1023,16 +1023,16 @@
         <v>7200000</v>
       </c>
       <c r="G6" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="H6" t="n">
-        <v>347892000</v>
+        <v>335537000</v>
       </c>
       <c r="I6" t="n">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="J6" t="n">
-        <v>101079000</v>
+        <v>35540000</v>
       </c>
       <c r="K6" t="n">
         <v>129</v>
@@ -1041,13 +1041,13 @@
         <v>104106000</v>
       </c>
       <c r="M6" t="n">
-        <v>29.92</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,16 +1070,16 @@
         <v>8100000</v>
       </c>
       <c r="G7" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H7" t="n">
-        <v>510017000</v>
+        <v>489012000</v>
       </c>
       <c r="I7" t="n">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="J7" t="n">
-        <v>270546000</v>
+        <v>134632000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>52700000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.33</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1117,31 +1117,31 @@
         <v>3600000</v>
       </c>
       <c r="G8" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="H8" t="n">
-        <v>327894000</v>
+        <v>318624000</v>
       </c>
       <c r="I8" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J8" t="n">
-        <v>94016000</v>
+        <v>49257000</v>
       </c>
       <c r="K8" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L8" t="n">
-        <v>133835000</v>
+        <v>129935000</v>
       </c>
       <c r="M8" t="n">
-        <v>40.82</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>55800000</v>
+        <v>77400000</v>
       </c>
       <c r="G10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="H10" t="n">
-        <v>568250000</v>
+        <v>569350000</v>
       </c>
       <c r="I10" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>123035000</v>
+        <v>27285000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>21600000</v>
+        <v>26100000</v>
       </c>
       <c r="G11" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H11" t="n">
-        <v>717773000</v>
+        <v>699998000</v>
       </c>
       <c r="I11" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>162722000</v>
+        <v>27950000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>28025000</v>
+        <v>27675000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>3600000</v>
+        <v>7200000</v>
       </c>
       <c r="G12" t="n">
         <v>260</v>
       </c>
       <c r="H12" t="n">
-        <v>302860000</v>
+        <v>301200000</v>
       </c>
       <c r="I12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>31440000</v>
+        <v>2610000</v>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>64504000</v>
+        <v>64004000</v>
       </c>
       <c r="M12" t="n">
-        <v>21.3</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>365</v>
       </c>
       <c r="H13" t="n">
-        <v>300913000</v>
+        <v>293418000</v>
       </c>
       <c r="I13" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="J13" t="n">
-        <v>120710000</v>
+        <v>81035000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>107527000</v>
       </c>
       <c r="M13" t="n">
-        <v>35.73</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>16200000</v>
+        <v>27000000</v>
       </c>
       <c r="G14" t="n">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H14" t="n">
-        <v>693216000</v>
+        <v>681038000</v>
       </c>
       <c r="I14" t="n">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="J14" t="n">
-        <v>200872000</v>
+        <v>76702000</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L14" t="n">
-        <v>59426000</v>
+        <v>57386000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.57</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,31 +1446,31 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="H15" t="n">
-        <v>427062000</v>
+        <v>420372000</v>
       </c>
       <c r="I15" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="J15" t="n">
-        <v>90562000</v>
+        <v>60260000</v>
       </c>
       <c r="K15" t="n">
         <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>87180000</v>
+        <v>86930000</v>
       </c>
       <c r="M15" t="n">
-        <v>20.41</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,13 +1496,13 @@
         <v>325</v>
       </c>
       <c r="H16" t="n">
-        <v>366022000</v>
+        <v>363962000</v>
       </c>
       <c r="I16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>38015000</v>
+        <v>20755000</v>
       </c>
       <c r="K16" t="n">
         <v>112</v>
@@ -1511,13 +1511,13 @@
         <v>125500000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.29</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>110700000</v>
+        <v>143400000</v>
       </c>
       <c r="G17" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H17" t="n">
-        <v>872460000</v>
+        <v>872430000</v>
       </c>
       <c r="I17" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="J17" t="n">
-        <v>372955000</v>
+        <v>214979000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>37850000</v>
+        <v>37500000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1587,16 +1587,16 @@
         <v>34200000</v>
       </c>
       <c r="G18" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H18" t="n">
-        <v>625956000</v>
+        <v>604421000</v>
       </c>
       <c r="I18" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>164368000</v>
+        <v>36685000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
@@ -1605,13 +1605,13 @@
         <v>63940000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.21</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>80050000</v>
       </c>
       <c r="G19" t="n">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="H19" t="n">
-        <v>485165000</v>
+        <v>464875000</v>
       </c>
       <c r="I19" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>117668000</v>
+        <v>4851000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,16 +1728,16 @@
         <v>20000000</v>
       </c>
       <c r="G21" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H21" t="n">
-        <v>279648000</v>
+        <v>270173000</v>
       </c>
       <c r="I21" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>75126000</v>
+        <v>11518000</v>
       </c>
       <c r="K21" t="n">
         <v>54</v>
@@ -1746,13 +1746,13 @@
         <v>49170000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.58</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,25 +1766,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="G22" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H22" t="n">
-        <v>479634000</v>
+        <v>456136000</v>
       </c>
       <c r="I22" t="n">
-        <v>273</v>
+        <v>131</v>
       </c>
       <c r="J22" t="n">
-        <v>287272000</v>
+        <v>96009000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1793,13 +1793,13 @@
         <v>73717000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.37</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
-        <v>53600000</v>
+        <v>83300000</v>
       </c>
       <c r="G23" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="H23" t="n">
-        <v>687724000</v>
+        <v>691369000</v>
       </c>
       <c r="I23" t="n">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="J23" t="n">
-        <v>187495000</v>
+        <v>64361000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,13 +1840,13 @@
         <v>45795000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>6500000</v>
+        <v>20000000</v>
       </c>
       <c r="G24" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H24" t="n">
-        <v>169342000</v>
+        <v>178292000</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>24944000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,13 +1887,13 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.02</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H25" t="n">
-        <v>66295000</v>
+        <v>60185000</v>
       </c>
       <c r="I25" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>15935000</v>
+        <v>9500000</v>
       </c>
       <c r="K25" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
-        <v>48860000</v>
+        <v>42660000</v>
       </c>
       <c r="M25" t="n">
-        <v>73.7</v>
+        <v>70.88</v>
       </c>
     </row>
   </sheetData>
@@ -2201,10 +2201,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>170700000</v>
+        <v>214200000</v>
       </c>
       <c r="L2" t="n">
-        <v>470348000</v>
+        <v>406728000</v>
       </c>
     </row>
     <row r="3">
@@ -2239,10 +2239,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>160150000</v>
+        <v>209350000</v>
       </c>
       <c r="L3" t="n">
-        <v>312302000</v>
+        <v>241542000</v>
       </c>
     </row>
     <row r="4">
@@ -2280,7 +2280,7 @@
         <v>35500000</v>
       </c>
       <c r="L4" t="n">
-        <v>607211000</v>
+        <v>520086000</v>
       </c>
     </row>
     <row r="5">
@@ -2315,10 +2315,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>84600000</v>
+        <v>114300000</v>
       </c>
       <c r="L5" t="n">
-        <v>448129001</v>
+        <v>395689001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>520086000</v>
+        <v>510466000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>406728000</v>
+        <v>390923000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>395689001</v>
+        <v>389254001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>241542000</v>
+        <v>237232000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,52 +526,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>66600000</v>
+        <v>151400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>49400000</v>
+        <v>134890000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>48300000</v>
+        <v>107900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>32700000</v>
+        <v>93860000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>214200000</v>
+        <v>297600000</v>
       </c>
       <c r="D2" t="n">
-        <v>2280</v>
+        <v>2387</v>
       </c>
       <c r="E2" t="n">
-        <v>2942223000</v>
+        <v>3366119720</v>
       </c>
       <c r="F2" t="n">
-        <v>371256000</v>
+        <v>506503040</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>209350000</v>
+        <v>265250000</v>
       </c>
       <c r="D3" t="n">
-        <v>1843</v>
+        <v>1945</v>
       </c>
       <c r="E3" t="n">
-        <v>2133530000</v>
+        <v>2462454160</v>
       </c>
       <c r="F3" t="n">
-        <v>232342000</v>
+        <v>296014160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114300000</v>
+        <v>166500000</v>
       </c>
       <c r="D4" t="n">
-        <v>1952</v>
+        <v>2089</v>
       </c>
       <c r="E4" t="n">
-        <v>2230570000</v>
+        <v>2555134440.32</v>
       </c>
       <c r="F4" t="n">
-        <v>379121000</v>
+        <v>377398120.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35500000</v>
+        <v>119800000</v>
       </c>
       <c r="D5" t="n">
-        <v>2382</v>
+        <v>2482</v>
       </c>
       <c r="E5" t="n">
-        <v>2615186000</v>
+        <v>2988990080.6</v>
       </c>
       <c r="F5" t="n">
-        <v>503437000</v>
+        <v>555562080.6</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,40 +826,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>8000000</v>
+        <v>17600000</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H2" t="n">
-        <v>458564000</v>
+        <v>526154680</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>6402000</v>
+        <v>5625000</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>700000</v>
+        <v>4889680</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,44 +869,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Hussein . Kadhum Dhahi -</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3200000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>362760000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10842000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>178361000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>49.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>16400000</v>
       </c>
       <c r="G4" t="n">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="H4" t="n">
-        <v>301484000</v>
+        <v>402542520</v>
       </c>
       <c r="I4" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>43018000</v>
+        <v>12565000</v>
       </c>
       <c r="K4" t="n">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>143095000</v>
+        <v>183464520</v>
       </c>
       <c r="M4" t="n">
-        <v>47.46</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,44 +963,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="H5" t="n">
-        <v>667829000</v>
+        <v>350530480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J5" t="n">
-        <v>19374000</v>
+        <v>26200000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="L5" t="n">
-        <v>24475000</v>
+        <v>177930480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.66</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>7200000</v>
+        <v>38400000</v>
       </c>
       <c r="G6" t="n">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="H6" t="n">
-        <v>335537000</v>
+        <v>777056600</v>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>35540000</v>
+        <v>9450000</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>104106000</v>
+        <v>27616600</v>
       </c>
       <c r="M6" t="n">
-        <v>31.03</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1057,91 +1057,91 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>8100000</v>
+        <v>18000000</v>
       </c>
       <c r="G7" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H7" t="n">
-        <v>489012000</v>
+        <v>373410000</v>
       </c>
       <c r="I7" t="n">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="J7" t="n">
-        <v>134632000</v>
+        <v>29950000</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="L7" t="n">
-        <v>52700000</v>
+        <v>106070000</v>
       </c>
       <c r="M7" t="n">
-        <v>10.78</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>3600000</v>
+        <v>29400000</v>
       </c>
       <c r="G8" t="n">
-        <v>356</v>
+        <v>484</v>
       </c>
       <c r="H8" t="n">
-        <v>318624000</v>
+        <v>559295800</v>
       </c>
       <c r="I8" t="n">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J8" t="n">
-        <v>49257000</v>
+        <v>146090000</v>
       </c>
       <c r="K8" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>129935000</v>
+        <v>55590800</v>
       </c>
       <c r="M8" t="n">
-        <v>40.78</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>356</v>
       </c>
       <c r="H9" t="n">
-        <v>47980000</v>
+        <v>340615000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>49405000</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="L9" t="n">
-        <v>47980000</v>
+        <v>128935000</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>92700000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>456</v>
+      </c>
+      <c r="H10" t="n">
+        <v>654885200</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18550000</v>
+      </c>
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="E10" t="n">
-        <v>29</v>
-      </c>
-      <c r="F10" t="n">
-        <v>77400000</v>
-      </c>
-      <c r="G10" t="n">
-        <v>445</v>
-      </c>
-      <c r="H10" t="n">
-        <v>569350000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>17</v>
-      </c>
-      <c r="J10" t="n">
-        <v>27285000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
       <c r="L10" t="n">
-        <v>2000000</v>
+        <v>7260200</v>
       </c>
       <c r="M10" t="n">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>26100000</v>
+        <v>45000000</v>
       </c>
       <c r="G11" t="n">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>699998000</v>
+        <v>792370000</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>27950000</v>
+        <v>14450000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>27675000</v>
+        <v>28875000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>7200000</v>
+        <v>16200000</v>
       </c>
       <c r="G12" t="n">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="H12" t="n">
-        <v>301200000</v>
+        <v>360625120.32</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2610000</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="L12" t="n">
-        <v>64004000</v>
+        <v>84990120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>21.25</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G13" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>293418000</v>
+        <v>340177800</v>
       </c>
       <c r="I13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>81035000</v>
+        <v>88475000</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>107527000</v>
+        <v>127337800</v>
       </c>
       <c r="M13" t="n">
-        <v>36.65</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>27000000</v>
+        <v>45900000</v>
       </c>
       <c r="G14" t="n">
-        <v>534</v>
+        <v>578</v>
       </c>
       <c r="H14" t="n">
-        <v>681038000</v>
+        <v>788071400</v>
       </c>
       <c r="I14" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J14" t="n">
-        <v>76702000</v>
+        <v>61961000</v>
       </c>
       <c r="K14" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>57386000</v>
+        <v>83020400</v>
       </c>
       <c r="M14" t="n">
-        <v>8.43</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1446,31 +1446,31 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>283</v>
+        <v>92</v>
       </c>
       <c r="H15" t="n">
-        <v>420372000</v>
+        <v>66461320</v>
       </c>
       <c r="I15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>60260000</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="L15" t="n">
-        <v>86930000</v>
+        <v>66461320</v>
       </c>
       <c r="M15" t="n">
-        <v>20.68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>9600000</v>
+        <v>36000000</v>
       </c>
       <c r="G16" t="n">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="H16" t="n">
-        <v>363962000</v>
+        <v>501639440</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J16" t="n">
-        <v>20755000</v>
+        <v>53100000</v>
       </c>
       <c r="K16" t="n">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="L16" t="n">
-        <v>125500000</v>
+        <v>101299440</v>
       </c>
       <c r="M16" t="n">
-        <v>34.48</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>143400000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>872430000</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>214979000</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>37500000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,76 +1574,76 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="n">
-        <v>14</v>
-      </c>
       <c r="F18" t="n">
-        <v>34200000</v>
+        <v>14100000</v>
       </c>
       <c r="G18" t="n">
-        <v>551</v>
+        <v>364</v>
       </c>
       <c r="H18" t="n">
-        <v>604421000</v>
+        <v>423241880</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>36685000</v>
+        <v>21365000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="L18" t="n">
-        <v>63940000</v>
+        <v>151311880</v>
       </c>
       <c r="M18" t="n">
-        <v>10.58</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Nadhir . Mohammad Kadhom -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>80050000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>464875000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4851000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,101 +1658,101 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>147900000</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>587</v>
       </c>
       <c r="H20" t="n">
-        <v>12500000</v>
+        <v>968647000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>203746000</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>12500000</v>
+        <v>37500000</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>20000000</v>
+        <v>53700000</v>
       </c>
       <c r="G21" t="n">
-        <v>217</v>
+        <v>563</v>
       </c>
       <c r="H21" t="n">
-        <v>270173000</v>
+        <v>684520000</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>11518000</v>
+        <v>30850000</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>49170000</v>
+        <v>66910000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.2</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1762,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Ahmed . Hassan Yusif -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>456136000</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>96009000</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>73717000</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>16.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>83300000</v>
+        <v>80050000</v>
       </c>
       <c r="G23" t="n">
-        <v>502</v>
+        <v>446</v>
       </c>
       <c r="H23" t="n">
-        <v>691369000</v>
+        <v>517526000</v>
       </c>
       <c r="I23" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>64361000</v>
+        <v>3150000</v>
       </c>
       <c r="K23" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>45795000</v>
+        <v>396000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.62</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,23 +1856,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>178292000</v>
+        <v>15470000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1881,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>8500000</v>
+        <v>15470000</v>
       </c>
       <c r="M24" t="n">
-        <v>4.77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,38 +1903,273 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Azher Alaa Yass .</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>239</v>
+      </c>
+      <c r="H25" t="n">
+        <v>331127360</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>68</v>
+      </c>
+      <c r="L25" t="n">
+        <v>56427360</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Baydaa . Hameed Mizher -</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ibtihal Hamza  Hussain -</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20400000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>458</v>
+      </c>
+      <c r="H27" t="n">
+        <v>544369200</v>
+      </c>
+      <c r="I27" t="n">
+        <v>128</v>
+      </c>
+      <c r="J27" t="n">
+        <v>103780000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>86</v>
+      </c>
+      <c r="L27" t="n">
+        <v>106344200</v>
+      </c>
+      <c r="M27" t="n">
+        <v>119.09</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" t="n">
+        <v>44</v>
+      </c>
+      <c r="F28" t="n">
+        <v>83300000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>502</v>
+      </c>
+      <c r="H28" t="n">
+        <v>769648000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>63150000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>49413000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>149</v>
+      </c>
+      <c r="H29" t="n">
+        <v>213169000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>23</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14044000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>115</v>
-      </c>
-      <c r="H25" t="n">
-        <v>60185000</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>133</v>
+      </c>
+      <c r="H30" t="n">
+        <v>70088600</v>
+      </c>
+      <c r="I30" t="n">
         <v>20</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J30" t="n">
         <v>9500000</v>
       </c>
-      <c r="K25" t="n">
-        <v>79</v>
-      </c>
-      <c r="L25" t="n">
-        <v>42660000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>70.88</v>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" t="n">
+        <v>52863600</v>
+      </c>
+      <c r="M30" t="n">
+        <v>75.42</v>
       </c>
     </row>
   </sheetData>
@@ -2201,10 +2436,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>214200000</v>
+        <v>297600000</v>
       </c>
       <c r="L2" t="n">
-        <v>406728000</v>
+        <v>390923000</v>
       </c>
     </row>
     <row r="3">
@@ -2239,10 +2474,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>209350000</v>
+        <v>265250000</v>
       </c>
       <c r="L3" t="n">
-        <v>241542000</v>
+        <v>237232000</v>
       </c>
     </row>
     <row r="4">
@@ -2277,10 +2512,10 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>35500000</v>
+        <v>119800000</v>
       </c>
       <c r="L4" t="n">
-        <v>520086000</v>
+        <v>510466000</v>
       </c>
     </row>
     <row r="5">
@@ -2315,10 +2550,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>114300000</v>
+        <v>166500000</v>
       </c>
       <c r="L5" t="n">
-        <v>395689001</v>
+        <v>389254001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>510466000</v>
+        <v>504266000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>390923000</v>
+        <v>382474001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>389254001</v>
+        <v>372934000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>237232000</v>
+        <v>235232000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,52 +526,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>151400000</v>
+        <v>95500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>134890000</v>
+        <v>86300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>107900000</v>
+        <v>72100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>93860000</v>
+        <v>51200000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>297600000</v>
+        <v>408100000</v>
       </c>
       <c r="D2" t="n">
-        <v>2387</v>
+        <v>2402</v>
       </c>
       <c r="E2" t="n">
-        <v>3366119720</v>
+        <v>3446880720</v>
       </c>
       <c r="F2" t="n">
-        <v>506503040</v>
+        <v>506403040</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,64 +668,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>265250000</v>
+        <v>309350000</v>
       </c>
       <c r="D3" t="n">
-        <v>1945</v>
+        <v>1967</v>
       </c>
       <c r="E3" t="n">
-        <v>2462454160</v>
+        <v>2499779160</v>
       </c>
       <c r="F3" t="n">
-        <v>296014160</v>
+        <v>295714160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>166500000</v>
+        <v>236390000</v>
       </c>
       <c r="D4" t="n">
-        <v>2089</v>
+        <v>2521</v>
       </c>
       <c r="E4" t="n">
-        <v>2555134440.32</v>
+        <v>3095310080.6</v>
       </c>
       <c r="F4" t="n">
-        <v>377398120.32</v>
+        <v>552962080.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>119800000</v>
+        <v>224460000</v>
       </c>
       <c r="D5" t="n">
-        <v>2482</v>
+        <v>2102</v>
       </c>
       <c r="E5" t="n">
-        <v>2988990080.6</v>
+        <v>2603564440.32</v>
       </c>
       <c r="F5" t="n">
-        <v>555562080.6</v>
+        <v>377048120.32</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>17600000</v>
+        <v>25240000</v>
       </c>
       <c r="G2" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>526154680</v>
+        <v>533249680</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>5625000</v>
+        <v>4500000</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
@@ -853,13 +853,13 @@
         <v>4889680</v>
       </c>
       <c r="M2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,25 +920,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>16400000</v>
+        <v>37400000</v>
       </c>
       <c r="G4" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H4" t="n">
-        <v>402542520</v>
+        <v>422767520</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>12565000</v>
+        <v>10440000</v>
       </c>
       <c r="K4" t="n">
         <v>200</v>
@@ -947,13 +947,13 @@
         <v>183464520</v>
       </c>
       <c r="M4" t="n">
-        <v>45.58</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H5" t="n">
-        <v>350530480.6</v>
+        <v>347930480.6</v>
       </c>
       <c r="I5" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>26200000</v>
+        <v>20300000</v>
       </c>
       <c r="K5" t="n">
         <v>142</v>
@@ -994,13 +994,13 @@
         <v>177930480.6</v>
       </c>
       <c r="M5" t="n">
-        <v>50.76</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>38400000</v>
+        <v>72900000</v>
       </c>
       <c r="G6" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="H6" t="n">
-        <v>777056600</v>
+        <v>808206600</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>9450000</v>
+        <v>10050000</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>27616600</v>
+        <v>25466600</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>18000000</v>
+        <v>43200000</v>
       </c>
       <c r="G7" t="n">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="H7" t="n">
-        <v>373410000</v>
+        <v>397110000</v>
       </c>
       <c r="I7" t="n">
         <v>40</v>
@@ -1088,13 +1088,13 @@
         <v>106070000</v>
       </c>
       <c r="M7" t="n">
-        <v>28.41</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>29400000</v>
+        <v>57650000</v>
       </c>
       <c r="G8" t="n">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="H8" t="n">
-        <v>559295800</v>
+        <v>586045800</v>
       </c>
       <c r="I8" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J8" t="n">
-        <v>146090000</v>
+        <v>143690000</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>55590800</v>
+        <v>55140800</v>
       </c>
       <c r="M8" t="n">
-        <v>9.94</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>3600000</v>
+        <v>9600000</v>
       </c>
       <c r="G9" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H9" t="n">
-        <v>340615000</v>
+        <v>343485000</v>
       </c>
       <c r="I9" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="J9" t="n">
-        <v>49405000</v>
+        <v>40305000</v>
       </c>
       <c r="K9" t="n">
         <v>156</v>
@@ -1182,13 +1182,13 @@
         <v>128935000</v>
       </c>
       <c r="M9" t="n">
-        <v>37.85</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,13 +1214,13 @@
         <v>456</v>
       </c>
       <c r="H10" t="n">
-        <v>654885200</v>
+        <v>653435200</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>18550000</v>
+        <v>4050000</v>
       </c>
       <c r="K10" t="n">
         <v>12</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>45000000</v>
+        <v>78060000</v>
       </c>
       <c r="G11" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H11" t="n">
-        <v>792370000</v>
+        <v>821580000</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>14450000</v>
+        <v>13950000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>28875000</v>
+        <v>28725000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>16200000</v>
+        <v>23400000</v>
       </c>
       <c r="G12" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H12" t="n">
-        <v>360625120.32</v>
+        <v>367625120.32</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1320,16 +1320,16 @@
         <v>108</v>
       </c>
       <c r="L12" t="n">
-        <v>84990120.31999999</v>
+        <v>84790120.31999999</v>
       </c>
       <c r="M12" t="n">
-        <v>23.57</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>9000000</v>
+        <v>20700000</v>
       </c>
       <c r="G13" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="H13" t="n">
-        <v>340177800</v>
+        <v>350977800</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J13" t="n">
-        <v>88475000</v>
+        <v>81725000</v>
       </c>
       <c r="K13" t="n">
         <v>153</v>
@@ -1370,13 +1370,13 @@
         <v>127337800</v>
       </c>
       <c r="M13" t="n">
-        <v>37.43</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
-        <v>45900000</v>
+        <v>56500000</v>
       </c>
       <c r="G14" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H14" t="n">
-        <v>788071400</v>
+        <v>794637400</v>
       </c>
       <c r="I14" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J14" t="n">
-        <v>61961000</v>
+        <v>31675000</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L14" t="n">
-        <v>83020400</v>
+        <v>82920400</v>
       </c>
       <c r="M14" t="n">
-        <v>10.53</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>36000000</v>
+        <v>94800000</v>
       </c>
       <c r="G16" t="n">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="H16" t="n">
-        <v>501639440</v>
+        <v>556439440</v>
       </c>
       <c r="I16" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>53100000</v>
+        <v>37100000</v>
       </c>
       <c r="K16" t="n">
         <v>63</v>
@@ -1511,13 +1511,13 @@
         <v>101299440</v>
       </c>
       <c r="M16" t="n">
-        <v>20.19</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,13 +1590,13 @@
         <v>364</v>
       </c>
       <c r="H18" t="n">
-        <v>423241880</v>
+        <v>421211880</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>21365000</v>
+        <v>10565000</v>
       </c>
       <c r="K18" t="n">
         <v>148</v>
@@ -1605,13 +1605,13 @@
         <v>151311880</v>
       </c>
       <c r="M18" t="n">
-        <v>35.75</v>
+        <v>35.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>147900000</v>
+        <v>170400000</v>
       </c>
       <c r="G20" t="n">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="H20" t="n">
-        <v>968647000</v>
+        <v>972072000</v>
       </c>
       <c r="I20" t="n">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="J20" t="n">
-        <v>203746000</v>
+        <v>123121000</v>
       </c>
       <c r="K20" t="n">
         <v>42</v>
@@ -1699,13 +1699,13 @@
         <v>37500000</v>
       </c>
       <c r="M20" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,25 +1719,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>53700000</v>
+        <v>72300000</v>
       </c>
       <c r="G21" t="n">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="H21" t="n">
-        <v>684520000</v>
+        <v>702520000</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>30850000</v>
+        <v>30250000</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1746,13 +1746,13 @@
         <v>66910000</v>
       </c>
       <c r="M21" t="n">
-        <v>9.77</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,19 +1813,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>80050000</v>
+        <v>84550000</v>
       </c>
       <c r="G23" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H23" t="n">
-        <v>517526000</v>
+        <v>522026000</v>
       </c>
       <c r="I23" t="n">
         <v>6</v>
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1907,40 +1907,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>47000000</v>
+        <v>57000000</v>
       </c>
       <c r="G25" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H25" t="n">
-        <v>331127360</v>
+        <v>339727360</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>7800000</v>
+        <v>7000000</v>
       </c>
       <c r="K25" t="n">
         <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>56427360</v>
+        <v>56127360</v>
       </c>
       <c r="M25" t="n">
-        <v>17.04</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2001,19 +2001,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>20400000</v>
+        <v>33000000</v>
       </c>
       <c r="G27" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H27" t="n">
-        <v>544369200</v>
+        <v>553594200</v>
       </c>
       <c r="I27" t="n">
         <v>128</v>
@@ -2028,13 +2028,13 @@
         <v>106344200</v>
       </c>
       <c r="M27" t="n">
-        <v>119.09</v>
+        <v>118.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2060,13 +2060,13 @@
         <v>502</v>
       </c>
       <c r="H28" t="n">
-        <v>769648000</v>
+        <v>767648000</v>
       </c>
       <c r="I28" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J28" t="n">
-        <v>63150000</v>
+        <v>56400000</v>
       </c>
       <c r="K28" t="n">
         <v>32</v>
@@ -2075,13 +2075,13 @@
         <v>49413000</v>
       </c>
       <c r="M28" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>34500000</v>
+        <v>51500000</v>
       </c>
       <c r="G29" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="H29" t="n">
-        <v>213169000</v>
+        <v>230169000</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2122,13 +2122,13 @@
         <v>14044000</v>
       </c>
       <c r="M29" t="n">
-        <v>6.59</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2436,10 +2436,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>297600000</v>
+        <v>408100000</v>
       </c>
       <c r="L2" t="n">
-        <v>390923000</v>
+        <v>372934000</v>
       </c>
     </row>
     <row r="3">
@@ -2474,10 +2474,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>265250000</v>
+        <v>309350000</v>
       </c>
       <c r="L3" t="n">
-        <v>237232000</v>
+        <v>235232000</v>
       </c>
     </row>
     <row r="4">
@@ -2512,10 +2512,10 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>119800000</v>
+        <v>236390000</v>
       </c>
       <c r="L4" t="n">
-        <v>510466000</v>
+        <v>504266000</v>
       </c>
     </row>
     <row r="5">
@@ -2550,10 +2550,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>166500000</v>
+        <v>224460000</v>
       </c>
       <c r="L5" t="n">
-        <v>389254001</v>
+        <v>382474001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>504266000</v>
+        <v>500886000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>382474001</v>
+        <v>376699001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>372934000</v>
+        <v>357299000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>235232000</v>
+        <v>230007000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>95500000</v>
+        <v>71400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>86300000</v>
+        <v>40600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>72100000</v>
+        <v>32700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>51200000</v>
+        <v>20800000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,70 +644,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>408100000</v>
+        <v>485600000</v>
       </c>
       <c r="D2" t="n">
-        <v>2402</v>
+        <v>2235</v>
       </c>
       <c r="E2" t="n">
-        <v>3446880720</v>
+        <v>3479680000</v>
       </c>
       <c r="F2" t="n">
-        <v>506403040</v>
+        <v>200420000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>309350000</v>
+        <v>390100000</v>
       </c>
       <c r="D3" t="n">
-        <v>1967</v>
+        <v>2304</v>
       </c>
       <c r="E3" t="n">
-        <v>2499779160</v>
+        <v>3376440000</v>
       </c>
       <c r="F3" t="n">
-        <v>295714160</v>
+        <v>387535002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>236390000</v>
+        <v>353100000</v>
       </c>
       <c r="D4" t="n">
-        <v>2521</v>
+        <v>1719</v>
       </c>
       <c r="E4" t="n">
-        <v>3095310080.6</v>
+        <v>2382980000</v>
       </c>
       <c r="F4" t="n">
-        <v>552962080.6</v>
+        <v>152080000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>224460000</v>
+        <v>301050000</v>
       </c>
       <c r="D5" t="n">
-        <v>2102</v>
+        <v>1873</v>
       </c>
       <c r="E5" t="n">
-        <v>2603564440.32</v>
+        <v>2658220000</v>
       </c>
       <c r="F5" t="n">
-        <v>377048120.32</v>
+        <v>467260000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,40 +826,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>25240000</v>
+        <v>90200000</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="H2" t="n">
-        <v>533249680</v>
+        <v>595600000</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4500000</v>
+        <v>2600000</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4889680</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -869,44 +869,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hussein . Kadhum Dhahi -</t>
+          <t>Mohammed Rasool AbedAl Ameer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>71100000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>641235000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>33469998</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>182615002</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohammed Rasool AbedAl Ameer</t>
+          <t>Murtadha . Saeed Raheem -</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>37400000</v>
+        <v>64700000</v>
       </c>
       <c r="G4" t="n">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="H4" t="n">
-        <v>422767520</v>
+        <v>476150000</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>10440000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>62</v>
       </c>
       <c r="L4" t="n">
-        <v>183464520</v>
+        <v>102400000</v>
       </c>
       <c r="M4" t="n">
-        <v>43.4</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -963,44 +963,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murtadha . Saeed Raheem -</t>
+          <t>Sanaa . Jawad Hasan -</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>78600000</v>
       </c>
       <c r="G5" t="n">
-        <v>353</v>
+        <v>437</v>
       </c>
       <c r="H5" t="n">
-        <v>347930480.6</v>
+        <v>840400000</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>20300000</v>
+        <v>6000000</v>
       </c>
       <c r="K5" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>177930480.6</v>
+        <v>3575000</v>
       </c>
       <c r="M5" t="n">
-        <v>51.14</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sanaa . Jawad Hasan -</t>
+          <t>Tariq .Abdul Reda Mohammed</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>72900000</v>
+        <v>6000000</v>
       </c>
       <c r="G6" t="n">
-        <v>436</v>
+        <v>230</v>
       </c>
       <c r="H6" t="n">
-        <v>808206600</v>
+        <v>165865000</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>10050000</v>
+        <v>8665000</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="L6" t="n">
-        <v>25466600</v>
+        <v>92195000</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1057,91 +1057,91 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tariq .Abdul Reda Mohammed</t>
+          <t>Thamir  . Musa Shimran -</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>43200000</v>
+        <v>79500000</v>
       </c>
       <c r="G7" t="n">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
-        <v>397110000</v>
+        <v>657190000</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>29950000</v>
+        <v>10800000</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>106070000</v>
+        <v>6750000</v>
       </c>
       <c r="M7" t="n">
-        <v>26.71</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thamir  . Musa Shimran -</t>
+          <t>Assad  . Kareem Otewi -</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>57650000</v>
+        <v>25200000</v>
       </c>
       <c r="G8" t="n">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="H8" t="n">
-        <v>586045800</v>
+        <v>549330000</v>
       </c>
       <c r="I8" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>143690000</v>
+        <v>44090000</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="L8" t="n">
-        <v>55140800</v>
+        <v>144125000</v>
       </c>
       <c r="M8" t="n">
-        <v>9.41</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assad  . Kareem Otewi -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9600000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>62</v>
       </c>
       <c r="H9" t="n">
-        <v>343485000</v>
+        <v>53380000</v>
       </c>
       <c r="I9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>40305000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="L9" t="n">
-        <v>128935000</v>
+        <v>53380000</v>
       </c>
       <c r="M9" t="n">
-        <v>37.54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>92700000</v>
+        <v>130200000</v>
       </c>
       <c r="G10" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H10" t="n">
-        <v>653435200</v>
+        <v>670520000</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4050000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7260200</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>78060000</v>
+        <v>139050000</v>
       </c>
       <c r="G11" t="n">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="H11" t="n">
-        <v>821580000</v>
+        <v>811970000</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>13950000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>28725000</v>
+        <v>8775000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>23400000</v>
+        <v>6600000</v>
       </c>
       <c r="G12" t="n">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="H12" t="n">
-        <v>367625120.32</v>
+        <v>386200000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>6450000</v>
       </c>
       <c r="K12" t="n">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="L12" t="n">
-        <v>84790120.31999999</v>
+        <v>115310000</v>
       </c>
       <c r="M12" t="n">
-        <v>23.06</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>165</v>
+      </c>
+      <c r="H13" t="n">
+        <v>186820000</v>
+      </c>
+      <c r="I13" t="n">
         <v>15</v>
       </c>
-      <c r="F13" t="n">
-        <v>20700000</v>
-      </c>
-      <c r="G13" t="n">
-        <v>404</v>
-      </c>
-      <c r="H13" t="n">
-        <v>350977800</v>
-      </c>
-      <c r="I13" t="n">
-        <v>90</v>
-      </c>
       <c r="J13" t="n">
-        <v>81725000</v>
+        <v>8125000</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="L13" t="n">
-        <v>127337800</v>
+        <v>145670000</v>
       </c>
       <c r="M13" t="n">
-        <v>36.28</v>
+        <v>77.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>56500000</v>
+        <v>104700000</v>
       </c>
       <c r="G14" t="n">
-        <v>579</v>
+        <v>480</v>
       </c>
       <c r="H14" t="n">
-        <v>794637400</v>
+        <v>760200000</v>
       </c>
       <c r="I14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>31675000</v>
+        <v>15400000</v>
       </c>
       <c r="K14" t="n">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>82920400</v>
+        <v>40875000</v>
       </c>
       <c r="M14" t="n">
-        <v>10.43</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>105600000</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>325</v>
       </c>
       <c r="H15" t="n">
-        <v>66461320</v>
+        <v>618075000</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>14500000</v>
       </c>
       <c r="K15" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>66461320</v>
+        <v>38300000</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>94800000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>308</v>
+        <v>31</v>
       </c>
       <c r="H16" t="n">
-        <v>556439440</v>
+        <v>29400000</v>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>37100000</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="L16" t="n">
-        <v>101299440</v>
+        <v>17050000</v>
       </c>
       <c r="M16" t="n">
-        <v>18.2</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>26300000</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>311995000</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>6445000</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>40070000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,44 +1574,44 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>14100000</v>
+        <v>128700000</v>
       </c>
       <c r="G18" t="n">
-        <v>364</v>
+        <v>521</v>
       </c>
       <c r="H18" t="n">
-        <v>421211880</v>
+        <v>865950000</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>10565000</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="L18" t="n">
-        <v>151311880</v>
+        <v>30675000</v>
       </c>
       <c r="M18" t="n">
-        <v>35.92</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1621,23 +1621,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nadhir . Mohammad Kadhom -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>120300000</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>763930000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1646,113 +1646,113 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>33450000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>170400000</v>
+        <v>54800000</v>
       </c>
       <c r="G20" t="n">
-        <v>579</v>
+        <v>384</v>
       </c>
       <c r="H20" t="n">
-        <v>972072000</v>
+        <v>490995000</v>
       </c>
       <c r="I20" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>123121000</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>37500000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>72300000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>572</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>702520000</v>
+        <v>14400000</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30250000</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>66910000</v>
+        <v>14400000</v>
       </c>
       <c r="M21" t="n">
-        <v>9.52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1762,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ahmed . Hassan Yusif -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>37500000</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>355620000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2520000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>34650000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>84550000</v>
+        <v>87600000</v>
       </c>
       <c r="G23" t="n">
-        <v>449</v>
+        <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>522026000</v>
+        <v>467280000</v>
       </c>
       <c r="I23" t="n">
         <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3150000</v>
+        <v>4500000</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="L23" t="n">
-        <v>396000</v>
+        <v>50930000</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,44 +1856,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>102600000</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>460</v>
       </c>
       <c r="H24" t="n">
-        <v>15470000</v>
+        <v>742045000</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
-        <v>15470000</v>
+        <v>41550000</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,44 +1903,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>57000000</v>
+        <v>9600000</v>
       </c>
       <c r="G25" t="n">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="H25" t="n">
-        <v>339727360</v>
+        <v>37850000</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>68</v>
-      </c>
       <c r="L25" t="n">
-        <v>56127360</v>
+        <v>8950000</v>
       </c>
       <c r="M25" t="n">
-        <v>16.52</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1950,226 +1950,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baydaa . Hameed Mizher -</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>61000000</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H26" t="n">
-        <v>1056000</v>
+        <v>274790000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>1056000</v>
+        <v>1600000</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ibtihal Hamza  Hussain -</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="G27" t="n">
-        <v>463</v>
-      </c>
-      <c r="H27" t="n">
-        <v>553594200</v>
-      </c>
-      <c r="I27" t="n">
-        <v>128</v>
-      </c>
-      <c r="J27" t="n">
-        <v>103780000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>86</v>
-      </c>
-      <c r="L27" t="n">
-        <v>106344200</v>
-      </c>
-      <c r="M27" t="n">
-        <v>118.77</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jawnaa . Radhi Shimran -</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>44</v>
-      </c>
-      <c r="F28" t="n">
-        <v>83300000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>502</v>
-      </c>
-      <c r="H28" t="n">
-        <v>767648000</v>
-      </c>
-      <c r="I28" t="n">
-        <v>36</v>
-      </c>
-      <c r="J28" t="n">
-        <v>56400000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>32</v>
-      </c>
-      <c r="L28" t="n">
-        <v>49413000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11</v>
-      </c>
-      <c r="E29" t="n">
-        <v>33</v>
-      </c>
-      <c r="F29" t="n">
-        <v>51500000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>161</v>
-      </c>
-      <c r="H29" t="n">
-        <v>230169000</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>23</v>
-      </c>
-      <c r="L29" t="n">
-        <v>14044000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>133</v>
-      </c>
-      <c r="H30" t="n">
-        <v>70088600</v>
-      </c>
-      <c r="I30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>100</v>
-      </c>
-      <c r="L30" t="n">
-        <v>52863600</v>
-      </c>
-      <c r="M30" t="n">
-        <v>75.42</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -2436,10 +2248,10 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>408100000</v>
+        <v>485600000</v>
       </c>
       <c r="L2" t="n">
-        <v>372934000</v>
+        <v>357299000</v>
       </c>
     </row>
     <row r="3">
@@ -2474,10 +2286,10 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>309350000</v>
+        <v>353100000</v>
       </c>
       <c r="L3" t="n">
-        <v>235232000</v>
+        <v>230007000</v>
       </c>
     </row>
     <row r="4">
@@ -2512,10 +2324,10 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>236390000</v>
+        <v>390100000</v>
       </c>
       <c r="L4" t="n">
-        <v>504266000</v>
+        <v>500886000</v>
       </c>
     </row>
     <row r="5">
@@ -2550,10 +2362,10 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>224460000</v>
+        <v>301050000</v>
       </c>
       <c r="L5" t="n">
-        <v>382474001</v>
+        <v>376699001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>485600000</v>
+        <v>488300000</v>
       </c>
       <c r="D2" t="n">
-        <v>2235</v>
+        <v>2342</v>
       </c>
       <c r="E2" t="n">
-        <v>3479680000</v>
+        <v>3401507000</v>
       </c>
       <c r="F2" t="n">
-        <v>200420000</v>
+        <v>361676000</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>390100000</v>
+        <v>389090000</v>
       </c>
       <c r="D3" t="n">
-        <v>2304</v>
+        <v>2482</v>
       </c>
       <c r="E3" t="n">
-        <v>3376440000</v>
+        <v>3167449000</v>
       </c>
       <c r="F3" t="n">
-        <v>387535002</v>
+        <v>495071000</v>
       </c>
     </row>
     <row r="4">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>353100000</v>
+        <v>369250000</v>
       </c>
       <c r="D4" t="n">
-        <v>1719</v>
+        <v>1885</v>
       </c>
       <c r="E4" t="n">
-        <v>2382980000</v>
+        <v>2464972000</v>
       </c>
       <c r="F4" t="n">
-        <v>152080000</v>
+        <v>230682000</v>
       </c>
     </row>
     <row r="5">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>301050000</v>
+        <v>305360000</v>
       </c>
       <c r="D5" t="n">
-        <v>1873</v>
+        <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>2658220000</v>
+        <v>2599644000</v>
       </c>
       <c r="F5" t="n">
-        <v>467260000</v>
+        <v>376854000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,34 +826,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>90200000</v>
+        <v>62940000</v>
       </c>
       <c r="G2" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="H2" t="n">
-        <v>595600000</v>
+        <v>561310000</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>2600000</v>
+        <v>3150000</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>71100000</v>
+        <v>61100000</v>
       </c>
       <c r="G3" t="n">
-        <v>450</v>
+        <v>365</v>
       </c>
       <c r="H3" t="n">
-        <v>641235000</v>
+        <v>439704000</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>33469998</v>
+        <v>7200000</v>
       </c>
       <c r="K3" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="L3" t="n">
-        <v>182615002</v>
+        <v>177061000</v>
       </c>
       <c r="M3" t="n">
-        <v>28.48</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="4">
@@ -920,34 +920,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>64700000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H4" t="n">
-        <v>476150000</v>
+        <v>309710000</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>20930000</v>
       </c>
       <c r="K4" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>102400000</v>
+        <v>140370000</v>
       </c>
       <c r="M4" t="n">
-        <v>21.51</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="5">
@@ -967,34 +967,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>78600000</v>
+        <v>132900000</v>
       </c>
       <c r="G5" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="H5" t="n">
-        <v>840400000</v>
+        <v>849665000</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>6000000</v>
+        <v>8550000</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>3575000</v>
+        <v>21825000</v>
       </c>
       <c r="M5" t="n">
-        <v>0.43</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="6">
@@ -1014,34 +1014,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>6000000</v>
+        <v>63700000</v>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>483</v>
       </c>
       <c r="H6" t="n">
-        <v>165865000</v>
+        <v>413105000</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" t="n">
-        <v>8665000</v>
+        <v>21150000</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>92195000</v>
+        <v>102865000</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="7">
@@ -1061,34 +1061,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>79500000</v>
+        <v>68450000</v>
       </c>
       <c r="G7" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H7" t="n">
-        <v>657190000</v>
+        <v>593955000</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
       <c r="J7" t="n">
-        <v>10800000</v>
+        <v>143690000</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>6750000</v>
+        <v>52250000</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>25200000</v>
+        <v>21800000</v>
       </c>
       <c r="G8" t="n">
-        <v>454</v>
+        <v>347</v>
       </c>
       <c r="H8" t="n">
-        <v>549330000</v>
+        <v>347530000</v>
       </c>
       <c r="I8" t="n">
         <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>44090000</v>
+        <v>18040000</v>
       </c>
       <c r="K8" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L8" t="n">
-        <v>144125000</v>
+        <v>126435000</v>
       </c>
       <c r="M8" t="n">
-        <v>26.24</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="9">
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>53380000</v>
+        <v>47980000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>53380000</v>
+        <v>47980000</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>130200000</v>
+        <v>92700000</v>
       </c>
       <c r="G10" t="n">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="H10" t="n">
-        <v>670520000</v>
+        <v>646485000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1223,13 +1223,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="11">
@@ -1249,34 +1249,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>139050000</v>
+        <v>98460000</v>
       </c>
       <c r="G11" t="n">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="H11" t="n">
-        <v>811970000</v>
+        <v>836405000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4200000</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>8775000</v>
+        <v>28725000</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="12">
@@ -1296,34 +1296,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>6600000</v>
+        <v>25800000</v>
       </c>
       <c r="G12" t="n">
         <v>273</v>
       </c>
       <c r="H12" t="n">
-        <v>386200000</v>
+        <v>347004000</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>6450000</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>115310000</v>
+        <v>63404000</v>
       </c>
       <c r="M12" t="n">
-        <v>29.86</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="13">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>66600000</v>
       </c>
       <c r="G13" t="n">
-        <v>165</v>
+        <v>398</v>
       </c>
       <c r="H13" t="n">
-        <v>186820000</v>
+        <v>374240000</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
-        <v>8125000</v>
+        <v>59585000</v>
       </c>
       <c r="K13" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>145670000</v>
+        <v>108310000</v>
       </c>
       <c r="M13" t="n">
-        <v>77.97</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="14">
@@ -1396,28 +1396,28 @@
         <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>104700000</v>
+        <v>65500000</v>
       </c>
       <c r="G14" t="n">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="H14" t="n">
-        <v>760200000</v>
+        <v>763628000</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>15400000</v>
+        <v>20825000</v>
       </c>
       <c r="K14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L14" t="n">
-        <v>40875000</v>
+        <v>52036000</v>
       </c>
       <c r="M14" t="n">
-        <v>5.38</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="15">
@@ -1440,31 +1440,31 @@
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>105600000</v>
+        <v>112200000</v>
       </c>
       <c r="G15" t="n">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="H15" t="n">
-        <v>618075000</v>
+        <v>551315000</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>14500000</v>
+        <v>18500000</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>38300000</v>
+        <v>84000000</v>
       </c>
       <c r="M15" t="n">
-        <v>6.2</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="16">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>29400000</v>
       </c>
       <c r="G16" t="n">
-        <v>31</v>
+        <v>334</v>
       </c>
       <c r="H16" t="n">
-        <v>29400000</v>
+        <v>408340000</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>8405000</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="L16" t="n">
-        <v>17050000</v>
+        <v>124200000</v>
       </c>
       <c r="M16" t="n">
-        <v>57.99</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="17">
@@ -1527,38 +1527,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>26300000</v>
+        <v>201900000</v>
       </c>
       <c r="G17" t="n">
-        <v>245</v>
+        <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>311995000</v>
+        <v>977024000</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>6445000</v>
+        <v>18385000</v>
       </c>
       <c r="K17" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>40070000</v>
+        <v>37500000</v>
       </c>
       <c r="M17" t="n">
-        <v>12.84</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="18">
@@ -1574,38 +1574,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>128700000</v>
+        <v>79300000</v>
       </c>
       <c r="G18" t="n">
-        <v>521</v>
+        <v>570</v>
       </c>
       <c r="H18" t="n">
-        <v>865950000</v>
+        <v>701200000</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>9600000</v>
       </c>
       <c r="K18" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>30675000</v>
+        <v>63940000</v>
       </c>
       <c r="M18" t="n">
-        <v>3.54</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1616,28 +1616,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
-        <v>120300000</v>
+        <v>84550000</v>
       </c>
       <c r="G19" t="n">
-        <v>531</v>
+        <v>443</v>
       </c>
       <c r="H19" t="n">
-        <v>763930000</v>
+        <v>519280000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1646,13 +1646,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>33450000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1668,23 +1668,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>54800000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>490995000</v>
+        <v>12500000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1693,13 +1693,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>12500000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1715,38 +1715,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>65900000</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>232</v>
       </c>
       <c r="H21" t="n">
-        <v>14400000</v>
+        <v>341370000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>14400000</v>
+        <v>48870000</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="22">
@@ -1762,38 +1762,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>37500000</v>
+        <v>62700000</v>
       </c>
       <c r="G22" t="n">
-        <v>265</v>
+        <v>441</v>
       </c>
       <c r="H22" t="n">
-        <v>355620000</v>
+        <v>537877000</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="J22" t="n">
-        <v>2520000</v>
+        <v>49200000</v>
       </c>
       <c r="K22" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="L22" t="n">
-        <v>34650000</v>
+        <v>73377000</v>
       </c>
       <c r="M22" t="n">
-        <v>9.74</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="23">
@@ -1809,38 +1809,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>87600000</v>
+        <v>91100000</v>
       </c>
       <c r="G23" t="n">
-        <v>350</v>
+        <v>493</v>
       </c>
       <c r="H23" t="n">
-        <v>467280000</v>
+        <v>758885000</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>4500000</v>
+        <v>26500000</v>
       </c>
       <c r="K23" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>50930000</v>
+        <v>46575000</v>
       </c>
       <c r="M23" t="n">
-        <v>10.9</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="24">
@@ -1856,38 +1856,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
-        <v>102600000</v>
+        <v>65000000</v>
       </c>
       <c r="G24" t="n">
-        <v>460</v>
+        <v>161</v>
       </c>
       <c r="H24" t="n">
-        <v>742045000</v>
+        <v>237675000</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>41550000</v>
+        <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="25">
@@ -1903,85 +1903,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>9600000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="H25" t="n">
-        <v>37850000</v>
+        <v>57385000</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>7050000</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>8950000</v>
+        <v>40860000</v>
       </c>
       <c r="M25" t="n">
-        <v>23.65</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
-        <v>36</v>
-      </c>
-      <c r="F26" t="n">
-        <v>61000000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>237</v>
-      </c>
-      <c r="H26" t="n">
-        <v>274790000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.58</v>
+        <v>71.2</v>
       </c>
     </row>
   </sheetData>
@@ -2248,7 +2201,7 @@
         <v>327656000</v>
       </c>
       <c r="K2" t="n">
-        <v>485600000</v>
+        <v>488300000</v>
       </c>
       <c r="L2" t="n">
         <v>357299000</v>
@@ -2286,7 +2239,7 @@
         <v>192417000</v>
       </c>
       <c r="K3" t="n">
-        <v>353100000</v>
+        <v>369250000</v>
       </c>
       <c r="L3" t="n">
         <v>230007000</v>
@@ -2324,7 +2277,7 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>390100000</v>
+        <v>389090000</v>
       </c>
       <c r="L4" t="n">
         <v>500886000</v>
@@ -2362,7 +2315,7 @@
         <v>356554001</v>
       </c>
       <c r="K5" t="n">
-        <v>301050000</v>
+        <v>305360000</v>
       </c>
       <c r="L5" t="n">
         <v>376699001</v>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500886000</v>
+        <v>494096000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>376699001</v>
+        <v>364444001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>357299000</v>
+        <v>335441000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>230007000</v>
+        <v>215107000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,52 +526,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>71400000</v>
+        <v>72400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>40600000</v>
+        <v>29700000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>32700000</v>
+        <v>27800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>20800000</v>
+        <v>18150000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -647,19 +647,19 @@
         <v>488300000</v>
       </c>
       <c r="D2" t="n">
-        <v>2342</v>
+        <v>2337</v>
       </c>
       <c r="E2" t="n">
-        <v>3401507000</v>
+        <v>3393647000</v>
       </c>
       <c r="F2" t="n">
-        <v>361676000</v>
+        <v>356076000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>389090000</v>
+        <v>392690000</v>
       </c>
       <c r="D3" t="n">
-        <v>2482</v>
+        <v>2475</v>
       </c>
       <c r="E3" t="n">
-        <v>3167449000</v>
+        <v>3163339000</v>
       </c>
       <c r="F3" t="n">
-        <v>495071000</v>
+        <v>492671000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>1885</v>
       </c>
       <c r="E4" t="n">
-        <v>2464972000</v>
+        <v>2461972000</v>
       </c>
       <c r="F4" t="n">
         <v>230682000</v>
@@ -707,7 +707,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>2010</v>
       </c>
       <c r="E5" t="n">
-        <v>2599644000</v>
+        <v>2591319000</v>
       </c>
       <c r="F5" t="n">
-        <v>376854000</v>
+        <v>376429000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H4" t="n">
-        <v>309710000</v>
+        <v>306225000</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>20930000</v>
+        <v>13195000</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L4" t="n">
-        <v>140370000</v>
+        <v>137970000</v>
       </c>
       <c r="M4" t="n">
-        <v>45.32</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,10 +976,10 @@
         <v>132900000</v>
       </c>
       <c r="G5" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H5" t="n">
-        <v>849665000</v>
+        <v>846640000</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -994,13 +994,13 @@
         <v>21825000</v>
       </c>
       <c r="M5" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1023,10 +1023,10 @@
         <v>63700000</v>
       </c>
       <c r="G6" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H6" t="n">
-        <v>413105000</v>
+        <v>412555000</v>
       </c>
       <c r="I6" t="n">
         <v>26</v>
@@ -1041,13 +1041,13 @@
         <v>102865000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.9</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>68450000</v>
+        <v>72050000</v>
       </c>
       <c r="G7" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="H7" t="n">
-        <v>593955000</v>
+        <v>596905000</v>
       </c>
       <c r="I7" t="n">
         <v>149</v>
@@ -1088,13 +1088,13 @@
         <v>52250000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>347</v>
       </c>
       <c r="H8" t="n">
-        <v>347530000</v>
+        <v>345440000</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>18040000</v>
+        <v>12630000</v>
       </c>
       <c r="K8" t="n">
         <v>154</v>
@@ -1135,13 +1135,13 @@
         <v>126435000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.38</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>446</v>
       </c>
       <c r="H10" t="n">
-        <v>646485000</v>
+        <v>644885000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,13 +1261,13 @@
         <v>490</v>
       </c>
       <c r="H11" t="n">
-        <v>836405000</v>
+        <v>835705000</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4200000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1276,13 +1276,13 @@
         <v>28725000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,7 +1308,7 @@
         <v>273</v>
       </c>
       <c r="H12" t="n">
-        <v>347004000</v>
+        <v>346579000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1320,16 +1320,16 @@
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>63404000</v>
+        <v>62979000</v>
       </c>
       <c r="M12" t="n">
-        <v>18.27</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>398</v>
       </c>
       <c r="H13" t="n">
-        <v>374240000</v>
+        <v>370730000</v>
       </c>
       <c r="I13" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="J13" t="n">
-        <v>59585000</v>
+        <v>40685000</v>
       </c>
       <c r="K13" t="n">
         <v>123</v>
@@ -1370,13 +1370,13 @@
         <v>108310000</v>
       </c>
       <c r="M13" t="n">
-        <v>28.94</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,16 +1399,16 @@
         <v>65500000</v>
       </c>
       <c r="G14" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H14" t="n">
-        <v>763628000</v>
+        <v>759178000</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>20825000</v>
+        <v>16625000</v>
       </c>
       <c r="K14" t="n">
         <v>55</v>
@@ -1417,13 +1417,13 @@
         <v>52036000</v>
       </c>
       <c r="M14" t="n">
-        <v>6.81</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,28 +1449,28 @@
         <v>306</v>
       </c>
       <c r="H15" t="n">
-        <v>551315000</v>
+        <v>550515000</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>18500000</v>
+        <v>23300000</v>
       </c>
       <c r="K15" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L15" t="n">
-        <v>84000000</v>
+        <v>78400000</v>
       </c>
       <c r="M15" t="n">
-        <v>15.24</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,16 +1493,16 @@
         <v>29400000</v>
       </c>
       <c r="G16" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H16" t="n">
-        <v>408340000</v>
+        <v>407530000</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>8405000</v>
+        <v>6875000</v>
       </c>
       <c r="K16" t="n">
         <v>112</v>
@@ -1511,13 +1511,13 @@
         <v>124200000</v>
       </c>
       <c r="M16" t="n">
-        <v>30.42</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1543,7 +1543,7 @@
         <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>977024000</v>
+        <v>976049000</v>
       </c>
       <c r="I17" t="n">
         <v>21</v>
@@ -1564,7 +1564,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,13 +1590,13 @@
         <v>570</v>
       </c>
       <c r="H18" t="n">
-        <v>701200000</v>
+        <v>700375000</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>9600000</v>
+        <v>6300000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
@@ -1605,13 +1605,13 @@
         <v>63940000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.119999999999999</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,7 +1825,7 @@
         <v>493</v>
       </c>
       <c r="H23" t="n">
-        <v>758885000</v>
+        <v>755885000</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
@@ -1840,13 +1840,13 @@
         <v>46575000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>488300000</v>
       </c>
       <c r="L2" t="n">
-        <v>357299000</v>
+        <v>335441000</v>
       </c>
     </row>
     <row r="3">
@@ -2242,7 +2242,7 @@
         <v>369250000</v>
       </c>
       <c r="L3" t="n">
-        <v>230007000</v>
+        <v>215107000</v>
       </c>
     </row>
     <row r="4">
@@ -2277,10 +2277,10 @@
         <v>457931000</v>
       </c>
       <c r="K4" t="n">
-        <v>389090000</v>
+        <v>392690000</v>
       </c>
       <c r="L4" t="n">
-        <v>500886000</v>
+        <v>494096000</v>
       </c>
     </row>
     <row r="5">
@@ -2318,7 +2318,7 @@
         <v>305360000</v>
       </c>
       <c r="L5" t="n">
-        <v>376699001</v>
+        <v>364444001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>131219000</v>
+        <v>81219000</v>
       </c>
     </row>
     <row r="3">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>210414000</v>
+        <v>118414000</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>335245310</v>
+        <v>263445310</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87253500</v>
+        <v>34263500</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>442924500</v>
+        <v>400924500</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>228974270</v>
+        <v>59496670</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>494096000</v>
+        <v>465066000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>364444001</v>
+        <v>361139001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>335441000</v>
+        <v>330166000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>215107000</v>
+        <v>203312000</v>
       </c>
     </row>
   </sheetData>
@@ -647,13 +647,13 @@
         <v>488300000</v>
       </c>
       <c r="D2" t="n">
-        <v>2337</v>
+        <v>2328</v>
       </c>
       <c r="E2" t="n">
-        <v>3393647000</v>
+        <v>3380722000</v>
       </c>
       <c r="F2" t="n">
-        <v>356076000</v>
+        <v>354401000</v>
       </c>
     </row>
     <row r="3">
@@ -671,13 +671,13 @@
         <v>392690000</v>
       </c>
       <c r="D3" t="n">
-        <v>2475</v>
+        <v>2454</v>
       </c>
       <c r="E3" t="n">
-        <v>3163339000</v>
+        <v>3130549000</v>
       </c>
       <c r="F3" t="n">
-        <v>492671000</v>
+        <v>491571000</v>
       </c>
     </row>
     <row r="4">
@@ -698,10 +698,10 @@
         <v>1885</v>
       </c>
       <c r="E4" t="n">
-        <v>2461972000</v>
+        <v>2446577000</v>
       </c>
       <c r="F4" t="n">
-        <v>230682000</v>
+        <v>223932000</v>
       </c>
     </row>
     <row r="5">
@@ -719,13 +719,13 @@
         <v>305360000</v>
       </c>
       <c r="D5" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>2591319000</v>
+        <v>2580054000</v>
       </c>
       <c r="F5" t="n">
-        <v>376429000</v>
+        <v>373729000</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +885,7 @@
         <v>365</v>
       </c>
       <c r="H3" t="n">
-        <v>439704000</v>
+        <v>438404000</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -900,7 +900,7 @@
         <v>177061000</v>
       </c>
       <c r="M3" t="n">
-        <v>40.27</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="4">
@@ -932,13 +932,13 @@
         <v>307</v>
       </c>
       <c r="H4" t="n">
-        <v>306225000</v>
+        <v>306000000</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>13195000</v>
+        <v>12970000</v>
       </c>
       <c r="K4" t="n">
         <v>98</v>
@@ -947,7 +947,7 @@
         <v>137970000</v>
       </c>
       <c r="M4" t="n">
-        <v>45.06</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="5">
@@ -979,22 +979,22 @@
         <v>424</v>
       </c>
       <c r="H5" t="n">
-        <v>846640000</v>
+        <v>845440000</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>8550000</v>
+        <v>7800000</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>21825000</v>
+        <v>21475000</v>
       </c>
       <c r="M5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="6">
@@ -1070,25 +1070,25 @@
         <v>72050000</v>
       </c>
       <c r="G7" t="n">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="H7" t="n">
-        <v>596905000</v>
+        <v>566840000</v>
       </c>
       <c r="I7" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>143690000</v>
+        <v>3600000</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>52250000</v>
+        <v>51500000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.75</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8">
@@ -1120,13 +1120,13 @@
         <v>347</v>
       </c>
       <c r="H8" t="n">
-        <v>345440000</v>
+        <v>343045000</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>12630000</v>
+        <v>5840000</v>
       </c>
       <c r="K8" t="n">
         <v>154</v>
@@ -1135,7 +1135,7 @@
         <v>126435000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.6</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="9">
@@ -1214,7 +1214,7 @@
         <v>446</v>
       </c>
       <c r="H10" t="n">
-        <v>644885000</v>
+        <v>643610000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>98460000</v>
       </c>
       <c r="G11" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H11" t="n">
-        <v>835705000</v>
+        <v>832755000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>28725000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12">
@@ -1308,7 +1308,7 @@
         <v>273</v>
       </c>
       <c r="H12" t="n">
-        <v>346579000</v>
+        <v>344104000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>62979000</v>
       </c>
       <c r="M12" t="n">
-        <v>18.17</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="13">
@@ -1355,22 +1355,22 @@
         <v>398</v>
       </c>
       <c r="H13" t="n">
-        <v>370730000</v>
+        <v>368560000</v>
       </c>
       <c r="I13" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J13" t="n">
-        <v>40685000</v>
+        <v>33295000</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L13" t="n">
-        <v>108310000</v>
+        <v>105610000</v>
       </c>
       <c r="M13" t="n">
-        <v>29.22</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="14">
@@ -1402,7 +1402,7 @@
         <v>548</v>
       </c>
       <c r="H14" t="n">
-        <v>759178000</v>
+        <v>757753000</v>
       </c>
       <c r="I14" t="n">
         <v>11</v>
@@ -1417,7 +1417,7 @@
         <v>52036000</v>
       </c>
       <c r="M14" t="n">
-        <v>6.85</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="15">
@@ -1446,25 +1446,25 @@
         <v>112200000</v>
       </c>
       <c r="G15" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>550515000</v>
+        <v>546240000</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>23300000</v>
+        <v>10700000</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L15" t="n">
-        <v>78400000</v>
+        <v>77075000</v>
       </c>
       <c r="M15" t="n">
-        <v>14.24</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="16">
@@ -1496,7 +1496,7 @@
         <v>331</v>
       </c>
       <c r="H16" t="n">
-        <v>407530000</v>
+        <v>407280000</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
@@ -1508,10 +1508,10 @@
         <v>112</v>
       </c>
       <c r="L16" t="n">
-        <v>124200000</v>
+        <v>123950000</v>
       </c>
       <c r="M16" t="n">
-        <v>30.48</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="17">
@@ -1543,13 +1543,13 @@
         <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>976049000</v>
+        <v>973499000</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>18385000</v>
+        <v>13435000</v>
       </c>
       <c r="K17" t="n">
         <v>42</v>
@@ -1558,7 +1558,7 @@
         <v>37500000</v>
       </c>
       <c r="M17" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="18">
@@ -1587,25 +1587,25 @@
         <v>79300000</v>
       </c>
       <c r="G18" t="n">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H18" t="n">
-        <v>700375000</v>
+        <v>695950000</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6300000</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>63940000</v>
+        <v>63840000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.130000000000001</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="19">
@@ -1731,7 +1731,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="n">
-        <v>341370000</v>
+        <v>340770000</v>
       </c>
       <c r="I21" t="n">
         <v>8</v>
@@ -1746,7 +1746,7 @@
         <v>48870000</v>
       </c>
       <c r="M21" t="n">
-        <v>14.32</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="22">
@@ -1778,22 +1778,22 @@
         <v>441</v>
       </c>
       <c r="H22" t="n">
-        <v>537877000</v>
+        <v>528382000</v>
       </c>
       <c r="I22" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>49200000</v>
+        <v>15460000</v>
       </c>
       <c r="K22" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L22" t="n">
-        <v>73377000</v>
+        <v>66627000</v>
       </c>
       <c r="M22" t="n">
-        <v>13.64</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="23">
@@ -1825,13 +1825,13 @@
         <v>493</v>
       </c>
       <c r="H23" t="n">
-        <v>755885000</v>
+        <v>750885000</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>26500000</v>
+        <v>11150000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
@@ -1840,7 +1840,7 @@
         <v>46575000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.16</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="24">
@@ -1872,7 +1872,7 @@
         <v>161</v>
       </c>
       <c r="H24" t="n">
-        <v>237675000</v>
+        <v>237375000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>488300000</v>
       </c>
       <c r="L2" t="n">
-        <v>335441000</v>
+        <v>330166000</v>
       </c>
     </row>
     <row r="3">
@@ -2242,7 +2242,7 @@
         <v>369250000</v>
       </c>
       <c r="L3" t="n">
-        <v>215107000</v>
+        <v>203312000</v>
       </c>
     </row>
     <row r="4">
@@ -2280,7 +2280,7 @@
         <v>392690000</v>
       </c>
       <c r="L4" t="n">
-        <v>494096000</v>
+        <v>465066000</v>
       </c>
     </row>
     <row r="5">
@@ -2318,7 +2318,7 @@
         <v>305360000</v>
       </c>
       <c r="L5" t="n">
-        <v>364444001</v>
+        <v>361139001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -441,21 +441,21 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>465066000</v>
+        <v>371990000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>361139001</v>
+        <v>306195000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>330166000</v>
+        <v>214750000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>203312000</v>
+        <v>120220000</v>
       </c>
     </row>
   </sheetData>
@@ -2204,7 +2204,7 @@
         <v>488300000</v>
       </c>
       <c r="L2" t="n">
-        <v>330166000</v>
+        <v>214750000</v>
       </c>
     </row>
     <row r="3">
@@ -2242,7 +2242,7 @@
         <v>369250000</v>
       </c>
       <c r="L3" t="n">
-        <v>203312000</v>
+        <v>120220000</v>
       </c>
     </row>
     <row r="4">
@@ -2280,7 +2280,7 @@
         <v>392690000</v>
       </c>
       <c r="L4" t="n">
-        <v>465066000</v>
+        <v>306195000</v>
       </c>
     </row>
     <row r="5">
@@ -2318,7 +2318,7 @@
         <v>305360000</v>
       </c>
       <c r="L5" t="n">
-        <v>361139001</v>
+        <v>371990000</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -441,21 +441,21 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>371990000</v>
+        <v>461506000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>306195000</v>
+        <v>358139001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>214750000</v>
+        <v>328441000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120220000</v>
+        <v>201892000</v>
       </c>
     </row>
   </sheetData>
@@ -2204,7 +2204,7 @@
         <v>488300000</v>
       </c>
       <c r="L2" t="n">
-        <v>214750000</v>
+        <v>328441000</v>
       </c>
     </row>
     <row r="3">
@@ -2242,7 +2242,7 @@
         <v>369250000</v>
       </c>
       <c r="L3" t="n">
-        <v>120220000</v>
+        <v>201892000</v>
       </c>
     </row>
     <row r="4">
@@ -2280,7 +2280,7 @@
         <v>392690000</v>
       </c>
       <c r="L4" t="n">
-        <v>306195000</v>
+        <v>461506000</v>
       </c>
     </row>
     <row r="5">
@@ -2318,7 +2318,7 @@
         <v>305360000</v>
       </c>
       <c r="L5" t="n">
-        <v>371990000</v>
+        <v>358139001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>461506000</v>
+        <v>623931000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>358139001</v>
+        <v>492152000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>328441000</v>
+        <v>438449001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>201892000</v>
+        <v>320942000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,34 +526,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>72400000</v>
+        <v>54300000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>29700000</v>
+        <v>42850000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,25 +565,25 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>27800000</v>
+        <v>39900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>18150000</v>
+        <v>16500000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,88 +644,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>488300000</v>
+        <v>133500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2328</v>
+        <v>2305</v>
       </c>
       <c r="E2" t="n">
-        <v>3380722000</v>
+        <v>3339093000</v>
       </c>
       <c r="F2" t="n">
-        <v>354401000</v>
+        <v>379136000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>392690000</v>
+        <v>127800000</v>
       </c>
       <c r="D3" t="n">
-        <v>2454</v>
+        <v>1906</v>
       </c>
       <c r="E3" t="n">
-        <v>3130549000</v>
+        <v>2424967000</v>
       </c>
       <c r="F3" t="n">
-        <v>491571000</v>
+        <v>236802000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>369250000</v>
+        <v>96600000</v>
       </c>
       <c r="D4" t="n">
-        <v>1885</v>
+        <v>2008</v>
       </c>
       <c r="E4" t="n">
-        <v>2446577000</v>
+        <v>2503187000</v>
       </c>
       <c r="F4" t="n">
-        <v>223932000</v>
+        <v>388164000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>305360000</v>
+        <v>43200000</v>
       </c>
       <c r="D5" t="n">
-        <v>2008</v>
+        <v>2439</v>
       </c>
       <c r="E5" t="n">
-        <v>2580054000</v>
+        <v>3029831000</v>
       </c>
       <c r="F5" t="n">
-        <v>373729000</v>
+        <v>516416000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,40 +826,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>62940000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="H2" t="n">
-        <v>561310000</v>
+        <v>520585000</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="J2" t="n">
-        <v>3150000</v>
+        <v>224400000</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>700000</v>
+        <v>300000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>61100000</v>
+        <v>19500000</v>
       </c>
       <c r="G3" t="n">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H3" t="n">
-        <v>438404000</v>
+        <v>447661000</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="J3" t="n">
-        <v>7200000</v>
+        <v>112320000</v>
       </c>
       <c r="K3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>177061000</v>
+        <v>179886000</v>
       </c>
       <c r="M3" t="n">
-        <v>40.39</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="H4" t="n">
-        <v>306000000</v>
+        <v>286580000</v>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="J4" t="n">
-        <v>12970000</v>
+        <v>86760000</v>
       </c>
       <c r="K4" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L4" t="n">
-        <v>137970000</v>
+        <v>143470000</v>
       </c>
       <c r="M4" t="n">
-        <v>45.09</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>132900000</v>
+        <v>6000000</v>
       </c>
       <c r="G5" t="n">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H5" t="n">
-        <v>845440000</v>
+        <v>801650000</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="J5" t="n">
-        <v>7800000</v>
+        <v>276315000</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>21475000</v>
+        <v>29275000</v>
       </c>
       <c r="M5" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>63700000</v>
+        <v>11400000</v>
       </c>
       <c r="G6" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H6" t="n">
-        <v>412555000</v>
+        <v>404045000</v>
       </c>
       <c r="I6" t="n">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="J6" t="n">
-        <v>21150000</v>
+        <v>129430000</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="L6" t="n">
-        <v>102865000</v>
+        <v>108385000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.93</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>72050000</v>
+        <v>6300000</v>
       </c>
       <c r="G7" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>566840000</v>
+        <v>569310000</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>360</v>
       </c>
       <c r="J7" t="n">
-        <v>3600000</v>
+        <v>395160000</v>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>51500000</v>
+        <v>55100000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.09</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>21800000</v>
+        <v>13500000</v>
       </c>
       <c r="G8" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H8" t="n">
-        <v>343045000</v>
+        <v>343423000</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="J8" t="n">
-        <v>5840000</v>
+        <v>117550000</v>
       </c>
       <c r="K8" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L8" t="n">
-        <v>126435000</v>
+        <v>125945000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.86</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H9" t="n">
-        <v>47980000</v>
+        <v>46130000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>47980000</v>
+        <v>46130000</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>92700000</v>
+        <v>57300000</v>
       </c>
       <c r="G10" t="n">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>643610000</v>
+        <v>645535000</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>216270000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>98460000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="H11" t="n">
-        <v>832755000</v>
+        <v>765830000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>239365000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1276,13 +1276,13 @@
         <v>28725000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
         <v>25800000</v>
       </c>
       <c r="G12" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="H12" t="n">
-        <v>344104000</v>
+        <v>346964000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>95630000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>62979000</v>
+        <v>62579000</v>
       </c>
       <c r="M12" t="n">
-        <v>18.3</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>66600000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>368560000</v>
+        <v>355305000</v>
       </c>
       <c r="I13" t="n">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="J13" t="n">
-        <v>33295000</v>
+        <v>128600000</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>105610000</v>
+        <v>122785000</v>
       </c>
       <c r="M13" t="n">
-        <v>28.65</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
-        <v>65500000</v>
+        <v>27300000</v>
       </c>
       <c r="G14" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="H14" t="n">
-        <v>757753000</v>
+        <v>739675000</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="J14" t="n">
-        <v>16625000</v>
+        <v>257467000</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L14" t="n">
-        <v>52036000</v>
+        <v>63861000</v>
       </c>
       <c r="M14" t="n">
-        <v>6.87</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>112200000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="H15" t="n">
-        <v>546240000</v>
+        <v>520840000</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="J15" t="n">
-        <v>10700000</v>
+        <v>158315000</v>
       </c>
       <c r="K15" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L15" t="n">
-        <v>77075000</v>
+        <v>84575000</v>
       </c>
       <c r="M15" t="n">
-        <v>14.11</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>29400000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="H16" t="n">
-        <v>407280000</v>
+        <v>382095000</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="J16" t="n">
-        <v>6875000</v>
+        <v>109000000</v>
       </c>
       <c r="K16" t="n">
         <v>112</v>
       </c>
       <c r="L16" t="n">
-        <v>123950000</v>
+        <v>122700000</v>
       </c>
       <c r="M16" t="n">
-        <v>30.43</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
-        <v>201900000</v>
+        <v>78600000</v>
       </c>
       <c r="G17" t="n">
         <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>973499000</v>
+        <v>1008995000</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>301</v>
       </c>
       <c r="J17" t="n">
-        <v>13435000</v>
+        <v>512428000</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L17" t="n">
-        <v>37500000</v>
+        <v>45160000</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>79300000</v>
+        <v>27600000</v>
       </c>
       <c r="G18" t="n">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="H18" t="n">
-        <v>695950000</v>
+        <v>687488000</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>315085000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>63840000</v>
+        <v>62840000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>84550000</v>
+        <v>54200000</v>
       </c>
       <c r="G19" t="n">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="H19" t="n">
-        <v>519280000</v>
+        <v>531755000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>222430000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>65900000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>232</v>
       </c>
       <c r="H21" t="n">
-        <v>340770000</v>
+        <v>325095000</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="J21" t="n">
-        <v>7000000</v>
+        <v>122050000</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L21" t="n">
-        <v>48870000</v>
+        <v>55870000</v>
       </c>
       <c r="M21" t="n">
-        <v>14.34</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>62700000</v>
+        <v>12500000</v>
       </c>
       <c r="G22" t="n">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="H22" t="n">
-        <v>528382000</v>
+        <v>516917000</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="J22" t="n">
-        <v>15460000</v>
+        <v>238185000</v>
       </c>
       <c r="K22" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L22" t="n">
-        <v>66627000</v>
+        <v>72247000</v>
       </c>
       <c r="M22" t="n">
-        <v>12.61</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1813,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>91100000</v>
+        <v>61100000</v>
       </c>
       <c r="G23" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="H23" t="n">
-        <v>750885000</v>
+        <v>761065000</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="J23" t="n">
-        <v>11150000</v>
+        <v>291470000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>46575000</v>
+        <v>46375000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>65000000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>161</v>
       </c>
       <c r="H24" t="n">
-        <v>237375000</v>
+        <v>223150000</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>81450000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,13 +1887,13 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H25" t="n">
-        <v>57385000</v>
+        <v>54485000</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>7050000</v>
+        <v>13175000</v>
       </c>
       <c r="K25" t="n">
         <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>40860000</v>
+        <v>41310000</v>
       </c>
       <c r="M25" t="n">
-        <v>71.2</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2104,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2160,10 +2160,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>صرف_2026-05</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-05</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>صرف_None</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>متأخر_None</t>
         </is>
@@ -2206,6 +2216,12 @@
       <c r="L2" t="n">
         <v>328441000</v>
       </c>
+      <c r="M2" t="n">
+        <v>133500000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>492152000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -2244,6 +2260,12 @@
       <c r="L3" t="n">
         <v>201892000</v>
       </c>
+      <c r="M3" t="n">
+        <v>127800000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>320942000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -2282,6 +2304,12 @@
       <c r="L4" t="n">
         <v>461506000</v>
       </c>
+      <c r="M4" t="n">
+        <v>43200000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>623931000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -2319,6 +2347,12 @@
       </c>
       <c r="L5" t="n">
         <v>358139001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>96600000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>438449001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>623931000</v>
+        <v>608301000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>492152000</v>
+        <v>467530000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>438449001</v>
+        <v>427579001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>320942000</v>
+        <v>273832000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>54300000</v>
+        <v>133450000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>42850000</v>
+        <v>83100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>39900000</v>
+        <v>76200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>16500000</v>
+        <v>24400000</v>
       </c>
     </row>
   </sheetData>
@@ -635,55 +635,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>133500000</v>
+        <v>177600000</v>
       </c>
       <c r="D2" t="n">
-        <v>2305</v>
+        <v>1894</v>
       </c>
       <c r="E2" t="n">
-        <v>3339093000</v>
+        <v>2399367000</v>
       </c>
       <c r="F2" t="n">
-        <v>379136000</v>
+        <v>229352000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>127800000</v>
+        <v>175200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1906</v>
+        <v>2312</v>
       </c>
       <c r="E3" t="n">
-        <v>2424967000</v>
+        <v>3304073000</v>
       </c>
       <c r="F3" t="n">
-        <v>236802000</v>
+        <v>371336000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>96600000</v>
+        <v>137700000</v>
       </c>
       <c r="D4" t="n">
         <v>2008</v>
       </c>
       <c r="E4" t="n">
-        <v>2503187000</v>
+        <v>2481622000</v>
       </c>
       <c r="F4" t="n">
-        <v>388164000</v>
+        <v>386714000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43200000</v>
+        <v>59100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2439</v>
+        <v>2427</v>
       </c>
       <c r="E5" t="n">
-        <v>3029831000</v>
+        <v>2974351000</v>
       </c>
       <c r="F5" t="n">
-        <v>516416000</v>
+        <v>514616000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G2" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H2" t="n">
-        <v>520585000</v>
+        <v>497185000</v>
       </c>
       <c r="I2" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="J2" t="n">
-        <v>224400000</v>
+        <v>67750000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>19500000</v>
+        <v>22500000</v>
       </c>
       <c r="G3" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H3" t="n">
-        <v>447661000</v>
+        <v>444316000</v>
       </c>
       <c r="I3" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="J3" t="n">
-        <v>112320000</v>
+        <v>53765000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -900,13 +900,13 @@
         <v>179886000</v>
       </c>
       <c r="M3" t="n">
-        <v>40.18</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,25 +920,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9300000</v>
       </c>
       <c r="G4" t="n">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="H4" t="n">
-        <v>286580000</v>
+        <v>285685000</v>
       </c>
       <c r="I4" t="n">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="J4" t="n">
-        <v>86760000</v>
+        <v>58710000</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -947,13 +947,13 @@
         <v>143470000</v>
       </c>
       <c r="M4" t="n">
-        <v>50.06</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>6000000</v>
       </c>
       <c r="G5" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H5" t="n">
-        <v>801650000</v>
+        <v>784640000</v>
       </c>
       <c r="I5" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="J5" t="n">
-        <v>276315000</v>
+        <v>175025000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>29275000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,28 +1026,28 @@
         <v>484</v>
       </c>
       <c r="H6" t="n">
-        <v>404045000</v>
+        <v>396430000</v>
       </c>
       <c r="I6" t="n">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="J6" t="n">
-        <v>129430000</v>
+        <v>93425000</v>
       </c>
       <c r="K6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>108385000</v>
+        <v>106585000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.82</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1073,13 @@
         <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>569310000</v>
+        <v>566095000</v>
       </c>
       <c r="I7" t="n">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="J7" t="n">
-        <v>395160000</v>
+        <v>367295000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>55100000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.68</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>352</v>
       </c>
       <c r="H8" t="n">
-        <v>343423000</v>
+        <v>339123000</v>
       </c>
       <c r="I8" t="n">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J8" t="n">
-        <v>117550000</v>
+        <v>87640000</v>
       </c>
       <c r="K8" t="n">
         <v>157</v>
@@ -1135,13 +1135,13 @@
         <v>125945000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.67</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1167,7 +1167,7 @@
         <v>53</v>
       </c>
       <c r="H9" t="n">
-        <v>46130000</v>
+        <v>45430000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>46130000</v>
+        <v>45430000</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>57300000</v>
+        <v>88500000</v>
       </c>
       <c r="G10" t="n">
         <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>645535000</v>
+        <v>656430000</v>
       </c>
       <c r="I10" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="J10" t="n">
-        <v>216270000</v>
+        <v>121730000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1229,13 +1229,13 @@
         <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="G11" t="n">
         <v>474</v>
       </c>
       <c r="H11" t="n">
-        <v>765830000</v>
+        <v>752045000</v>
       </c>
       <c r="I11" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="J11" t="n">
-        <v>239365000</v>
+        <v>93025000</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>28725000</v>
+        <v>28275000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,28 +1308,28 @@
         <v>291</v>
       </c>
       <c r="H12" t="n">
-        <v>346964000</v>
+        <v>337424000</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>95630000</v>
+        <v>20620000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>62579000</v>
+        <v>62279000</v>
       </c>
       <c r="M12" t="n">
-        <v>18.04</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>395</v>
       </c>
       <c r="H13" t="n">
-        <v>355305000</v>
+        <v>351170000</v>
       </c>
       <c r="I13" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J13" t="n">
-        <v>128600000</v>
+        <v>100815000</v>
       </c>
       <c r="K13" t="n">
         <v>141</v>
@@ -1370,13 +1370,13 @@
         <v>122785000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.56</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>27300000</v>
+        <v>41700000</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H14" t="n">
-        <v>739675000</v>
+        <v>739410000</v>
       </c>
       <c r="I14" t="n">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="J14" t="n">
-        <v>257467000</v>
+        <v>172512000</v>
       </c>
       <c r="K14" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L14" t="n">
-        <v>63861000</v>
+        <v>57861000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.630000000000001</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>289</v>
       </c>
       <c r="H15" t="n">
-        <v>520840000</v>
+        <v>512065000</v>
       </c>
       <c r="I15" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="J15" t="n">
-        <v>158315000</v>
+        <v>89990000</v>
       </c>
       <c r="K15" t="n">
         <v>58</v>
@@ -1464,13 +1464,13 @@
         <v>84575000</v>
       </c>
       <c r="M15" t="n">
-        <v>16.24</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,31 +1493,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
-        <v>382095000</v>
+        <v>371300000</v>
       </c>
       <c r="I16" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>109000000</v>
+        <v>42040000</v>
       </c>
       <c r="K16" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L16" t="n">
-        <v>122700000</v>
+        <v>120900000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.11</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>78600000</v>
+        <v>105900000</v>
       </c>
       <c r="G17" t="n">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="H17" t="n">
-        <v>1008995000</v>
+        <v>1020860000</v>
       </c>
       <c r="I17" t="n">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="J17" t="n">
-        <v>512428000</v>
+        <v>400238000</v>
       </c>
       <c r="K17" t="n">
         <v>49</v>
@@ -1558,13 +1558,13 @@
         <v>45160000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,13 +1590,13 @@
         <v>557</v>
       </c>
       <c r="H18" t="n">
-        <v>687488000</v>
+        <v>660438000</v>
       </c>
       <c r="I18" t="n">
-        <v>248</v>
+        <v>103</v>
       </c>
       <c r="J18" t="n">
-        <v>315085000</v>
+        <v>123860000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
@@ -1605,13 +1605,13 @@
         <v>62840000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>54200000</v>
+        <v>63200000</v>
       </c>
       <c r="G19" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H19" t="n">
-        <v>531755000</v>
+        <v>517590000</v>
       </c>
       <c r="I19" t="n">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="J19" t="n">
-        <v>222430000</v>
+        <v>65785000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1731,28 +1731,28 @@
         <v>232</v>
       </c>
       <c r="H21" t="n">
-        <v>325095000</v>
+        <v>316895000</v>
       </c>
       <c r="I21" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="J21" t="n">
-        <v>122050000</v>
+        <v>67400000</v>
       </c>
       <c r="K21" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L21" t="n">
-        <v>55870000</v>
+        <v>50970000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.19</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,16 +1775,16 @@
         <v>12500000</v>
       </c>
       <c r="G22" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H22" t="n">
-        <v>516917000</v>
+        <v>502457000</v>
       </c>
       <c r="I22" t="n">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="J22" t="n">
-        <v>238185000</v>
+        <v>133455000</v>
       </c>
       <c r="K22" t="n">
         <v>61</v>
@@ -1793,13 +1793,13 @@
         <v>72247000</v>
       </c>
       <c r="M22" t="n">
-        <v>13.98</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1813,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>61100000</v>
+        <v>101900000</v>
       </c>
       <c r="G23" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H23" t="n">
-        <v>761065000</v>
+        <v>784215000</v>
       </c>
       <c r="I23" t="n">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="J23" t="n">
-        <v>291470000</v>
+        <v>160720000</v>
       </c>
       <c r="K23" t="n">
         <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>46375000</v>
+        <v>46175000</v>
       </c>
       <c r="M23" t="n">
-        <v>6.09</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,13 +1872,13 @@
         <v>161</v>
       </c>
       <c r="H24" t="n">
-        <v>223150000</v>
+        <v>216050000</v>
       </c>
       <c r="I24" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>81450000</v>
+        <v>17350000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,13 +1887,13 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.81</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1916,25 +1916,25 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H25" t="n">
-        <v>54485000</v>
+        <v>49660000</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>13175000</v>
+        <v>5350000</v>
       </c>
       <c r="K25" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L25" t="n">
-        <v>41310000</v>
+        <v>38960000</v>
       </c>
       <c r="M25" t="n">
-        <v>75.81999999999999</v>
+        <v>78.45</v>
       </c>
     </row>
   </sheetData>
@@ -2217,10 +2217,10 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
-        <v>133500000</v>
+        <v>175200000</v>
       </c>
       <c r="N2" t="n">
-        <v>492152000</v>
+        <v>467530000</v>
       </c>
     </row>
     <row r="3">
@@ -2261,10 +2261,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>127800000</v>
+        <v>177600000</v>
       </c>
       <c r="N3" t="n">
-        <v>320942000</v>
+        <v>273832000</v>
       </c>
     </row>
     <row r="4">
@@ -2305,10 +2305,10 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
-        <v>43200000</v>
+        <v>59100000</v>
       </c>
       <c r="N4" t="n">
-        <v>623931000</v>
+        <v>608301000</v>
       </c>
     </row>
     <row r="5">
@@ -2349,10 +2349,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>96600000</v>
+        <v>137700000</v>
       </c>
       <c r="N5" t="n">
-        <v>438449001</v>
+        <v>427579001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>543256000</v>
+        <v>525951000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>422508000</v>
+        <v>395280000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>401654001</v>
+        <v>380234001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>244442000</v>
+        <v>233217000</v>
       </c>
     </row>
   </sheetData>
@@ -517,25 +517,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>128950000</v>
+        <v>54900000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>76200000</v>
+        <v>37000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>70500000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>19900000</v>
+        <v>11350000</v>
       </c>
     </row>
   </sheetData>
@@ -635,55 +635,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>177600000</v>
+        <v>324300000</v>
       </c>
       <c r="D2" t="n">
-        <v>1889</v>
+        <v>2321</v>
       </c>
       <c r="E2" t="n">
-        <v>2360697000</v>
+        <v>3361713000</v>
       </c>
       <c r="F2" t="n">
-        <v>228902000</v>
+        <v>370336000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>175200000</v>
+        <v>278400000</v>
       </c>
       <c r="D3" t="n">
-        <v>2291</v>
+        <v>1922</v>
       </c>
       <c r="E3" t="n">
-        <v>3253991000</v>
+        <v>2441872000</v>
       </c>
       <c r="F3" t="n">
-        <v>370736000</v>
+        <v>228452000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>150300000</v>
+        <v>263700000</v>
       </c>
       <c r="D4" t="n">
-        <v>2014</v>
+        <v>2032</v>
       </c>
       <c r="E4" t="n">
-        <v>2463472000</v>
+        <v>2538602000</v>
       </c>
       <c r="F4" t="n">
-        <v>381824000</v>
+        <v>378949000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63600000</v>
+        <v>199300000</v>
       </c>
       <c r="D5" t="n">
-        <v>2409</v>
+        <v>2448</v>
       </c>
       <c r="E5" t="n">
-        <v>2910156000</v>
+        <v>3021706000</v>
       </c>
       <c r="F5" t="n">
-        <v>510466000</v>
+        <v>508596000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3600000</v>
+        <v>18000000</v>
       </c>
       <c r="G2" t="n">
         <v>385</v>
       </c>
       <c r="H2" t="n">
-        <v>486685000</v>
+        <v>496810000</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>10950000</v>
+        <v>6250000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>27000000</v>
+        <v>53400000</v>
       </c>
       <c r="G3" t="n">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="H3" t="n">
-        <v>445661000</v>
+        <v>469941000</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>25980000</v>
+        <v>15480000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>179786000</v>
+        <v>178966000</v>
       </c>
       <c r="M3" t="n">
-        <v>40.34</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,25 +920,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9300000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="H4" t="n">
-        <v>280010000</v>
+        <v>268500000</v>
       </c>
       <c r="I4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J4" t="n">
-        <v>28660000</v>
+        <v>18500000</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -947,13 +947,13 @@
         <v>143020000</v>
       </c>
       <c r="M4" t="n">
-        <v>51.08</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>6000000</v>
+        <v>50800000</v>
       </c>
       <c r="G5" t="n">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="H5" t="n">
-        <v>765915000</v>
+        <v>802590000</v>
       </c>
       <c r="I5" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>50700000</v>
+        <v>16050000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>29275000</v>
+        <v>29125000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.82</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>11400000</v>
+        <v>46800000</v>
       </c>
       <c r="G6" t="n">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="H6" t="n">
-        <v>391960000</v>
+        <v>423490000</v>
       </c>
       <c r="I6" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="J6" t="n">
-        <v>66815000</v>
+        <v>53195000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>106585000</v>
       </c>
       <c r="M6" t="n">
-        <v>27.19</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>6300000</v>
+        <v>30300000</v>
       </c>
       <c r="G7" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="H7" t="n">
-        <v>539925000</v>
+        <v>560375000</v>
       </c>
       <c r="I7" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J7" t="n">
-        <v>191065000</v>
+        <v>188415000</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>51500000</v>
+        <v>50600000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>22500000</v>
+        <v>25800000</v>
       </c>
       <c r="G8" t="n">
         <v>358</v>
       </c>
       <c r="H8" t="n">
-        <v>342328000</v>
+        <v>340618000</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="J8" t="n">
-        <v>53210000</v>
+        <v>40085000</v>
       </c>
       <c r="K8" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L8" t="n">
-        <v>125945000</v>
+        <v>123070000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.79</v>
+        <v>36.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,23 +1151,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Hashim Hazem Talib .</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4800000</v>
       </c>
       <c r="G9" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>44980000</v>
+        <v>4800000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1176,19 +1176,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>44980000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1198,44 +1198,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hussein . Flaih Abdul Hassan -</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>93900000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>446</v>
+        <v>53</v>
       </c>
       <c r="H10" t="n">
-        <v>651120000</v>
+        <v>44980000</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>49700000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="L10" t="n">
-        <v>2000000</v>
+        <v>44980000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1245,44 +1245,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sadikh . Najee Jawad -</t>
+          <t>Hussein . Flaih Abdul Hassan -</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>4500000</v>
+        <v>131100000</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="H11" t="n">
-        <v>742070000</v>
+        <v>671870000</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>64400000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>28275000</v>
+        <v>2000000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.81</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1292,44 +1292,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shamil Kamil Hadhod .</t>
+          <t>Sadikh . Najee Jawad -</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>25800000</v>
+        <v>49800000</v>
       </c>
       <c r="G12" t="n">
-        <v>291</v>
+        <v>483</v>
       </c>
       <c r="H12" t="n">
-        <v>334264000</v>
+        <v>772320000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>14300000</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>62279000</v>
+        <v>28275000</v>
       </c>
       <c r="M12" t="n">
-        <v>18.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1339,91 +1339,91 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shiab Ghanim Abd zaid</t>
+          <t>Shamil Kamil Hadhod .</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>3600000</v>
+        <v>48600000</v>
       </c>
       <c r="G13" t="n">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>348710000</v>
+        <v>355664000</v>
       </c>
       <c r="I13" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>78915000</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="L13" t="n">
-        <v>118345000</v>
+        <v>62279000</v>
       </c>
       <c r="M13" t="n">
-        <v>33.94</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hasanen Nadher Muhammed .</t>
+          <t>Shiab Ghanim Abd zaid</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>41700000</v>
+        <v>3600000</v>
       </c>
       <c r="G14" t="n">
-        <v>551</v>
+        <v>395</v>
       </c>
       <c r="H14" t="n">
-        <v>727740000</v>
+        <v>348350000</v>
       </c>
       <c r="I14" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="J14" t="n">
-        <v>104652000</v>
+        <v>76755000</v>
       </c>
       <c r="K14" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="L14" t="n">
-        <v>57861000</v>
+        <v>118345000</v>
       </c>
       <c r="M14" t="n">
-        <v>7.95</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hasanen Nadher Muhammed .</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>106500000</v>
       </c>
       <c r="G15" t="n">
-        <v>289</v>
+        <v>554</v>
       </c>
       <c r="H15" t="n">
-        <v>506565000</v>
+        <v>776830000</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="J15" t="n">
-        <v>48690000</v>
+        <v>69852000</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L15" t="n">
-        <v>84575000</v>
+        <v>57861000</v>
       </c>
       <c r="M15" t="n">
-        <v>16.7</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1493,31 +1493,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="H16" t="n">
-        <v>368090000</v>
+        <v>503815000</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>30440000</v>
+        <v>41440000</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="L16" t="n">
-        <v>120300000</v>
+        <v>84575000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.68</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>105900000</v>
+        <v>23400000</v>
       </c>
       <c r="G17" t="n">
-        <v>584</v>
+        <v>322</v>
       </c>
       <c r="H17" t="n">
-        <v>1001960000</v>
+        <v>390865000</v>
       </c>
       <c r="I17" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>290363000</v>
+        <v>26065000</v>
       </c>
       <c r="K17" t="n">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>45160000</v>
+        <v>120300000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.51</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,91 +1574,91 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>27600000</v>
+        <v>124500000</v>
       </c>
       <c r="G18" t="n">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="H18" t="n">
-        <v>649636000</v>
+        <v>1006712000</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>54180000</v>
+        <v>187350000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="L18" t="n">
-        <v>62840000</v>
+        <v>44760000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.67</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F19" t="n">
-        <v>63200000</v>
+        <v>69900000</v>
       </c>
       <c r="G19" t="n">
-        <v>464</v>
+        <v>575</v>
       </c>
       <c r="H19" t="n">
-        <v>506970000</v>
+        <v>683491000</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>6300000</v>
+        <v>33225000</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>62840000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1668,23 +1668,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>70700000</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>464</v>
       </c>
       <c r="H20" t="n">
-        <v>12500000</v>
+        <v>511095000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Anwar . Jalil Abbas -</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1728,31 +1728,31 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>232</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>309070000</v>
+        <v>12500000</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30600000</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>50970000</v>
+        <v>12500000</v>
       </c>
       <c r="M21" t="n">
-        <v>16.49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1762,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>12500000</v>
+        <v>10000000</v>
       </c>
       <c r="G22" t="n">
-        <v>431</v>
+        <v>237</v>
       </c>
       <c r="H22" t="n">
-        <v>495307000</v>
+        <v>314670000</v>
       </c>
       <c r="I22" t="n">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
-        <v>86185000</v>
+        <v>14600000</v>
       </c>
       <c r="K22" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>72247000</v>
+        <v>50970000</v>
       </c>
       <c r="M22" t="n">
-        <v>14.59</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>101900000</v>
+        <v>32800000</v>
       </c>
       <c r="G23" t="n">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="H23" t="n">
-        <v>772865000</v>
+        <v>513257000</v>
       </c>
       <c r="I23" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="J23" t="n">
-        <v>59470000</v>
+        <v>77185000</v>
       </c>
       <c r="K23" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L23" t="n">
-        <v>46175000</v>
+        <v>72247000</v>
       </c>
       <c r="M23" t="n">
-        <v>5.97</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,44 +1856,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>112700000</v>
       </c>
       <c r="G24" t="n">
-        <v>161</v>
+        <v>495</v>
       </c>
       <c r="H24" t="n">
-        <v>214775000</v>
+        <v>777465000</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="J24" t="n">
-        <v>4600000</v>
+        <v>34620000</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>8500000</v>
+        <v>46175000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,38 +1903,85 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>52200000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>182</v>
+      </c>
+      <c r="H25" t="n">
+        <v>264575000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>94</v>
-      </c>
-      <c r="H25" t="n">
-        <v>49210000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5350000</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>91</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48310000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="K26" t="n">
         <v>70</v>
       </c>
-      <c r="L25" t="n">
-        <v>38510000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>78.26000000000001</v>
+      <c r="L26" t="n">
+        <v>38060000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>78.78</v>
       </c>
     </row>
   </sheetData>
@@ -2217,10 +2264,10 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
-        <v>175200000</v>
+        <v>324300000</v>
       </c>
       <c r="N2" t="n">
-        <v>422508000</v>
+        <v>395280000</v>
       </c>
     </row>
     <row r="3">
@@ -2261,10 +2308,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>177600000</v>
+        <v>278400000</v>
       </c>
       <c r="N3" t="n">
-        <v>244442000</v>
+        <v>233217000</v>
       </c>
     </row>
     <row r="4">
@@ -2305,10 +2352,10 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
-        <v>63600000</v>
+        <v>199300000</v>
       </c>
       <c r="N4" t="n">
-        <v>543256000</v>
+        <v>525951000</v>
       </c>
     </row>
     <row r="5">
@@ -2349,10 +2396,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>150300000</v>
+        <v>263700000</v>
       </c>
       <c r="N5" t="n">
-        <v>401654001</v>
+        <v>380234001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81219000</v>
+        <v>131239000</v>
       </c>
     </row>
     <row r="3">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118414000</v>
+        <v>239914000</v>
       </c>
     </row>
     <row r="4">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>263445310</v>
+        <v>368065310</v>
       </c>
     </row>
     <row r="5">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34263500</v>
+        <v>68258500</v>
       </c>
     </row>
     <row r="6">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>400924500</v>
+        <v>417624500</v>
       </c>
     </row>
     <row r="7">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59496670</v>
+        <v>101808310</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>525951000</v>
+        <v>502611000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>395280000</v>
+        <v>370589001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>380234001</v>
+        <v>368596000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>233217000</v>
+        <v>228892000</v>
       </c>
     </row>
   </sheetData>
@@ -517,43 +517,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>54900000</v>
+        <v>73500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>37000000</v>
+        <v>64000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>30000000</v>
+        <v>58800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>11350000</v>
+        <v>38050000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,70 +644,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>324300000</v>
+        <v>395500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="E2" t="n">
-        <v>3361713000</v>
+        <v>3401154000</v>
       </c>
       <c r="F2" t="n">
-        <v>370336000</v>
+        <v>367336000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>278400000</v>
+        <v>373800000</v>
       </c>
       <c r="D3" t="n">
-        <v>1922</v>
+        <v>2055</v>
       </c>
       <c r="E3" t="n">
-        <v>2441872000</v>
+        <v>2625427000</v>
       </c>
       <c r="F3" t="n">
-        <v>228452000</v>
+        <v>376299000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>263700000</v>
+        <v>323400000</v>
       </c>
       <c r="D4" t="n">
-        <v>2032</v>
+        <v>1933</v>
       </c>
       <c r="E4" t="n">
-        <v>2538602000</v>
+        <v>2480947000</v>
       </c>
       <c r="F4" t="n">
-        <v>378949000</v>
+        <v>228452000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>199300000</v>
+        <v>299600000</v>
       </c>
       <c r="D5" t="n">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="E5" t="n">
-        <v>3021706000</v>
+        <v>3080486000</v>
       </c>
       <c r="F5" t="n">
-        <v>508596000</v>
+        <v>507546000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>18000000</v>
+        <v>53400000</v>
       </c>
       <c r="G2" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H2" t="n">
-        <v>496810000</v>
+        <v>517160000</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>6250000</v>
+        <v>1350000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -885,28 +885,28 @@
         <v>397</v>
       </c>
       <c r="H3" t="n">
-        <v>469941000</v>
+        <v>469191000</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>15480000</v>
+        <v>14130000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>178966000</v>
+        <v>178366000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.08</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H4" t="n">
-        <v>268500000</v>
+        <v>265375000</v>
       </c>
       <c r="I4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>18500000</v>
+        <v>11650000</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L4" t="n">
-        <v>143020000</v>
+        <v>142570000</v>
       </c>
       <c r="M4" t="n">
-        <v>53.27</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>50800000</v>
+        <v>95200000</v>
       </c>
       <c r="G5" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H5" t="n">
-        <v>802590000</v>
+        <v>841490000</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>16050000</v>
+        <v>500000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>29125000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.63</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>46800000</v>
+        <v>49800000</v>
       </c>
       <c r="G6" t="n">
         <v>496</v>
       </c>
       <c r="H6" t="n">
-        <v>423490000</v>
+        <v>421830000</v>
       </c>
       <c r="I6" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J6" t="n">
-        <v>53195000</v>
+        <v>35675000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>106585000</v>
       </c>
       <c r="M6" t="n">
-        <v>25.17</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>30300000</v>
+        <v>47800000</v>
       </c>
       <c r="G7" t="n">
         <v>472</v>
       </c>
       <c r="H7" t="n">
-        <v>560375000</v>
+        <v>565440000</v>
       </c>
       <c r="I7" t="n">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="J7" t="n">
-        <v>188415000</v>
+        <v>122715000</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
@@ -1088,13 +1088,13 @@
         <v>50600000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.029999999999999</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,28 +1120,28 @@
         <v>358</v>
       </c>
       <c r="H8" t="n">
-        <v>340618000</v>
+        <v>336068000</v>
       </c>
       <c r="I8" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
-        <v>40085000</v>
+        <v>19545000</v>
       </c>
       <c r="K8" t="n">
         <v>155</v>
       </c>
       <c r="L8" t="n">
-        <v>123070000</v>
+        <v>122170000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.13</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>131100000</v>
+        <v>148500000</v>
       </c>
       <c r="G11" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H11" t="n">
-        <v>671870000</v>
+        <v>689270000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>2000000</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>49800000</v>
+        <v>125100000</v>
       </c>
       <c r="G12" t="n">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="H12" t="n">
-        <v>772320000</v>
+        <v>834620000</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>14300000</v>
+        <v>7550000</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>28275000</v>
+        <v>28125000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.66</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>48600000</v>
+        <v>62400000</v>
       </c>
       <c r="G13" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="H13" t="n">
-        <v>355664000</v>
+        <v>369464000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1370,13 +1370,13 @@
         <v>62279000</v>
       </c>
       <c r="M13" t="n">
-        <v>17.51</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>3600000</v>
+        <v>7200000</v>
       </c>
       <c r="G14" t="n">
         <v>395</v>
       </c>
       <c r="H14" t="n">
-        <v>348350000</v>
+        <v>346225000</v>
       </c>
       <c r="I14" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="J14" t="n">
-        <v>76755000</v>
+        <v>55860000</v>
       </c>
       <c r="K14" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L14" t="n">
-        <v>118345000</v>
+        <v>116745000</v>
       </c>
       <c r="M14" t="n">
-        <v>33.97</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,25 +1437,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>106500000</v>
+        <v>115500000</v>
       </c>
       <c r="G15" t="n">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H15" t="n">
-        <v>776830000</v>
+        <v>778021000</v>
       </c>
       <c r="I15" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="J15" t="n">
-        <v>69852000</v>
+        <v>41800000</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1464,13 +1464,13 @@
         <v>57861000</v>
       </c>
       <c r="M15" t="n">
-        <v>7.45</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>32400000</v>
       </c>
       <c r="G16" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H16" t="n">
-        <v>503815000</v>
+        <v>530825000</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>41440000</v>
+        <v>23450000</v>
       </c>
       <c r="K16" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L16" t="n">
-        <v>84575000</v>
+        <v>83175000</v>
       </c>
       <c r="M16" t="n">
-        <v>16.79</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>23400000</v>
+        <v>46000000</v>
       </c>
       <c r="G17" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H17" t="n">
-        <v>390865000</v>
+        <v>409980000</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>26065000</v>
+        <v>23195000</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>120300000</v>
+        <v>118700000</v>
       </c>
       <c r="M17" t="n">
-        <v>30.78</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>124500000</v>
+        <v>131700000</v>
       </c>
       <c r="G18" t="n">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H18" t="n">
-        <v>1006712000</v>
+        <v>999187000</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="J18" t="n">
-        <v>187350000</v>
+        <v>84325000</v>
       </c>
       <c r="K18" t="n">
         <v>49</v>
@@ -1605,13 +1605,13 @@
         <v>44760000</v>
       </c>
       <c r="M18" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,10 +1634,10 @@
         <v>69900000</v>
       </c>
       <c r="G19" t="n">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H19" t="n">
-        <v>683491000</v>
+        <v>683141000</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
@@ -1652,13 +1652,13 @@
         <v>62840000</v>
       </c>
       <c r="M19" t="n">
-        <v>9.19</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1684,7 +1684,7 @@
         <v>464</v>
       </c>
       <c r="H20" t="n">
-        <v>511095000</v>
+        <v>510595000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,25 +1766,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>10000000</v>
+        <v>25000000</v>
       </c>
       <c r="G22" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H22" t="n">
-        <v>314670000</v>
+        <v>328420000</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>14600000</v>
+        <v>6450000</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1793,13 +1793,13 @@
         <v>50970000</v>
       </c>
       <c r="M22" t="n">
-        <v>16.2</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>32800000</v>
+        <v>49300000</v>
       </c>
       <c r="G23" t="n">
         <v>448</v>
       </c>
       <c r="H23" t="n">
-        <v>513257000</v>
+        <v>527582000</v>
       </c>
       <c r="I23" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J23" t="n">
-        <v>77185000</v>
+        <v>64210000</v>
       </c>
       <c r="K23" t="n">
         <v>61</v>
@@ -1840,13 +1840,13 @@
         <v>72247000</v>
       </c>
       <c r="M23" t="n">
-        <v>14.08</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>112700000</v>
+        <v>118700000</v>
       </c>
       <c r="G24" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H24" t="n">
-        <v>777465000</v>
+        <v>781465000</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>34620000</v>
+        <v>25720000</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
@@ -1887,13 +1887,13 @@
         <v>46175000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.94</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,44 +1903,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Muna Abed Alkareem Madlol</t>
+          <t>Maytham Salah Mahdie .</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>52200000</v>
+        <v>7500000</v>
       </c>
       <c r="G25" t="n">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>264575000</v>
+        <v>7500000</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>4600000</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>8500000</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1950,37 +1950,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Muna Abed Alkareem Madlol</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>23</v>
+      </c>
+      <c r="F26" t="n">
+        <v>52200000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>182</v>
+      </c>
+      <c r="H26" t="n">
+        <v>264575000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Nisreen . Nadum Waheed -</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>91</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>48310000</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>4900000</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>70</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>38060000</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>78.78</v>
       </c>
     </row>
@@ -2057,7 +2104,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>239914000</v>
+        <v>137544000</v>
       </c>
     </row>
     <row r="4">
@@ -2077,7 +2124,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>368065310</v>
+        <v>299465310</v>
       </c>
     </row>
     <row r="5">
@@ -2097,7 +2144,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68258500</v>
+        <v>32108500</v>
       </c>
     </row>
     <row r="6">
@@ -2137,7 +2184,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101808310</v>
+        <v>107681310</v>
       </c>
     </row>
   </sheetData>
@@ -2264,10 +2311,10 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
-        <v>324300000</v>
+        <v>395500000</v>
       </c>
       <c r="N2" t="n">
-        <v>395280000</v>
+        <v>368596000</v>
       </c>
     </row>
     <row r="3">
@@ -2308,10 +2355,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>278400000</v>
+        <v>323400000</v>
       </c>
       <c r="N3" t="n">
-        <v>233217000</v>
+        <v>228892000</v>
       </c>
     </row>
     <row r="4">
@@ -2352,10 +2399,10 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
-        <v>199300000</v>
+        <v>299600000</v>
       </c>
       <c r="N4" t="n">
-        <v>525951000</v>
+        <v>502611000</v>
       </c>
     </row>
     <row r="5">
@@ -2396,10 +2443,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>263700000</v>
+        <v>373800000</v>
       </c>
       <c r="N5" t="n">
-        <v>380234001</v>
+        <v>370589001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>502611000</v>
+        <v>465566000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>370589001</v>
+        <v>353144001</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>368596000</v>
+        <v>336401000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>228892000</v>
+        <v>211362000</v>
       </c>
     </row>
   </sheetData>
@@ -517,61 +517,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>73500000</v>
+        <v>64800000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>64000000</v>
+        <v>32400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>58800000</v>
+        <v>27400000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>38050000</v>
+        <v>5850000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>395500000</v>
+        <v>467500000</v>
       </c>
       <c r="D2" t="n">
-        <v>2318</v>
+        <v>2329</v>
       </c>
       <c r="E2" t="n">
-        <v>3401154000</v>
+        <v>3410977000</v>
       </c>
       <c r="F2" t="n">
-        <v>367336000</v>
+        <v>355801000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,64 +668,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>373800000</v>
+        <v>462000000</v>
       </c>
       <c r="D3" t="n">
-        <v>2055</v>
+        <v>2080</v>
       </c>
       <c r="E3" t="n">
-        <v>2625427000</v>
+        <v>2687858000</v>
       </c>
       <c r="F3" t="n">
-        <v>376299000</v>
+        <v>363299000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>323400000</v>
+        <v>457200000</v>
       </c>
       <c r="D4" t="n">
-        <v>1933</v>
+        <v>2480</v>
       </c>
       <c r="E4" t="n">
-        <v>2480947000</v>
+        <v>3185816000</v>
       </c>
       <c r="F4" t="n">
-        <v>228452000</v>
+        <v>486826000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>299600000</v>
+        <v>357300000</v>
       </c>
       <c r="D5" t="n">
-        <v>2447</v>
+        <v>1931</v>
       </c>
       <c r="E5" t="n">
-        <v>3080486000</v>
+        <v>2485252000</v>
       </c>
       <c r="F5" t="n">
-        <v>507546000</v>
+        <v>224032000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>53400000</v>
+        <v>135000000</v>
       </c>
       <c r="G2" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H2" t="n">
-        <v>517160000</v>
+        <v>589310000</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1350000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -853,13 +853,13 @@
         <v>300000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>53400000</v>
+        <v>68400000</v>
       </c>
       <c r="G3" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
-        <v>469191000</v>
+        <v>480441000</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>14130000</v>
+        <v>5880000</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L3" t="n">
-        <v>178366000</v>
+        <v>176746000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.02</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H4" t="n">
-        <v>265375000</v>
+        <v>260790000</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>11650000</v>
+        <v>11525000</v>
       </c>
       <c r="K4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>142570000</v>
+        <v>135220000</v>
       </c>
       <c r="M4" t="n">
-        <v>53.72</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>95200000</v>
+        <v>106400000</v>
       </c>
       <c r="G5" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H5" t="n">
-        <v>841490000</v>
+        <v>848685000</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>500000</v>
+        <v>7020000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>29125000</v>
+        <v>20975000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.46</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>49800000</v>
+        <v>67800000</v>
       </c>
       <c r="G6" t="n">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H6" t="n">
-        <v>421830000</v>
+        <v>436120000</v>
       </c>
       <c r="I6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J6" t="n">
-        <v>35675000</v>
+        <v>22525000</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L6" t="n">
-        <v>106585000</v>
+        <v>103585000</v>
       </c>
       <c r="M6" t="n">
-        <v>25.27</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>47800000</v>
+        <v>79600000</v>
       </c>
       <c r="G7" t="n">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="H7" t="n">
-        <v>565440000</v>
+        <v>570470000</v>
       </c>
       <c r="I7" t="n">
-        <v>125</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>122715000</v>
+        <v>3150000</v>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>50600000</v>
+        <v>50000000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.949999999999999</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1117,31 +1117,31 @@
         <v>25800000</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H8" t="n">
-        <v>336068000</v>
+        <v>329283000</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>19545000</v>
+        <v>1640000</v>
       </c>
       <c r="K8" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L8" t="n">
-        <v>122170000</v>
+        <v>120370000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.35</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,7 +1261,7 @@
         <v>450</v>
       </c>
       <c r="H11" t="n">
-        <v>689270000</v>
+        <v>688570000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>125100000</v>
+        <v>138600000</v>
       </c>
       <c r="G12" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H12" t="n">
-        <v>834620000</v>
+        <v>843281000</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>7550000</v>
+        <v>1450000</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
@@ -1323,13 +1323,13 @@
         <v>28125000</v>
       </c>
       <c r="M12" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>62400000</v>
+        <v>73800000</v>
       </c>
       <c r="G13" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H13" t="n">
-        <v>369464000</v>
+        <v>379654000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1367,16 +1367,16 @@
         <v>63</v>
       </c>
       <c r="L13" t="n">
-        <v>62279000</v>
+        <v>61879000</v>
       </c>
       <c r="M13" t="n">
-        <v>16.86</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>7200000</v>
+        <v>70500000</v>
       </c>
       <c r="G14" t="n">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="H14" t="n">
-        <v>346225000</v>
+        <v>397290000</v>
       </c>
       <c r="I14" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="J14" t="n">
-        <v>55860000</v>
+        <v>33150000</v>
       </c>
       <c r="K14" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="L14" t="n">
-        <v>116745000</v>
+        <v>105945000</v>
       </c>
       <c r="M14" t="n">
-        <v>33.72</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,16 +1446,16 @@
         <v>115500000</v>
       </c>
       <c r="G15" t="n">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H15" t="n">
-        <v>778021000</v>
+        <v>760514000</v>
       </c>
       <c r="I15" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>41800000</v>
+        <v>18000000</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1464,13 +1464,13 @@
         <v>57861000</v>
       </c>
       <c r="M15" t="n">
-        <v>7.44</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>32400000</v>
+        <v>72000000</v>
       </c>
       <c r="G16" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="H16" t="n">
-        <v>530825000</v>
+        <v>558775000</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>23450000</v>
+        <v>11250000</v>
       </c>
       <c r="K16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L16" t="n">
-        <v>83175000</v>
+        <v>80200000</v>
       </c>
       <c r="M16" t="n">
-        <v>15.67</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1543,13 +1543,13 @@
         <v>325</v>
       </c>
       <c r="H17" t="n">
-        <v>409980000</v>
+        <v>407540000</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>23195000</v>
+        <v>15475000</v>
       </c>
       <c r="K17" t="n">
         <v>100</v>
@@ -1558,13 +1558,13 @@
         <v>118700000</v>
       </c>
       <c r="M17" t="n">
-        <v>28.95</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>131700000</v>
+        <v>159900000</v>
       </c>
       <c r="G18" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H18" t="n">
-        <v>999187000</v>
+        <v>1003907000</v>
       </c>
       <c r="I18" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>84325000</v>
+        <v>11575000</v>
       </c>
       <c r="K18" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
-        <v>44760000</v>
+        <v>36200000</v>
       </c>
       <c r="M18" t="n">
-        <v>4.48</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F19" t="n">
-        <v>69900000</v>
+        <v>74100000</v>
       </c>
       <c r="G19" t="n">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H19" t="n">
-        <v>683141000</v>
+        <v>680241000</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>33225000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>70</v>
@@ -1652,13 +1652,13 @@
         <v>62840000</v>
       </c>
       <c r="M19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1684,7 +1684,7 @@
         <v>464</v>
       </c>
       <c r="H20" t="n">
-        <v>510595000</v>
+        <v>509145000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,7 +1778,7 @@
         <v>241</v>
       </c>
       <c r="H22" t="n">
-        <v>328420000</v>
+        <v>327530000</v>
       </c>
       <c r="I22" t="n">
         <v>6</v>
@@ -1793,13 +1793,13 @@
         <v>50970000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.52</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1813,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>49300000</v>
+        <v>83200000</v>
       </c>
       <c r="G23" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H23" t="n">
-        <v>527582000</v>
+        <v>541252000</v>
       </c>
       <c r="I23" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>64210000</v>
+        <v>13310000</v>
       </c>
       <c r="K23" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L23" t="n">
-        <v>72247000</v>
+        <v>68527000</v>
       </c>
       <c r="M23" t="n">
-        <v>13.69</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,28 +1872,28 @@
         <v>497</v>
       </c>
       <c r="H24" t="n">
-        <v>781465000</v>
+        <v>775840000</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>25720000</v>
+        <v>20470000</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>46175000</v>
+        <v>45475000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.91</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1966,13 +1966,13 @@
         <v>182</v>
       </c>
       <c r="H26" t="n">
-        <v>264575000</v>
+        <v>263625000</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>4600000</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>14</v>
@@ -1981,13 +1981,13 @@
         <v>8500000</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2010,16 +2010,16 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H27" t="n">
-        <v>48310000</v>
+        <v>47860000</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>4900000</v>
+        <v>4450000</v>
       </c>
       <c r="K27" t="n">
         <v>70</v>
@@ -2028,7 +2028,7 @@
         <v>38060000</v>
       </c>
       <c r="M27" t="n">
-        <v>78.78</v>
+        <v>79.52</v>
       </c>
     </row>
   </sheetData>
@@ -2311,10 +2311,10 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
-        <v>395500000</v>
+        <v>467500000</v>
       </c>
       <c r="N2" t="n">
-        <v>368596000</v>
+        <v>336401000</v>
       </c>
     </row>
     <row r="3">
@@ -2355,10 +2355,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>323400000</v>
+        <v>357300000</v>
       </c>
       <c r="N3" t="n">
-        <v>228892000</v>
+        <v>211362000</v>
       </c>
     </row>
     <row r="4">
@@ -2399,10 +2399,10 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
-        <v>299600000</v>
+        <v>457200000</v>
       </c>
       <c r="N4" t="n">
-        <v>502611000</v>
+        <v>465566000</v>
       </c>
     </row>
     <row r="5">
@@ -2443,10 +2443,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>373800000</v>
+        <v>462000000</v>
       </c>
       <c r="N5" t="n">
-        <v>370589001</v>
+        <v>353144001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>465566000</v>
+        <v>612693000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>353144001</v>
+        <v>500961000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>336401000</v>
+        <v>436704001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>211362000</v>
+        <v>335277000</v>
       </c>
     </row>
   </sheetData>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,73 +517,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>64800000</v>
+        <v>91500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>32400000</v>
+        <v>54000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>27400000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>الحلة</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5850000</v>
+        <v>10350000</v>
       </c>
     </row>
   </sheetData>
@@ -635,31 +617,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>467500000</v>
+        <v>112100000</v>
       </c>
       <c r="D2" t="n">
-        <v>2329</v>
+        <v>2029</v>
       </c>
       <c r="E2" t="n">
-        <v>3410977000</v>
+        <v>2482074160</v>
       </c>
       <c r="F2" t="n">
-        <v>355801000</v>
+        <v>351399160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,64 +650,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>462000000</v>
+        <v>72400000</v>
       </c>
       <c r="D3" t="n">
-        <v>2080</v>
+        <v>2172</v>
       </c>
       <c r="E3" t="n">
-        <v>2687858000</v>
+        <v>2595372960</v>
       </c>
       <c r="F3" t="n">
-        <v>363299000</v>
+        <v>455026960</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>457200000</v>
+        <v>64650000</v>
       </c>
       <c r="D4" t="n">
-        <v>2480</v>
+        <v>2405</v>
       </c>
       <c r="E4" t="n">
-        <v>3185816000</v>
+        <v>3332179200</v>
       </c>
       <c r="F4" t="n">
-        <v>486826000</v>
+        <v>520620200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>357300000</v>
+        <v>41400000</v>
       </c>
       <c r="D5" t="n">
-        <v>1931</v>
+        <v>2524</v>
       </c>
       <c r="E5" t="n">
-        <v>2485252000</v>
+        <v>3071519600.6</v>
       </c>
       <c r="F5" t="n">
-        <v>224032000</v>
+        <v>581157600.6</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,40 +808,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>135000000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="H2" t="n">
-        <v>589310000</v>
+        <v>542695200</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>87950000</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>300000</v>
+        <v>4240200</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +855,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>68400000</v>
+        <v>12000000</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="H3" t="n">
-        <v>480441000</v>
+        <v>478386520</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="J3" t="n">
-        <v>5880000</v>
+        <v>86650000</v>
       </c>
       <c r="K3" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="L3" t="n">
-        <v>176746000</v>
+        <v>185574520</v>
       </c>
       <c r="M3" t="n">
-        <v>36.79</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +911,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="H4" t="n">
-        <v>260790000</v>
+        <v>276930480.6</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J4" t="n">
-        <v>11525000</v>
+        <v>47040000</v>
       </c>
       <c r="K4" t="n">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="L4" t="n">
-        <v>135220000</v>
+        <v>179095480.6</v>
       </c>
       <c r="M4" t="n">
-        <v>51.85</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +949,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>106400000</v>
+        <v>18000000</v>
       </c>
       <c r="G5" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H5" t="n">
-        <v>848685000</v>
+        <v>796746600</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="J5" t="n">
-        <v>7020000</v>
+        <v>175705000</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>20975000</v>
+        <v>32336600</v>
       </c>
       <c r="M5" t="n">
-        <v>2.47</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +996,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>67800000</v>
+        <v>11400000</v>
       </c>
       <c r="G6" t="n">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H6" t="n">
-        <v>436120000</v>
+        <v>422590000</v>
       </c>
       <c r="I6" t="n">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="J6" t="n">
-        <v>22525000</v>
+        <v>119060000</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="L6" t="n">
-        <v>103585000</v>
+        <v>115570000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.75</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1043,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>79600000</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="H7" t="n">
-        <v>570470000</v>
+        <v>554170800</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
       <c r="J7" t="n">
-        <v>3150000</v>
+        <v>280110000</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>50000000</v>
+        <v>64340800</v>
       </c>
       <c r="M7" t="n">
-        <v>8.76</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1090,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>25800000</v>
+        <v>3600000</v>
       </c>
       <c r="G8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H8" t="n">
-        <v>329283000</v>
+        <v>315420000</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="J8" t="n">
-        <v>1640000</v>
+        <v>67015000</v>
       </c>
       <c r="K8" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="L8" t="n">
-        <v>120370000</v>
+        <v>123750000</v>
       </c>
       <c r="M8" t="n">
-        <v>36.56</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1161,13 +1143,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>4800000</v>
+        <v>4000000</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="H9" t="n">
-        <v>4800000</v>
+        <v>71336320</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1176,19 +1158,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>62536320</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1198,44 +1180,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Hussein . Flaih Abdul Hassan -</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>50400000</v>
       </c>
       <c r="G10" t="n">
-        <v>53</v>
+        <v>453</v>
       </c>
       <c r="H10" t="n">
-        <v>44980000</v>
+        <v>667810200</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>127350000</v>
       </c>
       <c r="K10" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>44980000</v>
+        <v>7260200</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1245,44 +1227,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hussein . Flaih Abdul Hassan -</t>
+          <t>Sadikh . Najee Jawad -</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>148500000</v>
+        <v>14400000</v>
       </c>
       <c r="G11" t="n">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>688570000</v>
+        <v>776726000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>137255000</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>2000000</v>
+        <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>0.29</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1292,44 +1274,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sadikh . Najee Jawad -</t>
+          <t>Shamil Kamil Hadhod .</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>138600000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>491</v>
+        <v>348</v>
       </c>
       <c r="H12" t="n">
-        <v>843281000</v>
+        <v>368072640</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>1450000</v>
+        <v>47280000</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="L12" t="n">
-        <v>28125000</v>
+        <v>82122640</v>
       </c>
       <c r="M12" t="n">
-        <v>3.34</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1339,91 +1321,91 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shamil Kamil Hadhod .</t>
+          <t>Shiab Ghanim Abd zaid</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>73800000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>310</v>
+        <v>449</v>
       </c>
       <c r="H13" t="n">
-        <v>379654000</v>
+        <v>396007800</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>82680000</v>
       </c>
       <c r="K13" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="L13" t="n">
-        <v>61879000</v>
+        <v>150382800</v>
       </c>
       <c r="M13" t="n">
-        <v>16.3</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shiab Ghanim Abd zaid</t>
+          <t>Hasanen Nadher Muhammed .</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
-        <v>42</v>
-      </c>
       <c r="F14" t="n">
-        <v>70500000</v>
+        <v>30750000</v>
       </c>
       <c r="G14" t="n">
-        <v>419</v>
+        <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>397290000</v>
+        <v>763726880</v>
       </c>
       <c r="I14" t="n">
-        <v>45</v>
+        <v>176</v>
       </c>
       <c r="J14" t="n">
-        <v>33150000</v>
+        <v>205423000</v>
       </c>
       <c r="K14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L14" t="n">
-        <v>105945000</v>
+        <v>100343880</v>
       </c>
       <c r="M14" t="n">
-        <v>26.67</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,44 +1415,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hasanen Nadher Muhammed .</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>115500000</v>
+        <v>6000000</v>
       </c>
       <c r="G15" t="n">
-        <v>545</v>
+        <v>309</v>
       </c>
       <c r="H15" t="n">
-        <v>760514000</v>
+        <v>544299440</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J15" t="n">
-        <v>18000000</v>
+        <v>100500000</v>
       </c>
       <c r="K15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L15" t="n">
-        <v>57861000</v>
+        <v>113999440</v>
       </c>
       <c r="M15" t="n">
-        <v>7.61</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1462,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>72000000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="H16" t="n">
-        <v>558775000</v>
+        <v>406996880</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J16" t="n">
-        <v>11250000</v>
+        <v>38785000</v>
       </c>
       <c r="K16" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="L16" t="n">
-        <v>80200000</v>
+        <v>159541880</v>
       </c>
       <c r="M16" t="n">
-        <v>14.35</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1509,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>46000000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>325</v>
+        <v>576</v>
       </c>
       <c r="H17" t="n">
-        <v>407540000</v>
+        <v>954678000</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="J17" t="n">
-        <v>15475000</v>
+        <v>441115000</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="L17" t="n">
-        <v>118700000</v>
+        <v>73375000</v>
       </c>
       <c r="M17" t="n">
-        <v>29.13</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,91 +1556,91 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>159900000</v>
+        <v>27900000</v>
       </c>
       <c r="G18" t="n">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="H18" t="n">
-        <v>1003907000</v>
+        <v>662478000</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="J18" t="n">
-        <v>11575000</v>
+        <v>230388000</v>
       </c>
       <c r="K18" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="L18" t="n">
-        <v>36200000</v>
+        <v>73360000</v>
       </c>
       <c r="M18" t="n">
-        <v>3.61</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>74100000</v>
+        <v>39200000</v>
       </c>
       <c r="G19" t="n">
-        <v>570</v>
+        <v>471</v>
       </c>
       <c r="H19" t="n">
-        <v>680241000</v>
+        <v>496621000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>158305000</v>
       </c>
       <c r="K19" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>62840000</v>
+        <v>2646000</v>
       </c>
       <c r="M19" t="n">
-        <v>9.24</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1668,44 +1650,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>70700000</v>
+        <v>15000000</v>
       </c>
       <c r="G20" t="n">
-        <v>464</v>
+        <v>272</v>
       </c>
       <c r="H20" t="n">
-        <v>509145000</v>
+        <v>340932360</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>85925000</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>81897360</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,7 +1697,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anwar . Jalil Abbas -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1728,31 +1710,31 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>471</v>
       </c>
       <c r="H21" t="n">
-        <v>12500000</v>
+        <v>562050200</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>296705000</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>12500000</v>
+        <v>121235200</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1744,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>25000000</v>
+        <v>41400000</v>
       </c>
       <c r="G22" t="n">
-        <v>241</v>
+        <v>504</v>
       </c>
       <c r="H22" t="n">
-        <v>327530000</v>
+        <v>754188000</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="J22" t="n">
-        <v>6450000</v>
+        <v>225050000</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L22" t="n">
-        <v>50970000</v>
+        <v>81913000</v>
       </c>
       <c r="M22" t="n">
-        <v>15.56</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1791,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Maytham Salah Mahdie .</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>83200000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>449</v>
+        <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>541252000</v>
+        <v>62738600</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>13310000</v>
+        <v>5050000</v>
       </c>
       <c r="K23" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="L23" t="n">
-        <v>68527000</v>
+        <v>49663600</v>
       </c>
       <c r="M23" t="n">
-        <v>12.66</v>
+        <v>79.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,179 +1838,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>118700000</v>
+        <v>16500000</v>
       </c>
       <c r="G24" t="n">
-        <v>497</v>
+        <v>200</v>
       </c>
       <c r="H24" t="n">
-        <v>775840000</v>
+        <v>265544000</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>20470000</v>
+        <v>46575000</v>
       </c>
       <c r="K24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L24" t="n">
-        <v>45475000</v>
+        <v>14044000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Maytham Salah Mahdie .</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" t="n">
-        <v>52200000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>182</v>
-      </c>
-      <c r="H26" t="n">
-        <v>263625000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>14</v>
-      </c>
-      <c r="L26" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>88</v>
-      </c>
-      <c r="H27" t="n">
-        <v>47860000</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4450000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>70</v>
-      </c>
-      <c r="L27" t="n">
-        <v>38060000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>79.52</v>
+        <v>5.29</v>
       </c>
     </row>
   </sheetData>
@@ -2311,10 +2152,10 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
-        <v>467500000</v>
+        <v>64650000</v>
       </c>
       <c r="N2" t="n">
-        <v>336401000</v>
+        <v>500961000</v>
       </c>
     </row>
     <row r="3">
@@ -2355,10 +2196,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>357300000</v>
+        <v>112100000</v>
       </c>
       <c r="N3" t="n">
-        <v>211362000</v>
+        <v>335277000</v>
       </c>
     </row>
     <row r="4">
@@ -2399,10 +2240,10 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
-        <v>457200000</v>
+        <v>41400000</v>
       </c>
       <c r="N4" t="n">
-        <v>465566000</v>
+        <v>612693000</v>
       </c>
     </row>
     <row r="5">
@@ -2443,10 +2284,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>462000000</v>
+        <v>72400000</v>
       </c>
       <c r="N5" t="n">
-        <v>353144001</v>
+        <v>436704001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>612693000</v>
+        <v>592026000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500961000</v>
+        <v>479828000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>436704001</v>
+        <v>424554001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>335277000</v>
+        <v>317477000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,46 +526,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>91500000</v>
+        <v>115000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>54000000</v>
+        <v>58650000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>10350000</v>
+        <v>32900000</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +617,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -626,22 +626,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112100000</v>
+        <v>142200000</v>
       </c>
       <c r="D2" t="n">
-        <v>2029</v>
+        <v>1943</v>
       </c>
       <c r="E2" t="n">
-        <v>2482074160</v>
+        <v>2428942000</v>
       </c>
       <c r="F2" t="n">
-        <v>351399160</v>
+        <v>278867000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72400000</v>
+        <v>96400000</v>
       </c>
       <c r="D3" t="n">
-        <v>2172</v>
+        <v>2066</v>
       </c>
       <c r="E3" t="n">
-        <v>2595372960</v>
+        <v>2538730000</v>
       </c>
       <c r="F3" t="n">
-        <v>455026960</v>
+        <v>391364000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -677,19 +677,19 @@
         <v>64650000</v>
       </c>
       <c r="D4" t="n">
-        <v>2405</v>
+        <v>2315</v>
       </c>
       <c r="E4" t="n">
-        <v>3332179200</v>
+        <v>3234507000</v>
       </c>
       <c r="F4" t="n">
-        <v>520620200</v>
+        <v>446351000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -701,13 +701,13 @@
         <v>41400000</v>
       </c>
       <c r="D5" t="n">
-        <v>2524</v>
+        <v>2436</v>
       </c>
       <c r="E5" t="n">
-        <v>3071519600.6</v>
+        <v>2998291000</v>
       </c>
       <c r="F5" t="n">
-        <v>581157600.6</v>
+        <v>513896000</v>
       </c>
     </row>
   </sheetData>
@@ -794,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H2" t="n">
-        <v>542695200</v>
+        <v>532255000</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J2" t="n">
-        <v>87950000</v>
+        <v>48250000</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>4240200</v>
+        <v>300000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.78</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -864,31 +864,31 @@
         <v>12000000</v>
       </c>
       <c r="G3" t="n">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="H3" t="n">
-        <v>478386520</v>
+        <v>471523000</v>
       </c>
       <c r="I3" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J3" t="n">
-        <v>86650000</v>
+        <v>79990000</v>
       </c>
       <c r="K3" t="n">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>185574520</v>
+        <v>179521000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.79</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -911,31 +911,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="H4" t="n">
-        <v>276930480.6</v>
+        <v>239520000</v>
       </c>
       <c r="I4" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>47040000</v>
+        <v>42240000</v>
       </c>
       <c r="K4" t="n">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="L4" t="n">
-        <v>179095480.6</v>
+        <v>141235000</v>
       </c>
       <c r="M4" t="n">
-        <v>64.67</v>
+        <v>58.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -958,31 +958,31 @@
         <v>18000000</v>
       </c>
       <c r="G5" t="n">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="H5" t="n">
-        <v>796746600</v>
+        <v>787245000</v>
       </c>
       <c r="I5" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="J5" t="n">
-        <v>175705000</v>
+        <v>137875000</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>32336600</v>
+        <v>29195000</v>
       </c>
       <c r="M5" t="n">
-        <v>4.06</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1005,31 +1005,31 @@
         <v>11400000</v>
       </c>
       <c r="G6" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H6" t="n">
-        <v>422590000</v>
+        <v>417443000</v>
       </c>
       <c r="I6" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="J6" t="n">
-        <v>119060000</v>
+        <v>97590000</v>
       </c>
       <c r="K6" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="L6" t="n">
-        <v>115570000</v>
+        <v>111120000</v>
       </c>
       <c r="M6" t="n">
-        <v>27.35</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1052,31 +1052,31 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>554170800</v>
+        <v>550305000</v>
       </c>
       <c r="I7" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J7" t="n">
-        <v>280110000</v>
+        <v>282810000</v>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>64340800</v>
+        <v>52525000</v>
       </c>
       <c r="M7" t="n">
-        <v>11.61</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1090,40 +1090,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>3600000</v>
+        <v>12600000</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="H8" t="n">
-        <v>315420000</v>
+        <v>323500000</v>
       </c>
       <c r="I8" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J8" t="n">
-        <v>67015000</v>
+        <v>62695000</v>
       </c>
       <c r="K8" t="n">
         <v>164</v>
       </c>
       <c r="L8" t="n">
-        <v>123750000</v>
+        <v>123550000</v>
       </c>
       <c r="M8" t="n">
-        <v>39.23</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="G9" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>71336320</v>
+        <v>57355000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1158,19 +1158,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>62536320</v>
+        <v>44055000</v>
       </c>
       <c r="M9" t="n">
-        <v>87.66</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1193,31 +1193,31 @@
         <v>50400000</v>
       </c>
       <c r="G10" t="n">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>667810200</v>
+        <v>654525000</v>
       </c>
       <c r="I10" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="J10" t="n">
-        <v>127350000</v>
+        <v>68300000</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>7260200</v>
+        <v>2000000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1231,25 +1231,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>14400000</v>
+        <v>24900000</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="H11" t="n">
-        <v>776726000</v>
+        <v>781651000</v>
       </c>
       <c r="I11" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="J11" t="n">
-        <v>137255000</v>
+        <v>111205000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1258,13 +1258,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1287,31 +1287,31 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="H12" t="n">
-        <v>368072640</v>
+        <v>344719000</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>47280000</v>
+        <v>30840000</v>
       </c>
       <c r="K12" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>82122640</v>
+        <v>61429000</v>
       </c>
       <c r="M12" t="n">
-        <v>22.31</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>396007800</v>
+        <v>376980000</v>
       </c>
       <c r="I13" t="n">
         <v>111</v>
@@ -1346,19 +1346,19 @@
         <v>82680000</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="L13" t="n">
-        <v>150382800</v>
+        <v>131355000</v>
       </c>
       <c r="M13" t="n">
-        <v>37.97</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1381,31 +1381,31 @@
         <v>30750000</v>
       </c>
       <c r="G14" t="n">
-        <v>588</v>
+        <v>550</v>
       </c>
       <c r="H14" t="n">
-        <v>763726880</v>
+        <v>733844000</v>
       </c>
       <c r="I14" t="n">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="J14" t="n">
-        <v>205423000</v>
+        <v>178723000</v>
       </c>
       <c r="K14" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="L14" t="n">
-        <v>100343880</v>
+        <v>75186000</v>
       </c>
       <c r="M14" t="n">
-        <v>13.14</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1428,31 +1428,31 @@
         <v>6000000</v>
       </c>
       <c r="G15" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="H15" t="n">
-        <v>544299440</v>
+        <v>527950000</v>
       </c>
       <c r="I15" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J15" t="n">
-        <v>100500000</v>
+        <v>78500000</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L15" t="n">
-        <v>113999440</v>
+        <v>100150000</v>
       </c>
       <c r="M15" t="n">
-        <v>20.94</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1475,31 +1475,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="H16" t="n">
-        <v>406996880</v>
+        <v>379135000</v>
       </c>
       <c r="I16" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>38785000</v>
+        <v>36265000</v>
       </c>
       <c r="K16" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>159541880</v>
+        <v>131500000</v>
       </c>
       <c r="M16" t="n">
-        <v>39.2</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1525,19 +1525,19 @@
         <v>576</v>
       </c>
       <c r="H17" t="n">
-        <v>954678000</v>
+        <v>951278000</v>
       </c>
       <c r="I17" t="n">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="J17" t="n">
-        <v>441115000</v>
+        <v>411115000</v>
       </c>
       <c r="K17" t="n">
         <v>68</v>
       </c>
       <c r="L17" t="n">
-        <v>73375000</v>
+        <v>73175000</v>
       </c>
       <c r="M17" t="n">
         <v>7.69</v>
@@ -1546,7 +1546,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,31 +1569,31 @@
         <v>27900000</v>
       </c>
       <c r="G18" t="n">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="H18" t="n">
-        <v>662478000</v>
+        <v>642300000</v>
       </c>
       <c r="I18" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>230388000</v>
+        <v>117500000</v>
       </c>
       <c r="K18" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L18" t="n">
-        <v>73360000</v>
+        <v>66340000</v>
       </c>
       <c r="M18" t="n">
-        <v>11.07</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1607,40 +1607,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>39200000</v>
+        <v>63300000</v>
       </c>
       <c r="G19" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H19" t="n">
-        <v>496621000</v>
+        <v>511225000</v>
       </c>
       <c r="I19" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="J19" t="n">
-        <v>158305000</v>
+        <v>123955000</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>2646000</v>
+        <v>2250000</v>
       </c>
       <c r="M19" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1663,31 +1663,31 @@
         <v>15000000</v>
       </c>
       <c r="G20" t="n">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="H20" t="n">
-        <v>340932360</v>
+        <v>329855000</v>
       </c>
       <c r="I20" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J20" t="n">
-        <v>85925000</v>
+        <v>80525000</v>
       </c>
       <c r="K20" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="L20" t="n">
-        <v>81897360</v>
+        <v>71670000</v>
       </c>
       <c r="M20" t="n">
-        <v>24.02</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1710,31 +1710,31 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="H21" t="n">
-        <v>562050200</v>
+        <v>526227000</v>
       </c>
       <c r="I21" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="J21" t="n">
-        <v>296705000</v>
+        <v>270405000</v>
       </c>
       <c r="K21" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L21" t="n">
-        <v>121235200</v>
+        <v>83212000</v>
       </c>
       <c r="M21" t="n">
-        <v>21.57</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,40 +1748,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>41400000</v>
+        <v>47400000</v>
       </c>
       <c r="G22" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H22" t="n">
-        <v>754188000</v>
+        <v>750600000</v>
       </c>
       <c r="I22" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="J22" t="n">
-        <v>225050000</v>
+        <v>196900000</v>
       </c>
       <c r="K22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L22" t="n">
-        <v>81913000</v>
+        <v>73775000</v>
       </c>
       <c r="M22" t="n">
-        <v>10.86</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1804,31 +1804,31 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H23" t="n">
-        <v>62738600</v>
+        <v>52035000</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>5050000</v>
+        <v>4050000</v>
       </c>
       <c r="K23" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
-        <v>49663600</v>
+        <v>39460000</v>
       </c>
       <c r="M23" t="n">
-        <v>79.16</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1851,25 +1851,25 @@
         <v>16500000</v>
       </c>
       <c r="G24" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H24" t="n">
-        <v>265544000</v>
+        <v>259000000</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>46575000</v>
+        <v>36575000</v>
       </c>
       <c r="K24" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>14044000</v>
+        <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.29</v>
+        <v>3.28</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2155,7 @@
         <v>64650000</v>
       </c>
       <c r="N2" t="n">
-        <v>500961000</v>
+        <v>479828000</v>
       </c>
     </row>
     <row r="3">
@@ -2196,10 +2196,10 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
-        <v>112100000</v>
+        <v>142200000</v>
       </c>
       <c r="N3" t="n">
-        <v>335277000</v>
+        <v>317477000</v>
       </c>
     </row>
     <row r="4">
@@ -2243,7 +2243,7 @@
         <v>41400000</v>
       </c>
       <c r="N4" t="n">
-        <v>612693000</v>
+        <v>592026000</v>
       </c>
     </row>
     <row r="5">
@@ -2284,10 +2284,10 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
-        <v>72400000</v>
+        <v>96400000</v>
       </c>
       <c r="N5" t="n">
-        <v>436704001</v>
+        <v>424554001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -2039,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,10 +2105,21 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>صرف_2026-06</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>متأخر_2026-06</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>صرف_None</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>متأخر_None</t>
         </is>
@@ -2152,9 +2163,16 @@
         <v>328441000</v>
       </c>
       <c r="M2" t="n">
+        <v>467500000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>336401000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>64650000</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>479828000</v>
       </c>
     </row>
@@ -2196,9 +2214,16 @@
         <v>201892000</v>
       </c>
       <c r="M3" t="n">
+        <v>357300000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>211112000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>142200000</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>317477000</v>
       </c>
     </row>
@@ -2240,9 +2265,16 @@
         <v>461506000</v>
       </c>
       <c r="M4" t="n">
+        <v>457200000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>465566000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>41400000</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>592026000</v>
       </c>
     </row>
@@ -2284,9 +2316,16 @@
         <v>358139001</v>
       </c>
       <c r="M5" t="n">
+        <v>462000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>353144001</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>96400000</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>424554001</v>
       </c>
     </row>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>592026000</v>
+        <v>567176000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>479828000</v>
+        <v>465713000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>424554001</v>
+        <v>410739001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>317477000</v>
+        <v>289457000</v>
       </c>
     </row>
   </sheetData>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>115000000</v>
+        <v>96100000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,28 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>58650000</v>
+        <v>61450000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>النجف</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54300000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>كربلاء</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32900000</v>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>51000000</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -626,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142200000</v>
+        <v>184800000</v>
       </c>
       <c r="D2" t="n">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="E2" t="n">
-        <v>2428942000</v>
+        <v>2424972000</v>
       </c>
       <c r="F2" t="n">
-        <v>278867000</v>
+        <v>258517000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,64 +668,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>96400000</v>
+        <v>115300000</v>
       </c>
       <c r="D3" t="n">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="E3" t="n">
-        <v>2538730000</v>
+        <v>2542555000</v>
       </c>
       <c r="F3" t="n">
-        <v>391364000</v>
+        <v>391064000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64650000</v>
+        <v>86400000</v>
       </c>
       <c r="D4" t="n">
-        <v>2315</v>
+        <v>2442</v>
       </c>
       <c r="E4" t="n">
-        <v>3234507000</v>
+        <v>3012986000</v>
       </c>
       <c r="F4" t="n">
-        <v>446351000</v>
+        <v>512656000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41400000</v>
+        <v>79950000</v>
       </c>
       <c r="D5" t="n">
-        <v>2436</v>
+        <v>2313</v>
       </c>
       <c r="E5" t="n">
-        <v>2998291000</v>
+        <v>3226792000</v>
       </c>
       <c r="F5" t="n">
-        <v>513896000</v>
+        <v>425851000</v>
       </c>
     </row>
   </sheetData>
@@ -794,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -808,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>11400000</v>
       </c>
       <c r="G2" t="n">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H2" t="n">
-        <v>532255000</v>
+        <v>539580000</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J2" t="n">
-        <v>48250000</v>
+        <v>19125000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -841,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -867,13 +885,13 @@
         <v>409</v>
       </c>
       <c r="H3" t="n">
-        <v>471523000</v>
+        <v>470233000</v>
       </c>
       <c r="I3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J3" t="n">
-        <v>79990000</v>
+        <v>68470000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -882,13 +900,13 @@
         <v>179521000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.07</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -911,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>239520000</v>
+        <v>236720000</v>
       </c>
       <c r="I4" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="J4" t="n">
-        <v>42240000</v>
+        <v>32240000</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -929,13 +947,13 @@
         <v>141235000</v>
       </c>
       <c r="M4" t="n">
-        <v>58.97</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -949,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>18000000</v>
+        <v>44400000</v>
       </c>
       <c r="G5" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H5" t="n">
-        <v>787245000</v>
+        <v>807945000</v>
       </c>
       <c r="I5" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
-        <v>137875000</v>
+        <v>110125000</v>
       </c>
       <c r="K5" t="n">
         <v>20</v>
@@ -976,13 +994,13 @@
         <v>29195000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -996,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>11400000</v>
+        <v>18600000</v>
       </c>
       <c r="G6" t="n">
         <v>501</v>
       </c>
       <c r="H6" t="n">
-        <v>417443000</v>
+        <v>422393000</v>
       </c>
       <c r="I6" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="J6" t="n">
-        <v>97590000</v>
+        <v>88560000</v>
       </c>
       <c r="K6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>111120000</v>
+        <v>110880000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.62</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1055,28 +1073,28 @@
         <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>550305000</v>
+        <v>536115000</v>
       </c>
       <c r="I7" t="n">
-        <v>280</v>
+        <v>209</v>
       </c>
       <c r="J7" t="n">
-        <v>282810000</v>
+        <v>201515000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>52525000</v>
+        <v>51525000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1102,13 +1120,13 @@
         <v>364</v>
       </c>
       <c r="H8" t="n">
-        <v>323500000</v>
+        <v>322540000</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J8" t="n">
-        <v>62695000</v>
+        <v>58855000</v>
       </c>
       <c r="K8" t="n">
         <v>164</v>
@@ -1117,13 +1135,13 @@
         <v>123550000</v>
       </c>
       <c r="M8" t="n">
-        <v>38.19</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1137,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>8500000</v>
+        <v>12100000</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9" t="n">
-        <v>57355000</v>
+        <v>60655000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1161,16 +1179,16 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>44055000</v>
+        <v>43755000</v>
       </c>
       <c r="M9" t="n">
-        <v>76.81</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1184,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>50400000</v>
+        <v>54900000</v>
       </c>
       <c r="G10" t="n">
         <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>654525000</v>
+        <v>655025000</v>
       </c>
       <c r="I10" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>68300000</v>
+        <v>39300000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1217,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1231,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>24900000</v>
+        <v>32100000</v>
       </c>
       <c r="G11" t="n">
         <v>474</v>
       </c>
       <c r="H11" t="n">
-        <v>781651000</v>
+        <v>784016000</v>
       </c>
       <c r="I11" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="J11" t="n">
-        <v>111205000</v>
+        <v>78600000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1258,13 +1276,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1278,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G12" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H12" t="n">
-        <v>344719000</v>
+        <v>345259000</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>30840000</v>
+        <v>13650000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
@@ -1305,13 +1323,13 @@
         <v>61429000</v>
       </c>
       <c r="M12" t="n">
-        <v>17.82</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1337,13 +1355,13 @@
         <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>376980000</v>
+        <v>375060000</v>
       </c>
       <c r="I13" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>82680000</v>
+        <v>68190000</v>
       </c>
       <c r="K13" t="n">
         <v>159</v>
@@ -1352,13 +1370,13 @@
         <v>131355000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.84</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1372,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
-        <v>30750000</v>
+        <v>46050000</v>
       </c>
       <c r="G14" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H14" t="n">
-        <v>733844000</v>
+        <v>737694000</v>
       </c>
       <c r="I14" t="n">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="J14" t="n">
-        <v>178723000</v>
+        <v>134898000</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L14" t="n">
-        <v>75186000</v>
+        <v>73986000</v>
       </c>
       <c r="M14" t="n">
-        <v>10.25</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1452,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1478,28 +1496,28 @@
         <v>318</v>
       </c>
       <c r="H16" t="n">
-        <v>379135000</v>
+        <v>377145000</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>36265000</v>
+        <v>29765000</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>131500000</v>
+        <v>128600000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.68</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1525,28 +1543,28 @@
         <v>576</v>
       </c>
       <c r="H17" t="n">
-        <v>951278000</v>
+        <v>947328000</v>
       </c>
       <c r="I17" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J17" t="n">
-        <v>411115000</v>
+        <v>406915000</v>
       </c>
       <c r="K17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L17" t="n">
-        <v>73175000</v>
+        <v>60275000</v>
       </c>
       <c r="M17" t="n">
-        <v>7.69</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1572,28 +1590,28 @@
         <v>569</v>
       </c>
       <c r="H18" t="n">
-        <v>642300000</v>
+        <v>636675000</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="J18" t="n">
-        <v>117500000</v>
+        <v>80350000</v>
       </c>
       <c r="K18" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>66340000</v>
+        <v>62840000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.33</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1607,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>63300000</v>
+        <v>92100000</v>
       </c>
       <c r="G19" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H19" t="n">
-        <v>511225000</v>
+        <v>523800000</v>
       </c>
       <c r="I19" t="n">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J19" t="n">
-        <v>123955000</v>
+        <v>66705000</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1634,13 +1652,13 @@
         <v>2250000</v>
       </c>
       <c r="M19" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1654,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>15000000</v>
+        <v>24000000</v>
       </c>
       <c r="G20" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H20" t="n">
-        <v>329855000</v>
+        <v>337005000</v>
       </c>
       <c r="I20" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J20" t="n">
-        <v>80525000</v>
+        <v>64875000</v>
       </c>
       <c r="K20" t="n">
         <v>73</v>
@@ -1681,13 +1699,13 @@
         <v>71670000</v>
       </c>
       <c r="M20" t="n">
-        <v>21.73</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1713,28 +1731,28 @@
         <v>443</v>
       </c>
       <c r="H21" t="n">
-        <v>526227000</v>
+        <v>510482000</v>
       </c>
       <c r="I21" t="n">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="J21" t="n">
-        <v>270405000</v>
+        <v>160080000</v>
       </c>
       <c r="K21" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L21" t="n">
-        <v>83212000</v>
+        <v>81412000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.81</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>47400000</v>
+        <v>52200000</v>
       </c>
       <c r="G22" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H22" t="n">
-        <v>750600000</v>
+        <v>750200000</v>
       </c>
       <c r="I22" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="J22" t="n">
-        <v>196900000</v>
+        <v>161650000</v>
       </c>
       <c r="K22" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L22" t="n">
-        <v>73775000</v>
+        <v>63525000</v>
       </c>
       <c r="M22" t="n">
-        <v>9.83</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1804,31 +1822,31 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>52035000</v>
+        <v>45435000</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>4050000</v>
+        <v>5450000</v>
       </c>
       <c r="K23" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L23" t="n">
-        <v>39460000</v>
+        <v>31160000</v>
       </c>
       <c r="M23" t="n">
-        <v>75.83</v>
+        <v>68.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1854,13 +1872,13 @@
         <v>191</v>
       </c>
       <c r="H24" t="n">
-        <v>259000000</v>
+        <v>258050000</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>36575000</v>
+        <v>28525000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1869,7 +1887,7 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2131,11 @@
           <t>متأخر_2026-06</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr"/>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
       <c r="P1" t="inlineStr">
         <is>
           <t>صرف_None</t>
@@ -2170,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>64650000</v>
+        <v>79950000</v>
       </c>
       <c r="Q2" t="n">
-        <v>479828000</v>
+        <v>465713000</v>
       </c>
     </row>
     <row r="3">
@@ -2221,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>142200000</v>
+        <v>184800000</v>
       </c>
       <c r="Q3" t="n">
-        <v>317477000</v>
+        <v>289457000</v>
       </c>
     </row>
     <row r="4">
@@ -2272,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>41400000</v>
+        <v>86400000</v>
       </c>
       <c r="Q4" t="n">
-        <v>592026000</v>
+        <v>567176000</v>
       </c>
     </row>
     <row r="5">
@@ -2323,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>96400000</v>
+        <v>115300000</v>
       </c>
       <c r="Q5" t="n">
-        <v>424554001</v>
+        <v>410739001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>567176000</v>
+        <v>549751000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>465713000</v>
+        <v>440578000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>410739001</v>
+        <v>398819001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>289457000</v>
+        <v>265987000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>96100000</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>61450000</v>
+        <v>118200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>54300000</v>
+        <v>101500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>51000000</v>
+        <v>74550000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>184800000</v>
+        <v>199400000</v>
       </c>
       <c r="D2" t="n">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="E2" t="n">
-        <v>2424972000</v>
+        <v>2412352000</v>
       </c>
       <c r="F2" t="n">
-        <v>258517000</v>
+        <v>249117000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115300000</v>
+        <v>135700000</v>
       </c>
       <c r="D3" t="n">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="E3" t="n">
-        <v>2542555000</v>
+        <v>2544090000</v>
       </c>
       <c r="F3" t="n">
         <v>391064000</v>
@@ -683,7 +683,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86400000</v>
+        <v>130500000</v>
       </c>
       <c r="D4" t="n">
-        <v>2442</v>
+        <v>2448</v>
       </c>
       <c r="E4" t="n">
-        <v>3012986000</v>
+        <v>3036461000</v>
       </c>
       <c r="F4" t="n">
-        <v>512656000</v>
+        <v>512406000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>79950000</v>
       </c>
       <c r="D5" t="n">
-        <v>2313</v>
+        <v>2301</v>
       </c>
       <c r="E5" t="n">
-        <v>3226792000</v>
+        <v>3196932000</v>
       </c>
       <c r="F5" t="n">
-        <v>425851000</v>
+        <v>416451000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>11400000</v>
+        <v>18600000</v>
       </c>
       <c r="G2" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H2" t="n">
-        <v>539580000</v>
+        <v>542205000</v>
       </c>
       <c r="I2" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>19125000</v>
+        <v>6700000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>12000000</v>
+        <v>16500000</v>
       </c>
       <c r="G3" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="H3" t="n">
-        <v>470233000</v>
+        <v>472898000</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>68470000</v>
+        <v>50330000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -900,13 +900,13 @@
         <v>179521000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.18</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>236720000</v>
+        <v>233345000</v>
       </c>
       <c r="I4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>32240000</v>
+        <v>17215000</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
       </c>
       <c r="L4" t="n">
-        <v>141235000</v>
+        <v>140985000</v>
       </c>
       <c r="M4" t="n">
-        <v>59.66</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>44400000</v>
+        <v>67200000</v>
       </c>
       <c r="G5" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>807945000</v>
+        <v>825495000</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="J5" t="n">
-        <v>110125000</v>
+        <v>91775000</v>
       </c>
       <c r="K5" t="n">
         <v>20</v>
@@ -994,13 +994,13 @@
         <v>29195000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>18600000</v>
+        <v>28200000</v>
       </c>
       <c r="G6" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="H6" t="n">
-        <v>422393000</v>
+        <v>430163000</v>
       </c>
       <c r="I6" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="J6" t="n">
-        <v>88560000</v>
+        <v>79800000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>110880000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.25</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1073,13 @@
         <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>536115000</v>
+        <v>532355000</v>
       </c>
       <c r="I7" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J7" t="n">
-        <v>201515000</v>
+        <v>171835000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>51525000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>364</v>
       </c>
       <c r="H8" t="n">
-        <v>322540000</v>
+        <v>321040000</v>
       </c>
       <c r="I8" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J8" t="n">
-        <v>58855000</v>
+        <v>49855000</v>
       </c>
       <c r="K8" t="n">
         <v>164</v>
@@ -1135,13 +1135,13 @@
         <v>123550000</v>
       </c>
       <c r="M8" t="n">
-        <v>38.31</v>
+        <v>38.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,16 +1211,16 @@
         <v>54900000</v>
       </c>
       <c r="G10" t="n">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="H10" t="n">
-        <v>655025000</v>
+        <v>651050000</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>39300000</v>
+        <v>32025000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>32100000</v>
+        <v>45300000</v>
       </c>
       <c r="G11" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>784016000</v>
+        <v>787556000</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>78600000</v>
+        <v>48900000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1276,13 +1276,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>312</v>
+      </c>
+      <c r="H12" t="n">
+        <v>347109000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
         <v>3600000</v>
-      </c>
-      <c r="G12" t="n">
-        <v>309</v>
-      </c>
-      <c r="H12" t="n">
-        <v>345259000</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13650000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
@@ -1323,13 +1323,13 @@
         <v>61429000</v>
       </c>
       <c r="M12" t="n">
-        <v>17.79</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G13" t="n">
         <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>375060000</v>
+        <v>376680000</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="J13" t="n">
-        <v>68190000</v>
+        <v>62430000</v>
       </c>
       <c r="K13" t="n">
         <v>159</v>
@@ -1370,13 +1370,13 @@
         <v>131355000</v>
       </c>
       <c r="M13" t="n">
-        <v>35.02</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>46050000</v>
       </c>
       <c r="G14" t="n">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H14" t="n">
-        <v>737694000</v>
+        <v>730794000</v>
       </c>
       <c r="I14" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="J14" t="n">
-        <v>134898000</v>
+        <v>95148000</v>
       </c>
       <c r="K14" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L14" t="n">
-        <v>73986000</v>
+        <v>67986000</v>
       </c>
       <c r="M14" t="n">
-        <v>10.03</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>302</v>
       </c>
       <c r="H15" t="n">
-        <v>527950000</v>
+        <v>523700000</v>
       </c>
       <c r="I15" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>78500000</v>
+        <v>34000000</v>
       </c>
       <c r="K15" t="n">
         <v>63</v>
@@ -1464,13 +1464,13 @@
         <v>100150000</v>
       </c>
       <c r="M15" t="n">
-        <v>18.97</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,13 +1496,13 @@
         <v>318</v>
       </c>
       <c r="H16" t="n">
-        <v>377145000</v>
+        <v>374395000</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>29765000</v>
+        <v>11215000</v>
       </c>
       <c r="K16" t="n">
         <v>103</v>
@@ -1511,13 +1511,13 @@
         <v>128600000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.1</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1540,31 +1540,31 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="H17" t="n">
-        <v>947328000</v>
+        <v>935743000</v>
       </c>
       <c r="I17" t="n">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="J17" t="n">
-        <v>406915000</v>
+        <v>349395000</v>
       </c>
       <c r="K17" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L17" t="n">
-        <v>60275000</v>
+        <v>56875000</v>
       </c>
       <c r="M17" t="n">
-        <v>6.36</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,13 +1590,13 @@
         <v>569</v>
       </c>
       <c r="H18" t="n">
-        <v>636675000</v>
+        <v>632300000</v>
       </c>
       <c r="I18" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="J18" t="n">
-        <v>80350000</v>
+        <v>53475000</v>
       </c>
       <c r="K18" t="n">
         <v>70</v>
@@ -1605,13 +1605,13 @@
         <v>62840000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.869999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,31 +1634,31 @@
         <v>92100000</v>
       </c>
       <c r="G19" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H19" t="n">
-        <v>523800000</v>
+        <v>517710000</v>
       </c>
       <c r="I19" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="J19" t="n">
-        <v>66705000</v>
+        <v>32525000</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2250000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>24000000</v>
+        <v>27500000</v>
       </c>
       <c r="G20" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H20" t="n">
-        <v>337005000</v>
+        <v>334380000</v>
       </c>
       <c r="I20" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>64875000</v>
+        <v>29600000</v>
       </c>
       <c r="K20" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L20" t="n">
-        <v>71670000</v>
+        <v>69020000</v>
       </c>
       <c r="M20" t="n">
-        <v>21.27</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1731,13 +1731,13 @@
         <v>443</v>
       </c>
       <c r="H21" t="n">
-        <v>510482000</v>
+        <v>504602000</v>
       </c>
       <c r="I21" t="n">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="J21" t="n">
-        <v>160080000</v>
+        <v>130550000</v>
       </c>
       <c r="K21" t="n">
         <v>68</v>
@@ -1746,13 +1746,13 @@
         <v>81412000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.95</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>52200000</v>
+        <v>63300000</v>
       </c>
       <c r="G22" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H22" t="n">
-        <v>750200000</v>
+        <v>754450000</v>
       </c>
       <c r="I22" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="J22" t="n">
-        <v>161650000</v>
+        <v>121150000</v>
       </c>
       <c r="K22" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>63525000</v>
+        <v>59025000</v>
       </c>
       <c r="M22" t="n">
-        <v>8.470000000000001</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,13 +1825,13 @@
         <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>45435000</v>
+        <v>44535000</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>5450000</v>
+        <v>2750000</v>
       </c>
       <c r="K23" t="n">
         <v>65</v>
@@ -1840,13 +1840,13 @@
         <v>31160000</v>
       </c>
       <c r="M23" t="n">
-        <v>68.58</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,13 +1872,13 @@
         <v>191</v>
       </c>
       <c r="H24" t="n">
-        <v>258050000</v>
+        <v>256675000</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>28525000</v>
+        <v>20000000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
     </row>
   </sheetData>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>131239000</v>
+        <v>177409000</v>
       </c>
     </row>
     <row r="3">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>137544000</v>
+        <v>156267750</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>299465310</v>
+        <v>359193040</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32108500</v>
+        <v>122803750</v>
       </c>
     </row>
     <row r="6">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>417624500</v>
+        <v>415624500</v>
       </c>
     </row>
     <row r="7">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>107681310</v>
+        <v>263521640</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +2195,7 @@
         <v>79950000</v>
       </c>
       <c r="Q2" t="n">
-        <v>465713000</v>
+        <v>440578000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>184800000</v>
+        <v>199400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>289457000</v>
+        <v>265987000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>86400000</v>
+        <v>130500000</v>
       </c>
       <c r="Q4" t="n">
-        <v>567176000</v>
+        <v>549751000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>115300000</v>
+        <v>135700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>410739001</v>
+        <v>398819001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>549751000</v>
+        <v>533651000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>440578000</v>
+        <v>411148000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>398819001</v>
+        <v>389189001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>265987000</v>
+        <v>244887000</v>
       </c>
     </row>
   </sheetData>
@@ -517,25 +517,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>125000000</v>
+        <v>126700000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,34 +544,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>118200000</v>
+        <v>99600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>101500000</v>
+        <v>95100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>74550000</v>
+        <v>83650000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>199400000</v>
+        <v>269400000</v>
       </c>
       <c r="D2" t="n">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="E2" t="n">
-        <v>2412352000</v>
+        <v>2461252000</v>
       </c>
       <c r="F2" t="n">
-        <v>249117000</v>
+        <v>247217000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135700000</v>
+        <v>164800000</v>
       </c>
       <c r="D3" t="n">
-        <v>2067</v>
+        <v>2074</v>
       </c>
       <c r="E3" t="n">
-        <v>2544090000</v>
+        <v>2562360000</v>
       </c>
       <c r="F3" t="n">
-        <v>391064000</v>
+        <v>390864000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>130500000</v>
+        <v>162800000</v>
       </c>
       <c r="D4" t="n">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="E4" t="n">
-        <v>3036461000</v>
+        <v>3051501000</v>
       </c>
       <c r="F4" t="n">
-        <v>512406000</v>
+        <v>512046000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79950000</v>
+        <v>139050000</v>
       </c>
       <c r="D5" t="n">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="E5" t="n">
-        <v>3196932000</v>
+        <v>3217677000</v>
       </c>
       <c r="F5" t="n">
-        <v>416451000</v>
+        <v>416301000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>18600000</v>
+        <v>30600000</v>
       </c>
       <c r="G2" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H2" t="n">
-        <v>542205000</v>
+        <v>551880000</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>6700000</v>
+        <v>3025000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -853,13 +853,13 @@
         <v>300000</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>16500000</v>
+        <v>33100000</v>
       </c>
       <c r="G3" t="n">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="H3" t="n">
-        <v>472898000</v>
+        <v>486233000</v>
       </c>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>50330000</v>
+        <v>23860000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>179521000</v>
+        <v>179161000</v>
       </c>
       <c r="M3" t="n">
-        <v>37.96</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H4" t="n">
-        <v>233345000</v>
+        <v>231520000</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J4" t="n">
-        <v>17215000</v>
+        <v>15740000</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -947,13 +947,13 @@
         <v>140985000</v>
       </c>
       <c r="M4" t="n">
-        <v>60.42</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>67200000</v>
       </c>
       <c r="G5" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H5" t="n">
-        <v>825495000</v>
+        <v>821745000</v>
       </c>
       <c r="I5" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>91775000</v>
+        <v>67000000</v>
       </c>
       <c r="K5" t="n">
         <v>20</v>
@@ -994,13 +994,13 @@
         <v>29195000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>28200000</v>
+        <v>31900000</v>
       </c>
       <c r="G6" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="H6" t="n">
-        <v>430163000</v>
+        <v>432113000</v>
       </c>
       <c r="I6" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J6" t="n">
-        <v>79800000</v>
+        <v>70240000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>110880000</v>
       </c>
       <c r="M6" t="n">
-        <v>25.78</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1073,13 @@
         <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>532355000</v>
+        <v>528010000</v>
       </c>
       <c r="I7" t="n">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="J7" t="n">
-        <v>171835000</v>
+        <v>151325000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>51525000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.68</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>12600000</v>
+        <v>21000000</v>
       </c>
       <c r="G8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H8" t="n">
-        <v>321040000</v>
+        <v>328130000</v>
       </c>
       <c r="I8" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J8" t="n">
-        <v>49855000</v>
+        <v>41635000</v>
       </c>
       <c r="K8" t="n">
         <v>164</v>
       </c>
       <c r="L8" t="n">
-        <v>123550000</v>
+        <v>123350000</v>
       </c>
       <c r="M8" t="n">
-        <v>38.48</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>12100000</v>
+        <v>16300000</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>60655000</v>
+        <v>64855000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>43755000</v>
       </c>
       <c r="M9" t="n">
-        <v>72.14</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>54900000</v>
+        <v>58500000</v>
       </c>
       <c r="G10" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H10" t="n">
-        <v>651050000</v>
+        <v>649000000</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>32025000</v>
+        <v>8625000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>45300000</v>
+        <v>49800000</v>
       </c>
       <c r="G11" t="n">
         <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>787556000</v>
+        <v>789756000</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
-        <v>48900000</v>
+        <v>37000000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1276,13 +1276,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>7200000</v>
+        <v>15600000</v>
       </c>
       <c r="G12" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H12" t="n">
-        <v>347109000</v>
+        <v>354659000</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>3600000</v>
+        <v>50000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
@@ -1323,13 +1323,13 @@
         <v>61429000</v>
       </c>
       <c r="M12" t="n">
-        <v>17.7</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>376680000</v>
+        <v>375960000</v>
       </c>
       <c r="I13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J13" t="n">
-        <v>62430000</v>
+        <v>57390000</v>
       </c>
       <c r="K13" t="n">
         <v>159</v>
@@ -1370,13 +1370,13 @@
         <v>131355000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.87</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>46050000</v>
+        <v>70650000</v>
       </c>
       <c r="G14" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H14" t="n">
-        <v>730794000</v>
+        <v>750444000</v>
       </c>
       <c r="I14" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J14" t="n">
-        <v>95148000</v>
+        <v>73798000</v>
       </c>
       <c r="K14" t="n">
         <v>74</v>
@@ -1417,13 +1417,13 @@
         <v>67986000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>302</v>
       </c>
       <c r="H15" t="n">
-        <v>523700000</v>
+        <v>522100000</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>34000000</v>
+        <v>21200000</v>
       </c>
       <c r="K15" t="n">
         <v>63</v>
@@ -1464,13 +1464,13 @@
         <v>100150000</v>
       </c>
       <c r="M15" t="n">
-        <v>19.12</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,13 +1496,13 @@
         <v>318</v>
       </c>
       <c r="H16" t="n">
-        <v>374395000</v>
+        <v>373010000</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>11215000</v>
+        <v>2425000</v>
       </c>
       <c r="K16" t="n">
         <v>103</v>
@@ -1511,13 +1511,13 @@
         <v>128600000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.35</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>34500000</v>
       </c>
       <c r="G17" t="n">
         <v>567</v>
       </c>
       <c r="H17" t="n">
-        <v>935743000</v>
+        <v>942918000</v>
       </c>
       <c r="I17" t="n">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>349395000</v>
+        <v>217870000</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1558,13 +1558,13 @@
         <v>56875000</v>
       </c>
       <c r="M17" t="n">
-        <v>6.08</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1587,31 +1587,31 @@
         <v>27900000</v>
       </c>
       <c r="G18" t="n">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H18" t="n">
-        <v>632300000</v>
+        <v>629205000</v>
       </c>
       <c r="I18" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J18" t="n">
-        <v>53475000</v>
+        <v>38965000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L18" t="n">
-        <v>62840000</v>
+        <v>62690000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.94</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>92100000</v>
       </c>
       <c r="G19" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H19" t="n">
-        <v>517710000</v>
+        <v>512360000</v>
       </c>
       <c r="I19" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>32525000</v>
+        <v>3975000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>27500000</v>
+        <v>36500000</v>
       </c>
       <c r="G20" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H20" t="n">
-        <v>334380000</v>
+        <v>341130000</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
-        <v>29600000</v>
+        <v>23100000</v>
       </c>
       <c r="K20" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L20" t="n">
-        <v>69020000</v>
+        <v>68220000</v>
       </c>
       <c r="M20" t="n">
-        <v>20.64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,31 +1728,31 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H21" t="n">
-        <v>504602000</v>
+        <v>501102000</v>
       </c>
       <c r="I21" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="J21" t="n">
-        <v>130550000</v>
+        <v>112750000</v>
       </c>
       <c r="K21" t="n">
         <v>68</v>
       </c>
       <c r="L21" t="n">
-        <v>81412000</v>
+        <v>80912000</v>
       </c>
       <c r="M21" t="n">
-        <v>16.13</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,25 +1766,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>63300000</v>
+        <v>96100000</v>
       </c>
       <c r="G22" t="n">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="H22" t="n">
-        <v>754450000</v>
+        <v>778900000</v>
       </c>
       <c r="I22" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>121150000</v>
+        <v>54900000</v>
       </c>
       <c r="K22" t="n">
         <v>39</v>
@@ -1793,13 +1793,13 @@
         <v>59025000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H23" t="n">
-        <v>44535000</v>
+        <v>43935000</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -1834,19 +1834,19 @@
         <v>2750000</v>
       </c>
       <c r="K23" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L23" t="n">
-        <v>31160000</v>
+        <v>30560000</v>
       </c>
       <c r="M23" t="n">
-        <v>69.97</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>44700000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>203</v>
+      </c>
+      <c r="H24" t="n">
+        <v>283825000</v>
+      </c>
+      <c r="I24" t="n">
         <v>12</v>
       </c>
-      <c r="F24" t="n">
-        <v>16500000</v>
-      </c>
-      <c r="G24" t="n">
-        <v>191</v>
-      </c>
-      <c r="H24" t="n">
-        <v>256675000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>17</v>
-      </c>
       <c r="J24" t="n">
-        <v>20000000</v>
+        <v>11750000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>3.31</v>
+        <v>2.99</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>79950000</v>
+        <v>139050000</v>
       </c>
       <c r="Q2" t="n">
-        <v>440578000</v>
+        <v>411148000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>199400000</v>
+        <v>269400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>265987000</v>
+        <v>244887000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>130500000</v>
+        <v>162800000</v>
       </c>
       <c r="Q4" t="n">
-        <v>549751000</v>
+        <v>533651000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>135700000</v>
+        <v>164800000</v>
       </c>
       <c r="Q5" t="n">
-        <v>398819001</v>
+        <v>389189001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>533651000</v>
+        <v>521621000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>411148000</v>
+        <v>400308000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>389189001</v>
+        <v>383819001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>244887000</v>
+        <v>240212000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,64 +526,64 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>126700000</v>
+        <v>138400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>99600000</v>
+        <v>75900000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>95100000</v>
+        <v>71750000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>83650000</v>
+        <v>61600000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,88 +644,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>269400000</v>
+        <v>313900000</v>
       </c>
       <c r="D2" t="n">
-        <v>1958</v>
+        <v>1983</v>
       </c>
       <c r="E2" t="n">
-        <v>2461252000</v>
+        <v>2500452000</v>
       </c>
       <c r="F2" t="n">
-        <v>247217000</v>
+        <v>244517000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>164800000</v>
+        <v>232350000</v>
       </c>
       <c r="D3" t="n">
-        <v>2074</v>
+        <v>2336</v>
       </c>
       <c r="E3" t="n">
-        <v>2562360000</v>
+        <v>3294337000</v>
       </c>
       <c r="F3" t="n">
-        <v>390864000</v>
+        <v>405701000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>162800000</v>
+        <v>227200000</v>
       </c>
       <c r="D4" t="n">
-        <v>2449</v>
+        <v>2092</v>
       </c>
       <c r="E4" t="n">
-        <v>3051501000</v>
+        <v>2618015000</v>
       </c>
       <c r="F4" t="n">
-        <v>512046000</v>
+        <v>390864000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>139050000</v>
+        <v>222100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2300</v>
+        <v>2470</v>
       </c>
       <c r="E5" t="n">
-        <v>3217677000</v>
+        <v>3092741000</v>
       </c>
       <c r="F5" t="n">
-        <v>416301000</v>
+        <v>510446000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,16 +835,16 @@
         <v>30600000</v>
       </c>
       <c r="G2" t="n">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="H2" t="n">
-        <v>551880000</v>
+        <v>547980000</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>3025000</v>
+        <v>1675000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>33100000</v>
+        <v>36100000</v>
       </c>
       <c r="G3" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H3" t="n">
-        <v>486233000</v>
+        <v>488133000</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>23860000</v>
+        <v>18660000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
       </c>
       <c r="L3" t="n">
-        <v>179161000</v>
+        <v>178761000</v>
       </c>
       <c r="M3" t="n">
-        <v>36.85</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H4" t="n">
-        <v>231520000</v>
+        <v>231220000</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>15740000</v>
+        <v>15440000</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -947,13 +947,13 @@
         <v>140985000</v>
       </c>
       <c r="M4" t="n">
-        <v>60.9</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>67200000</v>
+        <v>81000000</v>
       </c>
       <c r="G5" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H5" t="n">
-        <v>821745000</v>
+        <v>826445000</v>
       </c>
       <c r="I5" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>67000000</v>
+        <v>10200000</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>29195000</v>
+        <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>31900000</v>
+        <v>53100000</v>
       </c>
       <c r="G6" t="n">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="H6" t="n">
-        <v>432113000</v>
+        <v>450733000</v>
       </c>
       <c r="I6" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J6" t="n">
-        <v>70240000</v>
+        <v>66520000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>110880000</v>
       </c>
       <c r="M6" t="n">
-        <v>25.66</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>21300000</v>
       </c>
       <c r="G7" t="n">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="H7" t="n">
-        <v>528010000</v>
+        <v>548230000</v>
       </c>
       <c r="I7" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J7" t="n">
-        <v>151325000</v>
+        <v>145925000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>51525000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.76</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>21000000</v>
+        <v>25800000</v>
       </c>
       <c r="G8" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>328130000</v>
+        <v>332580000</v>
       </c>
       <c r="I8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J8" t="n">
-        <v>41635000</v>
+        <v>38835000</v>
       </c>
       <c r="K8" t="n">
         <v>164</v>
@@ -1135,13 +1135,13 @@
         <v>123350000</v>
       </c>
       <c r="M8" t="n">
-        <v>37.59</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>58500000</v>
+        <v>63900000</v>
       </c>
       <c r="G10" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H10" t="n">
-        <v>649000000</v>
+        <v>654400000</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>49800000</v>
+        <v>88800000</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="H11" t="n">
-        <v>789756000</v>
+        <v>824656000</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>37000000</v>
+        <v>26800000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1276,13 +1276,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>15600000</v>
+        <v>28800000</v>
       </c>
       <c r="G12" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
-        <v>354659000</v>
+        <v>367484000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -1323,13 +1323,13 @@
         <v>61429000</v>
       </c>
       <c r="M12" t="n">
-        <v>17.32</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,13 +1355,13 @@
         <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>375960000</v>
+        <v>374040000</v>
       </c>
       <c r="I13" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
-        <v>57390000</v>
+        <v>42660000</v>
       </c>
       <c r="K13" t="n">
         <v>159</v>
@@ -1370,13 +1370,13 @@
         <v>131355000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.94</v>
+        <v>35.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>70650000</v>
+        <v>77250000</v>
       </c>
       <c r="G14" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H14" t="n">
-        <v>750444000</v>
+        <v>755284000</v>
       </c>
       <c r="I14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J14" t="n">
-        <v>73798000</v>
+        <v>66498000</v>
       </c>
       <c r="K14" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L14" t="n">
-        <v>67986000</v>
+        <v>66186000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.06</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,28 +1449,28 @@
         <v>302</v>
       </c>
       <c r="H15" t="n">
-        <v>522100000</v>
+        <v>517410000</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>21200000</v>
+        <v>1500000</v>
       </c>
       <c r="K15" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L15" t="n">
-        <v>100150000</v>
+        <v>91350000</v>
       </c>
       <c r="M15" t="n">
-        <v>19.18</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>15600000</v>
       </c>
       <c r="G16" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>373010000</v>
+        <v>388610000</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
@@ -1511,13 +1511,13 @@
         <v>128600000</v>
       </c>
       <c r="M16" t="n">
-        <v>34.48</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>34500000</v>
+        <v>61800000</v>
       </c>
       <c r="G17" t="n">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="H17" t="n">
-        <v>942918000</v>
+        <v>967368000</v>
       </c>
       <c r="I17" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>217870000</v>
+        <v>196495000</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1558,13 +1558,13 @@
         <v>56875000</v>
       </c>
       <c r="M17" t="n">
-        <v>6.03</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
-        <v>27900000</v>
+        <v>71700000</v>
       </c>
       <c r="G18" t="n">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="H18" t="n">
-        <v>629205000</v>
+        <v>665665000</v>
       </c>
       <c r="I18" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>38965000</v>
+        <v>29075000</v>
       </c>
       <c r="K18" t="n">
         <v>67</v>
@@ -1605,13 +1605,13 @@
         <v>62690000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.960000000000001</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,13 +1637,13 @@
         <v>461</v>
       </c>
       <c r="H19" t="n">
-        <v>512360000</v>
+        <v>511835000</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>3975000</v>
+        <v>2400000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>36500000</v>
+        <v>50000000</v>
       </c>
       <c r="G20" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H20" t="n">
-        <v>341130000</v>
+        <v>353630000</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>23100000</v>
+        <v>17100000</v>
       </c>
       <c r="K20" t="n">
         <v>67</v>
@@ -1699,13 +1699,13 @@
         <v>68220000</v>
       </c>
       <c r="M20" t="n">
-        <v>20</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="G21" t="n">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="H21" t="n">
-        <v>501102000</v>
+        <v>508602000</v>
       </c>
       <c r="I21" t="n">
         <v>133</v>
@@ -1746,13 +1746,13 @@
         <v>80912000</v>
       </c>
       <c r="M21" t="n">
-        <v>16.15</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>96100000</v>
+        <v>106600000</v>
       </c>
       <c r="G22" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H22" t="n">
-        <v>778900000</v>
+        <v>786250000</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>54900000</v>
+        <v>41750000</v>
       </c>
       <c r="K22" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L22" t="n">
-        <v>59025000</v>
+        <v>56325000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.58</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>44700000</v>
+        <v>57700000</v>
       </c>
       <c r="G24" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H24" t="n">
-        <v>283825000</v>
+        <v>296200000</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
@@ -1887,7 +1887,7 @@
         <v>8500000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>139050000</v>
+        <v>232350000</v>
       </c>
       <c r="Q2" t="n">
-        <v>411148000</v>
+        <v>400308000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>269400000</v>
+        <v>313900000</v>
       </c>
       <c r="Q3" t="n">
-        <v>244887000</v>
+        <v>240212000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>162800000</v>
+        <v>222100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>533651000</v>
+        <v>521621000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>164800000</v>
+        <v>227200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>389189001</v>
+        <v>383819001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>521621000</v>
+        <v>511791000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>400308000</v>
+        <v>377009001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>383819001</v>
+        <v>371761000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>240212000</v>
+        <v>224222000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,64 +526,64 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>138400000</v>
+        <v>84400000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>75900000</v>
+        <v>51500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>71750000</v>
+        <v>48900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>61600000</v>
+        <v>39050000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>313900000</v>
+        <v>385600000</v>
       </c>
       <c r="D2" t="n">
-        <v>1983</v>
+        <v>1999</v>
       </c>
       <c r="E2" t="n">
-        <v>2500452000</v>
+        <v>2552412000</v>
       </c>
       <c r="F2" t="n">
-        <v>244517000</v>
+        <v>231842000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>232350000</v>
+        <v>365720000</v>
       </c>
       <c r="D3" t="n">
-        <v>2336</v>
+        <v>2367</v>
       </c>
       <c r="E3" t="n">
-        <v>3294337000</v>
+        <v>3382700000</v>
       </c>
       <c r="F3" t="n">
-        <v>405701000</v>
+        <v>396276000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>227200000</v>
+        <v>362200000</v>
       </c>
       <c r="D4" t="n">
-        <v>2092</v>
+        <v>2122</v>
       </c>
       <c r="E4" t="n">
-        <v>2618015000</v>
+        <v>2734455000</v>
       </c>
       <c r="F4" t="n">
-        <v>390864000</v>
+        <v>385384000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>222100000</v>
+        <v>358900000</v>
       </c>
       <c r="D5" t="n">
-        <v>2470</v>
+        <v>2509</v>
       </c>
       <c r="E5" t="n">
-        <v>3092741000</v>
+        <v>3194941000</v>
       </c>
       <c r="F5" t="n">
-        <v>510446000</v>
+        <v>510196000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>30600000</v>
+        <v>98400000</v>
       </c>
       <c r="G2" t="n">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="H2" t="n">
-        <v>547980000</v>
+        <v>598255000</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>1675000</v>
+        <v>1300000</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>36100000</v>
+        <v>52300000</v>
       </c>
       <c r="G3" t="n">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H3" t="n">
-        <v>488133000</v>
+        <v>503013000</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>18660000</v>
+        <v>10140000</v>
       </c>
       <c r="K3" t="n">
         <v>188</v>
@@ -900,13 +900,13 @@
         <v>178761000</v>
       </c>
       <c r="M3" t="n">
-        <v>36.62</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H4" t="n">
-        <v>231220000</v>
+        <v>230160000</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>15440000</v>
+        <v>13550000</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
       </c>
       <c r="L4" t="n">
-        <v>140985000</v>
+        <v>140735000</v>
       </c>
       <c r="M4" t="n">
-        <v>60.97</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>81000000</v>
+        <v>98100000</v>
       </c>
       <c r="G5" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H5" t="n">
-        <v>826445000</v>
+        <v>835195000</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>10200000</v>
+        <v>3050000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>53100000</v>
+        <v>60300000</v>
       </c>
       <c r="G6" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H6" t="n">
-        <v>450733000</v>
+        <v>453358000</v>
       </c>
       <c r="I6" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
-        <v>66520000</v>
+        <v>43870000</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -1041,13 +1041,13 @@
         <v>110880000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.6</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>21300000</v>
+        <v>49800000</v>
       </c>
       <c r="G7" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>548230000</v>
+        <v>574960000</v>
       </c>
       <c r="I7" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J7" t="n">
-        <v>145925000</v>
+        <v>141965000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>51525000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.4</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>25800000</v>
+        <v>40200000</v>
       </c>
       <c r="G8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H8" t="n">
-        <v>332580000</v>
+        <v>342950000</v>
       </c>
       <c r="I8" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>38835000</v>
+        <v>21600000</v>
       </c>
       <c r="K8" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L8" t="n">
-        <v>123350000</v>
+        <v>123150000</v>
       </c>
       <c r="M8" t="n">
-        <v>37.09</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>16300000</v>
+        <v>31000000</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>64855000</v>
+        <v>79555000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>43755000</v>
       </c>
       <c r="M9" t="n">
-        <v>67.47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>63900000</v>
+        <v>67500000</v>
       </c>
       <c r="G10" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H10" t="n">
-        <v>654400000</v>
+        <v>653500000</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>88800000</v>
+        <v>152100000</v>
       </c>
       <c r="G11" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="H11" t="n">
-        <v>824656000</v>
+        <v>880506000</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>26800000</v>
+        <v>21000000</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1276,13 +1276,13 @@
         <v>28975000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>28800000</v>
+        <v>67800000</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H12" t="n">
-        <v>367484000</v>
+        <v>405284000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -1320,16 +1320,16 @@
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>61429000</v>
+        <v>61129000</v>
       </c>
       <c r="M12" t="n">
-        <v>16.72</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,28 +1355,28 @@
         <v>419</v>
       </c>
       <c r="H13" t="n">
-        <v>374040000</v>
+        <v>372660000</v>
       </c>
       <c r="I13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J13" t="n">
-        <v>42660000</v>
+        <v>45900000</v>
       </c>
       <c r="K13" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>131355000</v>
+        <v>126375000</v>
       </c>
       <c r="M13" t="n">
-        <v>35.12</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>77250000</v>
+        <v>95470000</v>
       </c>
       <c r="G14" t="n">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="H14" t="n">
-        <v>755284000</v>
+        <v>760685000</v>
       </c>
       <c r="I14" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="J14" t="n">
-        <v>66498000</v>
+        <v>23465000</v>
       </c>
       <c r="K14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L14" t="n">
-        <v>66186000</v>
+        <v>60686000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.76</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>6000000</v>
+        <v>29250000</v>
       </c>
       <c r="G15" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H15" t="n">
-        <v>517410000</v>
+        <v>535260000</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -1461,16 +1461,16 @@
         <v>60</v>
       </c>
       <c r="L15" t="n">
-        <v>91350000</v>
+        <v>90675000</v>
       </c>
       <c r="M15" t="n">
-        <v>17.66</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>15600000</v>
+        <v>19200000</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H16" t="n">
-        <v>388610000</v>
+        <v>390370000</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2425000</v>
+        <v>985000</v>
       </c>
       <c r="K16" t="n">
         <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>128600000</v>
+        <v>128100000</v>
       </c>
       <c r="M16" t="n">
-        <v>33.09</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>61800000</v>
+        <v>131700000</v>
       </c>
       <c r="G17" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="H17" t="n">
-        <v>967368000</v>
+        <v>1018945000</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>196495000</v>
+        <v>110605000</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1558,13 +1558,13 @@
         <v>56875000</v>
       </c>
       <c r="M17" t="n">
-        <v>5.88</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>71700000</v>
+        <v>90100000</v>
       </c>
       <c r="G18" t="n">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="H18" t="n">
-        <v>665665000</v>
+        <v>677440000</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>29075000</v>
+        <v>28525000</v>
       </c>
       <c r="K18" t="n">
         <v>67</v>
       </c>
       <c r="L18" t="n">
-        <v>62690000</v>
+        <v>59940000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.42</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>92100000</v>
       </c>
       <c r="G19" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H19" t="n">
-        <v>511835000</v>
+        <v>509035000</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>50000000</v>
+        <v>75300000</v>
       </c>
       <c r="G20" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H20" t="n">
-        <v>353630000</v>
+        <v>374030000</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>17100000</v>
+        <v>3500000</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L20" t="n">
-        <v>68220000</v>
+        <v>60570000</v>
       </c>
       <c r="M20" t="n">
-        <v>19.29</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>7500000</v>
+        <v>30100000</v>
       </c>
       <c r="G21" t="n">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="H21" t="n">
-        <v>508602000</v>
+        <v>525212000</v>
       </c>
       <c r="I21" t="n">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="J21" t="n">
-        <v>112750000</v>
+        <v>79780000</v>
       </c>
       <c r="K21" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L21" t="n">
-        <v>80912000</v>
+        <v>77312000</v>
       </c>
       <c r="M21" t="n">
-        <v>15.91</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>106600000</v>
+        <v>115400000</v>
       </c>
       <c r="G22" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="H22" t="n">
-        <v>786250000</v>
+        <v>790475000</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>41750000</v>
+        <v>18150000</v>
       </c>
       <c r="K22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>56325000</v>
+        <v>55925000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.16</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H23" t="n">
-        <v>43935000</v>
+        <v>43035000</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -1834,19 +1834,19 @@
         <v>2750000</v>
       </c>
       <c r="K23" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L23" t="n">
-        <v>30560000</v>
+        <v>29660000</v>
       </c>
       <c r="M23" t="n">
-        <v>69.56</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,34 +1860,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
-        <v>57700000</v>
+        <v>72700000</v>
       </c>
       <c r="G24" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H24" t="n">
-        <v>296200000</v>
+        <v>310625000</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>11750000</v>
+        <v>8600000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>8500000</v>
+        <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>232350000</v>
+        <v>365720000</v>
       </c>
       <c r="Q2" t="n">
-        <v>400308000</v>
+        <v>371761000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>313900000</v>
+        <v>385600000</v>
       </c>
       <c r="Q3" t="n">
-        <v>240212000</v>
+        <v>224222000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>222100000</v>
+        <v>358900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>521621000</v>
+        <v>511791000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>227200000</v>
+        <v>362200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>383819001</v>
+        <v>377009001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>511791000</v>
+        <v>529066000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>377009001</v>
+        <v>418878000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>371761000</v>
+        <v>387844001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>224222000</v>
+        <v>244857000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>84400000</v>
+        <v>123200000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>51500000</v>
+        <v>94750000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>48900000</v>
+        <v>87100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>39050000</v>
+        <v>69000000</v>
       </c>
     </row>
   </sheetData>
@@ -635,55 +635,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>385600000</v>
+        <v>230450000</v>
       </c>
       <c r="D2" t="n">
-        <v>1999</v>
+        <v>2336</v>
       </c>
       <c r="E2" t="n">
-        <v>2552412000</v>
+        <v>3250493000</v>
       </c>
       <c r="F2" t="n">
-        <v>231842000</v>
+        <v>409156000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>365720000</v>
+        <v>126800000</v>
       </c>
       <c r="D3" t="n">
-        <v>2367</v>
+        <v>1929</v>
       </c>
       <c r="E3" t="n">
-        <v>3382700000</v>
+        <v>2368532000</v>
       </c>
       <c r="F3" t="n">
-        <v>396276000</v>
+        <v>241722000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>362200000</v>
+        <v>124000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2122</v>
+        <v>2102</v>
       </c>
       <c r="E4" t="n">
-        <v>2734455000</v>
+        <v>2594642000</v>
       </c>
       <c r="F4" t="n">
-        <v>385384000</v>
+        <v>392874000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>358900000</v>
+        <v>84450000</v>
       </c>
       <c r="D5" t="n">
-        <v>2509</v>
+        <v>2435</v>
       </c>
       <c r="E5" t="n">
-        <v>3194941000</v>
+        <v>2937700000</v>
       </c>
       <c r="F5" t="n">
-        <v>510196000</v>
+        <v>509196000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,40 +826,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>98400000</v>
+        <v>7200000</v>
       </c>
       <c r="G2" t="n">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="H2" t="n">
-        <v>598255000</v>
+        <v>535450000</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1300000</v>
+        <v>1350000</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>52300000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H3" t="n">
-        <v>503013000</v>
+        <v>473565000</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J3" t="n">
-        <v>10140000</v>
+        <v>32495000</v>
       </c>
       <c r="K3" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>178761000</v>
+        <v>181906000</v>
       </c>
       <c r="M3" t="n">
-        <v>35.54</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
-        <v>230160000</v>
+        <v>204455000</v>
       </c>
       <c r="I4" t="n">
         <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>13550000</v>
+        <v>11640000</v>
       </c>
       <c r="K4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>140735000</v>
+        <v>139530000</v>
       </c>
       <c r="M4" t="n">
-        <v>61.15</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>98100000</v>
+        <v>50400000</v>
       </c>
       <c r="G5" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H5" t="n">
-        <v>835195000</v>
+        <v>776835000</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>3050000</v>
+        <v>41600000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>60300000</v>
+        <v>26850000</v>
       </c>
       <c r="G6" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="H6" t="n">
-        <v>453358000</v>
+        <v>434835000</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J6" t="n">
-        <v>43870000</v>
+        <v>59675000</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L6" t="n">
-        <v>110880000</v>
+        <v>112940000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.46</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>49800000</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H7" t="n">
-        <v>574960000</v>
+        <v>512560000</v>
       </c>
       <c r="I7" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J7" t="n">
-        <v>141965000</v>
+        <v>133770000</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>51525000</v>
+        <v>46825000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.960000000000001</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>40200000</v>
+        <v>8400000</v>
       </c>
       <c r="G8" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H8" t="n">
-        <v>342950000</v>
+        <v>345612000</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
-        <v>21600000</v>
+        <v>45295000</v>
       </c>
       <c r="K8" t="n">
         <v>161</v>
       </c>
       <c r="L8" t="n">
-        <v>123150000</v>
+        <v>123090000</v>
       </c>
       <c r="M8" t="n">
-        <v>35.91</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>31000000</v>
+        <v>3600000</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H9" t="n">
-        <v>79555000</v>
+        <v>107245000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1179,16 +1179,16 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>43755000</v>
+        <v>43355000</v>
       </c>
       <c r="M9" t="n">
-        <v>55</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>67500000</v>
+        <v>46000000</v>
       </c>
       <c r="G10" t="n">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="H10" t="n">
-        <v>653500000</v>
+        <v>598530000</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>8625000</v>
+        <v>12800000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2000000</v>
+        <v>1750000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>152100000</v>
+        <v>14400000</v>
       </c>
       <c r="G11" t="n">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="H11" t="n">
-        <v>880506000</v>
+        <v>780502000</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>21000000</v>
+        <v>17800000</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>28975000</v>
+        <v>33075000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.29</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>67800000</v>
+        <v>30000000</v>
       </c>
       <c r="G12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H12" t="n">
-        <v>405284000</v>
+        <v>393493000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>50000</v>
+        <v>3600000</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>61129000</v>
+        <v>58579000</v>
       </c>
       <c r="M12" t="n">
-        <v>15.08</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>3600000</v>
+        <v>21600000</v>
       </c>
       <c r="G13" t="n">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="H13" t="n">
-        <v>372660000</v>
+        <v>369260000</v>
       </c>
       <c r="I13" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="J13" t="n">
-        <v>45900000</v>
+        <v>58095000</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
-        <v>126375000</v>
+        <v>133025000</v>
       </c>
       <c r="M13" t="n">
-        <v>33.91</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>95470000</v>
+        <v>30450000</v>
       </c>
       <c r="G14" t="n">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H14" t="n">
-        <v>760685000</v>
+        <v>697743000</v>
       </c>
       <c r="I14" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="J14" t="n">
-        <v>23465000</v>
+        <v>58199000</v>
       </c>
       <c r="K14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L14" t="n">
-        <v>60686000</v>
+        <v>69461000</v>
       </c>
       <c r="M14" t="n">
-        <v>7.98</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>29250000</v>
+        <v>76200000</v>
       </c>
       <c r="G15" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H15" t="n">
-        <v>535260000</v>
+        <v>553010000</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>1500000</v>
+        <v>35760000</v>
       </c>
       <c r="K15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L15" t="n">
-        <v>90675000</v>
+        <v>84225000</v>
       </c>
       <c r="M15" t="n">
-        <v>16.94</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" t="n">
+        <v>32100000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>313</v>
+      </c>
+      <c r="H16" t="n">
+        <v>381285000</v>
+      </c>
+      <c r="I16" t="n">
         <v>11</v>
       </c>
-      <c r="F16" t="n">
-        <v>19200000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>329</v>
-      </c>
-      <c r="H16" t="n">
-        <v>390370000</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
       <c r="J16" t="n">
-        <v>985000</v>
+        <v>8210000</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L16" t="n">
-        <v>128100000</v>
+        <v>124250000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.82</v>
+        <v>32.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>131700000</v>
+        <v>39900000</v>
       </c>
       <c r="G17" t="n">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>1018945000</v>
+        <v>973606000</v>
       </c>
       <c r="I17" t="n">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="J17" t="n">
-        <v>110605000</v>
+        <v>256492000</v>
       </c>
       <c r="K17" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L17" t="n">
-        <v>56875000</v>
+        <v>58880000</v>
       </c>
       <c r="M17" t="n">
-        <v>5.58</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>90100000</v>
+        <v>51800000</v>
       </c>
       <c r="G18" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H18" t="n">
-        <v>677440000</v>
+        <v>644849000</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J18" t="n">
-        <v>28525000</v>
+        <v>37815000</v>
       </c>
       <c r="K18" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>59940000</v>
+        <v>72340000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.85</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>92100000</v>
+        <v>34100000</v>
       </c>
       <c r="G19" t="n">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="H19" t="n">
-        <v>509035000</v>
+        <v>461950000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>8100000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>75300000</v>
+        <v>4500000</v>
       </c>
       <c r="G20" t="n">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H20" t="n">
-        <v>374030000</v>
+        <v>344190000</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>3500000</v>
+        <v>34750000</v>
       </c>
       <c r="K20" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L20" t="n">
-        <v>60570000</v>
+        <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>16.19</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>30100000</v>
+        <v>20400000</v>
       </c>
       <c r="G21" t="n">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="H21" t="n">
-        <v>525212000</v>
+        <v>486227000</v>
       </c>
       <c r="I21" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J21" t="n">
-        <v>79780000</v>
+        <v>79460000</v>
       </c>
       <c r="K21" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="L21" t="n">
-        <v>77312000</v>
+        <v>85842000</v>
       </c>
       <c r="M21" t="n">
-        <v>14.72</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>115400000</v>
+        <v>57300000</v>
       </c>
       <c r="G22" t="n">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="H22" t="n">
-        <v>790475000</v>
+        <v>750080000</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="J22" t="n">
-        <v>18150000</v>
+        <v>65175000</v>
       </c>
       <c r="K22" t="n">
         <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>55925000</v>
+        <v>54475000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.07</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1813,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>10500000</v>
       </c>
       <c r="G23" t="n">
         <v>79</v>
       </c>
       <c r="H23" t="n">
-        <v>43035000</v>
+        <v>49310000</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>2750000</v>
+        <v>1500000</v>
       </c>
       <c r="K23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L23" t="n">
         <v>29660000</v>
       </c>
       <c r="M23" t="n">
-        <v>68.92</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>72700000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H24" t="n">
-        <v>310625000</v>
+        <v>276775000</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>8600000</v>
+        <v>6300000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>365720000</v>
+        <v>230450000</v>
       </c>
       <c r="Q2" t="n">
-        <v>371761000</v>
+        <v>418878000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>385600000</v>
+        <v>126800000</v>
       </c>
       <c r="Q3" t="n">
-        <v>224222000</v>
+        <v>244857000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>358900000</v>
+        <v>84450000</v>
       </c>
       <c r="Q4" t="n">
-        <v>511791000</v>
+        <v>529066000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>362200000</v>
+        <v>124000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>377009001</v>
+        <v>387844001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>529066000</v>
+        <v>515021000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>418878000</v>
+        <v>397438000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>387844001</v>
+        <v>381704001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>244857000</v>
+        <v>238957000</v>
       </c>
     </row>
   </sheetData>
@@ -517,25 +517,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>123200000</v>
+        <v>135000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,34 +544,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>94750000</v>
+        <v>64800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>87100000</v>
+        <v>56900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>69000000</v>
+        <v>47700000</v>
       </c>
     </row>
   </sheetData>
@@ -635,97 +635,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>230450000</v>
+        <v>558750000</v>
       </c>
       <c r="D2" t="n">
-        <v>2336</v>
+        <v>2398</v>
       </c>
       <c r="E2" t="n">
-        <v>3250493000</v>
+        <v>3797229000</v>
       </c>
       <c r="F2" t="n">
-        <v>409156000</v>
+        <v>152715000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>126800000</v>
+        <v>432000000</v>
       </c>
       <c r="D3" t="n">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="E3" t="n">
-        <v>2368532000</v>
+        <v>3116505000</v>
       </c>
       <c r="F3" t="n">
-        <v>241722000</v>
+        <v>116920000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>124000000</v>
+        <v>366800000</v>
       </c>
       <c r="D4" t="n">
-        <v>2102</v>
+        <v>2268</v>
       </c>
       <c r="E4" t="n">
-        <v>2594642000</v>
+        <v>3250450000</v>
       </c>
       <c r="F4" t="n">
-        <v>392874000</v>
+        <v>117750000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84450000</v>
+        <v>346100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2435</v>
+        <v>1621</v>
       </c>
       <c r="E5" t="n">
-        <v>2937700000</v>
+        <v>2240590000</v>
       </c>
       <c r="F5" t="n">
-        <v>509196000</v>
+        <v>46300000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>7200000</v>
+        <v>105400000</v>
       </c>
       <c r="G2" t="n">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="H2" t="n">
-        <v>535450000</v>
+        <v>651245000</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1350000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>121450000</v>
       </c>
       <c r="G3" t="n">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="H3" t="n">
-        <v>473565000</v>
+        <v>710860000</v>
       </c>
       <c r="I3" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>32495000</v>
+        <v>33270000</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>42</v>
       </c>
       <c r="L3" t="n">
-        <v>181906000</v>
+        <v>48470000</v>
       </c>
       <c r="M3" t="n">
-        <v>38.41</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,40 +920,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>82800000</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>420</v>
       </c>
       <c r="H4" t="n">
-        <v>204455000</v>
+        <v>643709000</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>11640000</v>
+        <v>44250000</v>
       </c>
       <c r="K4" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>139530000</v>
+        <v>60000000</v>
       </c>
       <c r="M4" t="n">
-        <v>68.23999999999999</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>50400000</v>
+        <v>108700000</v>
       </c>
       <c r="G5" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H5" t="n">
-        <v>776835000</v>
+        <v>826065000</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>41600000</v>
+        <v>4800000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>27995000</v>
+        <v>21775000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>26850000</v>
+        <v>54900000</v>
       </c>
       <c r="G6" t="n">
-        <v>504</v>
+        <v>269</v>
       </c>
       <c r="H6" t="n">
-        <v>434835000</v>
+        <v>339775000</v>
       </c>
       <c r="I6" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="J6" t="n">
-        <v>59675000</v>
+        <v>71025000</v>
       </c>
       <c r="K6" t="n">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>112940000</v>
+        <v>22470000</v>
       </c>
       <c r="M6" t="n">
-        <v>25.97</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>85500000</v>
       </c>
       <c r="G7" t="n">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H7" t="n">
-        <v>512560000</v>
+        <v>625575000</v>
       </c>
       <c r="I7" t="n">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>133770000</v>
+        <v>4200000</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>46825000</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
-        <v>8400000</v>
+        <v>47100000</v>
       </c>
       <c r="G8" t="n">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="H8" t="n">
-        <v>345612000</v>
+        <v>548800000</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>45295000</v>
+        <v>49820000</v>
       </c>
       <c r="K8" t="n">
-        <v>161</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>123090000</v>
+        <v>7100000</v>
       </c>
       <c r="M8" t="n">
-        <v>35.62</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,44 +1151,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hashim Hazem Talib .</t>
+          <t>Hussain . Ali Atchan -</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>107245000</v>
+        <v>79820000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>22950000</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
-        <v>43355000</v>
+        <v>47470000</v>
       </c>
       <c r="M9" t="n">
-        <v>40.43</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>46000000</v>
+        <v>88200000</v>
       </c>
       <c r="G10" t="n">
-        <v>421</v>
+        <v>537</v>
       </c>
       <c r="H10" t="n">
-        <v>598530000</v>
+        <v>888220000</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12800000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1750000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1245,44 +1245,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sadikh . Najee Jawad -</t>
+          <t>Sabreen Falih  Lafta -</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>14400000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>457</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>780502000</v>
+        <v>3500000</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>17800000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>33075000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1292,44 +1292,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shamil Kamil Hadhod .</t>
+          <t>Sadikh . Najee Jawad -</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>122700000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>466</v>
+      </c>
+      <c r="H12" t="n">
+        <v>842445000</v>
+      </c>
+      <c r="I12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F12" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="G12" t="n">
-        <v>337</v>
-      </c>
-      <c r="H12" t="n">
-        <v>393493000</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>5975000</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>63</v>
-      </c>
       <c r="L12" t="n">
-        <v>58579000</v>
+        <v>1800000</v>
       </c>
       <c r="M12" t="n">
-        <v>14.89</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1339,91 +1339,91 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shiab Ghanim Abd zaid</t>
+          <t>Shamil Kamil Hadhod .</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>21600000</v>
+        <v>68700000</v>
       </c>
       <c r="G13" t="n">
-        <v>428</v>
+        <v>259</v>
       </c>
       <c r="H13" t="n">
-        <v>369260000</v>
+        <v>501675000</v>
       </c>
       <c r="I13" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>58095000</v>
+        <v>55950000</v>
       </c>
       <c r="K13" t="n">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>133025000</v>
+        <v>60550000</v>
       </c>
       <c r="M13" t="n">
-        <v>36.02</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hasanen Nadher Muhammed .</t>
+          <t>Shiab Ghanim Abd zaid</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>30450000</v>
+        <v>105300000</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>156</v>
       </c>
       <c r="H14" t="n">
-        <v>697743000</v>
+        <v>252045000</v>
       </c>
       <c r="I14" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>58199000</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>69461000</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>9.960000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Hasanen Nadher Muhammed .</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
-        <v>76200000</v>
+        <v>65800000</v>
       </c>
       <c r="G15" t="n">
-        <v>307</v>
+        <v>460</v>
       </c>
       <c r="H15" t="n">
-        <v>553010000</v>
+        <v>670985000</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>35760000</v>
+        <v>20875000</v>
       </c>
       <c r="K15" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>84225000</v>
+        <v>33650000</v>
       </c>
       <c r="M15" t="n">
-        <v>15.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>310</v>
+      </c>
+      <c r="H16" t="n">
+        <v>520275000</v>
+      </c>
+      <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="F16" t="n">
-        <v>32100000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>313</v>
-      </c>
-      <c r="H16" t="n">
-        <v>381285000</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11</v>
-      </c>
       <c r="J16" t="n">
-        <v>8210000</v>
+        <v>18900000</v>
       </c>
       <c r="K16" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>124250000</v>
+        <v>16500000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.59</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1527,44 +1527,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Muhannad . Abdul Ameer Kadhum -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>39900000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>578</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>973606000</v>
+        <v>38650000</v>
       </c>
       <c r="I17" t="n">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>256492000</v>
+        <v>9450000</v>
       </c>
       <c r="K17" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>58880000</v>
+        <v>3600000</v>
       </c>
       <c r="M17" t="n">
-        <v>6.05</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,138 +1574,138 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>369</v>
+      </c>
+      <c r="H18" t="n">
+        <v>448475000</v>
+      </c>
+      <c r="I18" t="n">
         <v>22</v>
       </c>
-      <c r="F18" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="G18" t="n">
-        <v>583</v>
-      </c>
-      <c r="H18" t="n">
-        <v>644849000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>40</v>
-      </c>
       <c r="J18" t="n">
-        <v>37815000</v>
+        <v>13570000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
-        <v>72340000</v>
+        <v>51450000</v>
       </c>
       <c r="M18" t="n">
-        <v>11.22</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>34100000</v>
+        <v>136200000</v>
       </c>
       <c r="G19" t="n">
-        <v>436</v>
+        <v>557</v>
       </c>
       <c r="H19" t="n">
-        <v>461950000</v>
+        <v>820850000</v>
       </c>
       <c r="I19" t="n">
+        <v>16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17450000</v>
+      </c>
+      <c r="K19" t="n">
         <v>11</v>
       </c>
-      <c r="J19" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10950000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="n">
+        <v>126700000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>519</v>
+      </c>
+      <c r="H20" t="n">
+        <v>714595000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="G20" t="n">
-        <v>261</v>
-      </c>
-      <c r="H20" t="n">
-        <v>344190000</v>
-      </c>
-      <c r="I20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J20" t="n">
-        <v>34750000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>62</v>
-      </c>
       <c r="L20" t="n">
-        <v>63370000</v>
+        <v>1600000</v>
       </c>
       <c r="M20" t="n">
-        <v>18.41</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,44 +1715,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>20400000</v>
+        <v>84600000</v>
       </c>
       <c r="G21" t="n">
-        <v>449</v>
+        <v>268</v>
       </c>
       <c r="H21" t="n">
-        <v>486227000</v>
+        <v>344640000</v>
       </c>
       <c r="I21" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>79460000</v>
+        <v>3600000</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>85842000</v>
+        <v>2100000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.65</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1762,44 +1762,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>57300000</v>
+        <v>61400000</v>
       </c>
       <c r="G22" t="n">
-        <v>489</v>
+        <v>363</v>
       </c>
       <c r="H22" t="n">
-        <v>750080000</v>
+        <v>449030000</v>
       </c>
       <c r="I22" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>65175000</v>
+        <v>17900000</v>
       </c>
       <c r="K22" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
-        <v>54475000</v>
+        <v>22300000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.26</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maytham Salah Mahdie .</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>10500000</v>
+        <v>22800000</v>
       </c>
       <c r="G23" t="n">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="H23" t="n">
-        <v>49310000</v>
+        <v>421400000</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>1500000</v>
+        <v>26130000</v>
       </c>
       <c r="K23" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>29660000</v>
+        <v>14700000</v>
       </c>
       <c r="M23" t="n">
-        <v>60.15</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1856,38 +1856,132 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Jawnaa . Radhi Shimran -</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" t="n">
+        <v>39</v>
+      </c>
+      <c r="F24" t="n">
+        <v>100400000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>444</v>
+      </c>
+      <c r="H24" t="n">
+        <v>722625000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4950000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>215</v>
-      </c>
-      <c r="H24" t="n">
-        <v>276775000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>كربلاء</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nisreen . Nadum Waheed -</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="L24" t="n">
-        <v>8375000</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.03</v>
+      <c r="E26" t="n">
+        <v>37</v>
+      </c>
+      <c r="F26" t="n">
+        <v>69900000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>252</v>
+      </c>
+      <c r="H26" t="n">
+        <v>290495000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2286,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>230450000</v>
+        <v>366800000</v>
       </c>
       <c r="Q2" t="n">
-        <v>418878000</v>
+        <v>397438000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2337,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>126800000</v>
+        <v>346100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>244857000</v>
+        <v>238957000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2388,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>84450000</v>
+        <v>558750000</v>
       </c>
       <c r="Q4" t="n">
-        <v>529066000</v>
+        <v>515021000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2439,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>124000000</v>
+        <v>432000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>387844001</v>
+        <v>381704001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -640,20 +640,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>558750000</v>
+        <v>298050000</v>
       </c>
       <c r="D2" t="n">
-        <v>2398</v>
+        <v>2347</v>
       </c>
       <c r="E2" t="n">
-        <v>3797229000</v>
+        <v>3294853000</v>
       </c>
       <c r="F2" t="n">
-        <v>152715000</v>
+        <v>403576000</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>432000000</v>
+        <v>230500000</v>
       </c>
       <c r="D3" t="n">
-        <v>1925</v>
+        <v>2121</v>
       </c>
       <c r="E3" t="n">
-        <v>3116505000</v>
+        <v>2693302000</v>
       </c>
       <c r="F3" t="n">
-        <v>116920000</v>
+        <v>389254000</v>
       </c>
     </row>
     <row r="4">
@@ -688,20 +688,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>366800000</v>
+        <v>219650000</v>
       </c>
       <c r="D4" t="n">
-        <v>2268</v>
+        <v>1968</v>
       </c>
       <c r="E4" t="n">
-        <v>3250450000</v>
+        <v>2451752000</v>
       </c>
       <c r="F4" t="n">
-        <v>117750000</v>
+        <v>241722000</v>
       </c>
     </row>
     <row r="5">
@@ -712,20 +712,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>346100000</v>
+        <v>209150000</v>
       </c>
       <c r="D5" t="n">
-        <v>1621</v>
+        <v>2479</v>
       </c>
       <c r="E5" t="n">
-        <v>2240590000</v>
+        <v>3038605000</v>
       </c>
       <c r="F5" t="n">
-        <v>46300000</v>
+        <v>503511000</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>105400000</v>
+        <v>25200000</v>
       </c>
       <c r="G2" t="n">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="H2" t="n">
-        <v>651245000</v>
+        <v>547200000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -873,34 +873,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>121450000</v>
+        <v>25200000</v>
       </c>
       <c r="G3" t="n">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="H3" t="n">
-        <v>710860000</v>
+        <v>495925000</v>
       </c>
       <c r="I3" t="n">
         <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>33270000</v>
+        <v>18235000</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="L3" t="n">
-        <v>48470000</v>
+        <v>179746000</v>
       </c>
       <c r="M3" t="n">
-        <v>6.82</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="4">
@@ -920,34 +920,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>82800000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>420</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
-        <v>643709000</v>
+        <v>200130000</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>44250000</v>
+        <v>11490000</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>60000000</v>
+        <v>136005000</v>
       </c>
       <c r="M4" t="n">
-        <v>9.32</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -967,34 +967,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>108700000</v>
+        <v>100650000</v>
       </c>
       <c r="G5" t="n">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H5" t="n">
-        <v>826065000</v>
+        <v>819085000</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>4800000</v>
+        <v>11100000</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>21775000</v>
+        <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>2.64</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="6">
@@ -1014,34 +1014,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>54900000</v>
+        <v>54500000</v>
       </c>
       <c r="G6" t="n">
-        <v>269</v>
+        <v>518</v>
       </c>
       <c r="H6" t="n">
-        <v>339775000</v>
+        <v>460105000</v>
       </c>
       <c r="I6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J6" t="n">
-        <v>71025000</v>
+        <v>44355000</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="L6" t="n">
-        <v>22470000</v>
+        <v>112940000</v>
       </c>
       <c r="M6" t="n">
-        <v>6.61</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="7">
@@ -1061,34 +1061,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>85500000</v>
+        <v>3600000</v>
       </c>
       <c r="G7" t="n">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="H7" t="n">
-        <v>625575000</v>
+        <v>516160000</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="J7" t="n">
-        <v>4200000</v>
+        <v>133770000</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>46825000</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="8">
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>47100000</v>
+        <v>8400000</v>
       </c>
       <c r="G8" t="n">
-        <v>434</v>
+        <v>358</v>
       </c>
       <c r="H8" t="n">
-        <v>548800000</v>
+        <v>342712000</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>49820000</v>
+        <v>28245000</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="L8" t="n">
-        <v>7100000</v>
+        <v>123090000</v>
       </c>
       <c r="M8" t="n">
-        <v>1.29</v>
+        <v>35.92</v>
       </c>
     </row>
     <row r="9">
@@ -1151,38 +1151,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hussain . Ali Atchan -</t>
+          <t>Hashim Hazem Talib .</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>112775000</v>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>68</v>
-      </c>
-      <c r="H9" t="n">
-        <v>79820000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22950000</v>
-      </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>47470000</v>
+        <v>42885000</v>
       </c>
       <c r="M9" t="n">
-        <v>59.47</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="10">
@@ -1202,34 +1202,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>88200000</v>
+        <v>46000000</v>
       </c>
       <c r="G10" t="n">
-        <v>537</v>
+        <v>418</v>
       </c>
       <c r="H10" t="n">
-        <v>888220000</v>
+        <v>598080000</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>12800000</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1750000</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
@@ -1245,38 +1245,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sabreen Falih  Lafta -</t>
+          <t>Sadikh . Najee Jawad -</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>84000000</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>470</v>
       </c>
       <c r="H11" t="n">
-        <v>3500000</v>
+        <v>848602000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>16300000</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>33075000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sadikh . Najee Jawad -</t>
+          <t>Shamil Kamil Hadhod .</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>122700000</v>
+        <v>52500000</v>
       </c>
       <c r="G12" t="n">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="H12" t="n">
-        <v>842445000</v>
+        <v>414733000</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>5975000</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>1800000</v>
+        <v>58579000</v>
       </c>
       <c r="M12" t="n">
-        <v>0.21</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="13">
@@ -1339,38 +1339,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shamil Kamil Hadhod .</t>
+          <t>Shiab Ghanim Abd zaid</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>68700000</v>
+        <v>30000000</v>
       </c>
       <c r="G13" t="n">
-        <v>259</v>
+        <v>429</v>
       </c>
       <c r="H13" t="n">
-        <v>501675000</v>
+        <v>376400000</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="J13" t="n">
-        <v>55950000</v>
+        <v>56745000</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="L13" t="n">
-        <v>60550000</v>
+        <v>129875000</v>
       </c>
       <c r="M13" t="n">
-        <v>12.07</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="14">
@@ -1381,43 +1381,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shiab Ghanim Abd zaid</t>
+          <t>Hasanen Nadher Muhammed .</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>105300000</v>
+        <v>54150000</v>
       </c>
       <c r="G14" t="n">
-        <v>156</v>
+        <v>558</v>
       </c>
       <c r="H14" t="n">
-        <v>252045000</v>
+        <v>715143000</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>34299000</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>69461000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1433,38 +1433,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hasanen Nadher Muhammed .</t>
+          <t>Maki  . Malik Tahir -</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>65800000</v>
+        <v>76200000</v>
       </c>
       <c r="G15" t="n">
-        <v>460</v>
+        <v>307</v>
       </c>
       <c r="H15" t="n">
-        <v>670985000</v>
+        <v>550670000</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>20875000</v>
+        <v>17300000</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="L15" t="n">
-        <v>33650000</v>
+        <v>84225000</v>
       </c>
       <c r="M15" t="n">
-        <v>5.02</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="16">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maki  . Malik Tahir -</t>
+          <t>Muslem Aqeel Ghazi Ghazi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>4800000</v>
+        <v>40300000</v>
       </c>
       <c r="G16" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
-        <v>520275000</v>
+        <v>389485000</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>18900000</v>
+        <v>8210000</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="L16" t="n">
-        <v>16500000</v>
+        <v>124250000</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="17">
@@ -1527,38 +1527,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muhannad . Abdul Ameer Kadhum -</t>
+          <t>Sanaa . Mahdi Ahmed -</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>75600000</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="H17" t="n">
-        <v>38650000</v>
+        <v>997751000</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="J17" t="n">
-        <v>9450000</v>
+        <v>205567000</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="L17" t="n">
-        <v>3600000</v>
+        <v>53300000</v>
       </c>
       <c r="M17" t="n">
-        <v>9.31</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="18">
@@ -1574,38 +1574,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muslem Aqeel Ghazi Ghazi</t>
+          <t>Zainab . Salim Essa -</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>33300000</v>
+        <v>51800000</v>
       </c>
       <c r="G18" t="n">
-        <v>369</v>
+        <v>583</v>
       </c>
       <c r="H18" t="n">
-        <v>448475000</v>
+        <v>641804000</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>13570000</v>
+        <v>21250000</v>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>51450000</v>
+        <v>72340000</v>
       </c>
       <c r="M18" t="n">
-        <v>11.47</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="19">
@@ -1616,43 +1616,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanaa . Mahdi Ahmed -</t>
+          <t>Ali  . Abbas khalaf -</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>136200000</v>
+        <v>62250000</v>
       </c>
       <c r="G19" t="n">
-        <v>557</v>
+        <v>451</v>
       </c>
       <c r="H19" t="n">
-        <v>820850000</v>
+        <v>488300000</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>17450000</v>
+        <v>3600000</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10950000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1663,43 +1663,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zainab . Salim Essa -</t>
+          <t>Azher Alaa Yass .</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>126700000</v>
+        <v>14000000</v>
       </c>
       <c r="G20" t="n">
-        <v>519</v>
+        <v>267</v>
       </c>
       <c r="H20" t="n">
-        <v>714595000</v>
+        <v>352990000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>32650000</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="L20" t="n">
-        <v>1600000</v>
+        <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>0.22</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="21">
@@ -1715,38 +1715,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ali  . Abbas khalaf -</t>
+          <t>Ibtihal Hamza  Hussain -</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>84600000</v>
+        <v>20400000</v>
       </c>
       <c r="G21" t="n">
-        <v>268</v>
+        <v>449</v>
       </c>
       <c r="H21" t="n">
-        <v>344640000</v>
+        <v>485927000</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="J21" t="n">
-        <v>3600000</v>
+        <v>77060000</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="L21" t="n">
-        <v>2100000</v>
+        <v>85842000</v>
       </c>
       <c r="M21" t="n">
-        <v>0.61</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="22">
@@ -1762,38 +1762,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azher Alaa Yass .</t>
+          <t>Jawnaa . Radhi Shimran -</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>61400000</v>
+        <v>93300000</v>
       </c>
       <c r="G22" t="n">
-        <v>363</v>
+        <v>502</v>
       </c>
       <c r="H22" t="n">
-        <v>449030000</v>
+        <v>781050000</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J22" t="n">
-        <v>17900000</v>
+        <v>42325000</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>22300000</v>
+        <v>54475000</v>
       </c>
       <c r="M22" t="n">
-        <v>4.97</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="23">
@@ -1809,38 +1809,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ibtihal Hamza  Hussain -</t>
+          <t>Maytham Salah Mahdie .</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>22800000</v>
+        <v>10500000</v>
       </c>
       <c r="G23" t="n">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="H23" t="n">
-        <v>421400000</v>
+        <v>49310000</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>26130000</v>
+        <v>1500000</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="L23" t="n">
-        <v>14700000</v>
+        <v>29660000</v>
       </c>
       <c r="M23" t="n">
-        <v>3.49</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="24">
@@ -1856,132 +1856,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jawnaa . Radhi Shimran -</t>
+          <t>Muna Abed Alkareem Madlol</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>19200000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>220</v>
+      </c>
+      <c r="H24" t="n">
+        <v>294175000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>14</v>
       </c>
-      <c r="E24" t="n">
-        <v>39</v>
-      </c>
-      <c r="F24" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="G24" t="n">
-        <v>444</v>
-      </c>
-      <c r="H24" t="n">
-        <v>722625000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>17</v>
-      </c>
-      <c r="J24" t="n">
-        <v>22400000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>9</v>
-      </c>
       <c r="L24" t="n">
-        <v>4950000</v>
+        <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Muna Abed Alkareem Madlol</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>12400000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>18.15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>كربلاء</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nisreen . Nadum Waheed -</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
-        <v>37</v>
-      </c>
-      <c r="F26" t="n">
-        <v>69900000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>252</v>
-      </c>
-      <c r="H26" t="n">
-        <v>290495000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>12</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12700000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2192,7 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>366800000</v>
+        <v>298050000</v>
       </c>
       <c r="Q2" t="n">
         <v>397438000</v>
@@ -2337,7 +2243,7 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>346100000</v>
+        <v>219650000</v>
       </c>
       <c r="Q3" t="n">
         <v>238957000</v>
@@ -2388,7 +2294,7 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>558750000</v>
+        <v>209150000</v>
       </c>
       <c r="Q4" t="n">
         <v>515021000</v>
@@ -2439,7 +2345,7 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>432000000</v>
+        <v>230500000</v>
       </c>
       <c r="Q5" t="n">
         <v>381704001</v>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>135000000</v>
+        <v>121800000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>64800000</v>
+        <v>67300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>56900000</v>
+        <v>58300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>47700000</v>
+        <v>39900000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,88 +644,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>298050000</v>
+        <v>450150000</v>
       </c>
       <c r="D2" t="n">
-        <v>2347</v>
+        <v>2369</v>
       </c>
       <c r="E2" t="n">
-        <v>3294853000</v>
+        <v>3393879000</v>
       </c>
       <c r="F2" t="n">
-        <v>403576000</v>
+        <v>384336000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>230500000</v>
+        <v>316750000</v>
       </c>
       <c r="D3" t="n">
-        <v>2121</v>
+        <v>2014</v>
       </c>
       <c r="E3" t="n">
-        <v>2693302000</v>
+        <v>2530597000</v>
       </c>
       <c r="F3" t="n">
-        <v>389254000</v>
+        <v>230822000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>219650000</v>
+        <v>291250000</v>
       </c>
       <c r="D4" t="n">
-        <v>1968</v>
+        <v>2516</v>
       </c>
       <c r="E4" t="n">
-        <v>2451752000</v>
+        <v>3095745000</v>
       </c>
       <c r="F4" t="n">
-        <v>241722000</v>
+        <v>502151000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>209150000</v>
+        <v>266200000</v>
       </c>
       <c r="D5" t="n">
-        <v>2479</v>
+        <v>2120</v>
       </c>
       <c r="E5" t="n">
-        <v>3038605000</v>
+        <v>2709283000</v>
       </c>
       <c r="F5" t="n">
-        <v>503511000</v>
+        <v>369170000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>25200000</v>
+        <v>51800000</v>
       </c>
       <c r="G2" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H2" t="n">
-        <v>547200000</v>
+        <v>565625000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>25200000</v>
+        <v>47300000</v>
       </c>
       <c r="G3" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="H3" t="n">
-        <v>495925000</v>
+        <v>514135000</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>18235000</v>
+        <v>16135000</v>
       </c>
       <c r="K3" t="n">
         <v>191</v>
       </c>
       <c r="L3" t="n">
-        <v>179746000</v>
+        <v>179646000</v>
       </c>
       <c r="M3" t="n">
-        <v>36.24</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>212</v>
       </c>
       <c r="H4" t="n">
-        <v>200130000</v>
+        <v>198180000</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>11490000</v>
+        <v>5040000</v>
       </c>
       <c r="K4" t="n">
         <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>136005000</v>
+        <v>135105000</v>
       </c>
       <c r="M4" t="n">
-        <v>67.95999999999999</v>
+        <v>68.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>100650000</v>
+        <v>109250000</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="H5" t="n">
-        <v>819085000</v>
+        <v>824985000</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>11100000</v>
+        <v>2100000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>54500000</v>
+        <v>64900000</v>
       </c>
       <c r="G6" t="n">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="H6" t="n">
-        <v>460105000</v>
+        <v>467330000</v>
       </c>
       <c r="I6" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
-        <v>44355000</v>
+        <v>26310000</v>
       </c>
       <c r="K6" t="n">
         <v>143</v>
       </c>
       <c r="L6" t="n">
-        <v>112940000</v>
+        <v>112580000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.55</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>3600000</v>
+        <v>18000000</v>
       </c>
       <c r="G7" t="n">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="H7" t="n">
-        <v>516160000</v>
+        <v>525490000</v>
       </c>
       <c r="I7" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="J7" t="n">
-        <v>133770000</v>
+        <v>113310000</v>
       </c>
       <c r="K7" t="n">
         <v>39</v>
@@ -1088,13 +1088,13 @@
         <v>46825000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.07</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8400000</v>
+        <v>21000000</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H8" t="n">
-        <v>342712000</v>
+        <v>351497000</v>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
-        <v>28245000</v>
+        <v>20625000</v>
       </c>
       <c r="K8" t="n">
         <v>161</v>
@@ -1135,13 +1135,13 @@
         <v>123090000</v>
       </c>
       <c r="M8" t="n">
-        <v>35.92</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,10 +1211,10 @@
         <v>46000000</v>
       </c>
       <c r="G10" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H10" t="n">
-        <v>598080000</v>
+        <v>597780000</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>84000000</v>
+        <v>96900000</v>
       </c>
       <c r="G11" t="n">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H11" t="n">
-        <v>848602000</v>
+        <v>857802000</v>
       </c>
       <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="K11" t="n">
         <v>17</v>
       </c>
-      <c r="J11" t="n">
-        <v>16300000</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20</v>
-      </c>
       <c r="L11" t="n">
-        <v>33075000</v>
+        <v>27075000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>52500000</v>
+        <v>59100000</v>
       </c>
       <c r="G12" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H12" t="n">
-        <v>414733000</v>
+        <v>421119000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1317,19 +1317,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L12" t="n">
-        <v>58579000</v>
+        <v>58365000</v>
       </c>
       <c r="M12" t="n">
-        <v>14.12</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>30000000</v>
+        <v>33600000</v>
       </c>
       <c r="G13" t="n">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H13" t="n">
-        <v>376400000</v>
+        <v>368310000</v>
       </c>
       <c r="I13" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J13" t="n">
-        <v>56745000</v>
+        <v>29675000</v>
       </c>
       <c r="K13" t="n">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>129875000</v>
+        <v>116005000</v>
       </c>
       <c r="M13" t="n">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>54150000</v>
+        <v>97050000</v>
       </c>
       <c r="G14" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H14" t="n">
-        <v>715143000</v>
+        <v>744459000</v>
       </c>
       <c r="I14" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>34299000</v>
+        <v>10675000</v>
       </c>
       <c r="K14" t="n">
         <v>78</v>
@@ -1417,13 +1417,13 @@
         <v>69461000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>76200000</v>
+        <v>90600000</v>
       </c>
       <c r="G15" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>550670000</v>
+        <v>559120000</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>17300000</v>
+        <v>18500000</v>
       </c>
       <c r="K15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>84225000</v>
+        <v>74175000</v>
       </c>
       <c r="M15" t="n">
-        <v>15.3</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>40300000</v>
+        <v>51400000</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
-        <v>389485000</v>
+        <v>396010000</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>8210000</v>
+        <v>4335000</v>
       </c>
       <c r="K16" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L16" t="n">
-        <v>124250000</v>
+        <v>123600000</v>
       </c>
       <c r="M16" t="n">
-        <v>31.9</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>75600000</v>
+        <v>107100000</v>
       </c>
       <c r="G17" t="n">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="H17" t="n">
-        <v>997751000</v>
+        <v>1009876000</v>
       </c>
       <c r="I17" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="J17" t="n">
-        <v>205567000</v>
+        <v>81567000</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L17" t="n">
-        <v>53300000</v>
+        <v>46550000</v>
       </c>
       <c r="M17" t="n">
-        <v>5.34</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F18" t="n">
-        <v>51800000</v>
+        <v>104000000</v>
       </c>
       <c r="G18" t="n">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="H18" t="n">
-        <v>641804000</v>
+        <v>684414000</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>21250000</v>
+        <v>15850000</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L18" t="n">
-        <v>72340000</v>
+        <v>70550000</v>
       </c>
       <c r="M18" t="n">
-        <v>11.27</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>451</v>
       </c>
       <c r="H19" t="n">
-        <v>488300000</v>
+        <v>487900000</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>59400000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>289</v>
+      </c>
+      <c r="H20" t="n">
+        <v>391590000</v>
+      </c>
+      <c r="I20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="G20" t="n">
-        <v>267</v>
-      </c>
-      <c r="H20" t="n">
-        <v>352990000</v>
-      </c>
-      <c r="I20" t="n">
-        <v>23</v>
-      </c>
       <c r="J20" t="n">
-        <v>32650000</v>
+        <v>7500000</v>
       </c>
       <c r="K20" t="n">
         <v>62</v>
@@ -1699,13 +1699,13 @@
         <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>17.95</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>20400000</v>
+        <v>44700000</v>
       </c>
       <c r="G21" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="H21" t="n">
-        <v>485927000</v>
+        <v>505897000</v>
       </c>
       <c r="I21" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J21" t="n">
-        <v>77060000</v>
+        <v>83830000</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L21" t="n">
-        <v>85842000</v>
+        <v>74942000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.67</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,25 +1766,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" t="n">
-        <v>93300000</v>
+        <v>95700000</v>
       </c>
       <c r="G22" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H22" t="n">
-        <v>781050000</v>
+        <v>777725000</v>
       </c>
       <c r="I22" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>42325000</v>
+        <v>26850000</v>
       </c>
       <c r="K22" t="n">
         <v>34</v>
@@ -1793,13 +1793,13 @@
         <v>54475000</v>
       </c>
       <c r="M22" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>19200000</v>
+        <v>44200000</v>
       </c>
       <c r="G24" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="H24" t="n">
-        <v>294175000</v>
+        <v>318175000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +2148,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2190,7 +2189,6 @@
       <c r="N2" t="n">
         <v>336401000</v>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>298050000</v>
       </c>
@@ -2199,7 +2197,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2241,7 +2238,6 @@
       <c r="N3" t="n">
         <v>211112000</v>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>219650000</v>
       </c>
@@ -2250,7 +2246,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2292,7 +2287,6 @@
       <c r="N4" t="n">
         <v>465566000</v>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>209150000</v>
       </c>
@@ -2301,7 +2295,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>
@@ -2343,7 +2336,6 @@
       <c r="N5" t="n">
         <v>353144001</v>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>230500000</v>
       </c>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>515021000</v>
+        <v>503526000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>397438000</v>
+        <v>368339000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>381704001</v>
+        <v>364285001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>238957000</v>
+        <v>227772000</v>
       </c>
     </row>
   </sheetData>
@@ -2148,6 +2148,7 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2189,14 +2190,16 @@
       <c r="N2" t="n">
         <v>336401000</v>
       </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>298050000</v>
+        <v>450150000</v>
       </c>
       <c r="Q2" t="n">
-        <v>397438000</v>
+        <v>368339000</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2238,14 +2241,16 @@
       <c r="N3" t="n">
         <v>211112000</v>
       </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>219650000</v>
+        <v>316750000</v>
       </c>
       <c r="Q3" t="n">
-        <v>238957000</v>
+        <v>227772000</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2287,14 +2292,16 @@
       <c r="N4" t="n">
         <v>465566000</v>
       </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>209150000</v>
+        <v>291250000</v>
       </c>
       <c r="Q4" t="n">
-        <v>515021000</v>
+        <v>503526000</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>
@@ -2336,11 +2343,12 @@
       <c r="N5" t="n">
         <v>353144001</v>
       </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>230500000</v>
+        <v>266200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>381704001</v>
+        <v>364285001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>503526000</v>
+        <v>492546000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>368339000</v>
+        <v>357420001</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>364285001</v>
+        <v>353366000</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>227772000</v>
+        <v>213282000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,52 +526,52 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>121800000</v>
+        <v>73800000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>67300000</v>
+        <v>58350000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>58300000</v>
+        <v>40100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>39900000</v>
+        <v>8600000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,88 +644,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>450150000</v>
+        <v>489450000</v>
       </c>
       <c r="D2" t="n">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="E2" t="n">
-        <v>3393879000</v>
+        <v>3396586000</v>
       </c>
       <c r="F2" t="n">
-        <v>384336000</v>
+        <v>366536000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>316750000</v>
+        <v>402450000</v>
       </c>
       <c r="D3" t="n">
-        <v>2014</v>
+        <v>2547</v>
       </c>
       <c r="E3" t="n">
-        <v>2530597000</v>
+        <v>3184000000</v>
       </c>
       <c r="F3" t="n">
-        <v>230822000</v>
+        <v>500801000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>291250000</v>
+        <v>378400000</v>
       </c>
       <c r="D4" t="n">
-        <v>2516</v>
+        <v>2179</v>
       </c>
       <c r="E4" t="n">
-        <v>3095745000</v>
+        <v>2810718000</v>
       </c>
       <c r="F4" t="n">
-        <v>502151000</v>
+        <v>365495000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>266200000</v>
+        <v>353250000</v>
       </c>
       <c r="D5" t="n">
-        <v>2120</v>
+        <v>2013</v>
       </c>
       <c r="E5" t="n">
-        <v>2709283000</v>
+        <v>2545372000</v>
       </c>
       <c r="F5" t="n">
-        <v>369170000</v>
+        <v>217672000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>51800000</v>
+        <v>98000000</v>
       </c>
       <c r="G2" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H2" t="n">
-        <v>565625000</v>
+        <v>607775000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>47300000</v>
+        <v>73800000</v>
       </c>
       <c r="G3" t="n">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="H3" t="n">
-        <v>514135000</v>
+        <v>538240000</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>16135000</v>
+        <v>4320000</v>
       </c>
       <c r="K3" t="n">
         <v>191</v>
       </c>
       <c r="L3" t="n">
-        <v>179646000</v>
+        <v>179296000</v>
       </c>
       <c r="M3" t="n">
-        <v>34.94</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H4" t="n">
-        <v>198180000</v>
+        <v>196080000</v>
       </c>
       <c r="I4" t="n">
         <v>14</v>
@@ -944,16 +944,16 @@
         <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>135105000</v>
+        <v>134105000</v>
       </c>
       <c r="M4" t="n">
-        <v>68.17</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,7 +979,7 @@
         <v>452</v>
       </c>
       <c r="H5" t="n">
-        <v>824985000</v>
+        <v>822860000</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>527</v>
       </c>
       <c r="H6" t="n">
-        <v>467330000</v>
+        <v>464600000</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J6" t="n">
-        <v>26310000</v>
+        <v>20190000</v>
       </c>
       <c r="K6" t="n">
         <v>143</v>
@@ -1041,13 +1041,13 @@
         <v>112580000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.09</v>
+        <v>24.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>18000000</v>
+        <v>56500000</v>
       </c>
       <c r="G7" t="n">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="H7" t="n">
-        <v>525490000</v>
+        <v>554445000</v>
       </c>
       <c r="I7" t="n">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="J7" t="n">
-        <v>113310000</v>
+        <v>87380000</v>
       </c>
       <c r="K7" t="n">
         <v>39</v>
@@ -1088,13 +1088,13 @@
         <v>46825000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.91</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>21000000</v>
+        <v>50700000</v>
       </c>
       <c r="G8" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="H8" t="n">
-        <v>351497000</v>
+        <v>380822000</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>20625000</v>
+        <v>20250000</v>
       </c>
       <c r="K8" t="n">
         <v>161</v>
@@ -1135,13 +1135,13 @@
         <v>123090000</v>
       </c>
       <c r="M8" t="n">
-        <v>35.02</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>9600000</v>
+        <v>56400000</v>
       </c>
       <c r="G9" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="H9" t="n">
-        <v>112775000</v>
+        <v>159450000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1179,16 +1179,16 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>42885000</v>
+        <v>42760000</v>
       </c>
       <c r="M9" t="n">
-        <v>38.03</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>415</v>
       </c>
       <c r="H10" t="n">
-        <v>597780000</v>
+        <v>594380000</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>96900000</v>
+        <v>119100000</v>
       </c>
       <c r="G11" t="n">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>857802000</v>
+        <v>877002000</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>13600000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>27075000</v>
+        <v>26775000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>59100000</v>
+        <v>62700000</v>
       </c>
       <c r="G12" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H12" t="n">
-        <v>421119000</v>
+        <v>424469000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1320,16 +1320,16 @@
         <v>61</v>
       </c>
       <c r="L12" t="n">
-        <v>58365000</v>
+        <v>58115000</v>
       </c>
       <c r="M12" t="n">
-        <v>13.86</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>33600000</v>
+        <v>43500000</v>
       </c>
       <c r="G13" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H13" t="n">
-        <v>368310000</v>
+        <v>374595000</v>
       </c>
       <c r="I13" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="J13" t="n">
-        <v>29675000</v>
+        <v>22310000</v>
       </c>
       <c r="K13" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L13" t="n">
-        <v>116005000</v>
+        <v>113005000</v>
       </c>
       <c r="M13" t="n">
-        <v>31.5</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>97050000</v>
       </c>
       <c r="G14" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H14" t="n">
-        <v>744459000</v>
+        <v>736609000</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>10675000</v>
+        <v>14875000</v>
       </c>
       <c r="K14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L14" t="n">
-        <v>69461000</v>
+        <v>64661000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.33</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,19 +1449,19 @@
         <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>559120000</v>
+        <v>555870000</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>18500000</v>
+        <v>17500000</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>74175000</v>
+        <v>73775000</v>
       </c>
       <c r="M15" t="n">
         <v>13.27</v>
@@ -1470,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>51400000</v>
+        <v>71800000</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>396010000</v>
+        <v>415165000</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -1511,13 +1511,13 @@
         <v>123600000</v>
       </c>
       <c r="M16" t="n">
-        <v>31.21</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>107100000</v>
+        <v>118800000</v>
       </c>
       <c r="G17" t="n">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H17" t="n">
-        <v>1009876000</v>
+        <v>1006878000</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>81567000</v>
+        <v>43450000</v>
       </c>
       <c r="K17" t="n">
         <v>62</v>
@@ -1558,13 +1558,13 @@
         <v>46550000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>104000000</v>
+        <v>111200000</v>
       </c>
       <c r="G18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H18" t="n">
-        <v>684414000</v>
+        <v>682064000</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>15850000</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L18" t="n">
-        <v>70550000</v>
+        <v>57950000</v>
       </c>
       <c r="M18" t="n">
-        <v>10.31</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>62250000</v>
       </c>
       <c r="G19" t="n">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="H19" t="n">
-        <v>487900000</v>
+        <v>484825000</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1684,7 +1684,7 @@
         <v>289</v>
       </c>
       <c r="H20" t="n">
-        <v>391590000</v>
+        <v>390740000</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
@@ -1699,13 +1699,13 @@
         <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>16.18</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F21" t="n">
-        <v>44700000</v>
+        <v>47700000</v>
       </c>
       <c r="G21" t="n">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="H21" t="n">
-        <v>505897000</v>
+        <v>496897000</v>
       </c>
       <c r="I21" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J21" t="n">
-        <v>83830000</v>
+        <v>30520000</v>
       </c>
       <c r="K21" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L21" t="n">
-        <v>74942000</v>
+        <v>71542000</v>
       </c>
       <c r="M21" t="n">
-        <v>14.81</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
-        <v>95700000</v>
+        <v>102900000</v>
       </c>
       <c r="G22" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H22" t="n">
-        <v>777725000</v>
+        <v>780975000</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>26850000</v>
+        <v>33950000</v>
       </c>
       <c r="K22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>54475000</v>
+        <v>45475000</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,31 +1822,31 @@
         <v>10500000</v>
       </c>
       <c r="G23" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H23" t="n">
-        <v>49310000</v>
+        <v>48560000</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>1500000</v>
       </c>
       <c r="K23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L23" t="n">
-        <v>29660000</v>
+        <v>28910000</v>
       </c>
       <c r="M23" t="n">
-        <v>60.15</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>44200000</v>
+        <v>70500000</v>
       </c>
       <c r="G24" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="H24" t="n">
-        <v>318175000</v>
+        <v>343375000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>450150000</v>
+        <v>489450000</v>
       </c>
       <c r="Q2" t="n">
-        <v>368339000</v>
+        <v>353366000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>316750000</v>
+        <v>353250000</v>
       </c>
       <c r="Q3" t="n">
-        <v>227772000</v>
+        <v>213282000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>291250000</v>
+        <v>402450000</v>
       </c>
       <c r="Q4" t="n">
-        <v>503526000</v>
+        <v>492546000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>266200000</v>
+        <v>378400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>364285001</v>
+        <v>357420001</v>
       </c>
     </row>
   </sheetData>
